--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5100,10 +5100,10 @@
         <v>6.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.021182</v>
+        <v>0.021256</v>
       </c>
       <c r="AG22" t="n">
         <v>1.16</v>
@@ -5481,10 +5481,10 @@
         <v>1.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.003062</v>
+        <v>0.002988</v>
       </c>
       <c r="BJ23" t="n">
         <v>-0.01</v>
@@ -24993,10 +24993,10 @@
         <v>447.350006</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1237</v>
+        <v>5.1259</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9496</v>
+        <v>5.9594</v>
       </c>
       <c r="H82" t="n">
         <v>7718.600098</v>
@@ -25017,10 +25017,10 @@
         <v>96.279999</v>
       </c>
       <c r="N82" t="n">
-        <v>1309.75</v>
+        <v>1293.75</v>
       </c>
       <c r="O82" t="n">
-        <v>536.75</v>
+        <v>512</v>
       </c>
       <c r="P82" t="n">
         <v>4.355791</v>
@@ -25035,10 +25035,10 @@
         <v>-0.445087</v>
       </c>
       <c r="T82" t="n">
-        <v>-1.30027</v>
+        <v>-1.257898</v>
       </c>
       <c r="U82" t="n">
-        <v>-0.998645</v>
+        <v>-0.835574</v>
       </c>
       <c r="V82" t="n">
         <v>0.422318</v>
@@ -25059,10 +25059,10 @@
         <v>6.398498</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.705352</v>
+        <v>1.450696</v>
       </c>
       <c r="AC82" t="n">
-        <v>4.223301</v>
+        <v>-0.582524</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -24996,7 +24996,7 @@
         <v>5.1259</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9594</v>
+        <v>5.9606</v>
       </c>
       <c r="H82" t="n">
         <v>7718.600098</v>
@@ -25038,7 +25038,7 @@
         <v>-1.257898</v>
       </c>
       <c r="U82" t="n">
-        <v>-0.835574</v>
+        <v>-0.8156099999999999</v>
       </c>
       <c r="V82" t="n">
         <v>0.422318</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -24981,88 +24981,88 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>185147</v>
+        <v>188913.453125</v>
       </c>
       <c r="C82" t="n">
-        <v>181.940002</v>
+        <v>186.029999</v>
       </c>
       <c r="D82" t="n">
-        <v>110.989998</v>
+        <v>112.760002</v>
       </c>
       <c r="E82" t="n">
-        <v>447.350006</v>
+        <v>439.269989</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1259</v>
+        <v>5.0806</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9606</v>
+        <v>5.9044</v>
       </c>
       <c r="H82" t="n">
-        <v>7718.600098</v>
+        <v>7684.339844</v>
       </c>
       <c r="I82" t="n">
-        <v>26506.990234</v>
+        <v>26390.132812</v>
       </c>
       <c r="J82" t="n">
-        <v>53414.25</v>
+        <v>52819.558594</v>
       </c>
       <c r="K82" t="n">
-        <v>4476.600098</v>
+        <v>4442</v>
       </c>
       <c r="L82" t="n">
-        <v>91.480003</v>
+        <v>93.269997</v>
       </c>
       <c r="M82" t="n">
-        <v>96.279999</v>
+        <v>98.08000199999999</v>
       </c>
       <c r="N82" t="n">
-        <v>1293.75</v>
+        <v>1307.25</v>
       </c>
       <c r="O82" t="n">
-        <v>512</v>
+        <v>535.5</v>
       </c>
       <c r="P82" t="n">
-        <v>4.355791</v>
+        <v>6.478705</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.096581</v>
+        <v>6.436663</v>
       </c>
       <c r="R82" t="n">
-        <v>4.57929</v>
+        <v>6.24706</v>
       </c>
       <c r="S82" t="n">
-        <v>-0.445087</v>
+        <v>-2.243244</v>
       </c>
       <c r="T82" t="n">
-        <v>-1.257898</v>
+        <v>-2.130529</v>
       </c>
       <c r="U82" t="n">
-        <v>-0.8156099999999999</v>
+        <v>-1.750779</v>
       </c>
       <c r="V82" t="n">
-        <v>0.422318</v>
+        <v>-0.023423</v>
       </c>
       <c r="W82" t="n">
-        <v>0.5160979999999999</v>
+        <v>0.07296800000000001</v>
       </c>
       <c r="X82" t="n">
-        <v>0.429346</v>
+        <v>-0.688791</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.026833</v>
+        <v>0.245986</v>
       </c>
       <c r="Z82" t="n">
-        <v>6.669777</v>
+        <v>8.75699</v>
       </c>
       <c r="AA82" t="n">
-        <v>6.398498</v>
+        <v>8.387672</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.450696</v>
+        <v>2.509312</v>
       </c>
       <c r="AC82" t="n">
-        <v>-0.582524</v>
+        <v>3.980583</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5100,10 +5100,10 @@
         <v>6.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.021256</v>
+        <v>0.021339</v>
       </c>
       <c r="AG22" t="n">
         <v>1.16</v>
@@ -5481,10 +5481,10 @@
         <v>1.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.002988</v>
+        <v>0.002905</v>
       </c>
       <c r="BJ23" t="n">
         <v>-0.01</v>
@@ -24805,7 +24805,9 @@
       <c r="AR81" t="inlineStr"/>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr"/>
-      <c r="AU81" t="inlineStr"/>
+      <c r="AU81" t="n">
+        <v>372616</v>
+      </c>
       <c r="AV81" t="inlineStr"/>
       <c r="AW81" t="inlineStr"/>
       <c r="AX81" t="n">
@@ -24817,7 +24819,9 @@
       <c r="AZ81" t="inlineStr"/>
       <c r="BA81" t="inlineStr"/>
       <c r="BB81" t="inlineStr"/>
-      <c r="BC81" t="inlineStr"/>
+      <c r="BC81" t="n">
+        <v>0.777299</v>
+      </c>
       <c r="BD81" t="inlineStr"/>
       <c r="BE81" t="n">
         <v>2.178243</v>
@@ -24981,88 +24985,88 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>188913.453125</v>
+        <v>187042.90625</v>
       </c>
       <c r="C82" t="n">
-        <v>186.029999</v>
+        <v>184.070007</v>
       </c>
       <c r="D82" t="n">
-        <v>112.760002</v>
+        <v>111.110001</v>
       </c>
       <c r="E82" t="n">
-        <v>439.269989</v>
+        <v>440.329987</v>
       </c>
       <c r="F82" t="n">
-        <v>5.0806</v>
+        <v>5.0937</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9044</v>
+        <v>5.9353</v>
       </c>
       <c r="H82" t="n">
-        <v>7684.339844</v>
+        <v>7653.459961</v>
       </c>
       <c r="I82" t="n">
-        <v>26390.132812</v>
+        <v>26360.449219</v>
       </c>
       <c r="J82" t="n">
-        <v>52819.558594</v>
+        <v>52381.640625</v>
       </c>
       <c r="K82" t="n">
-        <v>4442</v>
+        <v>4456.600098</v>
       </c>
       <c r="L82" t="n">
-        <v>93.269997</v>
+        <v>95.75</v>
       </c>
       <c r="M82" t="n">
-        <v>98.08000199999999</v>
+        <v>100.669998</v>
       </c>
       <c r="N82" t="n">
-        <v>1307.25</v>
+        <v>1308.75</v>
       </c>
       <c r="O82" t="n">
-        <v>535.5</v>
+        <v>527.25</v>
       </c>
       <c r="P82" t="n">
-        <v>6.478705</v>
+        <v>5.424394</v>
       </c>
       <c r="Q82" t="n">
-        <v>6.436663</v>
+        <v>5.315258</v>
       </c>
       <c r="R82" t="n">
-        <v>6.24706</v>
+        <v>4.692362</v>
       </c>
       <c r="S82" t="n">
-        <v>-2.243244</v>
+        <v>-2.007348</v>
       </c>
       <c r="T82" t="n">
-        <v>-2.130529</v>
+        <v>-1.878176</v>
       </c>
       <c r="U82" t="n">
-        <v>-1.750779</v>
+        <v>-1.236603</v>
       </c>
       <c r="V82" t="n">
-        <v>-0.023423</v>
+        <v>-0.425183</v>
       </c>
       <c r="W82" t="n">
-        <v>0.07296800000000001</v>
+        <v>-0.039594</v>
       </c>
       <c r="X82" t="n">
-        <v>-0.688791</v>
+        <v>-1.512164</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.245986</v>
+        <v>0.575478</v>
       </c>
       <c r="Z82" t="n">
-        <v>8.75699</v>
+        <v>11.648785</v>
       </c>
       <c r="AA82" t="n">
-        <v>8.387672</v>
+        <v>11.249862</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.509312</v>
+        <v>2.626936</v>
       </c>
       <c r="AC82" t="n">
-        <v>3.980583</v>
+        <v>2.378641</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>
@@ -25079,10 +25083,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.1253</v>
+        <v>5.0856</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.1247</v>
+        <v>5.085</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25095,10 +25099,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-1.086537</v>
+        <v>-1.85271</v>
       </c>
       <c r="AY82" t="n">
-        <v>-1.086663</v>
+        <v>-1.852924</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5100,10 +5100,10 @@
         <v>6.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.021339</v>
+        <v>0.021433</v>
       </c>
       <c r="AG22" t="n">
         <v>1.16</v>
@@ -5481,10 +5481,10 @@
         <v>1.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.002905</v>
+        <v>0.002811</v>
       </c>
       <c r="BJ23" t="n">
         <v>-0.01</v>
@@ -24985,88 +24985,88 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>187042.90625</v>
+        <v>185144.859375</v>
       </c>
       <c r="C82" t="n">
-        <v>184.070007</v>
+        <v>182.330002</v>
       </c>
       <c r="D82" t="n">
-        <v>111.110001</v>
+        <v>109.870003</v>
       </c>
       <c r="E82" t="n">
-        <v>440.329987</v>
+        <v>440.929993</v>
       </c>
       <c r="F82" t="n">
-        <v>5.0937</v>
+        <v>5.1422</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9353</v>
+        <v>5.9703</v>
       </c>
       <c r="H82" t="n">
-        <v>7653.459961</v>
+        <v>7583.859863</v>
       </c>
       <c r="I82" t="n">
-        <v>26360.449219</v>
+        <v>26037.785156</v>
       </c>
       <c r="J82" t="n">
-        <v>52381.640625</v>
+        <v>52079.46875</v>
       </c>
       <c r="K82" t="n">
-        <v>4456.600098</v>
+        <v>4409.5</v>
       </c>
       <c r="L82" t="n">
-        <v>95.75</v>
+        <v>99.300003</v>
       </c>
       <c r="M82" t="n">
-        <v>100.669998</v>
+        <v>104.540001</v>
       </c>
       <c r="N82" t="n">
-        <v>1308.75</v>
+        <v>1316</v>
       </c>
       <c r="O82" t="n">
-        <v>527.25</v>
+        <v>528</v>
       </c>
       <c r="P82" t="n">
-        <v>5.424394</v>
+        <v>4.354584</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.315258</v>
+        <v>4.319718</v>
       </c>
       <c r="R82" t="n">
-        <v>4.692362</v>
+        <v>3.523985</v>
       </c>
       <c r="S82" t="n">
-        <v>-2.007348</v>
+        <v>-1.873821</v>
       </c>
       <c r="T82" t="n">
-        <v>-1.878176</v>
+        <v>-0.943901</v>
       </c>
       <c r="U82" t="n">
-        <v>-1.236603</v>
+        <v>-0.654197</v>
       </c>
       <c r="V82" t="n">
-        <v>-0.425183</v>
+        <v>-1.33071</v>
       </c>
       <c r="W82" t="n">
-        <v>-0.039594</v>
+        <v>-1.263156</v>
       </c>
       <c r="X82" t="n">
-        <v>-1.512164</v>
+        <v>-2.080306</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.575478</v>
+        <v>-0.487466</v>
       </c>
       <c r="Z82" t="n">
-        <v>11.648785</v>
+        <v>15.788247</v>
       </c>
       <c r="AA82" t="n">
-        <v>11.249862</v>
+        <v>15.526581</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.626936</v>
+        <v>3.195452</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.378641</v>
+        <v>2.524272</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>
@@ -25083,10 +25083,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.0856</v>
+        <v>5.0979</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.085</v>
+        <v>5.0973</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25099,10 +25099,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-1.85271</v>
+        <v>-1.615331</v>
       </c>
       <c r="AY82" t="n">
-        <v>-1.852924</v>
+        <v>-1.615518</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5100,10 +5100,10 @@
         <v>6.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.021433</v>
+        <v>0.02154</v>
       </c>
       <c r="AG22" t="n">
         <v>1.16</v>
@@ -5481,10 +5481,10 @@
         <v>1.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.002811</v>
+        <v>0.002704</v>
       </c>
       <c r="BJ23" t="n">
         <v>-0.01</v>
@@ -24785,11 +24785,15 @@
       <c r="AF81" t="n">
         <v>0.051784</v>
       </c>
-      <c r="AG81" t="inlineStr"/>
+      <c r="AG81" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="AH81" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AI81" t="inlineStr"/>
+      <c r="AI81" t="n">
+        <v>-0.32</v>
+      </c>
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="n">
@@ -24822,11 +24826,15 @@
       <c r="BC81" t="n">
         <v>0.777299</v>
       </c>
-      <c r="BD81" t="inlineStr"/>
+      <c r="BD81" t="n">
+        <v>4.223453</v>
+      </c>
       <c r="BE81" t="n">
         <v>2.178243</v>
       </c>
-      <c r="BF81" t="inlineStr"/>
+      <c r="BF81" t="n">
+        <v>3.983297</v>
+      </c>
       <c r="BG81" t="n">
         <v>-0.25</v>
       </c>
@@ -24985,88 +24993,88 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>185144.859375</v>
+        <v>187021.609375</v>
       </c>
       <c r="C82" t="n">
-        <v>182.330002</v>
+        <v>184.119995</v>
       </c>
       <c r="D82" t="n">
-        <v>109.870003</v>
+        <v>111.400002</v>
       </c>
       <c r="E82" t="n">
-        <v>440.929993</v>
+        <v>440.160004</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1422</v>
+        <v>5.083</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9703</v>
+        <v>5.9061</v>
       </c>
       <c r="H82" t="n">
-        <v>7583.859863</v>
+        <v>7675.77002</v>
       </c>
       <c r="I82" t="n">
-        <v>26037.785156</v>
+        <v>26405.673828</v>
       </c>
       <c r="J82" t="n">
-        <v>52079.46875</v>
+        <v>52662.679688</v>
       </c>
       <c r="K82" t="n">
-        <v>4409.5</v>
+        <v>4432.399902</v>
       </c>
       <c r="L82" t="n">
-        <v>99.300003</v>
+        <v>98.75</v>
       </c>
       <c r="M82" t="n">
-        <v>104.540001</v>
+        <v>104.110001</v>
       </c>
       <c r="N82" t="n">
-        <v>1316</v>
+        <v>1311.5</v>
       </c>
       <c r="O82" t="n">
-        <v>528</v>
+        <v>525.5</v>
       </c>
       <c r="P82" t="n">
-        <v>4.354584</v>
+        <v>5.412391</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.319718</v>
+        <v>5.343859</v>
       </c>
       <c r="R82" t="n">
-        <v>3.523985</v>
+        <v>4.965612</v>
       </c>
       <c r="S82" t="n">
-        <v>-1.873821</v>
+        <v>-2.045177</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.943901</v>
+        <v>-2.084289</v>
       </c>
       <c r="U82" t="n">
-        <v>-0.654197</v>
+        <v>-1.722492</v>
       </c>
       <c r="V82" t="n">
-        <v>-1.33071</v>
+        <v>-0.13492</v>
       </c>
       <c r="W82" t="n">
-        <v>-1.263156</v>
+        <v>0.1319</v>
       </c>
       <c r="X82" t="n">
-        <v>-2.080306</v>
+        <v>-0.983755</v>
       </c>
       <c r="Y82" t="n">
-        <v>-0.487466</v>
+        <v>0.029334</v>
       </c>
       <c r="Z82" t="n">
-        <v>15.788247</v>
+        <v>15.146919</v>
       </c>
       <c r="AA82" t="n">
-        <v>15.526581</v>
+        <v>15.05139</v>
       </c>
       <c r="AB82" t="n">
-        <v>3.195452</v>
+        <v>2.84258</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.524272</v>
+        <v>2.038835</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>
@@ -25083,10 +25091,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.0979</v>
+        <v>5.1149</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.0973</v>
+        <v>5.1143</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25099,10 +25107,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-1.615331</v>
+        <v>-1.287247</v>
       </c>
       <c r="AY82" t="n">
-        <v>-1.615518</v>
+        <v>-1.287396</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -24996,13 +24996,13 @@
         <v>187207</v>
       </c>
       <c r="C82" t="n">
-        <v>185.210007</v>
+        <v>183.850006</v>
       </c>
       <c r="D82" t="n">
-        <v>112.300003</v>
+        <v>110.830002</v>
       </c>
       <c r="E82" t="n">
-        <v>437.649994</v>
+        <v>443.149994</v>
       </c>
       <c r="F82" t="n">
         <v>5.1262</v>
@@ -25020,7 +25020,7 @@
         <v>52573.289062</v>
       </c>
       <c r="K82" t="n">
-        <v>4366.200195</v>
+        <v>4408.899902</v>
       </c>
       <c r="L82" t="n">
         <v>100.050003</v>
@@ -25029,22 +25029,22 @@
         <v>104.610001</v>
       </c>
       <c r="N82" t="n">
-        <v>1280.25</v>
+        <v>1299</v>
       </c>
       <c r="O82" t="n">
-        <v>510.25</v>
+        <v>532</v>
       </c>
       <c r="P82" t="n">
         <v>5.516884</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.967507</v>
+        <v>5.189385</v>
       </c>
       <c r="R82" t="n">
-        <v>5.81363</v>
+        <v>4.428535</v>
       </c>
       <c r="S82" t="n">
-        <v>-2.603764</v>
+        <v>-1.379773</v>
       </c>
       <c r="T82" t="n">
         <v>-1.252111</v>
@@ -25062,7 +25062,7 @@
         <v>-1.151827</v>
       </c>
       <c r="Y82" t="n">
-        <v>-1.464645</v>
+        <v>-0.501009</v>
       </c>
       <c r="Z82" t="n">
         <v>16.662781</v>
@@ -25071,10 +25071,10 @@
         <v>15.603938</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.39208</v>
+        <v>1.86238</v>
       </c>
       <c r="AC82" t="n">
-        <v>-0.92233</v>
+        <v>3.300971</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5068,7 +5068,7 @@
         <v>33843.921875</v>
       </c>
       <c r="K22" t="n">
-        <v>1755.300049</v>
+        <v>1757</v>
       </c>
       <c r="L22" t="n">
         <v>75.029999</v>
@@ -5100,10 +5100,10 @@
         <v>6.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.021664</v>
+        <v>0.021808</v>
       </c>
       <c r="AG22" t="n">
         <v>1.16</v>
@@ -5340,7 +5340,7 @@
         <v>35819.558594</v>
       </c>
       <c r="K23" t="n">
-        <v>1783</v>
+        <v>1783.900024</v>
       </c>
       <c r="L23" t="n">
         <v>83.56999999999999</v>
@@ -5382,7 +5382,7 @@
         <v>5.837493</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.578075</v>
+        <v>1.53102</v>
       </c>
       <c r="Z23" t="n">
         <v>11.382115</v>
@@ -5481,10 +5481,10 @@
         <v>1.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.00258</v>
+        <v>0.002435</v>
       </c>
       <c r="BJ23" t="n">
         <v>-0.01</v>
@@ -5708,7 +5708,7 @@
         <v>-3.729359</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.527203</v>
+        <v>-0.577389</v>
       </c>
       <c r="Z24" t="n">
         <v>-20.808902</v>
@@ -6000,7 +6000,7 @@
         <v>36338.300781</v>
       </c>
       <c r="K25" t="n">
-        <v>1827.5</v>
+        <v>1828.599976</v>
       </c>
       <c r="L25" t="n">
         <v>75.209999</v>
@@ -6042,7 +6042,7 @@
         <v>5.378138</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.039018</v>
+        <v>3.101037</v>
       </c>
       <c r="Z25" t="n">
         <v>13.644604</v>
@@ -6372,7 +6372,7 @@
         <v>-3.320027</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1.778386</v>
+        <v>-1.83747</v>
       </c>
       <c r="Z26" t="n">
         <v>17.205162</v>
@@ -6652,7 +6652,7 @@
         <v>33892.601562</v>
       </c>
       <c r="K27" t="n">
-        <v>1899.400024</v>
+        <v>1900.699951</v>
       </c>
       <c r="L27" t="n">
         <v>95.720001</v>
@@ -6694,7 +6694,7 @@
         <v>-3.527447</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.816157</v>
+        <v>5.888577</v>
       </c>
       <c r="Z27" t="n">
         <v>8.587634</v>
@@ -7020,7 +7020,7 @@
         <v>2.318353</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.621877</v>
+        <v>2.551692</v>
       </c>
       <c r="Z28" t="n">
         <v>4.763892</v>
@@ -7300,7 +7300,7 @@
         <v>32977.210938</v>
       </c>
       <c r="K29" t="n">
-        <v>1909.300049</v>
+        <v>1911.699951</v>
       </c>
       <c r="L29" t="n">
         <v>104.690002</v>
@@ -7342,7 +7342,7 @@
         <v>-4.905483</v>
       </c>
       <c r="Y29" t="n">
-        <v>-2.046989</v>
+        <v>-1.923866</v>
       </c>
       <c r="Z29" t="n">
         <v>4.39769</v>
@@ -7676,7 +7676,7 @@
         <v>0.039149</v>
       </c>
       <c r="Y30" t="n">
-        <v>-3.488194</v>
+        <v>-3.609353</v>
       </c>
       <c r="Z30" t="n">
         <v>9.532902</v>
@@ -7964,7 +7964,7 @@
         <v>30775.429688</v>
       </c>
       <c r="K31" t="n">
-        <v>1804.099976</v>
+        <v>1807.300049</v>
       </c>
       <c r="L31" t="n">
         <v>105.760002</v>
@@ -8006,7 +8006,7 @@
         <v>-6.713196</v>
       </c>
       <c r="Y31" t="n">
-        <v>-2.094751</v>
+        <v>-1.921089</v>
       </c>
       <c r="Z31" t="n">
         <v>-7.77012</v>
@@ -8336,7 +8336,7 @@
         <v>6.725168</v>
       </c>
       <c r="Y32" t="n">
-        <v>-2.283684</v>
+        <v>-2.456705</v>
       </c>
       <c r="Z32" t="n">
         <v>-6.751134</v>
@@ -8628,7 +8628,7 @@
         <v>31510.429688</v>
       </c>
       <c r="K33" t="n">
-        <v>1712.800049</v>
+        <v>1726.199951</v>
       </c>
       <c r="L33" t="n">
         <v>89.550003</v>
@@ -8670,7 +8670,7 @@
         <v>-4.063614</v>
       </c>
       <c r="Y33" t="n">
-        <v>-2.841907</v>
+        <v>-2.081801</v>
       </c>
       <c r="Z33" t="n">
         <v>-9.196916999999999</v>
@@ -8964,7 +8964,7 @@
         <v>28725.509766</v>
       </c>
       <c r="K34" t="n">
-        <v>1662.400024</v>
+        <v>1672</v>
       </c>
       <c r="L34" t="n">
         <v>79.489998</v>
@@ -9006,7 +9006,7 @@
         <v>-8.838089</v>
       </c>
       <c r="Y34" t="n">
-        <v>-2.942552</v>
+        <v>-3.139842</v>
       </c>
       <c r="Z34" t="n">
         <v>-11.233953</v>
@@ -9304,7 +9304,7 @@
         <v>32732.949219</v>
       </c>
       <c r="K35" t="n">
-        <v>1635.900024</v>
+        <v>1640.699951</v>
       </c>
       <c r="L35" t="n">
         <v>86.529999</v>
@@ -9346,7 +9346,7 @@
         <v>13.950804</v>
       </c>
       <c r="Y35" t="n">
-        <v>-1.594081</v>
+        <v>-1.872012</v>
       </c>
       <c r="Z35" t="n">
         <v>8.856460999999999</v>
@@ -9682,7 +9682,7 @@
         <v>5.672634</v>
       </c>
       <c r="Y36" t="n">
-        <v>6.730239</v>
+        <v>6.417995</v>
       </c>
       <c r="Z36" t="n">
         <v>-6.910893</v>
@@ -9968,7 +9968,7 @@
         <v>33147.25</v>
       </c>
       <c r="K37" t="n">
-        <v>1819.699951</v>
+        <v>1826.199951</v>
       </c>
       <c r="L37" t="n">
         <v>80.260002</v>
@@ -10010,7 +10010,7 @@
         <v>-4.170365</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.221074</v>
+        <v>4.593353</v>
       </c>
       <c r="Z37" t="n">
         <v>-0.360026</v>
@@ -10342,7 +10342,7 @@
         <v>2.832178</v>
       </c>
       <c r="Y38" t="n">
-        <v>6.033964</v>
+        <v>5.656557</v>
       </c>
       <c r="Z38" t="n">
         <v>-1.731871</v>
@@ -10640,7 +10640,7 @@
         <v>32656.699219</v>
       </c>
       <c r="K39" t="n">
-        <v>1828.900024</v>
+        <v>1836.699951</v>
       </c>
       <c r="L39" t="n">
         <v>77.050003</v>
@@ -10682,7 +10682,7 @@
         <v>-4.193329</v>
       </c>
       <c r="Y39" t="n">
-        <v>-5.213785</v>
+        <v>-4.809539</v>
       </c>
       <c r="Z39" t="n">
         <v>-2.307594</v>
@@ -11022,7 +11022,7 @@
         <v>1.890728</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.660341</v>
+        <v>7.203139</v>
       </c>
       <c r="Z40" t="n">
         <v>-1.791051</v>
@@ -11320,7 +11320,7 @@
         <v>34098.160156</v>
       </c>
       <c r="K41" t="n">
-        <v>1990.099976</v>
+        <v>1999.099976</v>
       </c>
       <c r="L41" t="n">
         <v>76.779999</v>
@@ -11362,7 +11362,7 @@
         <v>2.476432</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.071609</v>
+        <v>1.528694</v>
       </c>
       <c r="Z41" t="n">
         <v>1.466897</v>
@@ -11690,7 +11690,7 @@
         <v>-3.489604</v>
       </c>
       <c r="Y42" t="n">
-        <v>-1.316514</v>
+        <v>-1.76079</v>
       </c>
       <c r="Z42" t="n">
         <v>-11.318055</v>
@@ -11984,7 +11984,7 @@
         <v>34407.601562</v>
       </c>
       <c r="K43" t="n">
-        <v>1921.099976</v>
+        <v>1929.400024</v>
       </c>
       <c r="L43" t="n">
         <v>70.639999</v>
@@ -12026,7 +12026,7 @@
         <v>4.556095</v>
       </c>
       <c r="Y43" t="n">
-        <v>-2.179339</v>
+        <v>-1.756709</v>
       </c>
       <c r="Z43" t="n">
         <v>3.745048</v>
@@ -12358,7 +12358,7 @@
         <v>3.347893</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.571445</v>
+        <v>2.130195</v>
       </c>
       <c r="Z44" t="n">
         <v>15.79842</v>
@@ -12648,7 +12648,7 @@
         <v>34721.910156</v>
       </c>
       <c r="K45" t="n">
-        <v>1938.199951</v>
+        <v>1965.900024</v>
       </c>
       <c r="L45" t="n">
         <v>83.629997</v>
@@ -12690,7 +12690,7 @@
         <v>-2.355546</v>
       </c>
       <c r="Y45" t="n">
-        <v>-1.63918</v>
+        <v>-0.233442</v>
       </c>
       <c r="Z45" t="n">
         <v>2.237157</v>
@@ -12984,7 +12984,7 @@
         <v>33507.5</v>
       </c>
       <c r="K46" t="n">
-        <v>1848.099976</v>
+        <v>1866.099976</v>
       </c>
       <c r="L46" t="n">
         <v>90.790001</v>
@@ -13026,7 +13026,7 @@
         <v>-3.497533</v>
       </c>
       <c r="Y46" t="n">
-        <v>-4.648642</v>
+        <v>-5.076558</v>
       </c>
       <c r="Z46" t="n">
         <v>8.561526000000001</v>
@@ -13316,7 +13316,7 @@
         <v>33052.871094</v>
       </c>
       <c r="K47" t="n">
-        <v>1985.199951</v>
+        <v>1994.300049</v>
       </c>
       <c r="L47" t="n">
         <v>81.019997</v>
@@ -13358,7 +13358,7 @@
         <v>-1.356797</v>
       </c>
       <c r="Y47" t="n">
-        <v>7.418429</v>
+        <v>6.869947</v>
       </c>
       <c r="Z47" t="n">
         <v>-10.761102</v>
@@ -13690,7 +13690,7 @@
         <v>8.76783</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.66472</v>
+        <v>2.196256</v>
       </c>
       <c r="Z48" t="n">
         <v>-6.245369</v>
@@ -13980,7 +13980,7 @@
         <v>37689.539062</v>
       </c>
       <c r="K49" t="n">
-        <v>2062.399902</v>
+        <v>2071.800049</v>
       </c>
       <c r="L49" t="n">
         <v>71.650002</v>
@@ -14022,7 +14022,7 @@
         <v>4.836176</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.192283</v>
+        <v>1.653504</v>
       </c>
       <c r="Z49" t="n">
         <v>-5.674036</v>
@@ -14358,7 +14358,7 @@
         <v>1.222519</v>
       </c>
       <c r="Y50" t="n">
-        <v>-0.678821</v>
+        <v>-1.12946</v>
       </c>
       <c r="Z50" t="n">
         <v>5.861824</v>
@@ -14648,7 +14648,7 @@
         <v>38996.390625</v>
       </c>
       <c r="K51" t="n">
-        <v>2045.699951</v>
+        <v>2054.699951</v>
       </c>
       <c r="L51" t="n">
         <v>78.260002</v>
@@ -14690,7 +14690,7 @@
         <v>2.21778</v>
       </c>
       <c r="Y51" t="n">
-        <v>-0.131808</v>
+        <v>0.30756</v>
       </c>
       <c r="Z51" t="n">
         <v>3.177329</v>
@@ -15018,7 +15018,7 @@
         <v>2.07963</v>
       </c>
       <c r="Y52" t="n">
-        <v>8.393212999999999</v>
+        <v>7.918429</v>
       </c>
       <c r="Z52" t="n">
         <v>6.273953</v>
@@ -15312,7 +15312,7 @@
         <v>37815.921875</v>
       </c>
       <c r="K53" t="n">
-        <v>2291.399902</v>
+        <v>2302.899902</v>
       </c>
       <c r="L53" t="n">
         <v>81.93000000000001</v>
@@ -15354,7 +15354,7 @@
         <v>-5.002715</v>
       </c>
       <c r="Y53" t="n">
-        <v>3.337242</v>
+        <v>3.855867</v>
       </c>
       <c r="Z53" t="n">
         <v>-1.49092</v>
@@ -15686,7 +15686,7 @@
         <v>2.301672</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.374705</v>
+        <v>0.86847</v>
       </c>
       <c r="Z54" t="n">
         <v>-6.02954</v>
@@ -15980,7 +15980,7 @@
         <v>39118.859375</v>
       </c>
       <c r="K55" t="n">
-        <v>2327.699951</v>
+        <v>2339.600098</v>
       </c>
       <c r="L55" t="n">
         <v>81.540001</v>
@@ -16022,7 +16022,7 @@
         <v>1.118067</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.20664</v>
+        <v>0.718937</v>
       </c>
       <c r="Z55" t="n">
         <v>5.909863</v>
@@ -16358,7 +16358,7 @@
         <v>4.406902</v>
       </c>
       <c r="Y56" t="n">
-        <v>4.244535</v>
+        <v>3.714306</v>
       </c>
       <c r="Z56" t="n">
         <v>-4.451799</v>
@@ -16652,7 +16652,7 @@
         <v>41563.078125</v>
       </c>
       <c r="K57" t="n">
-        <v>2493.800049</v>
+        <v>2527.600098</v>
       </c>
       <c r="L57" t="n">
         <v>73.550003</v>
@@ -16694,7 +16694,7 @@
         <v>1.763565</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.773544</v>
+        <v>4.166499</v>
       </c>
       <c r="Z57" t="n">
         <v>-5.596201</v>
@@ -16988,7 +16988,7 @@
         <v>42330.148438</v>
       </c>
       <c r="K58" t="n">
-        <v>2636.100098</v>
+        <v>2659.399902</v>
       </c>
       <c r="L58" t="n">
         <v>68.16999800000001</v>
@@ -17030,7 +17030,7 @@
         <v>1.845557</v>
       </c>
       <c r="Y58" t="n">
-        <v>5.706153</v>
+        <v>5.214425</v>
       </c>
       <c r="Z58" t="n">
         <v>-7.314758</v>
@@ -17324,7 +17324,7 @@
         <v>41763.460938</v>
       </c>
       <c r="K59" t="n">
-        <v>2738.300049</v>
+        <v>2749.300049</v>
       </c>
       <c r="L59" t="n">
         <v>69.260002</v>
@@ -17366,7 +17366,7 @@
         <v>-1.338733</v>
       </c>
       <c r="Y59" t="n">
-        <v>3.876937</v>
+        <v>3.380467</v>
       </c>
       <c r="Z59" t="n">
         <v>1.59895</v>
@@ -17694,7 +17694,7 @@
         <v>7.535744</v>
       </c>
       <c r="Y60" t="n">
-        <v>-2.968997</v>
+        <v>-3.35722</v>
       </c>
       <c r="Z60" t="n">
         <v>-1.819235</v>
@@ -17988,7 +17988,7 @@
         <v>42544.21875</v>
       </c>
       <c r="K61" t="n">
-        <v>2629.199951</v>
+        <v>2641</v>
       </c>
       <c r="L61" t="n">
         <v>71.720001</v>
@@ -18030,7 +18030,7 @@
         <v>-5.269195</v>
       </c>
       <c r="Y61" t="n">
-        <v>-1.046295</v>
+        <v>-0.602183</v>
       </c>
       <c r="Z61" t="n">
         <v>5.47059</v>
@@ -18366,7 +18366,7 @@
         <v>4.702029</v>
       </c>
       <c r="Y62" t="n">
-        <v>6.971704</v>
+        <v>6.493752</v>
       </c>
       <c r="Z62" t="n">
         <v>1.129389</v>
@@ -18664,7 +18664,7 @@
         <v>43840.910156</v>
       </c>
       <c r="K63" t="n">
-        <v>2836.800049</v>
+        <v>2848.5</v>
       </c>
       <c r="L63" t="n">
         <v>69.760002</v>
@@ -18706,7 +18706,7 @@
         <v>-1.579875</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.864002</v>
+        <v>1.28</v>
       </c>
       <c r="Z63" t="n">
         <v>-3.819105</v>
@@ -19042,7 +19042,7 @@
         <v>-4.195051</v>
       </c>
       <c r="Y64" t="n">
-        <v>10.081782</v>
+        <v>9.629631</v>
       </c>
       <c r="Z64" t="n">
         <v>2.465598</v>
@@ -19332,7 +19332,7 @@
         <v>40669.359375</v>
       </c>
       <c r="K65" t="n">
-        <v>3305</v>
+        <v>3319.100098</v>
       </c>
       <c r="L65" t="n">
         <v>58.209999</v>
@@ -19374,7 +19374,7 @@
         <v>-3.172253</v>
       </c>
       <c r="Y65" t="n">
-        <v>5.834506</v>
+        <v>6.286027</v>
       </c>
       <c r="Z65" t="n">
         <v>-18.564639</v>
@@ -19714,7 +19714,7 @@
         <v>3.935914</v>
       </c>
       <c r="Y66" t="n">
-        <v>-0.487144</v>
+        <v>-0.909891</v>
       </c>
       <c r="Z66" t="n">
         <v>4.432231</v>
@@ -20008,7 +20008,7 @@
         <v>44094.769531</v>
       </c>
       <c r="K67" t="n">
-        <v>3294.399902</v>
+        <v>3307.699951</v>
       </c>
       <c r="L67" t="n">
         <v>65.110001</v>
@@ -20050,7 +20050,7 @@
         <v>4.316764</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.167229</v>
+        <v>0.571621</v>
       </c>
       <c r="Z67" t="n">
         <v>7.106431</v>
@@ -20386,7 +20386,7 @@
         <v>0.082121</v>
       </c>
       <c r="Y68" t="n">
-        <v>-0.036424</v>
+        <v>-0.438371</v>
       </c>
       <c r="Z68" t="n">
         <v>6.373831</v>
@@ -20684,7 +20684,7 @@
         <v>45544.878906</v>
       </c>
       <c r="K69" t="n">
-        <v>3473.699951</v>
+        <v>3516.100098</v>
       </c>
       <c r="L69" t="n">
         <v>64.010002</v>
@@ -20726,7 +20726,7 @@
         <v>3.203868</v>
       </c>
       <c r="Y69" t="n">
-        <v>5.480991</v>
+        <v>6.768497</v>
       </c>
       <c r="Z69" t="n">
         <v>-7.580133</v>
@@ -21020,7 +21020,7 @@
         <v>46397.890625</v>
       </c>
       <c r="K70" t="n">
-        <v>3840.800049</v>
+        <v>3873.199951</v>
       </c>
       <c r="L70" t="n">
         <v>62.369999</v>
@@ -21062,7 +21062,7 @@
         <v>1.872904</v>
       </c>
       <c r="Y70" t="n">
-        <v>10.567985</v>
+        <v>10.156134</v>
       </c>
       <c r="Z70" t="n">
         <v>-2.562105</v>
@@ -21356,7 +21356,7 @@
         <v>47562.871094</v>
       </c>
       <c r="K71" t="n">
-        <v>3982.199951</v>
+        <v>3996.5</v>
       </c>
       <c r="L71" t="n">
         <v>60.98</v>
@@ -21398,7 +21398,7 @@
         <v>2.510848</v>
       </c>
       <c r="Y71" t="n">
-        <v>3.681522</v>
+        <v>3.183416</v>
       </c>
       <c r="Z71" t="n">
         <v>-2.228635</v>
@@ -21692,7 +21692,7 @@
         <v>47716.421875</v>
       </c>
       <c r="K72" t="n">
-        <v>4218.299805</v>
+        <v>4254.899902</v>
       </c>
       <c r="L72" t="n">
         <v>58.549999</v>
@@ -21734,7 +21734,7 @@
         <v>0.322837</v>
       </c>
       <c r="Y72" t="n">
-        <v>5.92888</v>
+        <v>6.465655</v>
       </c>
       <c r="Z72" t="n">
         <v>-3.984914</v>
@@ -22032,7 +22032,7 @@
         <v>48063.289062</v>
       </c>
       <c r="K73" t="n">
-        <v>4325.600098</v>
+        <v>4341.100098</v>
       </c>
       <c r="L73" t="n">
         <v>57.419998</v>
@@ -22074,7 +22074,7 @@
         <v>0.726935</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.543686</v>
+        <v>2.025904</v>
       </c>
       <c r="Z73" t="n">
         <v>-1.929976</v>
@@ -22364,7 +22364,7 @@
         <v>48892.46875</v>
       </c>
       <c r="K74" t="n">
-        <v>4713.899902</v>
+        <v>4745.100098</v>
       </c>
       <c r="L74" t="n">
         <v>65.209999</v>
@@ -22406,7 +22406,7 @@
         <v>1.725183</v>
       </c>
       <c r="Y74" t="n">
-        <v>8.976785</v>
+        <v>9.306397</v>
       </c>
       <c r="Z74" t="n">
         <v>13.566704</v>
@@ -22700,7 +22700,7 @@
         <v>48977.921875</v>
       </c>
       <c r="K75" t="n">
-        <v>5230.5</v>
+        <v>5247.899902</v>
       </c>
       <c r="L75" t="n">
         <v>67.019997</v>
@@ -22742,7 +22742,7 @@
         <v>0.174778</v>
       </c>
       <c r="Y75" t="n">
-        <v>10.959081</v>
+        <v>10.59619</v>
       </c>
       <c r="Z75" t="n">
         <v>2.775644</v>
@@ -23082,7 +23082,7 @@
         <v>-5.382854</v>
       </c>
       <c r="Y76" t="n">
-        <v>-11.144248</v>
+        <v>-11.438858</v>
       </c>
       <c r="Z76" t="n">
         <v>51.268282</v>
@@ -23376,7 +23376,7 @@
         <v>49652.140625</v>
       </c>
       <c r="K77" t="n">
-        <v>4614.700195</v>
+        <v>4629.600098</v>
       </c>
       <c r="L77" t="n">
         <v>105.07</v>
@@ -23418,7 +23418,7 @@
         <v>7.143981</v>
       </c>
       <c r="Y77" t="n">
-        <v>-0.70789</v>
+        <v>-0.387297</v>
       </c>
       <c r="Z77" t="n">
         <v>3.639774</v>
@@ -23712,7 +23712,7 @@
         <v>51032.460938</v>
       </c>
       <c r="K78" t="n">
-        <v>4560.5</v>
+        <v>4593</v>
       </c>
       <c r="L78" t="n">
         <v>87.360001</v>
@@ -23754,7 +23754,7 @@
         <v>2.779981</v>
       </c>
       <c r="Y78" t="n">
-        <v>-1.174512</v>
+        <v>-0.790567</v>
       </c>
       <c r="Z78" t="n">
         <v>-16.855429</v>
@@ -24052,7 +24052,7 @@
         <v>52319.199219</v>
       </c>
       <c r="K79" t="n">
-        <v>4022.899902</v>
+        <v>4038.5</v>
       </c>
       <c r="L79" t="n">
         <v>69.5</v>
@@ -24094,7 +24094,7 @@
         <v>2.521411</v>
       </c>
       <c r="Y79" t="n">
-        <v>-11.788183</v>
+        <v>-12.072719</v>
       </c>
       <c r="Z79" t="n">
         <v>-20.44414</v>
@@ -24388,7 +24388,7 @@
         <v>52485.03125</v>
       </c>
       <c r="K80" t="n">
-        <v>4049.100098</v>
+        <v>4107</v>
       </c>
       <c r="L80" t="n">
         <v>84.66999800000001</v>
@@ -24430,7 +24430,7 @@
         <v>0.316962</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.651276</v>
+        <v>1.696174</v>
       </c>
       <c r="Z80" t="n">
         <v>21.827335</v>
@@ -24720,7 +24720,7 @@
         <v>53185.898438</v>
       </c>
       <c r="K81" t="n">
-        <v>4431.100098</v>
+        <v>4481.5</v>
       </c>
       <c r="L81" t="n">
         <v>85.760002</v>
@@ -24762,7 +24762,7 @@
         <v>1.335366</v>
       </c>
       <c r="Y81" t="n">
-        <v>9.434195000000001</v>
+        <v>9.118577999999999</v>
       </c>
       <c r="Z81" t="n">
         <v>1.287356</v>
@@ -24993,88 +24993,88 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>185371.140625</v>
+        <v>185959.625</v>
       </c>
       <c r="C82" t="n">
-        <v>182.369995</v>
+        <v>183.039993</v>
       </c>
       <c r="D82" t="n">
-        <v>109.68</v>
+        <v>109.540001</v>
       </c>
       <c r="E82" t="n">
-        <v>443.630005</v>
+        <v>440.839996</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1539</v>
+        <v>5.1456</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9512</v>
+        <v>5.9456</v>
       </c>
       <c r="H82" t="n">
-        <v>7626.77002</v>
+        <v>7585.890137</v>
       </c>
       <c r="I82" t="n">
-        <v>26209.451172</v>
+        <v>26026.601562</v>
       </c>
       <c r="J82" t="n">
-        <v>52482.101562</v>
+        <v>51923.578125</v>
       </c>
       <c r="K82" t="n">
-        <v>4331.600098</v>
+        <v>4329.299805</v>
       </c>
       <c r="L82" t="n">
-        <v>102.970001</v>
+        <v>103.730003</v>
       </c>
       <c r="M82" t="n">
-        <v>107.419998</v>
+        <v>102.610001</v>
       </c>
       <c r="N82" t="n">
         <v>1306.5</v>
       </c>
       <c r="O82" t="n">
-        <v>530.5</v>
+        <v>531.25</v>
       </c>
       <c r="P82" t="n">
-        <v>4.482125</v>
+        <v>4.813816</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.3426</v>
+        <v>4.725938</v>
       </c>
       <c r="R82" t="n">
-        <v>3.344957</v>
+        <v>3.213044</v>
       </c>
       <c r="S82" t="n">
-        <v>-1.27295</v>
+        <v>-1.893849</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.718517</v>
+        <v>-0.878408</v>
       </c>
       <c r="U82" t="n">
-        <v>-0.972025</v>
+        <v>-1.065208</v>
       </c>
       <c r="V82" t="n">
-        <v>-0.772431</v>
+        <v>-1.304296</v>
       </c>
       <c r="W82" t="n">
-        <v>-0.612188</v>
+        <v>-1.305565</v>
       </c>
       <c r="X82" t="n">
-        <v>-1.323277</v>
+        <v>-2.373412</v>
       </c>
       <c r="Y82" t="n">
-        <v>-2.245492</v>
+        <v>-3.396189</v>
       </c>
       <c r="Z82" t="n">
-        <v>20.067629</v>
+        <v>20.953826</v>
       </c>
       <c r="AA82" t="n">
-        <v>18.70925</v>
+        <v>13.393749</v>
       </c>
       <c r="AB82" t="n">
         <v>2.4505</v>
       </c>
       <c r="AC82" t="n">
-        <v>3.009709</v>
+        <v>3.15534</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>
@@ -25091,10 +25091,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.0918</v>
+        <v>5.1696</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.0912</v>
+        <v>5.169</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25107,10 +25107,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-1.733055</v>
+        <v>-0.231589</v>
       </c>
       <c r="AY82" t="n">
-        <v>-1.733256</v>
+        <v>-0.231616</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5100,10 +5100,10 @@
         <v>6.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.021808</v>
+        <v>0.021979</v>
       </c>
       <c r="AG22" t="n">
         <v>1.16</v>
@@ -5115,10 +5115,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>96.95313</v>
+        <v>96.96513</v>
       </c>
       <c r="AK22" t="n">
-        <v>97.10569</v>
+        <v>97.10777</v>
       </c>
       <c r="AL22" t="n">
         <v>5.4394</v>
@@ -5415,10 +5415,10 @@
         <v>1.16</v>
       </c>
       <c r="AJ23" t="n">
-        <v>97.47790999999999</v>
+        <v>97.48671</v>
       </c>
       <c r="AK23" t="n">
-        <v>96.52863000000001</v>
+        <v>96.53041</v>
       </c>
       <c r="AL23" t="n">
         <v>5.643</v>
@@ -5451,10 +5451,10 @@
         <v>367927</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.541272</v>
+        <v>0.537905</v>
       </c>
       <c r="AW23" t="n">
-        <v>-0.59426</v>
+        <v>-0.594556</v>
       </c>
       <c r="AX23" t="n">
         <v>3.74306</v>
@@ -5481,10 +5481,10 @@
         <v>1.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.002435</v>
+        <v>0.002265</v>
       </c>
       <c r="BJ23" t="n">
         <v>-0.01</v>
@@ -5741,10 +5741,10 @@
         <v>0.84</v>
       </c>
       <c r="AJ24" t="n">
-        <v>99.05295</v>
+        <v>99.05526</v>
       </c>
       <c r="AK24" t="n">
-        <v>97.85433</v>
+        <v>97.85277000000001</v>
       </c>
       <c r="AL24" t="n">
         <v>5.6199</v>
@@ -5777,10 +5777,10 @@
         <v>367772</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.615792</v>
+        <v>1.608989</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.373375</v>
+        <v>1.36989</v>
       </c>
       <c r="AX24" t="n">
         <v>-0.409357</v>
@@ -6075,10 +6075,10 @@
         <v>0.73</v>
       </c>
       <c r="AJ25" t="n">
-        <v>99.36759000000001</v>
+        <v>99.37716</v>
       </c>
       <c r="AK25" t="n">
-        <v>99.32245</v>
+        <v>99.32258</v>
       </c>
       <c r="AL25" t="n">
         <v>5.5805</v>
@@ -6111,10 +6111,10 @@
         <v>362204</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.317648</v>
+        <v>0.32497</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.500312</v>
+        <v>1.502063</v>
       </c>
       <c r="AX25" t="n">
         <v>-0.70108</v>
@@ -6405,10 +6405,10 @@
         <v>0.67</v>
       </c>
       <c r="AJ26" t="n">
-        <v>97.41759</v>
+        <v>97.4213</v>
       </c>
       <c r="AK26" t="n">
-        <v>91.67452</v>
+        <v>91.67776000000001</v>
       </c>
       <c r="AL26" t="n">
         <v>5.3574</v>
@@ -6441,10 +6441,10 @@
         <v>358398</v>
       </c>
       <c r="AV26" t="n">
-        <v>-1.96241</v>
+        <v>-1.968118</v>
       </c>
       <c r="AW26" t="n">
-        <v>-7.700102</v>
+        <v>-7.696961</v>
       </c>
       <c r="AX26" t="n">
         <v>-3.99785</v>
@@ -6727,10 +6727,10 @@
         <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>98.48287000000001</v>
+        <v>98.4804</v>
       </c>
       <c r="AK27" t="n">
-        <v>95.64045</v>
+        <v>95.63728999999999</v>
       </c>
       <c r="AL27" t="n">
         <v>5.1394</v>
@@ -6763,10 +6763,10 @@
         <v>357740</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.093519</v>
+        <v>1.087134</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.326098</v>
+        <v>4.318965</v>
       </c>
       <c r="AX27" t="n">
         <v>-4.069138</v>
@@ -7053,10 +7053,10 @@
         <v>1.71</v>
       </c>
       <c r="AJ28" t="n">
-        <v>99.54331000000001</v>
+        <v>99.54801999999999</v>
       </c>
       <c r="AK28" t="n">
-        <v>104.53224</v>
+        <v>104.53237</v>
       </c>
       <c r="AL28" t="n">
         <v>4.7378</v>
@@ -7089,10 +7089,10 @@
         <v>353169</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.076776</v>
+        <v>1.084094</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.297102000000001</v>
+        <v>9.300848999999999</v>
       </c>
       <c r="AX28" t="n">
         <v>-7.814142</v>
@@ -7375,10 +7375,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ29" t="n">
-        <v>99.44726</v>
+        <v>99.44118</v>
       </c>
       <c r="AK29" t="n">
-        <v>100.22451</v>
+        <v>100.22938</v>
       </c>
       <c r="AL29" t="n">
         <v>4.9191</v>
@@ -7411,10 +7411,10 @@
         <v>345097</v>
       </c>
       <c r="AV29" t="n">
-        <v>-0.09649099999999999</v>
+        <v>-0.107325</v>
       </c>
       <c r="AW29" t="n">
-        <v>-4.120958</v>
+        <v>-4.116419</v>
       </c>
       <c r="AX29" t="n">
         <v>3.826671</v>
@@ -7709,10 +7709,10 @@
         <v>0.45</v>
       </c>
       <c r="AJ30" t="n">
-        <v>99.65249</v>
+        <v>99.6454</v>
       </c>
       <c r="AK30" t="n">
-        <v>99.74639000000001</v>
+        <v>99.74383</v>
       </c>
       <c r="AL30" t="n">
         <v>4.7289</v>
@@ -7745,10 +7745,10 @@
         <v>346415</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.206371</v>
+        <v>0.205368</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.477049</v>
+        <v>-0.484439</v>
       </c>
       <c r="AX30" t="n">
         <v>-3.866561</v>
@@ -8039,10 +8039,10 @@
         <v>0.62</v>
       </c>
       <c r="AJ31" t="n">
-        <v>99.53077999999999</v>
+        <v>99.51048</v>
       </c>
       <c r="AK31" t="n">
-        <v>99.32053000000001</v>
+        <v>99.31653</v>
       </c>
       <c r="AL31" t="n">
         <v>5.238</v>
@@ -8075,10 +8075,10 @@
         <v>341958</v>
       </c>
       <c r="AV31" t="n">
-        <v>-0.122134</v>
+        <v>-0.1354</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.426943</v>
+        <v>-0.428397</v>
       </c>
       <c r="AX31" t="n">
         <v>10.765717</v>
@@ -8369,10 +8369,10 @@
         <v>-0.6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>101.43252</v>
+        <v>101.43172</v>
       </c>
       <c r="AK32" t="n">
-        <v>103.95413</v>
+        <v>103.95991</v>
       </c>
       <c r="AL32" t="n">
         <v>5.1884</v>
@@ -8405,10 +8405,10 @@
         <v>346403</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.910705</v>
+        <v>1.930691</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.665299</v>
+        <v>4.675335</v>
       </c>
       <c r="AX32" t="n">
         <v>-0.946926</v>
@@ -8703,10 +8703,10 @@
         <v>-0.31</v>
       </c>
       <c r="AJ33" t="n">
-        <v>101.09886</v>
+        <v>101.10583</v>
       </c>
       <c r="AK33" t="n">
-        <v>104.51426</v>
+        <v>104.51156</v>
       </c>
       <c r="AL33" t="n">
         <v>5.179</v>
@@ -8739,10 +8739,10 @@
         <v>339664</v>
       </c>
       <c r="AV33" t="n">
-        <v>-0.328948</v>
+        <v>-0.32129</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.538824</v>
+        <v>0.530637</v>
       </c>
       <c r="AX33" t="n">
         <v>-0.181173</v>
@@ -9039,10 +9039,10 @@
         <v>-0.32</v>
       </c>
       <c r="AJ34" t="n">
-        <v>101.15209</v>
+        <v>101.16034</v>
       </c>
       <c r="AK34" t="n">
-        <v>101.19157</v>
+        <v>101.1889</v>
       </c>
       <c r="AL34" t="n">
         <v>5.4066</v>
@@ -9075,10 +9075,10 @@
         <v>327580</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.052651</v>
+        <v>0.053914</v>
       </c>
       <c r="AW34" t="n">
-        <v>-3.179174</v>
+        <v>-3.179227</v>
       </c>
       <c r="AX34" t="n">
         <v>4.394671</v>
@@ -9379,10 +9379,10 @@
         <v>0.47</v>
       </c>
       <c r="AJ35" t="n">
-        <v>101.43094</v>
+        <v>101.44171</v>
       </c>
       <c r="AK35" t="n">
-        <v>100.07474</v>
+        <v>100.08177</v>
       </c>
       <c r="AL35" t="n">
         <v>5.257</v>
@@ -9415,10 +9415,10 @@
         <v>325546</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.275674</v>
+        <v>0.278143</v>
       </c>
       <c r="AW35" t="n">
-        <v>-1.103679</v>
+        <v>-1.094122</v>
       </c>
       <c r="AX35" t="n">
         <v>-2.766988</v>
@@ -9715,10 +9715,10 @@
         <v>0.38</v>
       </c>
       <c r="AJ36" t="n">
-        <v>100.7113</v>
+        <v>100.7146</v>
       </c>
       <c r="AK36" t="n">
-        <v>99.15328</v>
+        <v>99.15031999999999</v>
       </c>
       <c r="AL36" t="n">
         <v>5.2941</v>
@@ -9751,10 +9751,10 @@
         <v>331505</v>
       </c>
       <c r="AV36" t="n">
-        <v>-0.709488</v>
+        <v>-0.716776</v>
       </c>
       <c r="AW36" t="n">
-        <v>-0.920772</v>
+        <v>-0.930689</v>
       </c>
       <c r="AX36" t="n">
         <v>0.705726</v>
@@ -10043,10 +10043,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AJ37" t="n">
-        <v>100.58566</v>
+        <v>100.58818</v>
       </c>
       <c r="AK37" t="n">
-        <v>99.97338999999999</v>
+        <v>99.97037</v>
       </c>
       <c r="AL37" t="n">
         <v>5.2177</v>
@@ -10079,10 +10079,10 @@
         <v>324703</v>
       </c>
       <c r="AV37" t="n">
-        <v>-0.124753</v>
+        <v>-0.125523</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.827113</v>
+        <v>0.827078</v>
       </c>
       <c r="AX37" t="n">
         <v>-1.443116</v>
@@ -10375,10 +10375,10 @@
         <v>0.46</v>
       </c>
       <c r="AJ38" t="n">
-        <v>100.10937</v>
+        <v>100.10988</v>
       </c>
       <c r="AK38" t="n">
-        <v>95.09372999999999</v>
+        <v>95.09953</v>
       </c>
       <c r="AL38" t="n">
         <v>5.0993</v>
@@ -10411,10 +10411,10 @@
         <v>331122</v>
       </c>
       <c r="AV38" t="n">
-        <v>-0.473517</v>
+        <v>-0.475503</v>
       </c>
       <c r="AW38" t="n">
-        <v>-4.880959</v>
+        <v>-4.872284</v>
       </c>
       <c r="AX38" t="n">
         <v>-2.269199</v>
@@ -10715,10 +10715,10 @@
         <v>0.77</v>
       </c>
       <c r="AJ39" t="n">
-        <v>103.08344</v>
+        <v>103.07987</v>
       </c>
       <c r="AK39" t="n">
-        <v>98.65015</v>
+        <v>98.64798</v>
       </c>
       <c r="AL39" t="n">
         <v>5.2078</v>
@@ -10751,10 +10751,10 @@
         <v>328098</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.970821</v>
+        <v>2.96673</v>
       </c>
       <c r="AW39" t="n">
-        <v>3.73991</v>
+        <v>3.731301</v>
       </c>
       <c r="AX39" t="n">
         <v>2.127743</v>
@@ -11055,10 +11055,10 @@
         <v>0.64</v>
       </c>
       <c r="AJ40" t="n">
-        <v>103.08526</v>
+        <v>103.08494</v>
       </c>
       <c r="AK40" t="n">
-        <v>110.62045</v>
+        <v>110.61922</v>
       </c>
       <c r="AL40" t="n">
         <v>5.0804</v>
@@ -11091,10 +11091,10 @@
         <v>341158</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.001766</v>
+        <v>0.004919</v>
       </c>
       <c r="AW40" t="n">
-        <v>12.134092</v>
+        <v>12.135312</v>
       </c>
       <c r="AX40" t="n">
         <v>-2.446331</v>
@@ -11395,10 +11395,10 @@
         <v>0.53</v>
       </c>
       <c r="AJ41" t="n">
-        <v>103.96006</v>
+        <v>103.93573</v>
       </c>
       <c r="AK41" t="n">
-        <v>104.03539</v>
+        <v>104.04095</v>
       </c>
       <c r="AL41" t="n">
         <v>5.0007</v>
@@ -11431,10 +11431,10 @@
         <v>345725</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.848618</v>
+        <v>0.825329</v>
       </c>
       <c r="AW41" t="n">
-        <v>-5.952841</v>
+        <v>-5.946769</v>
       </c>
       <c r="AX41" t="n">
         <v>-1.568774</v>
@@ -11723,10 +11723,10 @@
         <v>0.36</v>
       </c>
       <c r="AJ42" t="n">
-        <v>102.40467</v>
+        <v>102.42973</v>
       </c>
       <c r="AK42" t="n">
-        <v>102.71665</v>
+        <v>102.71375</v>
       </c>
       <c r="AL42" t="n">
         <v>5.0959</v>
@@ -11759,10 +11759,10 @@
         <v>343489</v>
       </c>
       <c r="AV42" t="n">
-        <v>-1.496142</v>
+        <v>-1.448972</v>
       </c>
       <c r="AW42" t="n">
-        <v>-1.267588</v>
+        <v>-1.275652</v>
       </c>
       <c r="AX42" t="n">
         <v>1.903733</v>
@@ -12059,10 +12059,10 @@
         <v>-0.1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>102.4398</v>
+        <v>102.39935</v>
       </c>
       <c r="AK43" t="n">
-        <v>102.285</v>
+        <v>102.28352</v>
       </c>
       <c r="AL43" t="n">
         <v>4.8192</v>
@@ -12095,10 +12095,10 @@
         <v>343620</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.034305</v>
+        <v>-0.029659</v>
       </c>
       <c r="AW43" t="n">
-        <v>-0.420234</v>
+        <v>-0.418863</v>
       </c>
       <c r="AX43" t="n">
         <v>-5.429855</v>
@@ -12391,10 +12391,10 @@
         <v>-0.09</v>
       </c>
       <c r="AJ44" t="n">
-        <v>102.89895</v>
+        <v>102.90686</v>
       </c>
       <c r="AK44" t="n">
-        <v>105.33914</v>
+        <v>105.34474</v>
       </c>
       <c r="AL44" t="n">
         <v>4.7415</v>
@@ -12427,10 +12427,10 @@
         <v>345476</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.448214</v>
+        <v>0.495618</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.985912</v>
+        <v>2.992877</v>
       </c>
       <c r="AX44" t="n">
         <v>-1.612301</v>
@@ -12723,10 +12723,10 @@
         <v>0.2</v>
       </c>
       <c r="AJ45" t="n">
-        <v>102.48797</v>
+        <v>102.50239</v>
       </c>
       <c r="AK45" t="n">
-        <v>106.05945</v>
+        <v>106.05687</v>
       </c>
       <c r="AL45" t="n">
         <v>4.9219</v>
@@ -12759,10 +12759,10 @@
         <v>344177</v>
       </c>
       <c r="AV45" t="n">
-        <v>-0.399402</v>
+        <v>-0.393045</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.683801</v>
+        <v>0.676</v>
       </c>
       <c r="AX45" t="n">
         <v>3.804703</v>
@@ -13059,10 +13059,10 @@
         <v>0.11</v>
       </c>
       <c r="AJ46" t="n">
-        <v>102.50227</v>
+        <v>102.5153</v>
       </c>
       <c r="AK46" t="n">
-        <v>101.76242</v>
+        <v>101.75897</v>
       </c>
       <c r="AL46" t="n">
         <v>5.0076</v>
@@ -13095,10 +13095,10 @@
         <v>340324</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.013953</v>
+        <v>0.012595</v>
       </c>
       <c r="AW46" t="n">
-        <v>-4.05153</v>
+        <v>-4.052448</v>
       </c>
       <c r="AX46" t="n">
         <v>1.741198</v>
@@ -13391,10 +13391,10 @@
         <v>0.12</v>
       </c>
       <c r="AJ47" t="n">
-        <v>102.83037</v>
+        <v>102.83959</v>
       </c>
       <c r="AK47" t="n">
-        <v>101.92849</v>
+        <v>101.9338</v>
       </c>
       <c r="AL47" t="n">
         <v>5.0575</v>
@@ -13427,10 +13427,10 @@
         <v>340247</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.32009</v>
+        <v>0.316333</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.163194</v>
+        <v>0.171808</v>
       </c>
       <c r="AX47" t="n">
         <v>0.996485</v>
@@ -13723,10 +13723,10 @@
         <v>0.1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>103.58799</v>
+        <v>103.59456</v>
       </c>
       <c r="AK48" t="n">
-        <v>101.68208</v>
+        <v>101.68042</v>
       </c>
       <c r="AL48" t="n">
         <v>4.9355</v>
@@ -13759,10 +13759,10 @@
         <v>348406</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.7367669999999999</v>
+        <v>0.734124</v>
       </c>
       <c r="AW48" t="n">
-        <v>-0.241748</v>
+        <v>-0.248573</v>
       </c>
       <c r="AX48" t="n">
         <v>-2.412259</v>
@@ -14055,10 +14055,10 @@
         <v>0.55</v>
       </c>
       <c r="AJ49" t="n">
-        <v>104.88262</v>
+        <v>104.88818</v>
       </c>
       <c r="AK49" t="n">
-        <v>101.68652</v>
+        <v>101.68469</v>
       </c>
       <c r="AL49" t="n">
         <v>4.8413</v>
@@ -14091,10 +14091,10 @@
         <v>355034</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.249788</v>
+        <v>1.248734</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.004367</v>
+        <v>0.004199</v>
       </c>
       <c r="AX49" t="n">
         <v>-1.908621</v>
@@ -14391,10 +14391,10 @@
         <v>0.57</v>
       </c>
       <c r="AJ50" t="n">
-        <v>104.47589</v>
+        <v>104.473</v>
       </c>
       <c r="AK50" t="n">
-        <v>99.29136</v>
+        <v>99.29718</v>
       </c>
       <c r="AL50" t="n">
         <v>4.9535</v>
@@ -14427,10 +14427,10 @@
         <v>355066</v>
       </c>
       <c r="AV50" t="n">
-        <v>-0.387795</v>
+        <v>-0.395831</v>
       </c>
       <c r="AW50" t="n">
-        <v>-2.355435</v>
+        <v>-2.347954</v>
       </c>
       <c r="AX50" t="n">
         <v>2.317559</v>
@@ -14723,10 +14723,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ51" t="n">
-        <v>104.67291</v>
+        <v>104.65885</v>
       </c>
       <c r="AK51" t="n">
-        <v>102.15158</v>
+        <v>102.15036</v>
       </c>
       <c r="AL51" t="n">
         <v>4.9833</v>
@@ -14759,10 +14759,10 @@
         <v>352705</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.188579</v>
+        <v>0.177893</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.880633</v>
+        <v>2.873375</v>
       </c>
       <c r="AX51" t="n">
         <v>0.601595</v>
@@ -15051,10 +15051,10 @@
         <v>0.19</v>
       </c>
       <c r="AJ52" t="n">
-        <v>104.68779</v>
+        <v>104.6738</v>
       </c>
       <c r="AK52" t="n">
-        <v>109.57244</v>
+        <v>109.56901</v>
       </c>
       <c r="AL52" t="n">
         <v>4.9962</v>
@@ -15087,10 +15087,10 @@
         <v>355008</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.014216</v>
+        <v>0.014285</v>
       </c>
       <c r="AW52" t="n">
-        <v>7.264557</v>
+        <v>7.262481</v>
       </c>
       <c r="AX52" t="n">
         <v>0.258865</v>
@@ -15387,10 +15387,10 @@
         <v>0.37</v>
       </c>
       <c r="AJ53" t="n">
-        <v>104.6751</v>
+        <v>104.62771</v>
       </c>
       <c r="AK53" t="n">
-        <v>109.25226</v>
+        <v>109.2572</v>
       </c>
       <c r="AL53" t="n">
         <v>5.1718</v>
@@ -15423,10 +15423,10 @@
         <v>351599</v>
       </c>
       <c r="AV53" t="n">
-        <v>-0.012122</v>
+        <v>-0.044032</v>
       </c>
       <c r="AW53" t="n">
-        <v>-0.292209</v>
+        <v>-0.284579</v>
       </c>
       <c r="AX53" t="n">
         <v>3.514671</v>
@@ -15719,10 +15719,10 @@
         <v>0.46</v>
       </c>
       <c r="AJ54" t="n">
-        <v>105.5521</v>
+        <v>105.60427</v>
       </c>
       <c r="AK54" t="n">
-        <v>104.71219</v>
+        <v>104.71213</v>
       </c>
       <c r="AL54" t="n">
         <v>5.2416</v>
@@ -15755,10 +15755,10 @@
         <v>355560</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.837831</v>
+        <v>0.9333669999999999</v>
       </c>
       <c r="AW54" t="n">
-        <v>-4.155585</v>
+        <v>-4.159973</v>
       </c>
       <c r="AX54" t="n">
         <v>1.349627</v>
@@ -16055,10 +16055,10 @@
         <v>0.25</v>
       </c>
       <c r="AJ55" t="n">
-        <v>106.65779</v>
+        <v>106.5891</v>
       </c>
       <c r="AK55" t="n">
-        <v>105.87342</v>
+        <v>105.86915</v>
       </c>
       <c r="AL55" t="n">
         <v>5.5589</v>
@@ -16091,10 +16091,10 @@
         <v>357827</v>
       </c>
       <c r="AV55" t="n">
-        <v>1.04753</v>
+        <v>0.932566</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.108973</v>
+        <v>1.104953</v>
       </c>
       <c r="AX55" t="n">
         <v>6.053495</v>
@@ -16391,10 +16391,10 @@
         <v>0.26</v>
       </c>
       <c r="AJ56" t="n">
-        <v>107.01873</v>
+        <v>107.06237</v>
       </c>
       <c r="AK56" t="n">
-        <v>111.50432</v>
+        <v>111.509</v>
       </c>
       <c r="AL56" t="n">
         <v>5.6621</v>
@@ -16427,10 +16427,10 @@
         <v>363282</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.338409</v>
+        <v>0.444014</v>
       </c>
       <c r="AW56" t="n">
-        <v>5.318521</v>
+        <v>5.327189</v>
       </c>
       <c r="AX56" t="n">
         <v>1.856482</v>
@@ -16727,10 +16727,10 @@
         <v>-0.14</v>
       </c>
       <c r="AJ57" t="n">
-        <v>107.16697</v>
+        <v>107.19174</v>
       </c>
       <c r="AK57" t="n">
-        <v>110.06264</v>
+        <v>110.06254</v>
       </c>
       <c r="AL57" t="n">
         <v>5.6562</v>
@@ -16763,10 +16763,10 @@
         <v>369214</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.138518</v>
+        <v>0.120836</v>
       </c>
       <c r="AW57" t="n">
-        <v>-1.292936</v>
+        <v>-1.297169</v>
       </c>
       <c r="AX57" t="n">
         <v>-0.104202</v>
@@ -17063,10 +17063,10 @@
         <v>0.48</v>
       </c>
       <c r="AJ58" t="n">
-        <v>108.02415</v>
+        <v>108.04382</v>
       </c>
       <c r="AK58" t="n">
-        <v>107.08272</v>
+        <v>107.07852</v>
       </c>
       <c r="AL58" t="n">
         <v>5.4481</v>
@@ -17099,10 +17099,10 @@
         <v>372016</v>
       </c>
       <c r="AV58" t="n">
-        <v>0.799855</v>
+        <v>0.794912</v>
       </c>
       <c r="AW58" t="n">
-        <v>-2.707476</v>
+        <v>-2.711204</v>
       </c>
       <c r="AX58" t="n">
         <v>-3.679149</v>
@@ -17399,10 +17399,10 @@
         <v>0.61</v>
       </c>
       <c r="AJ59" t="n">
-        <v>108.23273</v>
+        <v>108.2446</v>
       </c>
       <c r="AK59" t="n">
-        <v>109.17883</v>
+        <v>109.18379</v>
       </c>
       <c r="AL59" t="n">
         <v>5.7779</v>
@@ -17435,10 +17435,10 @@
         <v>366096</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.193086</v>
+        <v>0.185832</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.957468</v>
+        <v>1.966099</v>
       </c>
       <c r="AX59" t="n">
         <v>6.053487</v>
@@ -17727,10 +17727,10 @@
         <v>0.33</v>
       </c>
       <c r="AJ60" t="n">
-        <v>107.99539</v>
+        <v>108.00109</v>
       </c>
       <c r="AK60" t="n">
-        <v>105.48993</v>
+        <v>105.49006</v>
       </c>
       <c r="AL60" t="n">
         <v>6.0535</v>
@@ -17763,10 +17763,10 @@
         <v>363003</v>
       </c>
       <c r="AV60" t="n">
-        <v>-0.219287</v>
+        <v>-0.224963</v>
       </c>
       <c r="AW60" t="n">
-        <v>-3.378769</v>
+        <v>-3.383039</v>
       </c>
       <c r="AX60" t="n">
         <v>4.769899</v>
@@ -18063,10 +18063,10 @@
         <v>0.48</v>
       </c>
       <c r="AJ61" t="n">
-        <v>107.3722</v>
+        <v>107.37012</v>
       </c>
       <c r="AK61" t="n">
-        <v>104.15749</v>
+        <v>104.15552</v>
       </c>
       <c r="AL61" t="n">
         <v>6.1923</v>
@@ -18099,10 +18099,10 @@
         <v>329730</v>
       </c>
       <c r="AV61" t="n">
-        <v>-0.577052</v>
+        <v>-0.584226</v>
       </c>
       <c r="AW61" t="n">
-        <v>-1.263097</v>
+        <v>-1.265086</v>
       </c>
       <c r="AX61" t="n">
         <v>2.292888</v>
@@ -18399,10 +18399,10 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>108.10202</v>
+        <v>108.09524</v>
       </c>
       <c r="AK62" t="n">
-        <v>102.62361</v>
+        <v>102.62949</v>
       </c>
       <c r="AL62" t="n">
         <v>5.8301</v>
@@ -18435,10 +18435,10 @@
         <v>328303</v>
       </c>
       <c r="AV62" t="n">
-        <v>0.67971</v>
+        <v>0.675346</v>
       </c>
       <c r="AW62" t="n">
-        <v>-1.472655</v>
+        <v>-1.465146</v>
       </c>
       <c r="AX62" t="n">
         <v>-5.8492</v>
@@ -18739,10 +18739,10 @@
         <v>1.48</v>
       </c>
       <c r="AJ63" t="n">
-        <v>108.64347</v>
+        <v>108.62006</v>
       </c>
       <c r="AK63" t="n">
-        <v>106.82695</v>
+        <v>106.82599</v>
       </c>
       <c r="AL63" t="n">
         <v>5.8488</v>
@@ -18775,10 +18775,10 @@
         <v>332508</v>
       </c>
       <c r="AV63" t="n">
-        <v>0.500869</v>
+        <v>0.485516</v>
       </c>
       <c r="AW63" t="n">
-        <v>4.09588</v>
+        <v>4.088981</v>
       </c>
       <c r="AX63" t="n">
         <v>0.320749</v>
@@ -19075,10 +19075,10 @@
         <v>0.51</v>
       </c>
       <c r="AJ64" t="n">
-        <v>110.0586</v>
+        <v>110.03287</v>
       </c>
       <c r="AK64" t="n">
-        <v>114.02633</v>
+        <v>114.02067</v>
       </c>
       <c r="AL64" t="n">
         <v>5.7422</v>
@@ -19111,10 +19111,10 @@
         <v>336157</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.302545</v>
+        <v>1.30069</v>
       </c>
       <c r="AW64" t="n">
-        <v>6.739292</v>
+        <v>6.734953</v>
       </c>
       <c r="AX64" t="n">
         <v>-1.822596</v>
@@ -19407,10 +19407,10 @@
         <v>0.48</v>
       </c>
       <c r="AJ65" t="n">
-        <v>109.59971</v>
+        <v>109.52766</v>
       </c>
       <c r="AK65" t="n">
-        <v>112.58856</v>
+        <v>112.59512</v>
       </c>
       <c r="AL65" t="n">
         <v>5.6608</v>
@@ -19443,10 +19443,10 @@
         <v>340789</v>
       </c>
       <c r="AV65" t="n">
-        <v>-0.416951</v>
+        <v>-0.459145</v>
       </c>
       <c r="AW65" t="n">
-        <v>-1.260911</v>
+        <v>-1.250256</v>
       </c>
       <c r="AX65" t="n">
         <v>-1.417575</v>
@@ -19747,10 +19747,10 @@
         <v>0.35</v>
       </c>
       <c r="AJ66" t="n">
-        <v>108.80425</v>
+        <v>108.8862</v>
       </c>
       <c r="AK66" t="n">
-        <v>108.55662</v>
+        <v>108.55704</v>
       </c>
       <c r="AL66" t="n">
         <v>5.7087</v>
@@ -19783,10 +19783,10 @@
         <v>341459</v>
       </c>
       <c r="AV66" t="n">
-        <v>-0.725787</v>
+        <v>-0.58566</v>
       </c>
       <c r="AW66" t="n">
-        <v>-3.581128</v>
+        <v>-3.586372</v>
       </c>
       <c r="AX66" t="n">
         <v>0.84617</v>
@@ -20083,10 +20083,10 @@
         <v>0.23</v>
       </c>
       <c r="AJ67" t="n">
-        <v>108.90168</v>
+        <v>108.80376</v>
       </c>
       <c r="AK67" t="n">
-        <v>107.36878</v>
+        <v>107.36219</v>
       </c>
       <c r="AL67" t="n">
         <v>5.4571</v>
@@ -20119,10 +20119,10 @@
         <v>344440</v>
       </c>
       <c r="AV67" t="n">
-        <v>0.089546</v>
+        <v>-0.075712</v>
       </c>
       <c r="AW67" t="n">
-        <v>-1.094212</v>
+        <v>-1.100666</v>
       </c>
       <c r="AX67" t="n">
         <v>-4.407308</v>
@@ -20419,10 +20419,10 @@
         <v>0.21</v>
       </c>
       <c r="AJ68" t="n">
-        <v>108.39998</v>
+        <v>108.49869</v>
       </c>
       <c r="AK68" t="n">
-        <v>113.10359</v>
+        <v>113.10928</v>
       </c>
       <c r="AL68" t="n">
         <v>5.6021</v>
@@ -20455,10 +20455,10 @@
         <v>345111</v>
       </c>
       <c r="AV68" t="n">
-        <v>-0.460691</v>
+        <v>-0.280386</v>
       </c>
       <c r="AW68" t="n">
-        <v>5.341227</v>
+        <v>5.352993</v>
       </c>
       <c r="AX68" t="n">
         <v>2.657089</v>
@@ -20759,10 +20759,10 @@
         <v>-0.21</v>
       </c>
       <c r="AJ69" t="n">
-        <v>108.79892</v>
+        <v>108.82893</v>
       </c>
       <c r="AK69" t="n">
-        <v>110.38013</v>
+        <v>110.38054</v>
       </c>
       <c r="AL69" t="n">
         <v>5.4264</v>
@@ -20795,10 +20795,10 @@
         <v>350767</v>
       </c>
       <c r="AV69" t="n">
-        <v>0.368026</v>
+        <v>0.304372</v>
       </c>
       <c r="AW69" t="n">
-        <v>-2.407934</v>
+        <v>-2.412481</v>
       </c>
       <c r="AX69" t="n">
         <v>-3.136324</v>
@@ -21095,10 +21095,10 @@
         <v>0.52</v>
       </c>
       <c r="AJ70" t="n">
-        <v>108.7209</v>
+        <v>108.73548</v>
       </c>
       <c r="AK70" t="n">
-        <v>109.48882</v>
+        <v>109.48375</v>
       </c>
       <c r="AL70" t="n">
         <v>5.3186</v>
@@ -21131,10 +21131,10 @@
         <v>356582</v>
       </c>
       <c r="AV70" t="n">
-        <v>-0.07171</v>
+        <v>-0.085869</v>
       </c>
       <c r="AW70" t="n">
-        <v>-0.807491</v>
+        <v>-0.812453</v>
       </c>
       <c r="AX70" t="n">
         <v>-1.986584</v>
@@ -21431,10 +21431,10 @@
         <v>0.03</v>
       </c>
       <c r="AJ71" t="n">
-        <v>108.73364</v>
+        <v>108.75326</v>
       </c>
       <c r="AK71" t="n">
-        <v>110.06407</v>
+        <v>110.07682</v>
       </c>
       <c r="AL71" t="n">
         <v>5.3843</v>
@@ -21467,10 +21467,10 @@
         <v>357103</v>
       </c>
       <c r="AV71" t="n">
-        <v>0.011718</v>
+        <v>0.016352</v>
       </c>
       <c r="AW71" t="n">
-        <v>0.525396</v>
+        <v>0.541697</v>
       </c>
       <c r="AX71" t="n">
         <v>1.235287</v>
@@ -21767,10 +21767,10 @@
         <v>0.03</v>
       </c>
       <c r="AJ72" t="n">
-        <v>109.24151</v>
+        <v>109.25005</v>
       </c>
       <c r="AK72" t="n">
-        <v>106.59541</v>
+        <v>106.59892</v>
       </c>
       <c r="AL72" t="n">
         <v>5.3338</v>
@@ -21803,10 +21803,10 @@
         <v>360578</v>
       </c>
       <c r="AV72" t="n">
-        <v>0.467077</v>
+        <v>0.456805</v>
       </c>
       <c r="AW72" t="n">
-        <v>-3.151492</v>
+        <v>-3.159521</v>
       </c>
       <c r="AX72" t="n">
         <v>-0.937912</v>
@@ -22107,10 +22107,10 @@
         <v>0.21</v>
       </c>
       <c r="AJ73" t="n">
-        <v>109.46142</v>
+        <v>109.4528</v>
       </c>
       <c r="AK73" t="n">
-        <v>107.19319</v>
+        <v>107.18417</v>
       </c>
       <c r="AL73" t="n">
         <v>5.5024</v>
@@ -22143,10 +22143,10 @@
         <v>358234</v>
       </c>
       <c r="AV73" t="n">
-        <v>0.201306</v>
+        <v>0.185583</v>
       </c>
       <c r="AW73" t="n">
-        <v>0.560793</v>
+        <v>0.549021</v>
       </c>
       <c r="AX73" t="n">
         <v>3.160973</v>
@@ -22439,10 +22439,10 @@
         <v>0.39</v>
       </c>
       <c r="AJ74" t="n">
-        <v>110.07661</v>
+        <v>110.04992</v>
       </c>
       <c r="AK74" t="n">
-        <v>103.78191</v>
+        <v>103.77761</v>
       </c>
       <c r="AL74" t="n">
         <v>5.2301</v>
@@ -22475,10 +22475,10 @@
         <v>364367</v>
       </c>
       <c r="AV74" t="n">
-        <v>0.562015</v>
+        <v>0.54555</v>
       </c>
       <c r="AW74" t="n">
-        <v>-3.182366</v>
+        <v>-3.178231</v>
       </c>
       <c r="AX74" t="n">
         <v>-4.94875</v>
@@ -22775,10 +22775,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AJ75" t="n">
-        <v>110.77581</v>
+        <v>110.7366</v>
       </c>
       <c r="AK75" t="n">
-        <v>106.77083</v>
+        <v>106.76075</v>
       </c>
       <c r="AL75" t="n">
         <v>5.1495</v>
@@ -22811,10 +22811,10 @@
         <v>371074</v>
       </c>
       <c r="AV75" t="n">
-        <v>0.635194</v>
+        <v>0.6239710000000001</v>
       </c>
       <c r="AW75" t="n">
-        <v>2.880001</v>
+        <v>2.874551</v>
       </c>
       <c r="AX75" t="n">
         <v>-1.54108</v>
@@ -23115,10 +23115,10 @@
         <v>0.91</v>
       </c>
       <c r="AJ76" t="n">
-        <v>110.60765</v>
+        <v>110.58808</v>
       </c>
       <c r="AK76" t="n">
-        <v>118.00063</v>
+        <v>118.01719</v>
       </c>
       <c r="AL76" t="n">
         <v>5.2194</v>
@@ -23151,10 +23151,10 @@
         <v>362002</v>
       </c>
       <c r="AV76" t="n">
-        <v>-0.151802</v>
+        <v>-0.13412</v>
       </c>
       <c r="AW76" t="n">
-        <v>10.517667</v>
+        <v>10.543613</v>
       </c>
       <c r="AX76" t="n">
         <v>1.357413</v>
@@ -23451,10 +23451,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ77" t="n">
-        <v>110.90086</v>
+        <v>110.90009</v>
       </c>
       <c r="AK77" t="n">
-        <v>113.89942</v>
+        <v>113.99295</v>
       </c>
       <c r="AL77" t="n">
         <v>4.9886</v>
@@ -23487,10 +23487,10 @@
         <v>366913</v>
       </c>
       <c r="AV77" t="n">
-        <v>0.26509</v>
+        <v>0.282137</v>
       </c>
       <c r="AW77" t="n">
-        <v>-3.475583</v>
+        <v>-3.409876</v>
       </c>
       <c r="AX77" t="n">
         <v>-4.421964</v>
@@ -23787,10 +23787,10 @@
         <v>0.65</v>
       </c>
       <c r="AJ78" t="n">
-        <v>110.93102</v>
+        <v>111.13846</v>
       </c>
       <c r="AK78" t="n">
-        <v>109.53002</v>
+        <v>109.65479</v>
       </c>
       <c r="AL78" t="n">
         <v>5.0569</v>
@@ -23823,10 +23823,10 @@
         <v>371137</v>
       </c>
       <c r="AV78" t="n">
-        <v>0.027195</v>
+        <v>0.214941</v>
       </c>
       <c r="AW78" t="n">
-        <v>-3.836192</v>
+        <v>-3.805639</v>
       </c>
       <c r="AX78" t="n">
         <v>1.369122</v>
@@ -24127,10 +24127,10 @@
         <v>0.14</v>
       </c>
       <c r="AJ79" t="n">
-        <v>110.22154</v>
+        <v>110.15775</v>
       </c>
       <c r="AK79" t="n">
-        <v>109.89427</v>
+        <v>109.94156</v>
       </c>
       <c r="AL79" t="n">
         <v>5.1766</v>
@@ -24163,10 +24163,10 @@
         <v>367558</v>
       </c>
       <c r="AV79" t="n">
-        <v>-0.6395690000000001</v>
+        <v>-0.882422</v>
       </c>
       <c r="AW79" t="n">
-        <v>0.332557</v>
+        <v>0.261521</v>
       </c>
       <c r="AX79" t="n">
         <v>2.367063</v>
@@ -24462,8 +24462,12 @@
       <c r="AI80" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
+      <c r="AJ80" t="n">
+        <v>109.91611</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>114.40189</v>
+      </c>
       <c r="AL80" t="n">
         <v>5.0773</v>
       </c>
@@ -24494,8 +24498,12 @@
       <c r="AU80" t="n">
         <v>369742</v>
       </c>
-      <c r="AV80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr"/>
+      <c r="AV80" t="n">
+        <v>-0.219358</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>4.057001</v>
+      </c>
       <c r="AX80" t="n">
         <v>-1.918247</v>
       </c>
@@ -24993,88 +25001,88 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>185959.625</v>
+        <v>185399.484375</v>
       </c>
       <c r="C82" t="n">
-        <v>183.039993</v>
+        <v>182.539993</v>
       </c>
       <c r="D82" t="n">
         <v>109.540001</v>
       </c>
       <c r="E82" t="n">
-        <v>440.839996</v>
+        <v>442.51001</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1456</v>
+        <v>5.1546</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9456</v>
+        <v>5.9476</v>
       </c>
       <c r="H82" t="n">
-        <v>7585.890137</v>
+        <v>7600.680176</v>
       </c>
       <c r="I82" t="n">
-        <v>26026.601562</v>
+        <v>26133.207031</v>
       </c>
       <c r="J82" t="n">
-        <v>51923.578125</v>
+        <v>51940.390625</v>
       </c>
       <c r="K82" t="n">
-        <v>4329.299805</v>
+        <v>4376.899902</v>
       </c>
       <c r="L82" t="n">
-        <v>103.730003</v>
+        <v>103.169998</v>
       </c>
       <c r="M82" t="n">
-        <v>102.610001</v>
+        <v>106.949997</v>
       </c>
       <c r="N82" t="n">
-        <v>1306.5</v>
+        <v>1320.25</v>
       </c>
       <c r="O82" t="n">
-        <v>531.25</v>
+        <v>535</v>
       </c>
       <c r="P82" t="n">
-        <v>4.813816</v>
+        <v>4.4981</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.725938</v>
+        <v>4.439864</v>
       </c>
       <c r="R82" t="n">
         <v>3.213044</v>
       </c>
       <c r="S82" t="n">
-        <v>-1.893849</v>
+        <v>-1.522198</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.878408</v>
+        <v>-0.705032</v>
       </c>
       <c r="U82" t="n">
-        <v>-1.065208</v>
+        <v>-1.031931</v>
       </c>
       <c r="V82" t="n">
-        <v>-1.304296</v>
+        <v>-1.111871</v>
       </c>
       <c r="W82" t="n">
-        <v>-1.305565</v>
+        <v>-0.9013099999999999</v>
       </c>
       <c r="X82" t="n">
-        <v>-2.373412</v>
+        <v>-2.341801</v>
       </c>
       <c r="Y82" t="n">
-        <v>-3.396189</v>
+        <v>-2.334042</v>
       </c>
       <c r="Z82" t="n">
-        <v>20.953826</v>
+        <v>20.300834</v>
       </c>
       <c r="AA82" t="n">
-        <v>13.393749</v>
+        <v>18.189855</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.4505</v>
+        <v>3.52872</v>
       </c>
       <c r="AC82" t="n">
-        <v>3.15534</v>
+        <v>3.883495</v>
       </c>
       <c r="AD82" t="n">
         <v>14</v>
@@ -25091,10 +25099,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.1696</v>
+        <v>5.149</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.169</v>
+        <v>5.1484</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25107,10 +25115,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-0.231589</v>
+        <v>-0.629149</v>
       </c>
       <c r="AY82" t="n">
-        <v>-0.231616</v>
+        <v>-0.6292219999999999</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5100,10 +5100,10 @@
         <v>6.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.021979</v>
+        <v>0.022184</v>
       </c>
       <c r="AG22" t="n">
         <v>1.16</v>
@@ -5481,10 +5481,10 @@
         <v>1.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.002265</v>
+        <v>0.00206</v>
       </c>
       <c r="BJ23" t="n">
         <v>-0.01</v>
@@ -25001,91 +25001,91 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>185399.484375</v>
+        <v>184544.75</v>
       </c>
       <c r="C82" t="n">
-        <v>182.539993</v>
+        <v>181.610001</v>
       </c>
       <c r="D82" t="n">
-        <v>109.540001</v>
+        <v>109.209999</v>
       </c>
       <c r="E82" t="n">
-        <v>442.51001</v>
+        <v>444.839996</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1546</v>
+        <v>5.1599</v>
       </c>
       <c r="G82" t="n">
-        <v>5.9476</v>
+        <v>5.9317</v>
       </c>
       <c r="H82" t="n">
-        <v>7600.680176</v>
+        <v>7630.069824</v>
       </c>
       <c r="I82" t="n">
-        <v>26133.207031</v>
+        <v>26407.919922</v>
       </c>
       <c r="J82" t="n">
-        <v>51940.390625</v>
+        <v>51741.929688</v>
       </c>
       <c r="K82" t="n">
-        <v>4376.899902</v>
+        <v>4410.5</v>
       </c>
       <c r="L82" t="n">
-        <v>103.169998</v>
+        <v>100.389999</v>
       </c>
       <c r="M82" t="n">
-        <v>106.949997</v>
+        <v>102.959999</v>
       </c>
       <c r="N82" t="n">
-        <v>1320.25</v>
+        <v>1312.5</v>
       </c>
       <c r="O82" t="n">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="P82" t="n">
-        <v>4.4981</v>
+        <v>4.01634</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.439864</v>
+        <v>3.907771</v>
       </c>
       <c r="R82" t="n">
-        <v>3.213044</v>
+        <v>2.902103</v>
       </c>
       <c r="S82" t="n">
-        <v>-1.522198</v>
+        <v>-1.003674</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.705032</v>
+        <v>-0.602936</v>
       </c>
       <c r="U82" t="n">
-        <v>-1.031931</v>
+        <v>-1.296501</v>
       </c>
       <c r="V82" t="n">
-        <v>-1.111871</v>
+        <v>-0.729499</v>
       </c>
       <c r="W82" t="n">
-        <v>-0.9013099999999999</v>
+        <v>0.140417</v>
       </c>
       <c r="X82" t="n">
-        <v>-2.341801</v>
+        <v>-2.714947</v>
       </c>
       <c r="Y82" t="n">
-        <v>-2.334042</v>
+        <v>-1.584291</v>
       </c>
       <c r="Z82" t="n">
-        <v>20.300834</v>
+        <v>17.059231</v>
       </c>
       <c r="AA82" t="n">
-        <v>18.189855</v>
+        <v>13.78053</v>
       </c>
       <c r="AB82" t="n">
-        <v>3.52872</v>
+        <v>2.920996</v>
       </c>
       <c r="AC82" t="n">
-        <v>3.883495</v>
+        <v>2.524272</v>
       </c>
       <c r="AD82" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AE82" t="n">
         <v>0.05166</v>
@@ -25099,10 +25099,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.149</v>
+        <v>5.1527</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.1484</v>
+        <v>5.152</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25115,10 +25115,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-0.629149</v>
+        <v>-0.557743</v>
       </c>
       <c r="AY82" t="n">
-        <v>-0.6292219999999999</v>
+        <v>-0.559738</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>
@@ -25128,7 +25128,7 @@
       <c r="BE82" t="inlineStr"/>
       <c r="BF82" t="inlineStr"/>
       <c r="BG82" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="BH82" t="n">
         <v>-0.000124</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -25001,97 +25001,97 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>187575.046875</v>
+        <v>185430.703125</v>
       </c>
       <c r="C82" t="n">
-        <v>184.679993</v>
+        <v>182.5</v>
       </c>
       <c r="D82" t="n">
-        <v>111.980003</v>
+        <v>110.760002</v>
       </c>
       <c r="E82" t="n">
-        <v>448.869995</v>
+        <v>449.720001</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1471</v>
+        <v>5.1764</v>
       </c>
       <c r="G82" t="n">
-        <v>5.8651</v>
+        <v>5.8909</v>
       </c>
       <c r="H82" t="n">
-        <v>7725.299805</v>
+        <v>7687.310059</v>
       </c>
       <c r="I82" t="n">
-        <v>26969.003906</v>
+        <v>26805.265625</v>
       </c>
       <c r="J82" t="n">
-        <v>51787.929688</v>
+        <v>51308.679688</v>
       </c>
       <c r="K82" t="n">
-        <v>4315.5</v>
+        <v>4298.899902</v>
       </c>
       <c r="L82" t="n">
-        <v>92.099998</v>
+        <v>94.66999800000001</v>
       </c>
       <c r="M82" t="n">
-        <v>97.620003</v>
+        <v>100.309998</v>
       </c>
       <c r="N82" t="n">
-        <v>1315.75</v>
+        <v>1316</v>
       </c>
       <c r="O82" t="n">
-        <v>528.75</v>
+        <v>527.75</v>
       </c>
       <c r="P82" t="n">
-        <v>5.724329</v>
+        <v>4.515696</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.66426</v>
+        <v>4.416982</v>
       </c>
       <c r="R82" t="n">
-        <v>5.512114</v>
+        <v>4.362579</v>
       </c>
       <c r="S82" t="n">
-        <v>-0.106823</v>
+        <v>0.08234</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.849511</v>
+        <v>-0.28509</v>
       </c>
       <c r="U82" t="n">
-        <v>-2.40473</v>
+        <v>-1.975415</v>
       </c>
       <c r="V82" t="n">
-        <v>0.509484</v>
+        <v>0.015221</v>
       </c>
       <c r="W82" t="n">
-        <v>2.268081</v>
+        <v>1.647176</v>
       </c>
       <c r="X82" t="n">
-        <v>-2.628458</v>
+        <v>-3.529542</v>
       </c>
       <c r="Y82" t="n">
-        <v>-3.704117</v>
+        <v>-4.074531</v>
       </c>
       <c r="Z82" t="n">
-        <v>7.392719</v>
+        <v>10.389454</v>
       </c>
       <c r="AA82" t="n">
-        <v>7.879329</v>
+        <v>10.852028</v>
       </c>
       <c r="AB82" t="n">
-        <v>3.175848</v>
+        <v>3.195452</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.669903</v>
+        <v>2.475728</v>
       </c>
       <c r="AD82" t="n">
         <v>13.75</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.051427</v>
+        <v>0.051387</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -25099,10 +25099,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.1161</v>
+        <v>5.1414</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.1155</v>
+        <v>5.1408</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25115,10 +25115,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-1.264088</v>
+        <v>-0.775822</v>
       </c>
       <c r="AY82" t="n">
-        <v>-1.264235</v>
+        <v>-0.775912</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>
@@ -25131,10 +25131,10 @@
         <v>-0.25</v>
       </c>
       <c r="BH82" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
       <c r="BI82" t="n">
-        <v>-0.000357</v>
+        <v>-0.000397</v>
       </c>
       <c r="BJ82" t="inlineStr"/>
       <c r="BK82" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -25001,88 +25001,88 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>185430.703125</v>
+        <v>185707.59375</v>
       </c>
       <c r="C82" t="n">
-        <v>182.5</v>
+        <v>182.770004</v>
       </c>
       <c r="D82" t="n">
-        <v>110.760002</v>
+        <v>110.959999</v>
       </c>
       <c r="E82" t="n">
-        <v>449.720001</v>
+        <v>449.549988</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1764</v>
+        <v>5.1808</v>
       </c>
       <c r="G82" t="n">
-        <v>5.8909</v>
+        <v>5.8912</v>
       </c>
       <c r="H82" t="n">
-        <v>7687.310059</v>
+        <v>7687.410156</v>
       </c>
       <c r="I82" t="n">
-        <v>26805.265625</v>
+        <v>26794.8125</v>
       </c>
       <c r="J82" t="n">
-        <v>51308.679688</v>
+        <v>51309.371094</v>
       </c>
       <c r="K82" t="n">
-        <v>4298.899902</v>
+        <v>4296.299805</v>
       </c>
       <c r="L82" t="n">
-        <v>94.66999800000001</v>
+        <v>94.720001</v>
       </c>
       <c r="M82" t="n">
-        <v>100.309998</v>
+        <v>100.32</v>
       </c>
       <c r="N82" t="n">
-        <v>1316</v>
+        <v>1317.5</v>
       </c>
       <c r="O82" t="n">
-        <v>527.75</v>
+        <v>530</v>
       </c>
       <c r="P82" t="n">
-        <v>4.515696</v>
+        <v>4.671762</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.416982</v>
+        <v>4.571464</v>
       </c>
       <c r="R82" t="n">
-        <v>4.362579</v>
+        <v>4.551024</v>
       </c>
       <c r="S82" t="n">
-        <v>0.08234</v>
+        <v>0.044505</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.28509</v>
+        <v>-0.200336</v>
       </c>
       <c r="U82" t="n">
-        <v>-1.975415</v>
+        <v>-1.970424</v>
       </c>
       <c r="V82" t="n">
-        <v>0.015221</v>
+        <v>0.016524</v>
       </c>
       <c r="W82" t="n">
-        <v>1.647176</v>
+        <v>1.607537</v>
       </c>
       <c r="X82" t="n">
-        <v>-3.529542</v>
+        <v>-3.528242</v>
       </c>
       <c r="Y82" t="n">
-        <v>-4.074531</v>
+        <v>-4.132549</v>
       </c>
       <c r="Z82" t="n">
-        <v>10.389454</v>
+        <v>10.44776</v>
       </c>
       <c r="AA82" t="n">
-        <v>10.852028</v>
+        <v>10.863081</v>
       </c>
       <c r="AB82" t="n">
-        <v>3.195452</v>
+        <v>3.313076</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.475728</v>
+        <v>2.912621</v>
       </c>
       <c r="AD82" t="n">
         <v>13.75</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -25001,97 +25001,97 @@
         <v>46295</v>
       </c>
       <c r="B82" t="n">
-        <v>185707.59375</v>
+        <v>182428.5</v>
       </c>
       <c r="C82" t="n">
-        <v>182.770004</v>
+        <v>179.610001</v>
       </c>
       <c r="D82" t="n">
-        <v>110.959999</v>
+        <v>109.449997</v>
       </c>
       <c r="E82" t="n">
-        <v>449.549988</v>
+        <v>453.279999</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1808</v>
+        <v>5.204</v>
       </c>
       <c r="G82" t="n">
-        <v>5.8912</v>
+        <v>5.9357</v>
       </c>
       <c r="H82" t="n">
-        <v>7687.410156</v>
+        <v>7712.609863</v>
       </c>
       <c r="I82" t="n">
-        <v>26794.8125</v>
+        <v>26965.560547</v>
       </c>
       <c r="J82" t="n">
-        <v>51309.371094</v>
+        <v>51492.351562</v>
       </c>
       <c r="K82" t="n">
-        <v>4296.299805</v>
+        <v>4306.899902</v>
       </c>
       <c r="L82" t="n">
-        <v>94.720001</v>
+        <v>94.099998</v>
       </c>
       <c r="M82" t="n">
-        <v>100.32</v>
+        <v>99.589996</v>
       </c>
       <c r="N82" t="n">
-        <v>1317.5</v>
+        <v>1305</v>
       </c>
       <c r="O82" t="n">
-        <v>530</v>
+        <v>521.25</v>
       </c>
       <c r="P82" t="n">
-        <v>4.671762</v>
+        <v>2.823542</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.571464</v>
+        <v>2.763475</v>
       </c>
       <c r="R82" t="n">
-        <v>4.551024</v>
+        <v>3.128239</v>
       </c>
       <c r="S82" t="n">
-        <v>0.044505</v>
+        <v>0.874595</v>
       </c>
       <c r="T82" t="n">
-        <v>-0.200336</v>
+        <v>0.246575</v>
       </c>
       <c r="U82" t="n">
-        <v>-1.970424</v>
+        <v>-1.229946</v>
       </c>
       <c r="V82" t="n">
-        <v>0.016524</v>
+        <v>0.344383</v>
       </c>
       <c r="W82" t="n">
-        <v>1.607537</v>
+        <v>2.255024</v>
       </c>
       <c r="X82" t="n">
-        <v>-3.528242</v>
+        <v>-3.184203</v>
       </c>
       <c r="Y82" t="n">
-        <v>-4.132549</v>
+        <v>-3.896019</v>
       </c>
       <c r="Z82" t="n">
-        <v>10.44776</v>
+        <v>9.724809</v>
       </c>
       <c r="AA82" t="n">
-        <v>10.863081</v>
+        <v>10.056358</v>
       </c>
       <c r="AB82" t="n">
-        <v>3.313076</v>
+        <v>2.332876</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.912621</v>
+        <v>1.213592</v>
       </c>
       <c r="AD82" t="n">
         <v>13.75</v>
       </c>
       <c r="AE82" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.051387</v>
+        <v>0.051352</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -25099,10 +25099,10 @@
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="n">
-        <v>5.1414</v>
+        <v>5.1795</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.1408</v>
+        <v>5.1789</v>
       </c>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
@@ -25115,10 +25115,10 @@
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="n">
-        <v>-0.775822</v>
+        <v>-0.040528</v>
       </c>
       <c r="AY82" t="n">
-        <v>-0.775912</v>
+        <v>-0.040533</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>
@@ -25131,10 +25131,10 @@
         <v>-0.25</v>
       </c>
       <c r="BH82" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
       <c r="BI82" t="n">
-        <v>-0.000397</v>
+        <v>-0.000432</v>
       </c>
       <c r="BJ82" t="inlineStr"/>
       <c r="BK82" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -24689,88 +24689,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>187130.234375</v>
+        <v>192115</v>
       </c>
       <c r="C83" t="n">
-        <v>184.320007</v>
+        <v>184.410004</v>
       </c>
       <c r="D83" t="n">
-        <v>113.379997</v>
+        <v>113.019997</v>
       </c>
       <c r="E83" t="n">
-        <v>454.670013</v>
+        <v>452.079987</v>
       </c>
       <c r="F83" t="n">
-        <v>5.2234</v>
+        <v>5.2223</v>
       </c>
       <c r="G83" t="n">
-        <v>5.8805</v>
+        <v>5.8702</v>
       </c>
       <c r="H83" t="n">
-        <v>7725.560059</v>
+        <v>7722.720215</v>
       </c>
       <c r="I83" t="n">
-        <v>27222.126953</v>
+        <v>27190.859375</v>
       </c>
       <c r="J83" t="n">
-        <v>51112.210938</v>
+        <v>51176.960938</v>
       </c>
       <c r="K83" t="n">
-        <v>4155.200195</v>
+        <v>4162.299805</v>
       </c>
       <c r="L83" t="n">
-        <v>90.970001</v>
+        <v>91.110001</v>
       </c>
       <c r="M83" t="n">
-        <v>101.400002</v>
+        <v>102.25</v>
       </c>
       <c r="N83" t="n">
-        <v>1279.25</v>
+        <v>1278.25</v>
       </c>
       <c r="O83" t="n">
-        <v>496.75</v>
+        <v>497.75</v>
       </c>
       <c r="P83" t="n">
-        <v>0.424082</v>
+        <v>3.099174</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.130381</v>
+        <v>0.179271</v>
       </c>
       <c r="R83" t="n">
-        <v>1.29545</v>
+        <v>0.97382</v>
       </c>
       <c r="S83" t="n">
-        <v>1.631763</v>
+        <v>1.052818</v>
       </c>
       <c r="T83" t="n">
-        <v>0.394015</v>
+        <v>0.372871</v>
       </c>
       <c r="U83" t="n">
-        <v>-0.266714</v>
+        <v>-0.441397</v>
       </c>
       <c r="V83" t="n">
-        <v>0.967387</v>
+        <v>0.930273</v>
       </c>
       <c r="W83" t="n">
-        <v>1.3442</v>
+        <v>1.227795</v>
       </c>
       <c r="X83" t="n">
-        <v>0.404982</v>
+        <v>0.532177</v>
       </c>
       <c r="Y83" t="n">
-        <v>-0.752383</v>
+        <v>-0.582807</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.608276</v>
+        <v>0.763108</v>
       </c>
       <c r="AA83" t="n">
-        <v>-2.057372</v>
+        <v>-1.236355</v>
       </c>
       <c r="AB83" t="n">
-        <v>-1.063418</v>
+        <v>-1.140758</v>
       </c>
       <c r="AC83" t="n">
-        <v>-0.798802</v>
+        <v>-0.599101</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -24692,13 +24692,13 @@
         <v>192115</v>
       </c>
       <c r="C83" t="n">
-        <v>184.410004</v>
+        <v>190</v>
       </c>
       <c r="D83" t="n">
-        <v>113.019997</v>
+        <v>116.339996</v>
       </c>
       <c r="E83" t="n">
-        <v>452.079987</v>
+        <v>454.700012</v>
       </c>
       <c r="F83" t="n">
         <v>5.2223</v>
@@ -24734,13 +24734,13 @@
         <v>3.099174</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.179271</v>
+        <v>3.215992</v>
       </c>
       <c r="R83" t="n">
-        <v>0.97382</v>
+        <v>3.939959</v>
       </c>
       <c r="S83" t="n">
-        <v>1.052818</v>
+        <v>1.638469</v>
       </c>
       <c r="T83" t="n">
         <v>0.372871</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -568,27 +568,27 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_meta</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
           <t>bcb_sgs_selic_over</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>bcb_sgs_cdi</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_igp_m</t>
+        </is>
+      </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
+          <t>bcb_sgs_inpc</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_meta</t>
+          <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
@@ -5253,19 +5253,19 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="n">
-        <v>7.75</v>
+        <v>0.024383</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.024342</v>
+        <v>0.024383</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.024342</v>
+        <v>1.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="AI23" t="n">
         <v>97.48671</v>
@@ -5545,19 +5545,19 @@
         <v>-0.219974</v>
       </c>
       <c r="AD24" t="n">
-        <v>7.75</v>
+        <v>0.029256</v>
       </c>
       <c r="AE24" t="n">
         <v>0.029256</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.029256</v>
+        <v>0.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="AI24" t="n">
         <v>99.05526</v>
@@ -5621,14 +5621,12 @@
       </c>
       <c r="BC24" t="inlineStr"/>
       <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="n">
-        <v>0</v>
-      </c>
+      <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="n">
-        <v>0.004914</v>
+        <v>0.004873</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.004914</v>
+        <v>0.004873</v>
       </c>
       <c r="BH24" t="n">
         <v>0.03</v>
@@ -5875,19 +5873,19 @@
         <v>4.62963</v>
       </c>
       <c r="AD25" t="n">
-        <v>9.25</v>
+        <v>0.033316</v>
       </c>
       <c r="AE25" t="n">
         <v>0.033316</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.033316</v>
+        <v>0.73</v>
       </c>
       <c r="AG25" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.73</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0.87</v>
       </c>
       <c r="AI25" t="n">
         <v>99.37716</v>
@@ -5951,9 +5949,7 @@
       </c>
       <c r="BC25" t="inlineStr"/>
       <c r="BD25" t="inlineStr"/>
-      <c r="BE25" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="n">
         <v>0.00406</v>
       </c>
@@ -6201,19 +6197,19 @@
         <v>5.520438</v>
       </c>
       <c r="AD26" t="n">
-        <v>9.25</v>
+        <v>0.034749</v>
       </c>
       <c r="AE26" t="n">
         <v>0.034749</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.034749</v>
+        <v>0.54</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="AI26" t="n">
         <v>97.4213</v>
@@ -6277,9 +6273,7 @@
       </c>
       <c r="BC26" t="inlineStr"/>
       <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
+      <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="n">
         <v>0.001433</v>
       </c>
@@ -6519,19 +6513,19 @@
         <v>11.421725</v>
       </c>
       <c r="AD27" t="n">
-        <v>10.75</v>
+        <v>0.039598</v>
       </c>
       <c r="AE27" t="n">
         <v>0.039598</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.039598</v>
+        <v>1.01</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>98.4804</v>
@@ -6595,9 +6589,7 @@
       </c>
       <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="n">
         <v>0.004849</v>
       </c>
@@ -6841,19 +6833,19 @@
         <v>7.34767</v>
       </c>
       <c r="AD28" t="n">
-        <v>11.75</v>
+        <v>0.041954</v>
       </c>
       <c r="AE28" t="n">
         <v>0.041954</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.041954</v>
+        <v>1.62</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AI28" t="n">
         <v>99.54801999999999</v>
@@ -6917,9 +6909,7 @@
       </c>
       <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="n">
-        <v>1</v>
-      </c>
+      <c r="BE28" t="inlineStr"/>
       <c r="BF28" t="n">
         <v>0.002356</v>
       </c>
@@ -7159,19 +7149,19 @@
         <v>9.282137000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>11.75</v>
+        <v>0.043739</v>
       </c>
       <c r="AE29" t="n">
         <v>0.043739</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.043739</v>
+        <v>1.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI29" t="n">
         <v>99.44118</v>
@@ -7235,9 +7225,7 @@
       </c>
       <c r="BC29" t="inlineStr"/>
       <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
+      <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="n">
         <v>0.001785</v>
       </c>
@@ -7489,19 +7477,19 @@
         <v>-7.913229</v>
       </c>
       <c r="AD30" t="n">
-        <v>12.75</v>
+        <v>0.046796</v>
       </c>
       <c r="AE30" t="n">
         <v>0.046796</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.046796</v>
+        <v>0.47</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="AI30" t="n">
         <v>99.6454</v>
@@ -7565,9 +7553,7 @@
       </c>
       <c r="BC30" t="inlineStr"/>
       <c r="BD30" t="inlineStr"/>
-      <c r="BE30" t="n">
-        <v>1</v>
-      </c>
+      <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="n">
         <v>0.003057</v>
       </c>
@@ -7815,19 +7801,19 @@
         <v>-1.293962</v>
       </c>
       <c r="AD31" t="n">
-        <v>13.25</v>
+        <v>0.048116</v>
       </c>
       <c r="AE31" t="n">
         <v>0.048116</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.048116</v>
+        <v>0.67</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AI31" t="n">
         <v>99.51048</v>
@@ -7891,9 +7877,7 @@
       </c>
       <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="n">
         <v>0.00132</v>
       </c>
@@ -8141,19 +8125,19 @@
         <v>-17.142857</v>
       </c>
       <c r="AD32" t="n">
-        <v>13.25</v>
+        <v>0.049037</v>
       </c>
       <c r="AE32" t="n">
         <v>0.049037</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.049037</v>
+        <v>-0.68</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AI32" t="n">
         <v>101.43172</v>
@@ -8217,9 +8201,7 @@
       </c>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
+      <c r="BE32" t="inlineStr"/>
       <c r="BF32" t="n">
         <v>0.0009210000000000001</v>
       </c>
@@ -8471,19 +8453,19 @@
         <v>9.330629</v>
       </c>
       <c r="AD33" t="n">
-        <v>13.75</v>
+        <v>0.05056</v>
       </c>
       <c r="AE33" t="n">
         <v>0.05056</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.05056</v>
+        <v>-0.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="AI33" t="n">
         <v>101.10583</v>
@@ -8547,9 +8529,7 @@
       </c>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="BE33" t="inlineStr"/>
       <c r="BF33" t="n">
         <v>0.001523</v>
       </c>
@@ -8797,19 +8777,19 @@
         <v>0.556586</v>
       </c>
       <c r="AD34" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE34" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.050788</v>
+        <v>-0.29</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.29</v>
+        <v>-0.95</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="AI34" t="n">
         <v>101.16034</v>
@@ -8878,7 +8858,7 @@
         <v>8.248760000000001</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>7.191214</v>
       </c>
       <c r="BF34" t="n">
         <v>0.000228</v>
@@ -9131,19 +9111,19 @@
         <v>2.066421</v>
       </c>
       <c r="AD35" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE35" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.050788</v>
+        <v>0.59</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="AI35" t="n">
         <v>101.44171</v>
@@ -9212,7 +9192,7 @@
         <v>6.517038</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>6.460076</v>
       </c>
       <c r="BF35" t="n">
         <v>0</v>
@@ -9461,19 +9441,19 @@
         <v>-4.266088</v>
       </c>
       <c r="AD36" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE36" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.050788</v>
+        <v>0.41</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AI36" t="n">
         <v>100.7146</v>
@@ -9542,7 +9522,7 @@
         <v>5.899363</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>5.974439</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -9783,19 +9763,19 @@
         <v>2.492447</v>
       </c>
       <c r="AD37" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE37" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.050788</v>
+        <v>0.62</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI37" t="n">
         <v>100.58818</v>
@@ -9864,7 +9844,7 @@
         <v>5.458422</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>5.932356</v>
       </c>
       <c r="BF37" t="n">
         <v>-0</v>
@@ -10109,19 +10089,19 @@
         <v>0.18423</v>
       </c>
       <c r="AD38" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE38" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.050788</v>
+        <v>0.53</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AI38" t="n">
         <v>100.10988</v>
@@ -10190,7 +10170,7 @@
         <v>3.79089</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>5.711379</v>
       </c>
       <c r="BF38" t="n">
         <v>0</v>
@@ -10443,19 +10423,19 @@
         <v>-7.392424</v>
       </c>
       <c r="AD39" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE39" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.050788</v>
+        <v>0.84</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.84</v>
+        <v>-0.06</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="AI39" t="n">
         <v>103.07987</v>
@@ -10524,7 +10504,7 @@
         <v>1.864495</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>5.47065</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -10777,19 +10757,19 @@
         <v>4.924543</v>
       </c>
       <c r="AD40" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE40" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.050788</v>
+        <v>0.71</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="AI40" t="n">
         <v>103.08494</v>
@@ -10858,7 +10838,7 @@
         <v>0.172427</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>4.361088</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -11111,19 +11091,19 @@
         <v>-3.709311</v>
       </c>
       <c r="AD41" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE41" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.050788</v>
+        <v>0.61</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="AI41" t="n">
         <v>103.93573</v>
@@ -11192,7 +11172,7 @@
         <v>-2.158772</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>3.834324</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -11433,19 +11413,19 @@
         <v>-6.603774</v>
       </c>
       <c r="AD42" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE42" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.050788</v>
+        <v>0.23</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.23</v>
+        <v>-1.84</v>
       </c>
       <c r="AH42" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="AI42" t="n">
         <v>102.42973</v>
@@ -11514,7 +11494,7 @@
         <v>-4.45588</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>3.741292</v>
       </c>
       <c r="BF42" t="n">
         <v>-0</v>
@@ -11763,19 +11743,19 @@
         <v>-6.649832</v>
       </c>
       <c r="AD43" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE43" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.050788</v>
+        <v>-0.08</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="AH43" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="AI43" t="n">
         <v>102.39935</v>
@@ -11844,7 +11824,7 @@
         <v>-6.84947</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2.998957</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -12089,19 +12069,19 @@
         <v>-9.107303999999999</v>
       </c>
       <c r="AD44" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE44" t="n">
         <v>0.050788</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.050788</v>
+        <v>0.12</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.12</v>
+        <v>-0.72</v>
       </c>
       <c r="AH44" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="AI44" t="n">
         <v>102.90686</v>
@@ -12170,7 +12150,7 @@
         <v>-7.713954</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>3.527423</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -12415,19 +12395,19 @@
         <v>-8.531746</v>
       </c>
       <c r="AD45" t="n">
-        <v>13.25</v>
+        <v>0.049189</v>
       </c>
       <c r="AE45" t="n">
         <v>0.049189</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.049189</v>
+        <v>0.23</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AI45" t="n">
         <v>102.50239</v>
@@ -12496,7 +12476,7 @@
         <v>-7.193509</v>
       </c>
       <c r="BE45" t="n">
-        <v>-0.5</v>
+        <v>4.057054</v>
       </c>
       <c r="BF45" t="n">
         <v>-0.001599</v>
@@ -12745,19 +12725,19 @@
         <v>3.416486</v>
       </c>
       <c r="AD46" t="n">
-        <v>12.75</v>
+        <v>0.048422</v>
       </c>
       <c r="AE46" t="n">
         <v>0.048422</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.048422</v>
+        <v>0.26</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="AI46" t="n">
         <v>102.5153</v>
@@ -12826,7 +12806,7 @@
         <v>-5.956714</v>
       </c>
       <c r="BE46" t="n">
-        <v>-0.5</v>
+        <v>4.505936</v>
       </c>
       <c r="BF46" t="n">
         <v>-0.000768</v>
@@ -13071,19 +13051,19 @@
         <v>0.419507</v>
       </c>
       <c r="AD47" t="n">
-        <v>12.75</v>
+        <v>0.047279</v>
       </c>
       <c r="AE47" t="n">
         <v>0.047279</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.047279</v>
+        <v>0.24</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI47" t="n">
         <v>102.83959</v>
@@ -13152,7 +13132,7 @@
         <v>-4.560737</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>4.141877</v>
       </c>
       <c r="BF47" t="n">
         <v>-0.001143</v>
@@ -13397,19 +13377,19 @@
         <v>-3.550914</v>
       </c>
       <c r="AD48" t="n">
-        <v>12.25</v>
+        <v>0.045601</v>
       </c>
       <c r="AE48" t="n">
         <v>0.045601</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.045601</v>
+        <v>0.28</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="AI48" t="n">
         <v>103.59456</v>
@@ -13478,7 +13458,7 @@
         <v>-3.457004</v>
       </c>
       <c r="BE48" t="n">
-        <v>-0.5</v>
+        <v>3.851383</v>
       </c>
       <c r="BF48" t="n">
         <v>-0.001678</v>
@@ -13723,19 +13703,19 @@
         <v>2.05739</v>
       </c>
       <c r="AD49" t="n">
-        <v>11.75</v>
+        <v>0.044537</v>
       </c>
       <c r="AE49" t="n">
         <v>0.044537</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.044537</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="AI49" t="n">
         <v>104.88818</v>
@@ -13804,7 +13784,7 @@
         <v>-3.178284</v>
       </c>
       <c r="BE49" t="n">
-        <v>-0.5</v>
+        <v>3.706988</v>
       </c>
       <c r="BF49" t="n">
         <v>-0.001064</v>
@@ -14053,19 +14033,19 @@
         <v>-4.880637</v>
       </c>
       <c r="AD50" t="n">
-        <v>11.75</v>
+        <v>0.043739</v>
       </c>
       <c r="AE50" t="n">
         <v>0.043739</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.043739</v>
+        <v>0.42</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AI50" t="n">
         <v>104.473</v>
@@ -14134,7 +14114,7 @@
         <v>-3.31355</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>3.820543</v>
       </c>
       <c r="BF50" t="n">
         <v>-0.000798</v>
@@ -14379,19 +14359,19 @@
         <v>-7.250418</v>
       </c>
       <c r="AD51" t="n">
-        <v>11.25</v>
+        <v>0.041957</v>
       </c>
       <c r="AE51" t="n">
         <v>0.041957</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.041957</v>
+        <v>0.83</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="AH51" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI51" t="n">
         <v>104.65885</v>
@@ -14460,7 +14440,7 @@
         <v>-3.758575</v>
       </c>
       <c r="BE51" t="n">
-        <v>-0.5</v>
+        <v>3.861754</v>
       </c>
       <c r="BF51" t="n">
         <v>-0.001782</v>
@@ -14701,19 +14681,19 @@
         <v>6.313891</v>
       </c>
       <c r="AD52" t="n">
-        <v>10.75</v>
+        <v>0.04142</v>
       </c>
       <c r="AE52" t="n">
         <v>0.04142</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.04142</v>
+        <v>0.16</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="AI52" t="n">
         <v>104.6738</v>
@@ -14782,7 +14762,7 @@
         <v>-4.25878</v>
       </c>
       <c r="BE52" t="n">
-        <v>-0.5</v>
+        <v>3.397348</v>
       </c>
       <c r="BF52" t="n">
         <v>-0.000537</v>
@@ -15031,19 +15011,19 @@
         <v>-0.565611</v>
       </c>
       <c r="AD53" t="n">
-        <v>10.75</v>
+        <v>0.040168</v>
       </c>
       <c r="AE53" t="n">
         <v>0.040168</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.040168</v>
+        <v>0.38</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="AI53" t="n">
         <v>104.62771</v>
@@ -15112,7 +15092,7 @@
         <v>-3.040871</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>3.232784</v>
       </c>
       <c r="BF53" t="n">
         <v>-0.001252</v>
@@ -15357,19 +15337,19 @@
         <v>1.535836</v>
       </c>
       <c r="AD54" t="n">
-        <v>10.5</v>
+        <v>0.039484</v>
       </c>
       <c r="AE54" t="n">
         <v>0.039484</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.039484</v>
+        <v>0.46</v>
       </c>
       <c r="AG54" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.46</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0.89</v>
       </c>
       <c r="AI54" t="n">
         <v>105.60427</v>
@@ -15438,7 +15418,7 @@
         <v>-0.344269</v>
       </c>
       <c r="BE54" t="n">
-        <v>-0.25</v>
+        <v>3.335647</v>
       </c>
       <c r="BF54" t="n">
         <v>-0.000684</v>
@@ -15687,19 +15667,19 @@
         <v>-10.980392</v>
       </c>
       <c r="AD55" t="n">
-        <v>10.5</v>
+        <v>0.03927</v>
       </c>
       <c r="AE55" t="n">
         <v>0.03927</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.03927</v>
+        <v>0.21</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AI55" t="n">
         <v>106.5891</v>
@@ -15768,7 +15748,7 @@
         <v>2.440035</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>3.697684</v>
       </c>
       <c r="BF55" t="n">
         <v>-0.000214</v>
@@ -16017,19 +15997,19 @@
         <v>-3.650094</v>
       </c>
       <c r="AD56" t="n">
-        <v>10.5</v>
+        <v>0.03927</v>
       </c>
       <c r="AE56" t="n">
         <v>0.03927</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.03927</v>
+        <v>0.38</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="AI56" t="n">
         <v>107.06237</v>
@@ -16098,7 +16078,7 @@
         <v>3.812368</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>4.060953</v>
       </c>
       <c r="BF56" t="n">
         <v>0</v>
@@ -16347,19 +16327,19 @@
         <v>-1.241019</v>
       </c>
       <c r="AD57" t="n">
-        <v>10.5</v>
+        <v>0.03927</v>
       </c>
       <c r="AE57" t="n">
         <v>0.03927</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.03927</v>
+        <v>-0.02</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="AI57" t="n">
         <v>107.19174</v>
@@ -16428,7 +16408,7 @@
         <v>4.259387</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>3.707852</v>
       </c>
       <c r="BF57" t="n">
         <v>0</v>
@@ -16677,19 +16657,19 @@
         <v>12.367725</v>
       </c>
       <c r="AD58" t="n">
-        <v>10.75</v>
+        <v>0.039612</v>
       </c>
       <c r="AE58" t="n">
         <v>0.039612</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.039612</v>
+        <v>0.44</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="AI58" t="n">
         <v>108.04382</v>
@@ -16758,7 +16738,7 @@
         <v>4.519075</v>
       </c>
       <c r="BE58" t="n">
-        <v>0.25</v>
+        <v>4.091149</v>
       </c>
       <c r="BF58" t="n">
         <v>0.000342</v>
@@ -17007,19 +16987,19 @@
         <v>-3.296057</v>
       </c>
       <c r="AD59" t="n">
-        <v>10.75</v>
+        <v>0.040168</v>
       </c>
       <c r="AE59" t="n">
         <v>0.040168</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.040168</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="AI59" t="n">
         <v>108.2446</v>
@@ -17088,7 +17068,7 @@
         <v>5.579866</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>4.600584</v>
       </c>
       <c r="BF59" t="n">
         <v>0.000556</v>
@@ -17329,19 +17309,19 @@
         <v>2.982349</v>
       </c>
       <c r="AD60" t="n">
-        <v>11.25</v>
+        <v>0.04158</v>
       </c>
       <c r="AE60" t="n">
         <v>0.04158</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.04158</v>
+        <v>0.39</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="AI60" t="n">
         <v>108.00109</v>
@@ -17410,7 +17390,7 @@
         <v>6.325086</v>
       </c>
       <c r="BE60" t="n">
-        <v>0.5</v>
+        <v>4.840925</v>
       </c>
       <c r="BF60" t="n">
         <v>0.001412</v>
@@ -17659,19 +17639,19 @@
         <v>8.392435000000001</v>
       </c>
       <c r="AD61" t="n">
-        <v>12.25</v>
+        <v>0.044158</v>
       </c>
       <c r="AE61" t="n">
         <v>0.044158</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.044158</v>
+        <v>0.52</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AI61" t="n">
         <v>107.37012</v>
@@ -17740,7 +17720,7 @@
         <v>6.536174</v>
       </c>
       <c r="BE61" t="n">
-        <v>1</v>
+        <v>4.767938</v>
       </c>
       <c r="BF61" t="n">
         <v>0.002578</v>
@@ -17989,19 +17969,19 @@
         <v>5.125409</v>
       </c>
       <c r="AD62" t="n">
-        <v>13.25</v>
+        <v>0.045833</v>
       </c>
       <c r="AE62" t="n">
         <v>0.045833</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.045833</v>
+        <v>0.16</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>108.09524</v>
@@ -18070,7 +18050,7 @@
         <v>6.749097</v>
       </c>
       <c r="BE62" t="n">
-        <v>1</v>
+        <v>4.174145</v>
       </c>
       <c r="BF62" t="n">
         <v>0.001675</v>
@@ -18323,19 +18303,19 @@
         <v>-5.912863</v>
       </c>
       <c r="AD63" t="n">
-        <v>13.25</v>
+        <v>0.049037</v>
       </c>
       <c r="AE63" t="n">
         <v>0.049037</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.049037</v>
+        <v>1.31</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AI63" t="n">
         <v>108.62006</v>
@@ -18404,7 +18384,7 @@
         <v>8.444549</v>
       </c>
       <c r="BE63" t="n">
-        <v>0</v>
+        <v>4.866504</v>
       </c>
       <c r="BF63" t="n">
         <v>0.003204</v>
@@ -18653,19 +18633,19 @@
         <v>0.826902</v>
       </c>
       <c r="AD64" t="n">
-        <v>14.25</v>
+        <v>0.050508</v>
       </c>
       <c r="AE64" t="n">
         <v>0.050508</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.050508</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="AH64" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="AI64" t="n">
         <v>110.03287</v>
@@ -18734,7 +18714,7 @@
         <v>8.586193</v>
       </c>
       <c r="BE64" t="n">
-        <v>1</v>
+        <v>5.201441</v>
       </c>
       <c r="BF64" t="n">
         <v>0.001471</v>
@@ -18979,19 +18959,19 @@
         <v>2.186987</v>
       </c>
       <c r="AD65" t="n">
-        <v>14.25</v>
+        <v>0.052531</v>
       </c>
       <c r="AE65" t="n">
         <v>0.052531</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.052531</v>
+        <v>0.43</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="AI65" t="n">
         <v>109.52766</v>
@@ -19060,7 +19040,7 @@
         <v>8.510418</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>5.316736</v>
       </c>
       <c r="BF65" t="n">
         <v>0.002023</v>
@@ -19313,19 +19293,19 @@
         <v>-4.975923</v>
       </c>
       <c r="AD66" t="n">
-        <v>14.75</v>
+        <v>0.053936</v>
       </c>
       <c r="AE66" t="n">
         <v>0.053936</v>
       </c>
       <c r="AF66" t="n">
-        <v>0.053936</v>
+        <v>0.26</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="AH66" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="AI66" t="n">
         <v>108.8862</v>
@@ -19394,7 +19374,7 @@
         <v>7.026183</v>
       </c>
       <c r="BE66" t="n">
-        <v>0.5</v>
+        <v>5.201418</v>
       </c>
       <c r="BF66" t="n">
         <v>0.001405</v>
@@ -19643,19 +19623,19 @@
         <v>-5.292793</v>
       </c>
       <c r="AD67" t="n">
-        <v>15</v>
+        <v>0.054569</v>
       </c>
       <c r="AE67" t="n">
         <v>0.054569</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.054569</v>
+        <v>0.24</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="AH67" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="AI67" t="n">
         <v>108.80376</v>
@@ -19724,7 +19704,7 @@
         <v>4.393261</v>
       </c>
       <c r="BE67" t="n">
-        <v>0.25</v>
+        <v>5.18043</v>
       </c>
       <c r="BF67" t="n">
         <v>0.000633</v>
@@ -19973,19 +19953,19 @@
         <v>-6.302021</v>
       </c>
       <c r="AD68" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE68" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF68" t="n">
-        <v>0.055131</v>
+        <v>0.26</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.26</v>
+        <v>-0.77</v>
       </c>
       <c r="AH68" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="AI68" t="n">
         <v>108.49869</v>
@@ -20054,7 +20034,7 @@
         <v>2.961368</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>5.127976</v>
       </c>
       <c r="BF68" t="n">
         <v>0.000562</v>
@@ -20307,19 +20287,19 @@
         <v>1.015228</v>
       </c>
       <c r="AD69" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE69" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF69" t="n">
-        <v>0.055131</v>
+        <v>-0.11</v>
       </c>
       <c r="AG69" t="n">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="AI69" t="n">
         <v>108.82893</v>
@@ -20388,7 +20368,7 @@
         <v>3.033233</v>
       </c>
       <c r="BE69" t="n">
-        <v>0</v>
+        <v>5.054283</v>
       </c>
       <c r="BF69" t="n">
         <v>0</v>
@@ -20637,19 +20617,19 @@
         <v>4.396985</v>
       </c>
       <c r="AD70" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE70" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.055131</v>
+        <v>0.48</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="AI70" t="n">
         <v>108.73548</v>
@@ -20718,7 +20698,7 @@
         <v>2.828436</v>
       </c>
       <c r="BE70" t="n">
-        <v>0</v>
+        <v>5.096104</v>
       </c>
       <c r="BF70" t="n">
         <v>0</v>
@@ -20967,19 +20947,19 @@
         <v>3.850782</v>
       </c>
       <c r="AD71" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE71" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF71" t="n">
-        <v>0.055131</v>
+        <v>0.09</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.09</v>
+        <v>-0.36</v>
       </c>
       <c r="AH71" t="n">
-        <v>-0.36</v>
+        <v>0.03</v>
       </c>
       <c r="AI71" t="n">
         <v>108.75326</v>
@@ -21048,7 +21028,7 @@
         <v>0.924206</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>4.490243</v>
       </c>
       <c r="BF71" t="n">
         <v>0</v>
@@ -21297,19 +21277,19 @@
         <v>0.926999</v>
       </c>
       <c r="AD72" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE72" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF72" t="n">
-        <v>0.055131</v>
+        <v>0.18</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="AI72" t="n">
         <v>109.25005</v>
@@ -21378,7 +21358,7 @@
         <v>-0.101973</v>
       </c>
       <c r="BE72" t="n">
-        <v>0</v>
+        <v>4.177803</v>
       </c>
       <c r="BF72" t="n">
         <v>-0</v>
@@ -21631,19 +21611,19 @@
         <v>1.0907</v>
       </c>
       <c r="AD73" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE73" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="AH73" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AI73" t="n">
         <v>109.4528</v>
@@ -21712,7 +21692,7 @@
         <v>-1.042167</v>
       </c>
       <c r="BE73" t="n">
-        <v>0</v>
+        <v>3.897866</v>
       </c>
       <c r="BF73" t="n">
         <v>0</v>
@@ -21957,19 +21937,19 @@
         <v>-2.725724</v>
       </c>
       <c r="AD74" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE74" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AI74" t="n">
         <v>110.04992</v>
@@ -22038,7 +22018,7 @@
         <v>-0.903999</v>
       </c>
       <c r="BE74" t="n">
-        <v>0</v>
+        <v>4.303068</v>
       </c>
       <c r="BF74" t="n">
         <v>0</v>
@@ -22059,34 +22039,34 @@
         <v>0.58</v>
       </c>
       <c r="BL74" t="n">
-        <v>24576605744</v>
+        <v>24573982812</v>
       </c>
       <c r="BM74" t="n">
-        <v>20831691725</v>
+        <v>20804455231</v>
       </c>
       <c r="BN74" t="n">
-        <v>3744914019</v>
+        <v>3769527581</v>
       </c>
       <c r="BO74" t="n">
-        <v>45408297469</v>
+        <v>45378438043</v>
       </c>
       <c r="BP74" t="n">
-        <v>59812186143</v>
+        <v>59760718624</v>
       </c>
       <c r="BQ74" t="n">
-        <v>14315306356</v>
+        <v>14315300646</v>
       </c>
       <c r="BR74" t="n">
-        <v>946935529</v>
+        <v>946779078</v>
       </c>
       <c r="BS74" t="n">
-        <v>19491349</v>
+        <v>19474260</v>
       </c>
       <c r="BT74" t="n">
-        <v>21798118603</v>
+        <v>21770708569</v>
       </c>
       <c r="BU74" t="n">
-        <v>619967622</v>
+        <v>621313185</v>
       </c>
       <c r="BV74" t="n">
         <v>1693480220</v>
@@ -22098,7 +22078,7 @@
         <v>61236</v>
       </c>
       <c r="BY74" t="n">
-        <v>1013528628</v>
+        <v>1013537659</v>
       </c>
       <c r="BZ74" t="n">
         <v>141224032</v>
@@ -22142,10 +22122,10 @@
         <v>6000000</v>
       </c>
       <c r="CO74" t="n">
-        <v>925674649</v>
+        <v>913562892</v>
       </c>
       <c r="CP74" t="n">
-        <v>4245185990</v>
+        <v>4193768101</v>
       </c>
       <c r="CQ74" t="n">
         <v>19110389</v>
@@ -22154,7 +22134,7 @@
         <v>116981840</v>
       </c>
       <c r="CS74" t="n">
-        <v>1843157505</v>
+        <v>1843476386</v>
       </c>
       <c r="CT74" t="n">
         <v>26379004618</v>
@@ -22287,19 +22267,19 @@
         <v>2.451839</v>
       </c>
       <c r="AD75" t="n">
-        <v>15</v>
+        <v>0.055131</v>
       </c>
       <c r="AE75" t="n">
         <v>0.055131</v>
       </c>
       <c r="AF75" t="n">
-        <v>0.055131</v>
+        <v>0.7</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="AH75" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI75" t="n">
         <v>110.7366</v>
@@ -22368,7 +22348,7 @@
         <v>-2.659212</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>3.357475</v>
       </c>
       <c r="BF75" t="n">
         <v>0</v>
@@ -22389,34 +22369,34 @@
         <v>0.18</v>
       </c>
       <c r="BL75" t="n">
-        <v>26276065434</v>
+        <v>26270542130</v>
       </c>
       <c r="BM75" t="n">
-        <v>22215553623</v>
+        <v>22218059385</v>
       </c>
       <c r="BN75" t="n">
-        <v>4060511811</v>
+        <v>4052482745</v>
       </c>
       <c r="BO75" t="n">
-        <v>48491619057</v>
+        <v>48488601515</v>
       </c>
       <c r="BP75" t="n">
-        <v>61246580653</v>
+        <v>61246448586</v>
       </c>
       <c r="BQ75" t="n">
-        <v>13059952654</v>
+        <v>13059878341</v>
       </c>
       <c r="BR75" t="n">
-        <v>887917741</v>
+        <v>887917882</v>
       </c>
       <c r="BS75" t="n">
-        <v>21747059</v>
+        <v>21747055</v>
       </c>
       <c r="BT75" t="n">
-        <v>23125218423</v>
+        <v>23127724322</v>
       </c>
       <c r="BU75" t="n">
-        <v>713726654</v>
+        <v>717030066</v>
       </c>
       <c r="BV75" t="n">
         <v>1982573452</v>
@@ -22488,7 +22468,7 @@
         <v>34072660</v>
       </c>
       <c r="CS75" t="n">
-        <v>1840522680</v>
+        <v>1833120931</v>
       </c>
       <c r="CT75" t="n">
         <v>26187389970</v>
@@ -22520,7 +22500,7 @@
       <c r="DC75" t="inlineStr"/>
       <c r="DD75" t="inlineStr"/>
       <c r="DE75" t="n">
-        <v>2897179100</v>
+        <v>2897179101</v>
       </c>
       <c r="DF75" t="n">
         <v>7101012525</v>
@@ -22621,19 +22601,19 @@
         <v>4.330484</v>
       </c>
       <c r="AD76" t="n">
-        <v>14.75</v>
+        <v>0.054777</v>
       </c>
       <c r="AE76" t="n">
         <v>0.054777</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.054777</v>
+        <v>0.88</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="AI76" t="n">
         <v>110.58808</v>
@@ -22702,7 +22682,7 @@
         <v>-1.819225</v>
       </c>
       <c r="BE76" t="n">
-        <v>-0.25</v>
+        <v>3.768807</v>
       </c>
       <c r="BF76" t="n">
         <v>-0.000354</v>
@@ -22723,34 +22703,34 @@
         <v>0.21</v>
       </c>
       <c r="BL76" t="n">
-        <v>31767869262</v>
+        <v>31766018083</v>
       </c>
       <c r="BM76" t="n">
-        <v>25308911941</v>
+        <v>25309170318</v>
       </c>
       <c r="BN76" t="n">
-        <v>6458957321</v>
+        <v>6456847765</v>
       </c>
       <c r="BO76" t="n">
-        <v>57076781203</v>
+        <v>57075188401</v>
       </c>
       <c r="BP76" t="n">
-        <v>69086532981</v>
+        <v>69086215319</v>
       </c>
       <c r="BQ76" t="n">
-        <v>15883329662</v>
+        <v>15883566500</v>
       </c>
       <c r="BR76" t="n">
-        <v>1095660149</v>
+        <v>1095622190</v>
       </c>
       <c r="BS76" t="n">
-        <v>30697751</v>
+        <v>30697718</v>
       </c>
       <c r="BT76" t="n">
-        <v>26435269841</v>
+        <v>26435490226</v>
       </c>
       <c r="BU76" t="n">
-        <v>543861591</v>
+        <v>545703069</v>
       </c>
       <c r="BV76" t="n">
         <v>1551914338</v>
@@ -22818,7 +22798,7 @@
         <v>103043600</v>
       </c>
       <c r="CS76" t="n">
-        <v>1779291584</v>
+        <v>1774813115</v>
       </c>
       <c r="CT76" t="n">
         <v>25768212538</v>
@@ -22951,19 +22931,19 @@
         <v>1.529219</v>
       </c>
       <c r="AD77" t="n">
-        <v>14.5</v>
+        <v>0.054223</v>
       </c>
       <c r="AE77" t="n">
         <v>0.054223</v>
       </c>
       <c r="AF77" t="n">
-        <v>0.054223</v>
+        <v>0.67</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.67</v>
+        <v>2.73</v>
       </c>
       <c r="AH77" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI77" t="n">
         <v>110.90009</v>
@@ -23032,7 +23012,7 @@
         <v>0.619623</v>
       </c>
       <c r="BE77" t="n">
-        <v>-0.25</v>
+        <v>4.109608</v>
       </c>
       <c r="BF77" t="n">
         <v>-0.000554</v>
@@ -23053,34 +23033,34 @@
         <v>0.52</v>
       </c>
       <c r="BL77" t="n">
-        <v>34303112660</v>
+        <v>34286658184</v>
       </c>
       <c r="BM77" t="n">
-        <v>23647082379</v>
+        <v>23650669724</v>
       </c>
       <c r="BN77" t="n">
-        <v>10656030281</v>
+        <v>10635988460</v>
       </c>
       <c r="BO77" t="n">
-        <v>57950195039</v>
+        <v>57937327908</v>
       </c>
       <c r="BP77" t="n">
-        <v>75020929456</v>
+        <v>75020841917</v>
       </c>
       <c r="BQ77" t="n">
-        <v>14068303977</v>
+        <v>14068462213</v>
       </c>
       <c r="BR77" t="n">
-        <v>1093353315</v>
+        <v>1093376528</v>
       </c>
       <c r="BS77" t="n">
-        <v>26781461</v>
+        <v>26781417</v>
       </c>
       <c r="BT77" t="n">
-        <v>24767217155</v>
+        <v>24770827669</v>
       </c>
       <c r="BU77" t="n">
-        <v>344673367</v>
+        <v>346153809</v>
       </c>
       <c r="BV77" t="n">
         <v>958119849</v>
@@ -23092,7 +23072,7 @@
         <v>81647</v>
       </c>
       <c r="BY77" t="n">
-        <v>1072315176</v>
+        <v>1072316499</v>
       </c>
       <c r="BZ77" t="n">
         <v>171392428</v>
@@ -23148,7 +23128,7 @@
         <v>64056000</v>
       </c>
       <c r="CS77" t="n">
-        <v>2137280898</v>
+        <v>2115096466</v>
       </c>
       <c r="CT77" t="n">
         <v>31609434000</v>
@@ -23172,7 +23152,7 @@
         <v>867908929</v>
       </c>
       <c r="DA77" t="n">
-        <v>632395834</v>
+        <v>632395835</v>
       </c>
       <c r="DB77" t="n">
         <v>1822814124</v>
@@ -23180,7 +23160,7 @@
       <c r="DC77" t="inlineStr"/>
       <c r="DD77" t="inlineStr"/>
       <c r="DE77" t="n">
-        <v>6962355250</v>
+        <v>6962355252</v>
       </c>
       <c r="DF77" t="n">
         <v>16750088436</v>
@@ -23281,19 +23261,19 @@
         <v>-3.87305</v>
       </c>
       <c r="AD78" t="n">
-        <v>14.5</v>
+        <v>0.0534</v>
       </c>
       <c r="AE78" t="n">
         <v>0.0534</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.0534</v>
+        <v>0.58</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="AI78" t="n">
         <v>111.13846</v>
@@ -23362,7 +23342,7 @@
         <v>1.964454</v>
       </c>
       <c r="BE78" t="n">
-        <v>0</v>
+        <v>4.420848</v>
       </c>
       <c r="BF78" t="n">
         <v>-0.0008229999999999999</v>
@@ -23383,34 +23363,34 @@
         <v>-0.39</v>
       </c>
       <c r="BL78" t="n">
-        <v>31557335963</v>
+        <v>31529852245</v>
       </c>
       <c r="BM78" t="n">
-        <v>24118232383</v>
+        <v>24120363018</v>
       </c>
       <c r="BN78" t="n">
-        <v>7439103580</v>
+        <v>7409489227</v>
       </c>
       <c r="BO78" t="n">
-        <v>55675568346</v>
+        <v>55650215263</v>
       </c>
       <c r="BP78" t="n">
-        <v>63575354725</v>
+        <v>63563467072</v>
       </c>
       <c r="BQ78" t="n">
-        <v>14126830781</v>
+        <v>14124507396</v>
       </c>
       <c r="BR78" t="n">
-        <v>1222605122</v>
+        <v>1222549479</v>
       </c>
       <c r="BS78" t="n">
-        <v>30748299</v>
+        <v>30748501</v>
       </c>
       <c r="BT78" t="n">
-        <v>25371585804</v>
+        <v>25373660998</v>
       </c>
       <c r="BU78" t="n">
-        <v>617450435</v>
+        <v>620395097</v>
       </c>
       <c r="BV78" t="n">
         <v>1806544416</v>
@@ -23422,10 +23402,10 @@
         <v>82398</v>
       </c>
       <c r="BY78" t="n">
-        <v>912935086</v>
+        <v>912871064</v>
       </c>
       <c r="BZ78" t="n">
-        <v>155169290</v>
+        <v>155153890</v>
       </c>
       <c r="CA78" t="n">
         <v>305848</v>
@@ -23482,7 +23462,7 @@
         <v>40053800</v>
       </c>
       <c r="CS78" t="n">
-        <v>1683117561</v>
+        <v>1657447109</v>
       </c>
       <c r="CT78" t="n">
         <v>25568797966</v>
@@ -23506,18 +23486,18 @@
         <v>430988678</v>
       </c>
       <c r="DA78" t="n">
-        <v>735872995</v>
+        <v>731859065</v>
       </c>
       <c r="DB78" t="n">
-        <v>2058375168</v>
+        <v>2046900168</v>
       </c>
       <c r="DC78" t="inlineStr"/>
       <c r="DD78" t="inlineStr"/>
       <c r="DE78" t="n">
-        <v>6290576208</v>
+        <v>6289797046</v>
       </c>
       <c r="DF78" t="n">
-        <v>14825071266</v>
+        <v>14825071267</v>
       </c>
       <c r="DG78" t="n">
         <v>33901960</v>
@@ -23615,19 +23595,19 @@
         <v>-7.61052</v>
       </c>
       <c r="AD79" t="n">
-        <v>14.25</v>
+        <v>0.053028</v>
       </c>
       <c r="AE79" t="n">
         <v>0.053028</v>
       </c>
       <c r="AF79" t="n">
-        <v>0.053028</v>
+        <v>0.16</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="AH79" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="AI79" t="n">
         <v>110.15775</v>
@@ -23696,7 +23676,7 @@
         <v>3.177699</v>
       </c>
       <c r="BE79" t="n">
-        <v>-0.25</v>
+        <v>4.327084</v>
       </c>
       <c r="BF79" t="n">
         <v>-0.000372</v>
@@ -23717,34 +23697,34 @@
         <v>-0.34</v>
       </c>
       <c r="BL79" t="n">
-        <v>35492956607</v>
+        <v>35499628278</v>
       </c>
       <c r="BM79" t="n">
-        <v>26493857835</v>
+        <v>26495200506</v>
       </c>
       <c r="BN79" t="n">
-        <v>8999098772</v>
+        <v>9004427772</v>
       </c>
       <c r="BO79" t="n">
-        <v>61986814442</v>
+        <v>61994828784</v>
       </c>
       <c r="BP79" t="n">
-        <v>82860091366</v>
+        <v>82859912220</v>
       </c>
       <c r="BQ79" t="n">
-        <v>14024278044</v>
+        <v>14023235066</v>
       </c>
       <c r="BR79" t="n">
-        <v>1322948542</v>
+        <v>1322972352</v>
       </c>
       <c r="BS79" t="n">
-        <v>23910838</v>
+        <v>23834159</v>
       </c>
       <c r="BT79" t="n">
-        <v>27840717215</v>
+        <v>27842007017</v>
       </c>
       <c r="BU79" t="n">
-        <v>938953227</v>
+        <v>950478133</v>
       </c>
       <c r="BV79" t="n">
         <v>2770311509</v>
@@ -23756,18 +23736,18 @@
         <v>184747</v>
       </c>
       <c r="BY79" t="n">
-        <v>934557701</v>
+        <v>934580723</v>
       </c>
       <c r="BZ79" t="n">
-        <v>167705205</v>
+        <v>167708805</v>
       </c>
       <c r="CA79" t="inlineStr"/>
       <c r="CB79" t="inlineStr"/>
       <c r="CC79" t="n">
-        <v>1602350318</v>
+        <v>1604689886</v>
       </c>
       <c r="CD79" t="n">
-        <v>248837040</v>
+        <v>248809399</v>
       </c>
       <c r="CE79" t="n">
         <v>8385042</v>
@@ -23812,7 +23792,7 @@
         <v>89731429</v>
       </c>
       <c r="CS79" t="n">
-        <v>2569324747</v>
+        <v>2561140623</v>
       </c>
       <c r="CT79" t="n">
         <v>39666979151</v>
@@ -23844,7 +23824,7 @@
       <c r="DC79" t="inlineStr"/>
       <c r="DD79" t="inlineStr"/>
       <c r="DE79" t="n">
-        <v>6266776914</v>
+        <v>6265912842</v>
       </c>
       <c r="DF79" t="n">
         <v>14505017737</v>
@@ -23945,19 +23925,19 @@
         <v>6.783767</v>
       </c>
       <c r="AD80" t="n">
-        <v>14.25</v>
+        <v>0.052531</v>
       </c>
       <c r="AE80" t="n">
         <v>0.052531</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.052531</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="AH80" t="n">
-        <v>-1.16</v>
+        <v>-0.01</v>
       </c>
       <c r="AI80" t="n">
         <v>109.91611</v>
@@ -24026,7 +24006,7 @@
         <v>2.772183</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>4.098046</v>
       </c>
       <c r="BF80" t="n">
         <v>-0.000497</v>
@@ -24047,34 +24027,34 @@
         <v>-0.57</v>
       </c>
       <c r="BL80" t="n">
-        <v>33723397019</v>
+        <v>33577433983</v>
       </c>
       <c r="BM80" t="n">
-        <v>27158319765</v>
+        <v>27159421177</v>
       </c>
       <c r="BN80" t="n">
-        <v>6565077254</v>
+        <v>6418012806</v>
       </c>
       <c r="BO80" t="n">
-        <v>60881716784</v>
+        <v>60736855160</v>
       </c>
       <c r="BP80" t="n">
-        <v>77871209960</v>
+        <v>77797817457</v>
       </c>
       <c r="BQ80" t="n">
-        <v>16655220670</v>
+        <v>16655525507</v>
       </c>
       <c r="BR80" t="n">
-        <v>1471041432</v>
+        <v>1471017620</v>
       </c>
       <c r="BS80" t="n">
-        <v>26306646</v>
+        <v>26306641</v>
       </c>
       <c r="BT80" t="n">
-        <v>28655667843</v>
+        <v>28656745438</v>
       </c>
       <c r="BU80" t="n">
-        <v>844057652</v>
+        <v>846757948</v>
       </c>
       <c r="BV80" t="n">
         <v>2529930057</v>
@@ -24086,7 +24066,7 @@
         <v>122615</v>
       </c>
       <c r="BY80" t="n">
-        <v>813952881</v>
+        <v>814022100</v>
       </c>
       <c r="BZ80" t="n">
         <v>152934524</v>
@@ -24098,7 +24078,7 @@
         <v>1560</v>
       </c>
       <c r="CC80" t="n">
-        <v>1201408088</v>
+        <v>1202269384</v>
       </c>
       <c r="CD80" t="n">
         <v>193061335</v>
@@ -24122,10 +24102,10 @@
         <v>904209</v>
       </c>
       <c r="CK80" t="n">
-        <v>589861744</v>
+        <v>547522432</v>
       </c>
       <c r="CL80" t="n">
-        <v>959864111</v>
+        <v>927703584</v>
       </c>
       <c r="CM80" t="n">
         <v>60</v>
@@ -24140,16 +24120,16 @@
         <v>1941216352</v>
       </c>
       <c r="CQ80" t="n">
-        <v>28986392</v>
+        <v>28970014</v>
       </c>
       <c r="CR80" t="n">
-        <v>175804570</v>
+        <v>175710260</v>
       </c>
       <c r="CS80" t="n">
-        <v>2131758139</v>
+        <v>2132007782</v>
       </c>
       <c r="CT80" t="n">
-        <v>35002833875</v>
+        <v>34974584205</v>
       </c>
       <c r="CU80" t="n">
         <v>1798</v>
@@ -24158,16 +24138,16 @@
         <v>1000</v>
       </c>
       <c r="CW80" t="n">
-        <v>4737463030</v>
+        <v>4629365093</v>
       </c>
       <c r="CX80" t="n">
-        <v>7674971451</v>
+        <v>7672032952</v>
       </c>
       <c r="CY80" t="n">
-        <v>736291615</v>
+        <v>737457317</v>
       </c>
       <c r="CZ80" t="n">
-        <v>1020215096</v>
+        <v>1020333259</v>
       </c>
       <c r="DA80" t="n">
         <v>647927068</v>
@@ -24178,16 +24158,16 @@
       <c r="DC80" t="inlineStr"/>
       <c r="DD80" t="inlineStr"/>
       <c r="DE80" t="n">
-        <v>5869552552</v>
+        <v>5870448703</v>
       </c>
       <c r="DF80" t="n">
         <v>13405907808</v>
       </c>
       <c r="DG80" t="n">
-        <v>24415856</v>
+        <v>23848605</v>
       </c>
       <c r="DH80" t="n">
-        <v>62866000</v>
+        <v>61696410</v>
       </c>
     </row>
     <row r="81">
@@ -24279,19 +24259,19 @@
         <v>16.846285</v>
       </c>
       <c r="AD81" t="n">
-        <v>14</v>
+        <v>0.051784</v>
       </c>
       <c r="AE81" t="n">
         <v>0.051784</v>
       </c>
       <c r="AF81" t="n">
-        <v>0.051784</v>
+        <v>-0.32</v>
       </c>
       <c r="AG81" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AH81" t="n">
         <v>-0.32</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>-0.22</v>
       </c>
       <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
@@ -24352,7 +24332,7 @@
         <v>2.178243</v>
       </c>
       <c r="BE81" t="n">
-        <v>-0.25</v>
+        <v>3.983297</v>
       </c>
       <c r="BF81" t="n">
         <v>-0.0007470000000000001</v>
@@ -24373,37 +24353,37 @@
         <v>0.2</v>
       </c>
       <c r="BL81" t="n">
-        <v>33157804370</v>
+        <v>32732183002</v>
       </c>
       <c r="BM81" t="n">
-        <v>25763862100</v>
+        <v>25823660146</v>
       </c>
       <c r="BN81" t="n">
-        <v>7393942270</v>
+        <v>6908522856</v>
       </c>
       <c r="BO81" t="n">
-        <v>58921666470</v>
+        <v>58555843148</v>
       </c>
       <c r="BP81" t="n">
-        <v>77119199389</v>
+        <v>76672534789</v>
       </c>
       <c r="BQ81" t="n">
-        <v>14073182023</v>
+        <v>14050480944</v>
       </c>
       <c r="BR81" t="n">
-        <v>1548184686</v>
+        <v>1546788681</v>
       </c>
       <c r="BS81" t="n">
-        <v>19241881</v>
+        <v>19260288</v>
       </c>
       <c r="BT81" t="n">
-        <v>27331288667</v>
+        <v>27389709115</v>
       </c>
       <c r="BU81" t="n">
-        <v>753147930</v>
+        <v>752297715</v>
       </c>
       <c r="BV81" t="n">
-        <v>2221291720</v>
+        <v>2220715368</v>
       </c>
       <c r="BW81" t="n">
         <v>170442</v>
@@ -24412,7 +24392,7 @@
         <v>143344</v>
       </c>
       <c r="BY81" t="n">
-        <v>1094109253</v>
+        <v>1094443369</v>
       </c>
       <c r="BZ81" t="n">
         <v>206264157</v>
@@ -24420,7 +24400,7 @@
       <c r="CA81" t="inlineStr"/>
       <c r="CB81" t="inlineStr"/>
       <c r="CC81" t="n">
-        <v>967242706</v>
+        <v>967264803</v>
       </c>
       <c r="CD81" t="n">
         <v>162300453</v>
@@ -24444,30 +24424,30 @@
         <v>1452782</v>
       </c>
       <c r="CK81" t="n">
-        <v>893582419</v>
+        <v>852206570</v>
       </c>
       <c r="CL81" t="n">
-        <v>1438094595</v>
+        <v>1383886863</v>
       </c>
       <c r="CM81" t="inlineStr"/>
       <c r="CN81" t="inlineStr"/>
       <c r="CO81" t="n">
-        <v>1002656682</v>
+        <v>989881482</v>
       </c>
       <c r="CP81" t="n">
-        <v>4653100189</v>
+        <v>4648770261</v>
       </c>
       <c r="CQ81" t="n">
-        <v>33273820</v>
+        <v>33267163</v>
       </c>
       <c r="CR81" t="n">
-        <v>199281400</v>
+        <v>199242360</v>
       </c>
       <c r="CS81" t="n">
-        <v>2051566400</v>
+        <v>2037904434</v>
       </c>
       <c r="CT81" t="n">
-        <v>34406447895</v>
+        <v>34351503645</v>
       </c>
       <c r="CU81" t="n">
         <v>6950029</v>
@@ -24476,22 +24456,22 @@
         <v>78331372</v>
       </c>
       <c r="CW81" t="n">
-        <v>4828191084</v>
+        <v>4588224684</v>
       </c>
       <c r="CX81" t="n">
-        <v>8379911835</v>
+        <v>8358755854</v>
       </c>
       <c r="CY81" t="n">
-        <v>547298813</v>
+        <v>561128509</v>
       </c>
       <c r="CZ81" t="n">
-        <v>797225701</v>
+        <v>798168982</v>
       </c>
       <c r="DA81" t="n">
-        <v>646488066</v>
+        <v>644929294</v>
       </c>
       <c r="DB81" t="n">
-        <v>1790486389</v>
+        <v>1785896563</v>
       </c>
       <c r="DC81" t="n">
         <v>360</v>
@@ -24500,10 +24480,10 @@
         <v>0</v>
       </c>
       <c r="DE81" t="n">
-        <v>4410039153</v>
+        <v>4414965758</v>
       </c>
       <c r="DF81" t="n">
-        <v>9808807495</v>
+        <v>9810807500</v>
       </c>
       <c r="DG81" t="n">
         <v>44621019</v>
@@ -24601,18 +24581,16 @@
         <v>-2.76699</v>
       </c>
       <c r="AD82" t="n">
-        <v>13.75</v>
+        <v>0.051245</v>
       </c>
       <c r="AE82" t="n">
         <v>0.051245</v>
       </c>
-      <c r="AF82" t="n">
-        <v>0.051245</v>
-      </c>
-      <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="n">
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="n">
         <v>1.57</v>
       </c>
+      <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="n">
@@ -24645,9 +24623,7 @@
       <c r="BD82" t="n">
         <v>3.348378</v>
       </c>
-      <c r="BE82" t="n">
-        <v>-0.25</v>
-      </c>
+      <c r="BE82" t="inlineStr"/>
       <c r="BF82" t="n">
         <v>-0.00054</v>
       </c>
@@ -24658,162 +24634,246 @@
       <c r="BI82" t="inlineStr"/>
       <c r="BJ82" t="inlineStr"/>
       <c r="BK82" t="inlineStr"/>
-      <c r="BL82" t="inlineStr"/>
-      <c r="BM82" t="inlineStr"/>
-      <c r="BN82" t="inlineStr"/>
-      <c r="BO82" t="inlineStr"/>
-      <c r="BP82" t="inlineStr"/>
-      <c r="BQ82" t="inlineStr"/>
-      <c r="BR82" t="inlineStr"/>
-      <c r="BS82" t="inlineStr"/>
-      <c r="BT82" t="inlineStr"/>
-      <c r="BU82" t="inlineStr"/>
-      <c r="BV82" t="inlineStr"/>
-      <c r="BW82" t="inlineStr"/>
-      <c r="BX82" t="inlineStr"/>
-      <c r="BY82" t="inlineStr"/>
-      <c r="BZ82" t="inlineStr"/>
+      <c r="BL82" t="n">
+        <v>34418070076</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>26677510096</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>7740559980</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>61095580172</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>76342513744</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>14665789542</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>1611232587</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>27463449</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>28316206132</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>809708916</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>2306235692</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>144681</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>122543</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>1292800592</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>235659946</v>
+      </c>
       <c r="CA82" t="inlineStr"/>
       <c r="CB82" t="inlineStr"/>
-      <c r="CC82" t="inlineStr"/>
-      <c r="CD82" t="inlineStr"/>
-      <c r="CE82" t="inlineStr"/>
-      <c r="CF82" t="inlineStr"/>
-      <c r="CG82" t="inlineStr"/>
-      <c r="CH82" t="inlineStr"/>
-      <c r="CI82" t="inlineStr"/>
-      <c r="CJ82" t="inlineStr"/>
-      <c r="CK82" t="inlineStr"/>
-      <c r="CL82" t="inlineStr"/>
+      <c r="CC82" t="n">
+        <v>950751177</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>156467198</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>10523613</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>988603</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>892280162</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>1801287673</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1255725</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1333748</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>649437972</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>942054629</v>
+      </c>
       <c r="CM82" t="inlineStr"/>
       <c r="CN82" t="inlineStr"/>
-      <c r="CO82" t="inlineStr"/>
-      <c r="CP82" t="inlineStr"/>
-      <c r="CQ82" t="inlineStr"/>
-      <c r="CR82" t="inlineStr"/>
-      <c r="CS82" t="inlineStr"/>
-      <c r="CT82" t="inlineStr"/>
-      <c r="CU82" t="inlineStr"/>
-      <c r="CV82" t="inlineStr"/>
-      <c r="CW82" t="inlineStr"/>
-      <c r="CX82" t="inlineStr"/>
-      <c r="CY82" t="inlineStr"/>
-      <c r="CZ82" t="inlineStr"/>
-      <c r="DA82" t="inlineStr"/>
-      <c r="DB82" t="inlineStr"/>
+      <c r="CO82" t="n">
+        <v>1228786726</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>5207728793</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>37058160</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>220704294</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>1771842975</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>31660490297</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>5139747</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>61011592</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>6498868606</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>11689652591</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>631617247</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>893774707</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>755950210</v>
+      </c>
+      <c r="DB82" t="n">
+        <v>1941525390</v>
+      </c>
       <c r="DC82" t="inlineStr"/>
       <c r="DD82" t="inlineStr"/>
-      <c r="DE82" t="inlineStr"/>
-      <c r="DF82" t="inlineStr"/>
-      <c r="DG82" t="inlineStr"/>
-      <c r="DH82" t="inlineStr"/>
+      <c r="DE82" t="n">
+        <v>3473089697</v>
+      </c>
+      <c r="DF82" t="n">
+        <v>7358383641</v>
+      </c>
+      <c r="DG82" t="n">
+        <v>51965570</v>
+      </c>
+      <c r="DH82" t="n">
+        <v>117130000</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>205427.203125</v>
+        <v>204957.3125</v>
       </c>
       <c r="C83" t="n">
-        <v>202.289993</v>
+        <v>201.839996</v>
       </c>
       <c r="D83" t="n">
-        <v>128.529999</v>
+        <v>130.240005</v>
       </c>
       <c r="E83" t="n">
-        <v>440.369995</v>
+        <v>439.339996</v>
       </c>
       <c r="F83" t="n">
-        <v>4.9748</v>
+        <v>4.9916</v>
       </c>
       <c r="G83" t="n">
-        <v>5.601</v>
+        <v>5.5874</v>
       </c>
       <c r="H83" t="n">
-        <v>7834.240234</v>
+        <v>7800.709961</v>
       </c>
       <c r="I83" t="n">
-        <v>27662.966797</v>
+        <v>27498.011719</v>
       </c>
       <c r="J83" t="n">
-        <v>51601.289062</v>
+        <v>51213.96875</v>
       </c>
       <c r="K83" t="n">
-        <v>4191.299805</v>
+        <v>4135.399902</v>
       </c>
       <c r="L83" t="n">
-        <v>89.220001</v>
+        <v>88.779999</v>
       </c>
       <c r="M83" t="n">
-        <v>99.75</v>
+        <v>100.699997</v>
       </c>
       <c r="N83" t="n">
-        <v>1295.75</v>
+        <v>1293.5</v>
       </c>
       <c r="O83" t="n">
-        <v>506.5</v>
+        <v>501.25</v>
       </c>
       <c r="P83" t="n">
-        <v>10.243213</v>
+        <v>9.991045</v>
       </c>
       <c r="Q83" t="n">
-        <v>9.892433</v>
+        <v>9.647976</v>
       </c>
       <c r="R83" t="n">
-        <v>14.830696</v>
+        <v>16.358443</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.5647</v>
+        <v>-1.794935</v>
       </c>
       <c r="T83" t="n">
-        <v>-4.38409</v>
+        <v>-4.061195</v>
       </c>
       <c r="U83" t="n">
-        <v>-5.007035</v>
+        <v>-5.237689</v>
       </c>
       <c r="V83" t="n">
-        <v>2.387757</v>
+        <v>1.949541</v>
       </c>
       <c r="W83" t="n">
-        <v>2.985386</v>
+        <v>2.371281</v>
       </c>
       <c r="X83" t="n">
-        <v>1.365728</v>
+        <v>0.6048750000000001</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.109862</v>
+        <v>-1.225316</v>
       </c>
       <c r="Z83" t="n">
-        <v>-1.327137</v>
+        <v>-1.813757</v>
       </c>
       <c r="AA83" t="n">
-        <v>-3.651114</v>
+        <v>-2.733509</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.212684</v>
+        <v>0.03867</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.148278</v>
+        <v>0.09984999999999999</v>
       </c>
       <c r="AD83" t="n">
-        <v>13.75</v>
+        <v>0.050788</v>
       </c>
       <c r="AE83" t="n">
         <v>0.050788</v>
       </c>
-      <c r="AF83" t="n">
-        <v>0.050788</v>
-      </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="n">
-        <v>4.9698</v>
+        <v>4.9935</v>
       </c>
       <c r="AL83" t="n">
-        <v>4.9853</v>
+        <v>4.9929</v>
       </c>
       <c r="AM83" t="inlineStr"/>
       <c r="AN83" t="inlineStr"/>
@@ -24826,10 +24886,10 @@
       <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr"/>
       <c r="AW83" t="n">
-        <v>-4.074582</v>
+        <v>-3.617132</v>
       </c>
       <c r="AX83" t="n">
-        <v>-3.764261</v>
+        <v>-3.617551</v>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr"/>
@@ -24837,9 +24897,7 @@
       <c r="BB83" t="inlineStr"/>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
-      <c r="BE83" t="n">
-        <v>0</v>
-      </c>
+      <c r="BE83" t="inlineStr"/>
       <c r="BF83" t="n">
         <v>-0.000457</v>
       </c>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -578,77 +578,77 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>bcb_sgs_cdi</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
@@ -688,32 +688,32 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>bcb_sgs_var_pct_reservas_internacionais</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
+          <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
@@ -5256,52 +5256,52 @@
         <v>7.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.02443</v>
+        <v>0.024483</v>
       </c>
       <c r="AF23" t="n">
+        <v>0.024483</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AH23" t="n">
         <v>0.64</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AI23" t="n">
         <v>1.16</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
         <v>97.48671</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>96.53041</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AL23" t="n">
         <v>5.643</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AM23" t="n">
         <v>5.6424</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AN23" t="n">
         <v>4511956</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>1910940</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>2601017</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>2.33</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AS23" t="n">
         <v>2.99</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>22.89</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>367927</v>
       </c>
       <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="inlineStr"/>
@@ -5551,49 +5551,49 @@
         <v>0.029256</v>
       </c>
       <c r="AF24" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0.95</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>0.84</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
         <v>99.05526</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AK24" t="n">
         <v>97.85277000000001</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AL24" t="n">
         <v>5.6199</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
         <v>5.6193</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AN24" t="n">
         <v>4597507</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>1933111</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>2664395</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AQ24" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AS24" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
         <v>23.91</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>367772</v>
       </c>
       <c r="AU24" t="n">
         <v>1.608989</v>
@@ -5616,17 +5616,17 @@
       <c r="BA24" t="n">
         <v>2.436662</v>
       </c>
-      <c r="BB24" t="n">
-        <v>-0.042128</v>
-      </c>
+      <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="inlineStr"/>
       <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr"/>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>0.004773</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.004826</v>
+        <v>0.004773</v>
       </c>
       <c r="BH24" t="n">
         <v>0.03</v>
@@ -5879,49 +5879,49 @@
         <v>0.033316</v>
       </c>
       <c r="AF25" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="AG25" t="n">
         <v>0.73</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>0.87</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>0.73</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
         <v>99.37716</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AK25" t="n">
         <v>99.32258</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AL25" t="n">
         <v>5.5805</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AM25" t="n">
         <v>5.5799</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AN25" t="n">
         <v>4682852</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>1974391</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>2708461</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AS25" t="n">
         <v>3.05</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
         <v>24.21</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>362204</v>
       </c>
       <c r="AU25" t="n">
         <v>0.32497</v>
@@ -5944,14 +5944,14 @@
       <c r="BA25" t="n">
         <v>1.653884</v>
       </c>
-      <c r="BB25" t="n">
-        <v>-1.513981</v>
-      </c>
+      <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr"/>
       <c r="BD25" t="inlineStr"/>
-      <c r="BE25" t="inlineStr"/>
+      <c r="BE25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BF25" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="BG25" t="n">
         <v>0.00406</v>
@@ -6203,49 +6203,49 @@
         <v>0.034749</v>
       </c>
       <c r="AF26" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.54</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AH26" t="n">
         <v>1.82</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
         <v>97.4213</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AK26" t="n">
         <v>91.67776000000001</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
         <v>5.3574</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AM26" t="n">
         <v>5.3568</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AN26" t="n">
         <v>4682131</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>1947035</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>2735096</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>2.51</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AS26" t="n">
         <v>3.26</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>25.23</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>358398</v>
       </c>
       <c r="AU26" t="n">
         <v>-1.968118</v>
@@ -6268,14 +6268,14 @@
       <c r="BA26" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="BB26" t="n">
-        <v>-1.050789</v>
-      </c>
+      <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="inlineStr"/>
       <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="inlineStr"/>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="BG26" t="n">
         <v>0.001433</v>
@@ -6519,49 +6519,49 @@
         <v>0.039598</v>
       </c>
       <c r="AF27" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.01</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AH27" t="n">
         <v>1.83</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>1</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>98.4804</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AK27" t="n">
         <v>95.63728999999999</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AL27" t="n">
         <v>5.1394</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AM27" t="n">
         <v>5.1388</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AN27" t="n">
         <v>4727818</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AO27" t="n">
         <v>1971524</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>2756295</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>2.57</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AS27" t="n">
         <v>3.38</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>25.63</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>357740</v>
       </c>
       <c r="AU27" t="n">
         <v>1.087134</v>
@@ -6584,14 +6584,14 @@
       <c r="BA27" t="n">
         <v>0.775073</v>
       </c>
-      <c r="BB27" t="n">
-        <v>-0.183595</v>
-      </c>
+      <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="inlineStr"/>
+      <c r="BE27" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BF27" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="BG27" t="n">
         <v>0.004849</v>
@@ -6839,49 +6839,49 @@
         <v>0.041954</v>
       </c>
       <c r="AF28" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="n">
         <v>1.74</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
         <v>99.54801999999999</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AK28" t="n">
         <v>104.53237</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AL28" t="n">
         <v>4.7378</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>4.7372</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AN28" t="n">
         <v>4794583</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AO28" t="n">
         <v>1994119</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>2800464</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AQ28" t="n">
         <v>2.66</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AR28" t="n">
         <v>1.55</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AS28" t="n">
         <v>3.45</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AT28" t="n">
         <v>26.54</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>353169</v>
       </c>
       <c r="AU28" t="n">
         <v>1.084094</v>
@@ -6904,14 +6904,14 @@
       <c r="BA28" t="n">
         <v>1.602477</v>
       </c>
-      <c r="BB28" t="n">
-        <v>-1.277744</v>
-      </c>
+      <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="inlineStr"/>
+      <c r="BE28" t="n">
+        <v>1</v>
+      </c>
       <c r="BF28" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="BG28" t="n">
         <v>0.002356</v>
@@ -7155,49 +7155,49 @@
         <v>0.043739</v>
       </c>
       <c r="AF29" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.06</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AH29" t="n">
         <v>1.41</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
         <v>1.04</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>99.44118</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AK29" t="n">
         <v>100.22938</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AL29" t="n">
         <v>4.9191</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AM29" t="n">
         <v>4.9185</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AN29" t="n">
         <v>4833732</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AO29" t="n">
         <v>2003312</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>2830420</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AQ29" t="n">
         <v>2.72</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AR29" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AS29" t="n">
         <v>3.54</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AT29" t="n">
         <v>27.46</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>345097</v>
       </c>
       <c r="AU29" t="n">
         <v>-0.107325</v>
@@ -7220,14 +7220,14 @@
       <c r="BA29" t="n">
         <v>1.06968</v>
       </c>
-      <c r="BB29" t="n">
-        <v>-2.285591</v>
-      </c>
+      <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
       <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="inlineStr"/>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="BG29" t="n">
         <v>0.001785</v>
@@ -7483,49 +7483,49 @@
         <v>0.046796</v>
       </c>
       <c r="AF30" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.47</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>0.45</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
         <v>99.6454</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AK30" t="n">
         <v>99.74383</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AL30" t="n">
         <v>4.7289</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AM30" t="n">
         <v>4.7283</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AN30" t="n">
         <v>4889397</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AO30" t="n">
         <v>2013726</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>2875671</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>2.79</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AS30" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>27.42</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>346415</v>
       </c>
       <c r="AU30" t="n">
         <v>0.205368</v>
@@ -7548,14 +7548,14 @@
       <c r="BA30" t="n">
         <v>1.598738</v>
       </c>
-      <c r="BB30" t="n">
-        <v>0.381922</v>
-      </c>
+      <c r="BB30" t="inlineStr"/>
       <c r="BC30" t="inlineStr"/>
       <c r="BD30" t="inlineStr"/>
-      <c r="BE30" t="inlineStr"/>
+      <c r="BE30" t="n">
+        <v>1</v>
+      </c>
       <c r="BF30" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="BG30" t="n">
         <v>0.003057</v>
@@ -7807,49 +7807,49 @@
         <v>0.048116</v>
       </c>
       <c r="AF31" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="AG31" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AI31" t="n">
         <v>0.62</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
         <v>99.51048</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AK31" t="n">
         <v>99.31653</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>5.238</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AM31" t="n">
         <v>5.2374</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AN31" t="n">
         <v>4965603</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AO31" t="n">
         <v>2052569</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>2913035</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>2.73</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AS31" t="n">
         <v>3.57</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>27.88</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>341958</v>
       </c>
       <c r="AU31" t="n">
         <v>-0.1354</v>
@@ -7872,14 +7872,14 @@
       <c r="BA31" t="n">
         <v>1.299314</v>
       </c>
-      <c r="BB31" t="n">
-        <v>-1.286607</v>
-      </c>
+      <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="inlineStr"/>
+      <c r="BE31" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BF31" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="BG31" t="n">
         <v>0.00132</v>
@@ -8131,49 +8131,49 @@
         <v>0.049037</v>
       </c>
       <c r="AF32" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG32" t="n">
         <v>-0.68</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AH32" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AI32" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
         <v>101.43172</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AK32" t="n">
         <v>103.95991</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AL32" t="n">
         <v>5.1884</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AM32" t="n">
         <v>5.1878</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AN32" t="n">
         <v>4999244</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
         <v>2047038</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>2952207</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>2.84</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AS32" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>29.24</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>346403</v>
       </c>
       <c r="AU32" t="n">
         <v>1.930691</v>
@@ -8196,14 +8196,14 @@
       <c r="BA32" t="n">
         <v>1.344714</v>
       </c>
-      <c r="BB32" t="n">
-        <v>1.299867</v>
-      </c>
+      <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="inlineStr"/>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BG32" t="n">
         <v>0.0009210000000000001</v>
@@ -8459,49 +8459,49 @@
         <v>0.05056</v>
       </c>
       <c r="AF33" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="AG33" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AI33" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
         <v>101.10583</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AK33" t="n">
         <v>104.51156</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AL33" t="n">
         <v>5.179</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AM33" t="n">
         <v>5.1784</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AN33" t="n">
         <v>5072711</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AO33" t="n">
         <v>2064183</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>3008528</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>2.9</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>1.62</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AS33" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>28.6</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>339664</v>
       </c>
       <c r="AU33" t="n">
         <v>-0.32129</v>
@@ -8524,14 +8524,14 @@
       <c r="BA33" t="n">
         <v>1.907759</v>
       </c>
-      <c r="BB33" t="n">
-        <v>-1.945422</v>
-      </c>
+      <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
+      <c r="BE33" t="n">
+        <v>0.5</v>
+      </c>
       <c r="BF33" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="BG33" t="n">
         <v>0.001523</v>
@@ -8783,49 +8783,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF34" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG34" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AH34" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AJ34" t="n">
         <v>101.16034</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AK34" t="n">
         <v>101.1889</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AL34" t="n">
         <v>5.4066</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AM34" t="n">
         <v>5.406</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
         <v>5164775</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>2109806</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>3054969</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>2.92</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>1.65</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>28.57</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>327580</v>
       </c>
       <c r="AU34" t="n">
         <v>0.053914</v>
@@ -8849,19 +8849,19 @@
         <v>1.543645</v>
       </c>
       <c r="BB34" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="BC34" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="BD34" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="BG34" t="n">
         <v>0.000228</v>
@@ -9117,49 +9117,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF35" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.59</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>-0.97</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>0.47</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AJ35" t="n">
         <v>101.44171</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AK35" t="n">
         <v>100.08177</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AL35" t="n">
         <v>5.257</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AM35" t="n">
         <v>5.2564</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
         <v>5215990</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>2105856</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>3110134</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>3.04</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>1.77</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AS35" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>29.68</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>325546</v>
       </c>
       <c r="AU35" t="n">
         <v>0.278143</v>
@@ -9183,16 +9183,16 @@
         <v>1.805747</v>
       </c>
       <c r="BB35" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="BC35" t="n">
-        <v>6.470016</v>
+        <v>6.517038</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.517038</v>
+        <v>6.460076</v>
       </c>
       <c r="BE35" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
         <v>0</v>
@@ -9447,49 +9447,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF36" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG36" t="n">
         <v>0.41</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AH36" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AI36" t="n">
         <v>0.38</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AJ36" t="n">
         <v>100.7146</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AK36" t="n">
         <v>99.15031999999999</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AL36" t="n">
         <v>5.2941</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AM36" t="n">
         <v>5.2935</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AN36" t="n">
         <v>5285657</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AO36" t="n">
         <v>2130312</v>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>3155345</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>1.81</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AS36" t="n">
         <v>3.92</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AT36" t="n">
         <v>30.52</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>331505</v>
       </c>
       <c r="AU36" t="n">
         <v>-0.716776</v>
@@ -9513,16 +9513,16 @@
         <v>1.453667</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="BC36" t="n">
-        <v>5.900488</v>
+        <v>5.899363</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.899363</v>
+        <v>5.974439</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -9769,49 +9769,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF37" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG37" t="n">
         <v>0.62</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AH37" t="n">
         <v>0.45</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AI37" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AJ37" t="n">
         <v>100.58818</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AK37" t="n">
         <v>99.97037</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AL37" t="n">
         <v>5.2177</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AM37" t="n">
         <v>5.2171</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AN37" t="n">
         <v>5366069</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AO37" t="n">
         <v>2178236</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>3187833</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>1.8</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AS37" t="n">
         <v>3.94</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AT37" t="n">
         <v>29.64</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>324703</v>
       </c>
       <c r="AU37" t="n">
         <v>-0.125523</v>
@@ -9835,19 +9835,19 @@
         <v>1.029618</v>
       </c>
       <c r="BB37" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="BC37" t="n">
-        <v>5.784842</v>
+        <v>5.458422</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.458422</v>
+        <v>5.932356</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.932356</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG37" t="n">
         <v>-0</v>
@@ -10095,49 +10095,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF38" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.53</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AH38" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AI38" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AJ38" t="n">
         <v>100.10988</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AK38" t="n">
         <v>95.09953</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AL38" t="n">
         <v>5.0993</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AM38" t="n">
         <v>5.0987</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AN38" t="n">
         <v>5373231</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AO38" t="n">
         <v>2151399</v>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>3221831</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AQ38" t="n">
         <v>3.24</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AR38" t="n">
         <v>1.94</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AS38" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AT38" t="n">
         <v>30.54</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>331122</v>
       </c>
       <c r="AU38" t="n">
         <v>-0.475503</v>
@@ -10161,16 +10161,16 @@
         <v>1.066493</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="BC38" t="n">
-        <v>5.77432</v>
+        <v>3.79089</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.79089</v>
+        <v>5.711379</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
         <v>0</v>
@@ -10429,49 +10429,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF39" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.84</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AH39" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AI39" t="n">
         <v>0.77</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AJ39" t="n">
         <v>103.07987</v>
       </c>
-      <c r="AJ39" t="n">
+      <c r="AK39" t="n">
         <v>98.64798</v>
       </c>
-      <c r="AK39" t="n">
+      <c r="AL39" t="n">
         <v>5.2078</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AM39" t="n">
         <v>5.2072</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AN39" t="n">
         <v>5370950</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>2136105</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>3234845</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>3.36</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>2.17</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AS39" t="n">
         <v>4.16</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>30.48</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>328098</v>
       </c>
       <c r="AU39" t="n">
         <v>2.96673</v>
@@ -10495,16 +10495,16 @@
         <v>0.403932</v>
       </c>
       <c r="BB39" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.596302</v>
+        <v>1.864495</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.864495</v>
+        <v>5.47065</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -10763,49 +10763,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF40" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.71</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AI40" t="n">
         <v>0.64</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AJ40" t="n">
         <v>103.08494</v>
       </c>
-      <c r="AJ40" t="n">
+      <c r="AK40" t="n">
         <v>110.61922</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AL40" t="n">
         <v>5.0804</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AM40" t="n">
         <v>5.0798</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AN40" t="n">
         <v>5424811</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AO40" t="n">
         <v>2154900</v>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>3269910</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AS40" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>30.99</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>341158</v>
       </c>
       <c r="AU40" t="n">
         <v>0.004919</v>
@@ -10829,16 +10829,16 @@
         <v>1.083978</v>
       </c>
       <c r="BB40" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.650694</v>
+        <v>0.172427</v>
       </c>
       <c r="BD40" t="n">
-        <v>0.172427</v>
+        <v>4.361088</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -11097,49 +11097,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF41" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG41" t="n">
         <v>0.61</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>0.53</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AJ41" t="n">
         <v>103.93573</v>
       </c>
-      <c r="AJ41" t="n">
+      <c r="AK41" t="n">
         <v>104.04095</v>
       </c>
-      <c r="AK41" t="n">
+      <c r="AL41" t="n">
         <v>5.0007</v>
       </c>
-      <c r="AL41" t="n">
+      <c r="AM41" t="n">
         <v>5.0001</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AN41" t="n">
         <v>5426307</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AO41" t="n">
         <v>2145000</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AP41" t="n">
         <v>3281308</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AQ41" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AR41" t="n">
         <v>2.45</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AS41" t="n">
         <v>4.26</v>
       </c>
-      <c r="AS41" t="n">
+      <c r="AT41" t="n">
         <v>31.62</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>345725</v>
       </c>
       <c r="AU41" t="n">
         <v>0.825329</v>
@@ -11163,16 +11163,16 @@
         <v>0.348572</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.184706</v>
+        <v>-2.158772</v>
       </c>
       <c r="BD41" t="n">
-        <v>-2.158772</v>
+        <v>3.834324</v>
       </c>
       <c r="BE41" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -11419,49 +11419,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF42" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG42" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AH42" t="n">
         <v>-1.84</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AI42" t="n">
         <v>0.36</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AJ42" t="n">
         <v>102.42973</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AK42" t="n">
         <v>102.71375</v>
       </c>
-      <c r="AK42" t="n">
+      <c r="AL42" t="n">
         <v>5.0959</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AM42" t="n">
         <v>5.0953</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AN42" t="n">
         <v>5453708</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>2145530</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
         <v>3308178</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AQ42" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AR42" t="n">
         <v>2.58</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AS42" t="n">
         <v>4.35</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AT42" t="n">
         <v>31.63</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>343489</v>
       </c>
       <c r="AU42" t="n">
         <v>-1.448972</v>
@@ -11485,19 +11485,19 @@
         <v>0.818881</v>
       </c>
       <c r="BB42" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.935832</v>
+        <v>-4.45588</v>
       </c>
       <c r="BD42" t="n">
-        <v>-4.45588</v>
+        <v>3.741292</v>
       </c>
       <c r="BE42" t="n">
-        <v>3.741292</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG42" t="n">
         <v>-0</v>
@@ -11749,49 +11749,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF43" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG43" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AH43" t="n">
         <v>-1.93</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AI43" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AJ43" t="n">
         <v>102.39935</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AK43" t="n">
         <v>102.28352</v>
       </c>
-      <c r="AK43" t="n">
+      <c r="AL43" t="n">
         <v>4.8192</v>
       </c>
-      <c r="AL43" t="n">
+      <c r="AM43" t="n">
         <v>4.8186</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AN43" t="n">
         <v>5479459</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AO43" t="n">
         <v>2169613</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AP43" t="n">
         <v>3309846</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AQ43" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
         <v>2.63</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AS43" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AT43" t="n">
         <v>30.85</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>343620</v>
       </c>
       <c r="AU43" t="n">
         <v>-0.029659</v>
@@ -11815,16 +11815,16 @@
         <v>0.050421</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.038138</v>
+        <v>3.161501</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.161501</v>
+        <v>-6.84947</v>
       </c>
       <c r="BD43" t="n">
-        <v>-6.84947</v>
+        <v>2.998957</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -12075,49 +12075,49 @@
         <v>0.050788</v>
       </c>
       <c r="AF44" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG44" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AH44" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AI44" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AJ44" t="n">
         <v>102.90686</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AK44" t="n">
         <v>105.34474</v>
       </c>
-      <c r="AK44" t="n">
+      <c r="AL44" t="n">
         <v>4.7415</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AM44" t="n">
         <v>4.7409</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AN44" t="n">
         <v>5484871</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>2153541</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>3331330</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>3.63</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>2.73</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>4.22</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AT44" t="n">
         <v>30.43</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>345476</v>
       </c>
       <c r="AU44" t="n">
         <v>0.495618</v>
@@ -12141,16 +12141,16 @@
         <v>0.6490939999999999</v>
       </c>
       <c r="BB44" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="BC44" t="n">
-        <v>3.992444</v>
+        <v>-7.713954</v>
       </c>
       <c r="BD44" t="n">
-        <v>-7.713954</v>
+        <v>3.527423</v>
       </c>
       <c r="BE44" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -12401,49 +12401,49 @@
         <v>0.049189</v>
       </c>
       <c r="AF45" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="AG45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AH45" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AI45" t="n">
         <v>0.2</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AJ45" t="n">
         <v>102.50239</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AK45" t="n">
         <v>106.05687</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AL45" t="n">
         <v>4.9219</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AM45" t="n">
         <v>4.9213</v>
       </c>
-      <c r="AM45" t="n">
+      <c r="AN45" t="n">
         <v>5559063</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AO45" t="n">
         <v>2172658</v>
       </c>
-      <c r="AO45" t="n">
+      <c r="AP45" t="n">
         <v>3386405</v>
       </c>
-      <c r="AP45" t="n">
+      <c r="AQ45" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AR45" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AS45" t="n">
         <v>4.12</v>
       </c>
-      <c r="AS45" t="n">
+      <c r="AT45" t="n">
         <v>29.92</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>344177</v>
       </c>
       <c r="AU45" t="n">
         <v>-0.393045</v>
@@ -12467,19 +12467,19 @@
         <v>1.653244</v>
       </c>
       <c r="BB45" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="BC45" t="n">
-        <v>4.608216</v>
+        <v>-7.193509</v>
       </c>
       <c r="BD45" t="n">
-        <v>-7.193509</v>
+        <v>4.057054</v>
       </c>
       <c r="BE45" t="n">
-        <v>4.057054</v>
+        <v>-0.5</v>
       </c>
       <c r="BF45" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="BG45" t="n">
         <v>-0.001599</v>
@@ -12731,49 +12731,49 @@
         <v>0.048422</v>
       </c>
       <c r="AF46" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AH46" t="n">
         <v>0.37</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AI46" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AJ46" t="n">
         <v>102.5153</v>
       </c>
-      <c r="AJ46" t="n">
+      <c r="AK46" t="n">
         <v>101.75897</v>
       </c>
-      <c r="AK46" t="n">
+      <c r="AL46" t="n">
         <v>5.0076</v>
       </c>
-      <c r="AL46" t="n">
+      <c r="AM46" t="n">
         <v>5.007</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AN46" t="n">
         <v>5625945</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>2215175</v>
       </c>
-      <c r="AO46" t="n">
+      <c r="AP46" t="n">
         <v>3410769</v>
       </c>
-      <c r="AP46" t="n">
+      <c r="AQ46" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AR46" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AS46" t="n">
         <v>4</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AT46" t="n">
         <v>29.66</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>340324</v>
       </c>
       <c r="AU46" t="n">
         <v>0.012595</v>
@@ -12797,19 +12797,19 @@
         <v>0.719465</v>
       </c>
       <c r="BB46" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="BC46" t="n">
-        <v>5.185235</v>
+        <v>-5.956714</v>
       </c>
       <c r="BD46" t="n">
-        <v>-5.956714</v>
+        <v>4.505936</v>
       </c>
       <c r="BE46" t="n">
-        <v>4.505936</v>
+        <v>-0.5</v>
       </c>
       <c r="BF46" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="BG46" t="n">
         <v>-0.000768</v>
@@ -13057,49 +13057,49 @@
         <v>0.047279</v>
       </c>
       <c r="AF47" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="AG47" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AJ47" t="n">
         <v>102.83959</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AK47" t="n">
         <v>101.9338</v>
       </c>
-      <c r="AK47" t="n">
+      <c r="AL47" t="n">
         <v>5.0575</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AM47" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AM47" t="n">
+      <c r="AN47" t="n">
         <v>5653808</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AO47" t="n">
         <v>2204808</v>
       </c>
-      <c r="AO47" t="n">
+      <c r="AP47" t="n">
         <v>3449000</v>
       </c>
-      <c r="AP47" t="n">
+      <c r="AQ47" t="n">
         <v>3.56</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AR47" t="n">
         <v>2.92</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AS47" t="n">
         <v>3.97</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AT47" t="n">
         <v>29.24</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>340247</v>
       </c>
       <c r="AU47" t="n">
         <v>0.316333</v>
@@ -13123,19 +13123,19 @@
         <v>1.120891</v>
       </c>
       <c r="BB47" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="BC47" t="n">
-        <v>4.819246</v>
+        <v>-4.560737</v>
       </c>
       <c r="BD47" t="n">
-        <v>-4.560737</v>
+        <v>4.141877</v>
       </c>
       <c r="BE47" t="n">
-        <v>4.141877</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="BG47" t="n">
         <v>-0.001143</v>
@@ -13383,49 +13383,49 @@
         <v>0.045601</v>
       </c>
       <c r="AF48" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="AG48" t="n">
         <v>0.28</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AH48" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AI48" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AJ48" t="n">
         <v>103.59456</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AK48" t="n">
         <v>101.68042</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AL48" t="n">
         <v>4.9355</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AM48" t="n">
         <v>4.9349</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AN48" t="n">
         <v>5711103</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AO48" t="n">
         <v>2220766</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>3490337</v>
       </c>
-      <c r="AP48" t="n">
+      <c r="AQ48" t="n">
         <v>3.53</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AR48" t="n">
         <v>2.99</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AS48" t="n">
         <v>3.88</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AT48" t="n">
         <v>29.01</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>348406</v>
       </c>
       <c r="AU48" t="n">
         <v>0.734124</v>
@@ -13449,19 +13449,19 @@
         <v>1.198521</v>
       </c>
       <c r="BB48" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="BC48" t="n">
-        <v>4.683537</v>
+        <v>-3.457004</v>
       </c>
       <c r="BD48" t="n">
-        <v>-3.457004</v>
+        <v>3.851383</v>
       </c>
       <c r="BE48" t="n">
-        <v>3.851383</v>
+        <v>-0.5</v>
       </c>
       <c r="BF48" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="BG48" t="n">
         <v>-0.001678</v>
@@ -13709,49 +13709,49 @@
         <v>0.044537</v>
       </c>
       <c r="AF49" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="AG49" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AH49" t="n">
         <v>0.74</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AJ49" t="n">
         <v>104.88818</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AK49" t="n">
         <v>101.68469</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AL49" t="n">
         <v>4.8413</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AM49" t="n">
         <v>4.8407</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AN49" t="n">
         <v>5805157</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>2283485</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
         <v>3521672</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AQ49" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
         <v>2.59</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AS49" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AT49" t="n">
         <v>28.14</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>355034</v>
       </c>
       <c r="AU49" t="n">
         <v>1.248734</v>
@@ -13775,19 +13775,19 @@
         <v>0.897764</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.621114</v>
+        <v>-3.178284</v>
       </c>
       <c r="BD49" t="n">
-        <v>-3.178284</v>
+        <v>3.706988</v>
       </c>
       <c r="BE49" t="n">
-        <v>3.706988</v>
+        <v>-0.5</v>
       </c>
       <c r="BF49" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="BG49" t="n">
         <v>-0.001064</v>
@@ -14039,49 +14039,49 @@
         <v>0.043739</v>
       </c>
       <c r="AF50" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG50" t="n">
         <v>0.42</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AH50" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AI50" t="n">
         <v>0.57</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AJ50" t="n">
         <v>104.473</v>
       </c>
-      <c r="AJ50" t="n">
+      <c r="AK50" t="n">
         <v>99.29718</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AL50" t="n">
         <v>4.9535</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AM50" t="n">
         <v>4.9529</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AN50" t="n">
         <v>5794707</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AO50" t="n">
         <v>2234362</v>
       </c>
-      <c r="AO50" t="n">
+      <c r="AP50" t="n">
         <v>3560345</v>
       </c>
-      <c r="AP50" t="n">
+      <c r="AQ50" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AR50" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AT50" t="n">
         <v>28</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>355066</v>
       </c>
       <c r="AU50" t="n">
         <v>-0.395831</v>
@@ -14105,19 +14105,19 @@
         <v>1.098143</v>
       </c>
       <c r="BB50" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.506637</v>
+        <v>-3.31355</v>
       </c>
       <c r="BD50" t="n">
-        <v>-3.31355</v>
+        <v>3.820543</v>
       </c>
       <c r="BE50" t="n">
-        <v>3.820543</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="BG50" t="n">
         <v>-0.000798</v>
@@ -14365,49 +14365,49 @@
         <v>0.041957</v>
       </c>
       <c r="AF51" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="AG51" t="n">
         <v>0.83</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AH51" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AI51" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AJ51" t="n">
         <v>104.65885</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AK51" t="n">
         <v>102.15036</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AL51" t="n">
         <v>4.9833</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AM51" t="n">
         <v>4.9827</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AN51" t="n">
         <v>5815954</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>2235302</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>3580652</v>
       </c>
-      <c r="AP51" t="n">
+      <c r="AQ51" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AR51" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AS51" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS51" t="n">
+      <c r="AT51" t="n">
         <v>27.85</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>352705</v>
       </c>
       <c r="AU51" t="n">
         <v>0.177893</v>
@@ -14431,19 +14431,19 @@
         <v>0.570366</v>
       </c>
       <c r="BB51" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.496274</v>
+        <v>-3.758575</v>
       </c>
       <c r="BD51" t="n">
-        <v>-3.758575</v>
+        <v>3.861754</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.861754</v>
+        <v>-0.5</v>
       </c>
       <c r="BF51" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="BG51" t="n">
         <v>-0.001782</v>
@@ -14687,49 +14687,49 @@
         <v>0.04142</v>
       </c>
       <c r="AF52" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="AG52" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AH52" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AI52" t="n">
         <v>0.19</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AJ52" t="n">
         <v>104.6738</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AK52" t="n">
         <v>109.56901</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AL52" t="n">
         <v>4.9962</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AM52" t="n">
         <v>4.9956</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AN52" t="n">
         <v>5899742</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AO52" t="n">
         <v>2285775</v>
       </c>
-      <c r="AO52" t="n">
+      <c r="AP52" t="n">
         <v>3613967</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AR52" t="n">
         <v>2.71</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AS52" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="AT52" t="n">
         <v>28.14</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>355008</v>
       </c>
       <c r="AU52" t="n">
         <v>0.014285</v>
@@ -14753,19 +14753,19 @@
         <v>0.930417</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="BC52" t="n">
-        <v>3.925596</v>
+        <v>-4.25878</v>
       </c>
       <c r="BD52" t="n">
-        <v>-4.25878</v>
+        <v>3.397348</v>
       </c>
       <c r="BE52" t="n">
-        <v>3.397348</v>
+        <v>-0.5</v>
       </c>
       <c r="BF52" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="BG52" t="n">
         <v>-0.000537</v>
@@ -15017,49 +15017,49 @@
         <v>0.040168</v>
       </c>
       <c r="AF53" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG53" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AH53" t="n">
         <v>0.31</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AI53" t="n">
         <v>0.37</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
         <v>104.62771</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AK53" t="n">
         <v>109.2572</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AL53" t="n">
         <v>5.1718</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AM53" t="n">
         <v>5.1712</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AN53" t="n">
         <v>5915538</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AO53" t="n">
         <v>2268879</v>
       </c>
-      <c r="AO53" t="n">
+      <c r="AP53" t="n">
         <v>3646659</v>
       </c>
-      <c r="AP53" t="n">
+      <c r="AQ53" t="n">
         <v>3.37</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AR53" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AS53" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS53" t="n">
+      <c r="AT53" t="n">
         <v>27.86</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>351599</v>
       </c>
       <c r="AU53" t="n">
         <v>-0.044032</v>
@@ -15083,19 +15083,19 @@
         <v>0.904602</v>
       </c>
       <c r="BB53" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="BC53" t="n">
-        <v>3.688016</v>
+        <v>-3.040871</v>
       </c>
       <c r="BD53" t="n">
-        <v>-3.040871</v>
+        <v>3.232784</v>
       </c>
       <c r="BE53" t="n">
-        <v>3.232784</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="BG53" t="n">
         <v>-0.001252</v>
@@ -15343,49 +15343,49 @@
         <v>0.039484</v>
       </c>
       <c r="AF54" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="AG54" t="n">
         <v>0.46</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AH54" t="n">
         <v>0.89</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AI54" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AJ54" t="n">
         <v>105.60427</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AK54" t="n">
         <v>104.71213</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AL54" t="n">
         <v>5.2416</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AM54" t="n">
         <v>5.241</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AN54" t="n">
         <v>5953960</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AO54" t="n">
         <v>2278309</v>
       </c>
-      <c r="AO54" t="n">
+      <c r="AP54" t="n">
         <v>3675652</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AQ54" t="n">
         <v>3.43</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AR54" t="n">
         <v>2.8</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AS54" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AT54" t="n">
         <v>27.75</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>355560</v>
       </c>
       <c r="AU54" t="n">
         <v>0.9333669999999999</v>
@@ -15409,19 +15409,19 @@
         <v>0.795057</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="BC54" t="n">
-        <v>3.925952</v>
+        <v>-0.344269</v>
       </c>
       <c r="BD54" t="n">
-        <v>-0.344269</v>
+        <v>3.335647</v>
       </c>
       <c r="BE54" t="n">
-        <v>3.335647</v>
+        <v>-0.25</v>
       </c>
       <c r="BF54" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="BG54" t="n">
         <v>-0.000684</v>
@@ -15673,49 +15673,49 @@
         <v>0.03927</v>
       </c>
       <c r="AF55" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG55" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AH55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AI55" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
         <v>106.5891</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AK55" t="n">
         <v>105.86915</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AL55" t="n">
         <v>5.5589</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AM55" t="n">
         <v>5.5583</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AN55" t="n">
         <v>6041898</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AO55" t="n">
         <v>2336858</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AP55" t="n">
         <v>3705041</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AQ55" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AR55" t="n">
         <v>2.64</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AS55" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AT55" t="n">
         <v>27.81</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>357827</v>
       </c>
       <c r="AU55" t="n">
         <v>0.932566</v>
@@ -15739,19 +15739,19 @@
         <v>0.799559</v>
       </c>
       <c r="BB55" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.227578</v>
+        <v>2.440035</v>
       </c>
       <c r="BD55" t="n">
-        <v>2.440035</v>
+        <v>3.697684</v>
       </c>
       <c r="BE55" t="n">
-        <v>3.697684</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="BG55" t="n">
         <v>-0.000214</v>
@@ -16003,49 +16003,49 @@
         <v>0.03927</v>
       </c>
       <c r="AF56" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG56" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AH56" t="n">
         <v>0.61</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AI56" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AJ56" t="n">
         <v>107.06237</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AK56" t="n">
         <v>111.509</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AL56" t="n">
         <v>5.6621</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AM56" t="n">
         <v>5.6615</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AN56" t="n">
         <v>6069205</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AO56" t="n">
         <v>2323362</v>
       </c>
-      <c r="AO56" t="n">
+      <c r="AP56" t="n">
         <v>3745844</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AQ56" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AR56" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AS56" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AT56" t="n">
         <v>27.74</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>363282</v>
       </c>
       <c r="AU56" t="n">
         <v>0.444014</v>
@@ -16069,16 +16069,16 @@
         <v>1.101283</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="BC56" t="n">
-        <v>4.498245</v>
+        <v>3.812368</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.812368</v>
+        <v>4.060953</v>
       </c>
       <c r="BE56" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
         <v>0</v>
@@ -16333,49 +16333,49 @@
         <v>0.03927</v>
       </c>
       <c r="AF57" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG57" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AH57" t="n">
         <v>0.29</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AI57" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AJ57" t="n">
         <v>107.19174</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AK57" t="n">
         <v>110.06254</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AL57" t="n">
         <v>5.6562</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AM57" t="n">
         <v>5.6556</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AN57" t="n">
         <v>6135298</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AO57" t="n">
         <v>2344397</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AP57" t="n">
         <v>3790900</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AQ57" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AR57" t="n">
         <v>2.55</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AS57" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AT57" t="n">
         <v>27.59</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>369214</v>
       </c>
       <c r="AU57" t="n">
         <v>0.120836</v>
@@ -16399,16 +16399,16 @@
         <v>1.202826</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="BC57" t="n">
-        <v>4.237599</v>
+        <v>4.259387</v>
       </c>
       <c r="BD57" t="n">
-        <v>4.259387</v>
+        <v>3.707852</v>
       </c>
       <c r="BE57" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
         <v>0</v>
@@ -16663,49 +16663,49 @@
         <v>0.039612</v>
       </c>
       <c r="AF58" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="AG58" t="n">
         <v>0.44</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AH58" t="n">
         <v>0.62</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AI58" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AJ58" t="n">
         <v>108.04382</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AK58" t="n">
         <v>107.07852</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AL58" t="n">
         <v>5.4481</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AM58" t="n">
         <v>5.4475</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AN58" t="n">
         <v>6216528</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AO58" t="n">
         <v>2384828</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AP58" t="n">
         <v>3831700</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AQ58" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AR58" t="n">
         <v>2.56</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AS58" t="n">
         <v>3.83</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AT58" t="n">
         <v>27.49</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>372016</v>
       </c>
       <c r="AU58" t="n">
         <v>0.794912</v>
@@ -16729,19 +16729,19 @@
         <v>1.076262</v>
       </c>
       <c r="BB58" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="BC58" t="n">
-        <v>4.42474</v>
+        <v>4.519075</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.519075</v>
+        <v>4.091149</v>
       </c>
       <c r="BE58" t="n">
-        <v>4.091149</v>
+        <v>0.25</v>
       </c>
       <c r="BF58" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="BG58" t="n">
         <v>0.000342</v>
@@ -16993,49 +16993,49 @@
         <v>0.040168</v>
       </c>
       <c r="AF59" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG59" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AH59" t="n">
         <v>1.52</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AI59" t="n">
         <v>0.61</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AJ59" t="n">
         <v>108.2446</v>
       </c>
-      <c r="AJ59" t="n">
+      <c r="AK59" t="n">
         <v>109.18379</v>
       </c>
-      <c r="AK59" t="n">
+      <c r="AL59" t="n">
         <v>5.7779</v>
       </c>
-      <c r="AL59" t="n">
+      <c r="AM59" t="n">
         <v>5.7773</v>
       </c>
-      <c r="AM59" t="n">
+      <c r="AN59" t="n">
         <v>6275117</v>
       </c>
-      <c r="AN59" t="n">
+      <c r="AO59" t="n">
         <v>2397533</v>
       </c>
-      <c r="AO59" t="n">
+      <c r="AP59" t="n">
         <v>3877584</v>
       </c>
-      <c r="AP59" t="n">
+      <c r="AQ59" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AR59" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AS59" t="n">
         <v>3.79</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AT59" t="n">
         <v>27.94</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>366096</v>
       </c>
       <c r="AU59" t="n">
         <v>0.185832</v>
@@ -17059,19 +17059,19 @@
         <v>1.197484</v>
       </c>
       <c r="BB59" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="BC59" t="n">
-        <v>4.758099</v>
+        <v>5.579866</v>
       </c>
       <c r="BD59" t="n">
-        <v>5.579866</v>
+        <v>4.600584</v>
       </c>
       <c r="BE59" t="n">
-        <v>4.600584</v>
+        <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="BG59" t="n">
         <v>0.000556</v>
@@ -17315,49 +17315,49 @@
         <v>0.04158</v>
       </c>
       <c r="AF60" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="AG60" t="n">
         <v>0.39</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AH60" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AI60" t="n">
         <v>0.33</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AJ60" t="n">
         <v>108.00109</v>
       </c>
-      <c r="AJ60" t="n">
+      <c r="AK60" t="n">
         <v>105.49006</v>
       </c>
-      <c r="AK60" t="n">
+      <c r="AL60" t="n">
         <v>6.0535</v>
       </c>
-      <c r="AL60" t="n">
+      <c r="AM60" t="n">
         <v>6.0529</v>
       </c>
-      <c r="AM60" t="n">
+      <c r="AN60" t="n">
         <v>6365690</v>
       </c>
-      <c r="AN60" t="n">
+      <c r="AO60" t="n">
         <v>2436022</v>
       </c>
-      <c r="AO60" t="n">
+      <c r="AP60" t="n">
         <v>3929668</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AQ60" t="n">
         <v>3.27</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AR60" t="n">
         <v>2.5</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AS60" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS60" t="n">
+      <c r="AT60" t="n">
         <v>28.45</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>363003</v>
       </c>
       <c r="AU60" t="n">
         <v>-0.224963</v>
@@ -17381,19 +17381,19 @@
         <v>1.343208</v>
       </c>
       <c r="BB60" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="BC60" t="n">
-        <v>4.873011</v>
+        <v>6.325086</v>
       </c>
       <c r="BD60" t="n">
-        <v>6.325086</v>
+        <v>4.840925</v>
       </c>
       <c r="BE60" t="n">
-        <v>4.840925</v>
+        <v>0.5</v>
       </c>
       <c r="BF60" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="BG60" t="n">
         <v>0.001412</v>
@@ -17645,49 +17645,49 @@
         <v>0.044158</v>
       </c>
       <c r="AF61" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="AG61" t="n">
         <v>0.52</v>
       </c>
-      <c r="AG61" t="n">
+      <c r="AH61" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AH61" t="n">
+      <c r="AI61" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI61" t="n">
+      <c r="AJ61" t="n">
         <v>107.37012</v>
       </c>
-      <c r="AJ61" t="n">
+      <c r="AK61" t="n">
         <v>104.15552</v>
       </c>
-      <c r="AK61" t="n">
+      <c r="AL61" t="n">
         <v>6.1923</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AM61" t="n">
         <v>6.1917</v>
       </c>
-      <c r="AM61" t="n">
+      <c r="AN61" t="n">
         <v>6464602</v>
       </c>
-      <c r="AN61" t="n">
+      <c r="AO61" t="n">
         <v>2499177</v>
       </c>
-      <c r="AO61" t="n">
+      <c r="AP61" t="n">
         <v>3965425</v>
       </c>
-      <c r="AP61" t="n">
+      <c r="AQ61" t="n">
         <v>3.08</v>
       </c>
-      <c r="AQ61" t="n">
+      <c r="AR61" t="n">
         <v>2.21</v>
       </c>
-      <c r="AR61" t="n">
+      <c r="AS61" t="n">
         <v>3.63</v>
       </c>
-      <c r="AS61" t="n">
+      <c r="AT61" t="n">
         <v>28.5</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>329730</v>
       </c>
       <c r="AU61" t="n">
         <v>-0.584226</v>
@@ -17711,19 +17711,19 @@
         <v>0.909924</v>
       </c>
       <c r="BB61" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="BC61" t="n">
-        <v>4.831296</v>
+        <v>6.536174</v>
       </c>
       <c r="BD61" t="n">
-        <v>6.536174</v>
+        <v>4.767938</v>
       </c>
       <c r="BE61" t="n">
-        <v>4.767938</v>
+        <v>1</v>
       </c>
       <c r="BF61" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="BG61" t="n">
         <v>0.002578</v>
@@ -17975,49 +17975,49 @@
         <v>0.045833</v>
       </c>
       <c r="AF62" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="AG62" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG62" t="n">
+      <c r="AH62" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH62" t="n">
+      <c r="AI62" t="n">
         <v>0</v>
       </c>
-      <c r="AI62" t="n">
+      <c r="AJ62" t="n">
         <v>108.09524</v>
       </c>
-      <c r="AJ62" t="n">
+      <c r="AK62" t="n">
         <v>102.62949</v>
       </c>
-      <c r="AK62" t="n">
+      <c r="AL62" t="n">
         <v>5.8301</v>
       </c>
-      <c r="AL62" t="n">
+      <c r="AM62" t="n">
         <v>5.8295</v>
       </c>
-      <c r="AM62" t="n">
+      <c r="AN62" t="n">
         <v>6465016</v>
       </c>
-      <c r="AN62" t="n">
+      <c r="AO62" t="n">
         <v>2451957</v>
       </c>
-      <c r="AO62" t="n">
+      <c r="AP62" t="n">
         <v>4013059</v>
       </c>
-      <c r="AP62" t="n">
+      <c r="AQ62" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ62" t="n">
+      <c r="AR62" t="n">
         <v>2.43</v>
       </c>
-      <c r="AR62" t="n">
+      <c r="AS62" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS62" t="n">
+      <c r="AT62" t="n">
         <v>29.88</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>328303</v>
       </c>
       <c r="AU62" t="n">
         <v>0.675346</v>
@@ -18041,19 +18041,19 @@
         <v>1.201233</v>
       </c>
       <c r="BB62" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="BC62" t="n">
-        <v>4.559874</v>
+        <v>6.749097</v>
       </c>
       <c r="BD62" t="n">
-        <v>6.749097</v>
+        <v>4.174145</v>
       </c>
       <c r="BE62" t="n">
-        <v>4.174145</v>
+        <v>1</v>
       </c>
       <c r="BF62" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="BG62" t="n">
         <v>0.001675</v>
@@ -18309,49 +18309,49 @@
         <v>0.049037</v>
       </c>
       <c r="AF63" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG63" t="n">
         <v>1.31</v>
       </c>
-      <c r="AG63" t="n">
+      <c r="AH63" t="n">
         <v>1.06</v>
       </c>
-      <c r="AH63" t="n">
+      <c r="AI63" t="n">
         <v>1.48</v>
       </c>
-      <c r="AI63" t="n">
+      <c r="AJ63" t="n">
         <v>108.62006</v>
       </c>
-      <c r="AJ63" t="n">
+      <c r="AK63" t="n">
         <v>106.82599</v>
       </c>
-      <c r="AK63" t="n">
+      <c r="AL63" t="n">
         <v>5.8488</v>
       </c>
-      <c r="AL63" t="n">
+      <c r="AM63" t="n">
         <v>5.8482</v>
       </c>
-      <c r="AM63" t="n">
+      <c r="AN63" t="n">
         <v>6511444</v>
       </c>
-      <c r="AN63" t="n">
+      <c r="AO63" t="n">
         <v>2477151</v>
       </c>
-      <c r="AO63" t="n">
+      <c r="AP63" t="n">
         <v>4034293</v>
       </c>
-      <c r="AP63" t="n">
+      <c r="AQ63" t="n">
         <v>3.41</v>
       </c>
-      <c r="AQ63" t="n">
+      <c r="AR63" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR63" t="n">
+      <c r="AS63" t="n">
         <v>3.96</v>
       </c>
-      <c r="AS63" t="n">
+      <c r="AT63" t="n">
         <v>30.53</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>332508</v>
       </c>
       <c r="AU63" t="n">
         <v>0.485516</v>
@@ -18375,19 +18375,19 @@
         <v>0.529123</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="BC63" t="n">
-        <v>5.05763</v>
+        <v>8.444549</v>
       </c>
       <c r="BD63" t="n">
-        <v>8.444549</v>
+        <v>4.866504</v>
       </c>
       <c r="BE63" t="n">
-        <v>4.866504</v>
+        <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="BG63" t="n">
         <v>0.003204</v>
@@ -18639,49 +18639,49 @@
         <v>0.050508</v>
       </c>
       <c r="AF64" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="AG64" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG64" t="n">
+      <c r="AH64" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AH64" t="n">
+      <c r="AI64" t="n">
         <v>0.51</v>
       </c>
-      <c r="AI64" t="n">
+      <c r="AJ64" t="n">
         <v>110.03287</v>
       </c>
-      <c r="AJ64" t="n">
+      <c r="AK64" t="n">
         <v>114.02067</v>
       </c>
-      <c r="AK64" t="n">
+      <c r="AL64" t="n">
         <v>5.7422</v>
       </c>
-      <c r="AL64" t="n">
+      <c r="AM64" t="n">
         <v>5.7416</v>
       </c>
-      <c r="AM64" t="n">
+      <c r="AN64" t="n">
         <v>6576464</v>
       </c>
-      <c r="AN64" t="n">
+      <c r="AO64" t="n">
         <v>2498262</v>
       </c>
-      <c r="AO64" t="n">
+      <c r="AP64" t="n">
         <v>4078202</v>
       </c>
-      <c r="AP64" t="n">
+      <c r="AQ64" t="n">
         <v>3.44</v>
       </c>
-      <c r="AQ64" t="n">
+      <c r="AR64" t="n">
         <v>2.49</v>
       </c>
-      <c r="AR64" t="n">
+      <c r="AS64" t="n">
         <v>4.03</v>
       </c>
-      <c r="AS64" t="n">
+      <c r="AT64" t="n">
         <v>31.34</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>336157</v>
       </c>
       <c r="AU64" t="n">
         <v>1.30069</v>
@@ -18705,19 +18705,19 @@
         <v>1.088394</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="BC64" t="n">
-        <v>5.47719</v>
+        <v>8.586193</v>
       </c>
       <c r="BD64" t="n">
-        <v>8.586193</v>
+        <v>5.201441</v>
       </c>
       <c r="BE64" t="n">
-        <v>5.201441</v>
+        <v>1</v>
       </c>
       <c r="BF64" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="BG64" t="n">
         <v>0.001471</v>
@@ -18965,49 +18965,49 @@
         <v>0.052531</v>
       </c>
       <c r="AF65" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="AG65" t="n">
         <v>0.43</v>
       </c>
-      <c r="AG65" t="n">
+      <c r="AH65" t="n">
         <v>0.24</v>
       </c>
-      <c r="AH65" t="n">
+      <c r="AI65" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI65" t="n">
+      <c r="AJ65" t="n">
         <v>109.52766</v>
       </c>
-      <c r="AJ65" t="n">
+      <c r="AK65" t="n">
         <v>112.59512</v>
       </c>
-      <c r="AK65" t="n">
+      <c r="AL65" t="n">
         <v>5.6608</v>
       </c>
-      <c r="AL65" t="n">
+      <c r="AM65" t="n">
         <v>5.6602</v>
       </c>
-      <c r="AM65" t="n">
+      <c r="AN65" t="n">
         <v>6623948</v>
       </c>
-      <c r="AN65" t="n">
+      <c r="AO65" t="n">
         <v>2512426</v>
       </c>
-      <c r="AO65" t="n">
+      <c r="AP65" t="n">
         <v>4111522</v>
       </c>
-      <c r="AP65" t="n">
+      <c r="AQ65" t="n">
         <v>3.67</v>
       </c>
-      <c r="AQ65" t="n">
+      <c r="AR65" t="n">
         <v>2.72</v>
       </c>
-      <c r="AR65" t="n">
+      <c r="AS65" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS65" t="n">
+      <c r="AT65" t="n">
         <v>31.63</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>340789</v>
       </c>
       <c r="AU65" t="n">
         <v>-0.459145</v>
@@ -19031,19 +19031,19 @@
         <v>0.8170269999999999</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="BC65" t="n">
-        <v>5.529729</v>
+        <v>8.510418</v>
       </c>
       <c r="BD65" t="n">
-        <v>8.510418</v>
+        <v>5.316736</v>
       </c>
       <c r="BE65" t="n">
-        <v>5.316736</v>
+        <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="BG65" t="n">
         <v>0.002023</v>
@@ -19299,49 +19299,49 @@
         <v>0.053936</v>
       </c>
       <c r="AF66" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="AG66" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG66" t="n">
+      <c r="AH66" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AH66" t="n">
+      <c r="AI66" t="n">
         <v>0.35</v>
       </c>
-      <c r="AI66" t="n">
+      <c r="AJ66" t="n">
         <v>108.8862</v>
       </c>
-      <c r="AJ66" t="n">
+      <c r="AK66" t="n">
         <v>108.55704</v>
       </c>
-      <c r="AK66" t="n">
+      <c r="AL66" t="n">
         <v>5.7087</v>
       </c>
-      <c r="AL66" t="n">
+      <c r="AM66" t="n">
         <v>5.7081</v>
       </c>
-      <c r="AM66" t="n">
+      <c r="AN66" t="n">
         <v>6666287</v>
       </c>
-      <c r="AN66" t="n">
+      <c r="AO66" t="n">
         <v>2532708</v>
       </c>
-      <c r="AO66" t="n">
+      <c r="AP66" t="n">
         <v>4133579</v>
       </c>
-      <c r="AP66" t="n">
+      <c r="AQ66" t="n">
         <v>3.72</v>
       </c>
-      <c r="AQ66" t="n">
+      <c r="AR66" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR66" t="n">
+      <c r="AS66" t="n">
         <v>4.36</v>
       </c>
-      <c r="AS66" t="n">
+      <c r="AT66" t="n">
         <v>31.7</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>341459</v>
       </c>
       <c r="AU66" t="n">
         <v>-0.58566</v>
@@ -19365,19 +19365,19 @@
         <v>0.5364679999999999</v>
       </c>
       <c r="BB66" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="BC66" t="n">
-        <v>5.319636</v>
+        <v>7.026183</v>
       </c>
       <c r="BD66" t="n">
-        <v>7.026183</v>
+        <v>5.201418</v>
       </c>
       <c r="BE66" t="n">
-        <v>5.201418</v>
+        <v>0.5</v>
       </c>
       <c r="BF66" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="BG66" t="n">
         <v>0.001405</v>
@@ -19629,49 +19629,49 @@
         <v>0.054569</v>
       </c>
       <c r="AF67" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="AG67" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG67" t="n">
+      <c r="AH67" t="n">
         <v>-1.67</v>
       </c>
-      <c r="AH67" t="n">
+      <c r="AI67" t="n">
         <v>0.23</v>
       </c>
-      <c r="AI67" t="n">
+      <c r="AJ67" t="n">
         <v>108.80376</v>
       </c>
-      <c r="AJ67" t="n">
+      <c r="AK67" t="n">
         <v>107.36219</v>
       </c>
-      <c r="AK67" t="n">
+      <c r="AL67" t="n">
         <v>5.4571</v>
       </c>
-      <c r="AL67" t="n">
+      <c r="AM67" t="n">
         <v>5.4565</v>
       </c>
-      <c r="AM67" t="n">
+      <c r="AN67" t="n">
         <v>6703663</v>
       </c>
-      <c r="AN67" t="n">
+      <c r="AO67" t="n">
         <v>2547693</v>
       </c>
-      <c r="AO67" t="n">
+      <c r="AP67" t="n">
         <v>4155970</v>
       </c>
-      <c r="AP67" t="n">
+      <c r="AQ67" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ67" t="n">
+      <c r="AR67" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR67" t="n">
+      <c r="AS67" t="n">
         <v>4.41</v>
       </c>
-      <c r="AS67" t="n">
+      <c r="AT67" t="n">
         <v>31.85</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>344440</v>
       </c>
       <c r="AU67" t="n">
         <v>-0.075712</v>
@@ -19695,19 +19695,19 @@
         <v>0.541686</v>
       </c>
       <c r="BB67" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="BC67" t="n">
-        <v>5.351165</v>
+        <v>4.393261</v>
       </c>
       <c r="BD67" t="n">
-        <v>4.393261</v>
+        <v>5.18043</v>
       </c>
       <c r="BE67" t="n">
-        <v>5.18043</v>
+        <v>0.25</v>
       </c>
       <c r="BF67" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="BG67" t="n">
         <v>0.000633</v>
@@ -19959,49 +19959,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF68" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG68" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG68" t="n">
+      <c r="AH68" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AH68" t="n">
+      <c r="AI68" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI68" t="n">
+      <c r="AJ68" t="n">
         <v>108.49869</v>
       </c>
-      <c r="AJ68" t="n">
+      <c r="AK68" t="n">
         <v>113.10928</v>
       </c>
-      <c r="AK68" t="n">
+      <c r="AL68" t="n">
         <v>5.6021</v>
       </c>
-      <c r="AL68" t="n">
+      <c r="AM68" t="n">
         <v>5.6015</v>
       </c>
-      <c r="AM68" t="n">
+      <c r="AN68" t="n">
         <v>6733209</v>
       </c>
-      <c r="AN68" t="n">
+      <c r="AO68" t="n">
         <v>2544400</v>
       </c>
-      <c r="AO68" t="n">
+      <c r="AP68" t="n">
         <v>4188808</v>
       </c>
-      <c r="AP68" t="n">
+      <c r="AQ68" t="n">
         <v>3.96</v>
       </c>
-      <c r="AQ68" t="n">
+      <c r="AR68" t="n">
         <v>2.79</v>
       </c>
-      <c r="AR68" t="n">
+      <c r="AS68" t="n">
         <v>4.66</v>
       </c>
-      <c r="AS68" t="n">
+      <c r="AT68" t="n">
         <v>31.75</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>345111</v>
       </c>
       <c r="AU68" t="n">
         <v>-0.280386</v>
@@ -20025,19 +20025,19 @@
         <v>0.79014</v>
       </c>
       <c r="BB68" t="n">
-        <v>0.194809</v>
+        <v>5.225222</v>
       </c>
       <c r="BC68" t="n">
-        <v>5.225222</v>
+        <v>2.961368</v>
       </c>
       <c r="BD68" t="n">
-        <v>2.961368</v>
+        <v>5.127976</v>
       </c>
       <c r="BE68" t="n">
-        <v>5.127976</v>
+        <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="BG68" t="n">
         <v>0.000562</v>
@@ -20293,49 +20293,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF69" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG69" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AG69" t="n">
+      <c r="AH69" t="n">
         <v>0.36</v>
       </c>
-      <c r="AH69" t="n">
+      <c r="AI69" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AI69" t="n">
+      <c r="AJ69" t="n">
         <v>108.82893</v>
       </c>
-      <c r="AJ69" t="n">
+      <c r="AK69" t="n">
         <v>110.38054</v>
       </c>
-      <c r="AK69" t="n">
+      <c r="AL69" t="n">
         <v>5.4264</v>
       </c>
-      <c r="AL69" t="n">
+      <c r="AM69" t="n">
         <v>5.4258</v>
       </c>
-      <c r="AM69" t="n">
+      <c r="AN69" t="n">
         <v>6774436</v>
       </c>
-      <c r="AN69" t="n">
+      <c r="AO69" t="n">
         <v>2546265</v>
       </c>
-      <c r="AO69" t="n">
+      <c r="AP69" t="n">
         <v>4228171</v>
       </c>
-      <c r="AP69" t="n">
+      <c r="AQ69" t="n">
         <v>4.14</v>
       </c>
-      <c r="AQ69" t="n">
+      <c r="AR69" t="n">
         <v>2.85</v>
       </c>
-      <c r="AR69" t="n">
+      <c r="AS69" t="n">
         <v>4.92</v>
       </c>
-      <c r="AS69" t="n">
+      <c r="AT69" t="n">
         <v>31.87</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>350767</v>
       </c>
       <c r="AU69" t="n">
         <v>0.304372</v>
@@ -20359,16 +20359,16 @@
         <v>0.9397180000000001</v>
       </c>
       <c r="BB69" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="BC69" t="n">
-        <v>5.130501</v>
+        <v>3.033233</v>
       </c>
       <c r="BD69" t="n">
-        <v>3.033233</v>
+        <v>5.054283</v>
       </c>
       <c r="BE69" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="BF69" t="n">
         <v>0</v>
@@ -20623,49 +20623,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF70" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG70" t="n">
         <v>0.48</v>
       </c>
-      <c r="AG70" t="n">
+      <c r="AH70" t="n">
         <v>0.42</v>
       </c>
-      <c r="AH70" t="n">
+      <c r="AI70" t="n">
         <v>0.52</v>
       </c>
-      <c r="AI70" t="n">
+      <c r="AJ70" t="n">
         <v>108.73548</v>
       </c>
-      <c r="AJ70" t="n">
+      <c r="AK70" t="n">
         <v>109.48375</v>
       </c>
-      <c r="AK70" t="n">
+      <c r="AL70" t="n">
         <v>5.3186</v>
       </c>
-      <c r="AL70" t="n">
+      <c r="AM70" t="n">
         <v>5.318</v>
       </c>
-      <c r="AM70" t="n">
+      <c r="AN70" t="n">
         <v>6852705</v>
       </c>
-      <c r="AN70" t="n">
+      <c r="AO70" t="n">
         <v>2589817</v>
       </c>
-      <c r="AO70" t="n">
+      <c r="AP70" t="n">
         <v>4262888</v>
       </c>
-      <c r="AP70" t="n">
+      <c r="AQ70" t="n">
         <v>4.09</v>
       </c>
-      <c r="AQ70" t="n">
+      <c r="AR70" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR70" t="n">
+      <c r="AS70" t="n">
         <v>4.89</v>
       </c>
-      <c r="AS70" t="n">
+      <c r="AT70" t="n">
         <v>31.47</v>
-      </c>
-      <c r="AT70" t="n">
-        <v>356582</v>
       </c>
       <c r="AU70" t="n">
         <v>-0.085869</v>
@@ -20689,16 +20689,16 @@
         <v>0.821088</v>
       </c>
       <c r="BB70" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="BC70" t="n">
-        <v>5.172369</v>
+        <v>2.828436</v>
       </c>
       <c r="BD70" t="n">
-        <v>2.828436</v>
+        <v>5.096104</v>
       </c>
       <c r="BE70" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="BF70" t="n">
         <v>0</v>
@@ -20953,49 +20953,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF71" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG71" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG71" t="n">
+      <c r="AH71" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AH71" t="n">
+      <c r="AI71" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI71" t="n">
+      <c r="AJ71" t="n">
         <v>108.75326</v>
       </c>
-      <c r="AJ71" t="n">
+      <c r="AK71" t="n">
         <v>110.07682</v>
       </c>
-      <c r="AK71" t="n">
+      <c r="AL71" t="n">
         <v>5.3843</v>
       </c>
-      <c r="AL71" t="n">
+      <c r="AM71" t="n">
         <v>5.3837</v>
       </c>
-      <c r="AM71" t="n">
+      <c r="AN71" t="n">
         <v>6923886</v>
       </c>
-      <c r="AN71" t="n">
+      <c r="AO71" t="n">
         <v>2597630</v>
       </c>
-      <c r="AO71" t="n">
+      <c r="AP71" t="n">
         <v>4326256</v>
       </c>
-      <c r="AP71" t="n">
+      <c r="AQ71" t="n">
         <v>4.18</v>
       </c>
-      <c r="AQ71" t="n">
+      <c r="AR71" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR71" t="n">
+      <c r="AS71" t="n">
         <v>4.99</v>
       </c>
-      <c r="AS71" t="n">
+      <c r="AT71" t="n">
         <v>32.04</v>
-      </c>
-      <c r="AT71" t="n">
-        <v>357103</v>
       </c>
       <c r="AU71" t="n">
         <v>0.016352</v>
@@ -21019,16 +21019,16 @@
         <v>1.486504</v>
       </c>
       <c r="BB71" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="BC71" t="n">
-        <v>4.680811</v>
+        <v>0.924206</v>
       </c>
       <c r="BD71" t="n">
-        <v>0.924206</v>
+        <v>4.490243</v>
       </c>
       <c r="BE71" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="BF71" t="n">
         <v>0</v>
@@ -21283,49 +21283,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF72" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG72" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG72" t="n">
+      <c r="AH72" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH72" t="n">
+      <c r="AI72" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI72" t="n">
+      <c r="AJ72" t="n">
         <v>109.25005</v>
       </c>
-      <c r="AJ72" t="n">
+      <c r="AK72" t="n">
         <v>106.59892</v>
       </c>
-      <c r="AK72" t="n">
+      <c r="AL72" t="n">
         <v>5.3338</v>
       </c>
-      <c r="AL72" t="n">
+      <c r="AM72" t="n">
         <v>5.3332</v>
       </c>
-      <c r="AM72" t="n">
+      <c r="AN72" t="n">
         <v>7004223</v>
       </c>
-      <c r="AN72" t="n">
+      <c r="AO72" t="n">
         <v>2616902</v>
       </c>
-      <c r="AO72" t="n">
+      <c r="AP72" t="n">
         <v>4387321</v>
       </c>
-      <c r="AP72" t="n">
+      <c r="AQ72" t="n">
         <v>4.24</v>
       </c>
-      <c r="AQ72" t="n">
+      <c r="AR72" t="n">
         <v>2.75</v>
       </c>
-      <c r="AR72" t="n">
+      <c r="AS72" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS72" t="n">
+      <c r="AT72" t="n">
         <v>32.2</v>
-      </c>
-      <c r="AT72" t="n">
-        <v>360578</v>
       </c>
       <c r="AU72" t="n">
         <v>0.456805</v>
@@ -21349,19 +21349,19 @@
         <v>1.411498</v>
       </c>
       <c r="BB72" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="BC72" t="n">
-        <v>4.461836</v>
+        <v>-0.101973</v>
       </c>
       <c r="BD72" t="n">
-        <v>-0.101973</v>
+        <v>4.177803</v>
       </c>
       <c r="BE72" t="n">
-        <v>4.177803</v>
+        <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG72" t="n">
         <v>-0</v>
@@ -21617,49 +21617,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF73" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG73" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG73" t="n">
+      <c r="AH73" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH73" t="n">
+      <c r="AI73" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI73" t="n">
+      <c r="AJ73" t="n">
         <v>109.4528</v>
       </c>
-      <c r="AJ73" t="n">
+      <c r="AK73" t="n">
         <v>107.18417</v>
       </c>
-      <c r="AK73" t="n">
+      <c r="AL73" t="n">
         <v>5.5024</v>
       </c>
-      <c r="AL73" t="n">
+      <c r="AM73" t="n">
         <v>5.5018</v>
       </c>
-      <c r="AM73" t="n">
+      <c r="AN73" t="n">
         <v>7137252</v>
       </c>
-      <c r="AN73" t="n">
+      <c r="AO73" t="n">
         <v>2701735</v>
       </c>
-      <c r="AO73" t="n">
+      <c r="AP73" t="n">
         <v>4435517</v>
       </c>
-      <c r="AP73" t="n">
+      <c r="AQ73" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ73" t="n">
+      <c r="AR73" t="n">
         <v>2.7</v>
       </c>
-      <c r="AR73" t="n">
+      <c r="AS73" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS73" t="n">
+      <c r="AT73" t="n">
         <v>31.87</v>
-      </c>
-      <c r="AT73" t="n">
-        <v>358234</v>
       </c>
       <c r="AU73" t="n">
         <v>0.185583</v>
@@ -21683,16 +21683,16 @@
         <v>1.098529</v>
       </c>
       <c r="BB73" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="BC73" t="n">
-        <v>4.264385</v>
+        <v>-1.042167</v>
       </c>
       <c r="BD73" t="n">
-        <v>-1.042167</v>
+        <v>3.897866</v>
       </c>
       <c r="BE73" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="BF73" t="n">
         <v>0</v>
@@ -21943,49 +21943,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF74" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG74" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG74" t="n">
+      <c r="AH74" t="n">
         <v>0.41</v>
       </c>
-      <c r="AH74" t="n">
+      <c r="AI74" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI74" t="n">
+      <c r="AJ74" t="n">
         <v>110.04992</v>
       </c>
-      <c r="AJ74" t="n">
+      <c r="AK74" t="n">
         <v>103.77761</v>
       </c>
-      <c r="AK74" t="n">
+      <c r="AL74" t="n">
         <v>5.2301</v>
       </c>
-      <c r="AL74" t="n">
+      <c r="AM74" t="n">
         <v>5.2295</v>
       </c>
-      <c r="AM74" t="n">
+      <c r="AN74" t="n">
         <v>7130762</v>
       </c>
-      <c r="AN74" t="n">
+      <c r="AO74" t="n">
         <v>2654220</v>
       </c>
-      <c r="AO74" t="n">
+      <c r="AP74" t="n">
         <v>4476542</v>
       </c>
-      <c r="AP74" t="n">
+      <c r="AQ74" t="n">
         <v>4.44</v>
       </c>
-      <c r="AQ74" t="n">
+      <c r="AR74" t="n">
         <v>2.87</v>
       </c>
-      <c r="AR74" t="n">
+      <c r="AS74" t="n">
         <v>5.38</v>
       </c>
-      <c r="AS74" t="n">
+      <c r="AT74" t="n">
         <v>32.45</v>
-      </c>
-      <c r="AT74" t="n">
-        <v>364367</v>
       </c>
       <c r="AU74" t="n">
         <v>0.54555</v>
@@ -22009,16 +22009,16 @@
         <v>0.92492</v>
       </c>
       <c r="BB74" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="BC74" t="n">
-        <v>4.441351</v>
+        <v>-0.903999</v>
       </c>
       <c r="BD74" t="n">
-        <v>-0.903999</v>
+        <v>4.303068</v>
       </c>
       <c r="BE74" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="BF74" t="n">
         <v>0</v>
@@ -22273,49 +22273,49 @@
         <v>0.055131</v>
       </c>
       <c r="AF75" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG75" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG75" t="n">
+      <c r="AH75" t="n">
         <v>-0.73</v>
       </c>
-      <c r="AH75" t="n">
+      <c r="AI75" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AI75" t="n">
+      <c r="AJ75" t="n">
         <v>110.7366</v>
       </c>
-      <c r="AJ75" t="n">
+      <c r="AK75" t="n">
         <v>106.76075</v>
       </c>
-      <c r="AK75" t="n">
+      <c r="AL75" t="n">
         <v>5.1495</v>
       </c>
-      <c r="AL75" t="n">
+      <c r="AM75" t="n">
         <v>5.1489</v>
       </c>
-      <c r="AM75" t="n">
+      <c r="AN75" t="n">
         <v>7157783</v>
       </c>
-      <c r="AN75" t="n">
+      <c r="AO75" t="n">
         <v>2656484</v>
       </c>
-      <c r="AO75" t="n">
+      <c r="AP75" t="n">
         <v>4501299</v>
       </c>
-      <c r="AP75" t="n">
+      <c r="AQ75" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ75" t="n">
+      <c r="AR75" t="n">
         <v>3.07</v>
       </c>
-      <c r="AR75" t="n">
+      <c r="AS75" t="n">
         <v>5.56</v>
       </c>
-      <c r="AS75" t="n">
+      <c r="AT75" t="n">
         <v>32.63</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>371074</v>
       </c>
       <c r="AU75" t="n">
         <v>0.6239710000000001</v>
@@ -22339,16 +22339,16 @@
         <v>0.553038</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="BC75" t="n">
-        <v>3.812497</v>
+        <v>-2.659212</v>
       </c>
       <c r="BD75" t="n">
-        <v>-2.659212</v>
+        <v>3.357475</v>
       </c>
       <c r="BE75" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="BF75" t="n">
         <v>0</v>
@@ -22607,49 +22607,49 @@
         <v>0.054777</v>
       </c>
       <c r="AF76" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="AG76" t="n">
         <v>0.88</v>
       </c>
-      <c r="AG76" t="n">
+      <c r="AH76" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH76" t="n">
+      <c r="AI76" t="n">
         <v>0.91</v>
       </c>
-      <c r="AI76" t="n">
+      <c r="AJ76" t="n">
         <v>110.58808</v>
       </c>
-      <c r="AJ76" t="n">
+      <c r="AK76" t="n">
         <v>118.01719</v>
       </c>
-      <c r="AK76" t="n">
+      <c r="AL76" t="n">
         <v>5.2194</v>
       </c>
-      <c r="AL76" t="n">
+      <c r="AM76" t="n">
         <v>5.2188</v>
       </c>
-      <c r="AM76" t="n">
+      <c r="AN76" t="n">
         <v>7240557</v>
       </c>
-      <c r="AN76" t="n">
+      <c r="AO76" t="n">
         <v>2687535</v>
       </c>
-      <c r="AO76" t="n">
+      <c r="AP76" t="n">
         <v>4553022</v>
       </c>
-      <c r="AP76" t="n">
+      <c r="AQ76" t="n">
         <v>4.52</v>
       </c>
-      <c r="AQ76" t="n">
+      <c r="AR76" t="n">
         <v>3.06</v>
       </c>
-      <c r="AR76" t="n">
+      <c r="AS76" t="n">
         <v>5.39</v>
       </c>
-      <c r="AS76" t="n">
+      <c r="AT76" t="n">
         <v>32.84</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>362002</v>
       </c>
       <c r="AU76" t="n">
         <v>-0.13412</v>
@@ -22673,19 +22673,19 @@
         <v>1.149068</v>
       </c>
       <c r="BB76" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="BC76" t="n">
-        <v>4.142847</v>
+        <v>-1.819225</v>
       </c>
       <c r="BD76" t="n">
-        <v>-1.819225</v>
+        <v>3.768807</v>
       </c>
       <c r="BE76" t="n">
-        <v>3.768807</v>
+        <v>-0.25</v>
       </c>
       <c r="BF76" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="BG76" t="n">
         <v>-0.000354</v>
@@ -22937,49 +22937,49 @@
         <v>0.054223</v>
       </c>
       <c r="AF77" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="AG77" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG77" t="n">
+      <c r="AH77" t="n">
         <v>2.73</v>
       </c>
-      <c r="AH77" t="n">
+      <c r="AI77" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI77" t="n">
+      <c r="AJ77" t="n">
         <v>110.90009</v>
       </c>
-      <c r="AJ77" t="n">
+      <c r="AK77" t="n">
         <v>113.99295</v>
       </c>
-      <c r="AK77" t="n">
+      <c r="AL77" t="n">
         <v>4.9886</v>
       </c>
-      <c r="AL77" t="n">
+      <c r="AM77" t="n">
         <v>4.988</v>
       </c>
-      <c r="AM77" t="n">
+      <c r="AN77" t="n">
         <v>7259766</v>
       </c>
-      <c r="AN77" t="n">
+      <c r="AO77" t="n">
         <v>2685397</v>
       </c>
-      <c r="AO77" t="n">
+      <c r="AP77" t="n">
         <v>4574368</v>
       </c>
-      <c r="AP77" t="n">
+      <c r="AQ77" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ77" t="n">
+      <c r="AR77" t="n">
         <v>3.15</v>
       </c>
-      <c r="AR77" t="n">
+      <c r="AS77" t="n">
         <v>5.51</v>
       </c>
-      <c r="AS77" t="n">
+      <c r="AT77" t="n">
         <v>33.36</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>366913</v>
       </c>
       <c r="AU77" t="n">
         <v>0.282137</v>
@@ -23003,19 +23003,19 @@
         <v>0.468831</v>
       </c>
       <c r="BB77" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="BC77" t="n">
-        <v>4.39172</v>
+        <v>0.619623</v>
       </c>
       <c r="BD77" t="n">
-        <v>0.619623</v>
+        <v>4.109608</v>
       </c>
       <c r="BE77" t="n">
-        <v>4.109608</v>
+        <v>-0.25</v>
       </c>
       <c r="BF77" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="BG77" t="n">
         <v>-0.000554</v>
@@ -23267,49 +23267,49 @@
         <v>0.0534</v>
       </c>
       <c r="AF78" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="AG78" t="n">
         <v>0.58</v>
       </c>
-      <c r="AG78" t="n">
+      <c r="AH78" t="n">
         <v>0.84</v>
       </c>
-      <c r="AH78" t="n">
+      <c r="AI78" t="n">
         <v>0.65</v>
       </c>
-      <c r="AI78" t="n">
+      <c r="AJ78" t="n">
         <v>111.13846</v>
       </c>
-      <c r="AJ78" t="n">
+      <c r="AK78" t="n">
         <v>109.65479</v>
       </c>
-      <c r="AK78" t="n">
+      <c r="AL78" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AL78" t="n">
+      <c r="AM78" t="n">
         <v>5.0563</v>
       </c>
-      <c r="AM78" t="n">
+      <c r="AN78" t="n">
         <v>7305322</v>
       </c>
-      <c r="AN78" t="n">
+      <c r="AO78" t="n">
         <v>2708154</v>
       </c>
-      <c r="AO78" t="n">
+      <c r="AP78" t="n">
         <v>4597168</v>
       </c>
-      <c r="AP78" t="n">
+      <c r="AQ78" t="n">
         <v>4.75</v>
       </c>
-      <c r="AQ78" t="n">
+      <c r="AR78" t="n">
         <v>3.25</v>
       </c>
-      <c r="AR78" t="n">
+      <c r="AS78" t="n">
         <v>5.63</v>
       </c>
-      <c r="AS78" t="n">
+      <c r="AT78" t="n">
         <v>32.97</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>371137</v>
       </c>
       <c r="AU78" t="n">
         <v>0.214941</v>
@@ -23333,19 +23333,19 @@
         <v>0.49843</v>
       </c>
       <c r="BB78" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="BC78" t="n">
-        <v>4.724907</v>
+        <v>1.964454</v>
       </c>
       <c r="BD78" t="n">
-        <v>1.964454</v>
+        <v>4.420848</v>
       </c>
       <c r="BE78" t="n">
-        <v>4.420848</v>
+        <v>0</v>
       </c>
       <c r="BF78" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BG78" t="n">
         <v>-0.0008229999999999999</v>
@@ -23601,49 +23601,49 @@
         <v>0.053028</v>
       </c>
       <c r="AF79" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="AG79" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG79" t="n">
+      <c r="AH79" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AH79" t="n">
+      <c r="AI79" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI79" t="n">
+      <c r="AJ79" t="n">
         <v>110.15775</v>
       </c>
-      <c r="AJ79" t="n">
+      <c r="AK79" t="n">
         <v>109.94156</v>
       </c>
-      <c r="AK79" t="n">
+      <c r="AL79" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AL79" t="n">
+      <c r="AM79" t="n">
         <v>5.176</v>
       </c>
-      <c r="AM79" t="n">
+      <c r="AN79" t="n">
         <v>7353302</v>
       </c>
-      <c r="AN79" t="n">
+      <c r="AO79" t="n">
         <v>2750634</v>
       </c>
-      <c r="AO79" t="n">
+      <c r="AP79" t="n">
         <v>4602668</v>
       </c>
-      <c r="AP79" t="n">
+      <c r="AQ79" t="n">
         <v>4.58</v>
       </c>
-      <c r="AQ79" t="n">
+      <c r="AR79" t="n">
         <v>3.18</v>
       </c>
-      <c r="AR79" t="n">
+      <c r="AS79" t="n">
         <v>5.42</v>
       </c>
-      <c r="AS79" t="n">
+      <c r="AT79" t="n">
         <v>32.63</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>367558</v>
       </c>
       <c r="AU79" t="n">
         <v>-0.882422</v>
@@ -23667,19 +23667,19 @@
         <v>0.119639</v>
       </c>
       <c r="BB79" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="BC79" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="BD79" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
       <c r="BE79" t="n">
-        <v>4.327084</v>
+        <v>-0.25</v>
       </c>
       <c r="BF79" t="n">
-        <v>-0.25</v>
+        <v>-0.000372</v>
       </c>
       <c r="BG79" t="n">
         <v>-0.000372</v>
@@ -23931,49 +23931,49 @@
         <v>0.052531</v>
       </c>
       <c r="AF80" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="AG80" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG80" t="n">
+      <c r="AH80" t="n">
         <v>-1.16</v>
       </c>
-      <c r="AH80" t="n">
+      <c r="AI80" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AI80" t="n">
+      <c r="AJ80" t="n">
         <v>109.91611</v>
       </c>
-      <c r="AJ80" t="n">
+      <c r="AK80" t="n">
         <v>114.40189</v>
       </c>
-      <c r="AK80" t="n">
+      <c r="AL80" t="n">
         <v>5.0773</v>
       </c>
-      <c r="AL80" t="n">
+      <c r="AM80" t="n">
         <v>5.0767</v>
       </c>
-      <c r="AM80" t="n">
+      <c r="AN80" t="n">
         <v>7362305</v>
       </c>
-      <c r="AN80" t="n">
+      <c r="AO80" t="n">
         <v>2729162</v>
       </c>
-      <c r="AO80" t="n">
+      <c r="AP80" t="n">
         <v>4633143</v>
       </c>
-      <c r="AP80" t="n">
+      <c r="AQ80" t="n">
         <v>4.88</v>
       </c>
-      <c r="AQ80" t="n">
+      <c r="AR80" t="n">
         <v>3.32</v>
       </c>
-      <c r="AR80" t="n">
+      <c r="AS80" t="n">
         <v>5.8</v>
       </c>
-      <c r="AS80" t="n">
+      <c r="AT80" t="n">
         <v>32.06</v>
-      </c>
-      <c r="AT80" t="n">
-        <v>369742</v>
       </c>
       <c r="AU80" t="n">
         <v>-0.219358</v>
@@ -23997,19 +23997,19 @@
         <v>0.662116</v>
       </c>
       <c r="BB80" t="n">
-        <v>0.5941920000000001</v>
+        <v>4.443025</v>
       </c>
       <c r="BC80" t="n">
-        <v>4.443025</v>
+        <v>2.772183</v>
       </c>
       <c r="BD80" t="n">
-        <v>2.772183</v>
+        <v>4.098046</v>
       </c>
       <c r="BE80" t="n">
-        <v>4.098046</v>
+        <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="BG80" t="n">
         <v>-0.000497</v>
@@ -24265,45 +24265,45 @@
         <v>0.051784</v>
       </c>
       <c r="AF81" t="n">
+        <v>0.051784</v>
+      </c>
+      <c r="AG81" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AG81" t="n">
+      <c r="AH81" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AH81" t="n">
+      <c r="AI81" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
-      <c r="AK81" t="n">
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="n">
         <v>5.1816</v>
       </c>
-      <c r="AL81" t="n">
+      <c r="AM81" t="n">
         <v>5.181</v>
       </c>
-      <c r="AM81" t="n">
+      <c r="AN81" t="n">
         <v>7397669</v>
       </c>
-      <c r="AN81" t="n">
+      <c r="AO81" t="n">
         <v>2727499</v>
       </c>
-      <c r="AO81" t="n">
+      <c r="AP81" t="n">
         <v>4670170</v>
       </c>
-      <c r="AP81" t="n">
+      <c r="AQ81" t="n">
         <v>5.04</v>
       </c>
-      <c r="AQ81" t="n">
+      <c r="AR81" t="n">
         <v>3.35</v>
       </c>
-      <c r="AR81" t="n">
+      <c r="AS81" t="n">
         <v>6.03</v>
       </c>
-      <c r="AS81" t="n">
+      <c r="AT81" t="n">
         <v>32.26</v>
-      </c>
-      <c r="AT81" t="n">
-        <v>372616</v>
       </c>
       <c r="AU81" t="inlineStr"/>
       <c r="AV81" t="inlineStr"/>
@@ -24323,19 +24323,19 @@
         <v>0.799177</v>
       </c>
       <c r="BB81" t="n">
-        <v>0.777299</v>
+        <v>4.223453</v>
       </c>
       <c r="BC81" t="n">
-        <v>4.223453</v>
+        <v>2.178243</v>
       </c>
       <c r="BD81" t="n">
-        <v>2.178243</v>
+        <v>3.983297</v>
       </c>
       <c r="BE81" t="n">
-        <v>3.983297</v>
+        <v>-0.25</v>
       </c>
       <c r="BF81" t="n">
-        <v>-0.25</v>
+        <v>-0.0007470000000000001</v>
       </c>
       <c r="BG81" t="n">
         <v>-0.0007470000000000001</v>
@@ -24586,29 +24586,33 @@
       <c r="AE82" t="n">
         <v>0.051245</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
+      <c r="AF82" t="n">
+        <v>0.051245</v>
+      </c>
       <c r="AG82" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AH82" t="n">
         <v>1.57</v>
       </c>
-      <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
+      <c r="AI82" t="n">
+        <v>0.82</v>
+      </c>
       <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="n">
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="n">
         <v>5.1809</v>
       </c>
-      <c r="AL82" t="n">
+      <c r="AM82" t="n">
         <v>5.1803</v>
       </c>
-      <c r="AM82" t="inlineStr"/>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
       <c r="AP82" t="inlineStr"/>
       <c r="AQ82" t="inlineStr"/>
       <c r="AR82" t="inlineStr"/>
       <c r="AS82" t="inlineStr"/>
-      <c r="AT82" t="n">
-        <v>362821</v>
-      </c>
+      <c r="AT82" t="inlineStr"/>
       <c r="AU82" t="inlineStr"/>
       <c r="AV82" t="inlineStr"/>
       <c r="AW82" t="n">
@@ -24621,15 +24625,19 @@
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="inlineStr"/>
       <c r="BB82" t="n">
-        <v>-2.628712</v>
-      </c>
-      <c r="BC82" t="inlineStr"/>
+        <v>4.57612</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>3.348378</v>
+      </c>
       <c r="BD82" t="n">
-        <v>3.348378</v>
-      </c>
-      <c r="BE82" t="inlineStr"/>
+        <v>4.293633</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="BF82" t="n">
-        <v>-0.25</v>
+        <v>-0.00054</v>
       </c>
       <c r="BG82" t="n">
         <v>-0.00054</v>
@@ -24779,88 +24787,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>206768.96875</v>
+        <v>208674.40625</v>
       </c>
       <c r="C83" t="n">
-        <v>203.580002</v>
+        <v>205.360001</v>
       </c>
       <c r="D83" t="n">
-        <v>133.729996</v>
+        <v>138.789993</v>
       </c>
       <c r="E83" t="n">
-        <v>438.649994</v>
+        <v>439.200012</v>
       </c>
       <c r="F83" t="n">
-        <v>5.0001</v>
+        <v>4.9842</v>
       </c>
       <c r="G83" t="n">
-        <v>5.6081</v>
+        <v>5.577</v>
       </c>
       <c r="H83" t="n">
-        <v>7758.700195</v>
+        <v>7807.779785</v>
       </c>
       <c r="I83" t="n">
-        <v>27225.183594</v>
+        <v>27350.091797</v>
       </c>
       <c r="J83" t="n">
-        <v>51122.460938</v>
+        <v>51618.488281</v>
       </c>
       <c r="K83" t="n">
-        <v>4157.899902</v>
+        <v>4210.899902</v>
       </c>
       <c r="L83" t="n">
-        <v>90.800003</v>
+        <v>91.480003</v>
       </c>
       <c r="M83" t="n">
-        <v>103.290001</v>
+        <v>104.099998</v>
       </c>
       <c r="N83" t="n">
-        <v>1287.75</v>
+        <v>1274.5</v>
       </c>
       <c r="O83" t="n">
-        <v>500.5</v>
+        <v>472.5</v>
       </c>
       <c r="P83" t="n">
-        <v>10.963276</v>
+        <v>11.985836</v>
       </c>
       <c r="Q83" t="n">
-        <v>10.59322</v>
+        <v>11.56019</v>
       </c>
       <c r="R83" t="n">
-        <v>19.476454</v>
+        <v>23.997135</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.94917</v>
+        <v>-1.826225</v>
       </c>
       <c r="T83" t="n">
-        <v>-3.897822</v>
+        <v>-4.203424</v>
       </c>
       <c r="U83" t="n">
-        <v>-4.886617</v>
+        <v>-5.41407</v>
       </c>
       <c r="V83" t="n">
-        <v>1.400504</v>
+        <v>2.041939</v>
       </c>
       <c r="W83" t="n">
-        <v>1.35558</v>
+        <v>1.820595</v>
       </c>
       <c r="X83" t="n">
-        <v>0.425117</v>
+        <v>1.399514</v>
       </c>
       <c r="Y83" t="n">
-        <v>-0.6879</v>
+        <v>0.578014</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.420266</v>
+        <v>1.172313</v>
       </c>
       <c r="AA83" t="n">
-        <v>-0.231815</v>
+        <v>0.550565</v>
       </c>
       <c r="AB83" t="n">
-        <v>-0.406032</v>
+        <v>-1.430781</v>
       </c>
       <c r="AC83" t="n">
-        <v>-0.049925</v>
+        <v>-5.641538</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>
@@ -24868,18 +24876,20 @@
       <c r="AE83" t="n">
         <v>0.050788</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
+      <c r="AF83" t="n">
+        <v>0.050788</v>
+      </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="n">
-        <v>5.0119</v>
-      </c>
+      <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="n">
-        <v>5.0113</v>
-      </c>
-      <c r="AM83" t="inlineStr"/>
+        <v>4.9892</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>4.9886</v>
+      </c>
       <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="inlineStr"/>
       <c r="AP83" t="inlineStr"/>
@@ -24890,10 +24900,10 @@
       <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr"/>
       <c r="AW83" t="n">
-        <v>-3.261982</v>
+        <v>-3.700129</v>
       </c>
       <c r="AX83" t="n">
-        <v>-3.262359</v>
+        <v>-3.700558</v>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr"/>
@@ -24901,9 +24911,11 @@
       <c r="BB83" t="inlineStr"/>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
-      <c r="BE83" t="inlineStr"/>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>-0.000457</v>
       </c>
       <c r="BG83" t="n">
         <v>-0.000457</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -25197,88 +25197,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>208473.4375</v>
+        <v>209067</v>
       </c>
       <c r="C83" t="n">
-        <v>205.149994</v>
+        <v>203.080002</v>
       </c>
       <c r="D83" t="n">
-        <v>138.770004</v>
+        <v>134.389999</v>
       </c>
       <c r="E83" t="n">
-        <v>439.23999</v>
+        <v>440.350006</v>
       </c>
       <c r="F83" t="n">
-        <v>4.9872</v>
+        <v>4.9772</v>
       </c>
       <c r="G83" t="n">
-        <v>5.5779</v>
+        <v>5.5828</v>
       </c>
       <c r="H83" t="n">
-        <v>7812.879883</v>
+        <v>7811.540039</v>
       </c>
       <c r="I83" t="n">
-        <v>27376.107422</v>
+        <v>27366.169922</v>
       </c>
       <c r="J83" t="n">
-        <v>51627.800781</v>
+        <v>51654.949219</v>
       </c>
       <c r="K83" t="n">
-        <v>4214.100098</v>
+        <v>4216.299805</v>
       </c>
       <c r="L83" t="n">
-        <v>91.199997</v>
+        <v>91.849998</v>
       </c>
       <c r="M83" t="n">
-        <v>103.879997</v>
+        <v>104.720001</v>
       </c>
       <c r="N83" t="n">
-        <v>1273</v>
+        <v>1292</v>
       </c>
       <c r="O83" t="n">
-        <v>470.25</v>
+        <v>479.75</v>
       </c>
       <c r="P83" t="n">
-        <v>11.877985</v>
+        <v>12.196522</v>
       </c>
       <c r="Q83" t="n">
-        <v>11.446106</v>
+        <v>10.321599</v>
       </c>
       <c r="R83" t="n">
-        <v>23.979276</v>
+        <v>20.066112</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.817289</v>
+        <v>-1.569168</v>
       </c>
       <c r="T83" t="n">
-        <v>-4.145768</v>
+        <v>-4.337964</v>
       </c>
       <c r="U83" t="n">
-        <v>-5.398809</v>
+        <v>-5.315706</v>
       </c>
       <c r="V83" t="n">
-        <v>2.108593</v>
+        <v>2.091082</v>
       </c>
       <c r="W83" t="n">
-        <v>1.917448</v>
+        <v>1.880452</v>
       </c>
       <c r="X83" t="n">
-        <v>1.417808</v>
+        <v>1.471138</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.654451</v>
+        <v>0.706991</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.86264</v>
+        <v>1.581509</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.338065</v>
+        <v>1.149428</v>
       </c>
       <c r="AB83" t="n">
-        <v>-1.54679</v>
+        <v>-0.07734000000000001</v>
       </c>
       <c r="AC83" t="n">
-        <v>-6.090864</v>
+        <v>-4.193709</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5308,10 +5308,10 @@
         <v>7.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.024483</v>
+        <v>0.024544</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
@@ -5685,10 +5685,10 @@
         <v>0</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.004773</v>
+        <v>0.004712</v>
       </c>
       <c r="BI24" t="n">
-        <v>0.004773</v>
+        <v>0.004712</v>
       </c>
       <c r="BJ24" t="n">
         <v>0.03</v>
@@ -25209,34 +25209,34 @@
         <v>439.25</v>
       </c>
       <c r="F83" t="n">
-        <v>4.9918</v>
+        <v>4.9863</v>
       </c>
       <c r="G83" t="n">
-        <v>5.5828</v>
+        <v>5.5628</v>
       </c>
       <c r="H83" t="n">
-        <v>7811.540039</v>
+        <v>7801.430176</v>
       </c>
       <c r="I83" t="n">
-        <v>27366.169922</v>
+        <v>27238.013672</v>
       </c>
       <c r="J83" t="n">
-        <v>51654.949219</v>
+        <v>51815.429688</v>
       </c>
       <c r="K83" t="n">
-        <v>4216.299805</v>
+        <v>4188.399902</v>
       </c>
       <c r="L83" t="n">
-        <v>91.849998</v>
+        <v>93.55999799999999</v>
       </c>
       <c r="M83" t="n">
-        <v>104.720001</v>
+        <v>106.470001</v>
       </c>
       <c r="N83" t="n">
-        <v>1292</v>
+        <v>1288.25</v>
       </c>
       <c r="O83" t="n">
-        <v>479.75</v>
+        <v>483.5</v>
       </c>
       <c r="P83" t="n">
         <v>12.196522</v>
@@ -25251,34 +25251,34 @@
         <v>-1.815051</v>
       </c>
       <c r="T83" t="n">
-        <v>-4.057355</v>
+        <v>-4.163062</v>
       </c>
       <c r="U83" t="n">
-        <v>-5.315706</v>
+        <v>-5.654905</v>
       </c>
       <c r="V83" t="n">
-        <v>2.091082</v>
+        <v>1.958954</v>
       </c>
       <c r="W83" t="n">
-        <v>1.880452</v>
+        <v>1.403344</v>
       </c>
       <c r="X83" t="n">
-        <v>1.471138</v>
+        <v>1.786387</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.706991</v>
+        <v>0.040598</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.581509</v>
+        <v>3.472682</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.149428</v>
+        <v>2.839759</v>
       </c>
       <c r="AB83" t="n">
-        <v>-0.07734000000000001</v>
+        <v>-0.367363</v>
       </c>
       <c r="AC83" t="n">
-        <v>-4.193709</v>
+        <v>-3.444833</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -25215,22 +25215,22 @@
         <v>5.5628</v>
       </c>
       <c r="H83" t="n">
-        <v>7801.430176</v>
+        <v>7805.220215</v>
       </c>
       <c r="I83" t="n">
-        <v>27238.013672</v>
+        <v>27254.84375</v>
       </c>
       <c r="J83" t="n">
-        <v>51815.429688</v>
+        <v>51821.851562</v>
       </c>
       <c r="K83" t="n">
-        <v>4188.399902</v>
+        <v>4192</v>
       </c>
       <c r="L83" t="n">
-        <v>93.55999799999999</v>
+        <v>93.540001</v>
       </c>
       <c r="M83" t="n">
-        <v>106.470001</v>
+        <v>106.489998</v>
       </c>
       <c r="N83" t="n">
         <v>1288.25</v>
@@ -25257,22 +25257,22 @@
         <v>-5.654905</v>
       </c>
       <c r="V83" t="n">
-        <v>1.958954</v>
+        <v>2.008487</v>
       </c>
       <c r="W83" t="n">
-        <v>1.403344</v>
+        <v>1.466</v>
       </c>
       <c r="X83" t="n">
-        <v>1.786387</v>
+        <v>1.799002</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.040598</v>
+        <v>0.126587</v>
       </c>
       <c r="Z83" t="n">
-        <v>3.472682</v>
+        <v>3.450567</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.839759</v>
+        <v>2.859074</v>
       </c>
       <c r="AB83" t="n">
         <v>-0.367363</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -25197,88 +25197,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>204498.546875</v>
+        <v>204599.5</v>
       </c>
       <c r="C83" t="n">
-        <v>201.429993</v>
+        <v>201.509995</v>
       </c>
       <c r="D83" t="n">
-        <v>131.199997</v>
+        <v>130.940002</v>
       </c>
       <c r="E83" t="n">
-        <v>441.929993</v>
+        <v>441.399994</v>
       </c>
       <c r="F83" t="n">
-        <v>5.0395</v>
+        <v>5.0385</v>
       </c>
       <c r="G83" t="n">
-        <v>5.6045</v>
+        <v>5.607</v>
       </c>
       <c r="H83" t="n">
-        <v>7748.819824</v>
+        <v>7748.359863</v>
       </c>
       <c r="I83" t="n">
-        <v>26954.634766</v>
+        <v>26941.662109</v>
       </c>
       <c r="J83" t="n">
-        <v>51627.679688</v>
+        <v>51619.429688</v>
       </c>
       <c r="K83" t="n">
-        <v>4118.200195</v>
+        <v>4125.299805</v>
       </c>
       <c r="L83" t="n">
-        <v>95.31999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="M83" t="n">
-        <v>105.910004</v>
+        <v>105.650002</v>
       </c>
       <c r="N83" t="n">
-        <v>1278</v>
+        <v>1278.25</v>
       </c>
       <c r="O83" t="n">
-        <v>480</v>
+        <v>479.75</v>
       </c>
       <c r="P83" t="n">
-        <v>9.744846000000001</v>
+        <v>9.799023</v>
       </c>
       <c r="Q83" t="n">
-        <v>9.425245</v>
+        <v>9.468705</v>
       </c>
       <c r="R83" t="n">
-        <v>17.216114</v>
+        <v>16.983831</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.215996</v>
+        <v>-1.334466</v>
       </c>
       <c r="T83" t="n">
-        <v>-3.14055</v>
+        <v>-3.159778</v>
       </c>
       <c r="U83" t="n">
-        <v>-4.947675</v>
+        <v>-4.905274</v>
       </c>
       <c r="V83" t="n">
-        <v>1.271375</v>
+        <v>1.265364</v>
       </c>
       <c r="W83" t="n">
-        <v>0.348364</v>
+        <v>0.300068</v>
       </c>
       <c r="X83" t="n">
-        <v>1.41757</v>
+        <v>1.401364</v>
       </c>
       <c r="Y83" t="n">
-        <v>-1.636133</v>
+        <v>-1.466558</v>
       </c>
       <c r="Z83" t="n">
-        <v>5.419157</v>
+        <v>4.987837</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.298855</v>
+        <v>2.047718</v>
       </c>
       <c r="AB83" t="n">
-        <v>-1.160093</v>
+        <v>-1.140758</v>
       </c>
       <c r="AC83" t="n">
-        <v>-4.143784</v>
+        <v>-4.193709</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -573,72 +573,72 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>bcb_sgs_selic_over</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
           <t>bcb_sgs_cdi</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_pj</t>
+        </is>
+      </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
@@ -713,22 +713,22 @@
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_selic_over</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
+        </is>
+      </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
@@ -5259,43 +5259,43 @@
         <v>0.024801</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.024801</v>
+        <v>1.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.16</v>
+        <v>97.48845</v>
       </c>
       <c r="AJ23" t="n">
-        <v>97.48845</v>
+        <v>96.53555</v>
       </c>
       <c r="AK23" t="n">
-        <v>96.53555</v>
+        <v>5.643</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="AN23" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="AO23" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="AP23" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="AS23" t="n">
         <v>22.89</v>
@@ -5551,43 +5551,43 @@
         <v>0.029256</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.029256</v>
+        <v>0.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.84</v>
+        <v>99.05624</v>
       </c>
       <c r="AJ24" t="n">
-        <v>99.05624</v>
+        <v>97.85102000000001</v>
       </c>
       <c r="AK24" t="n">
-        <v>97.85102000000001</v>
+        <v>5.6199</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="AN24" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="AO24" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="AP24" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="AS24" t="n">
         <v>23.91</v>
@@ -5629,13 +5629,13 @@
         <v>0.004455</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.004455</v>
+        <v>0.03</v>
       </c>
       <c r="BI24" t="n">
         <v>0.03</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BK24" t="n">
         <v>1.02</v>
@@ -5879,43 +5879,43 @@
         <v>0.033316</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.033316</v>
+        <v>0.73</v>
       </c>
       <c r="AG25" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.73</v>
       </c>
-      <c r="AH25" t="n">
-        <v>0.87</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0.73</v>
+        <v>99.38482</v>
       </c>
       <c r="AJ25" t="n">
-        <v>99.38482</v>
+        <v>99.31835</v>
       </c>
       <c r="AK25" t="n">
-        <v>99.31835</v>
+        <v>5.5805</v>
       </c>
       <c r="AL25" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="AM25" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="AN25" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="AO25" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="AP25" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="AS25" t="n">
         <v>24.21</v>
@@ -5957,13 +5957,13 @@
         <v>0.00406</v>
       </c>
       <c r="BH25" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="BI25" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="BK25" t="n">
         <v>0.3</v>
@@ -6203,43 +6203,43 @@
         <v>0.034749</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.034749</v>
+        <v>0.54</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.67</v>
+        <v>97.4208</v>
       </c>
       <c r="AJ26" t="n">
-        <v>97.4208</v>
+        <v>91.68112000000001</v>
       </c>
       <c r="AK26" t="n">
-        <v>91.68112000000001</v>
+        <v>5.3574</v>
       </c>
       <c r="AL26" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="AM26" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="AN26" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="AO26" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="AP26" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="AS26" t="n">
         <v>25.23</v>
@@ -6281,13 +6281,13 @@
         <v>0.001433</v>
       </c>
       <c r="BH26" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="BI26" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="BK26" t="n">
         <v>1.02</v>
@@ -6519,43 +6519,43 @@
         <v>0.039598</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.039598</v>
+        <v>1.01</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>98.49135</v>
       </c>
       <c r="AJ27" t="n">
-        <v>98.49135</v>
+        <v>95.64317</v>
       </c>
       <c r="AK27" t="n">
-        <v>95.64317</v>
+        <v>5.1394</v>
       </c>
       <c r="AL27" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="AM27" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="AN27" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="AO27" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="AP27" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AS27" t="n">
         <v>25.63</v>
@@ -6597,13 +6597,13 @@
         <v>0.004849</v>
       </c>
       <c r="BH27" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="BI27" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-0.02</v>
+        <v>0.12</v>
       </c>
       <c r="BK27" t="n">
         <v>0.4</v>
@@ -6839,43 +6839,43 @@
         <v>0.041954</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.041954</v>
+        <v>1.62</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.71</v>
+        <v>99.56176000000001</v>
       </c>
       <c r="AJ28" t="n">
-        <v>99.56176000000001</v>
+        <v>104.54148</v>
       </c>
       <c r="AK28" t="n">
-        <v>104.54148</v>
+        <v>4.7378</v>
       </c>
       <c r="AL28" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="AM28" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="AN28" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="AO28" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="AP28" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="AS28" t="n">
         <v>26.54</v>
@@ -6917,13 +6917,13 @@
         <v>0.002356</v>
       </c>
       <c r="BH28" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="BI28" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK28" t="n">
         <v>0.91</v>
@@ -7155,43 +7155,43 @@
         <v>0.043739</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.043739</v>
+        <v>1.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.04</v>
+        <v>99.45421</v>
       </c>
       <c r="AJ29" t="n">
-        <v>99.45421</v>
+        <v>100.24567</v>
       </c>
       <c r="AK29" t="n">
-        <v>100.24567</v>
+        <v>4.9191</v>
       </c>
       <c r="AL29" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="AM29" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="AN29" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="AO29" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="AP29" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="AS29" t="n">
         <v>27.46</v>
@@ -7233,13 +7233,13 @@
         <v>0.001785</v>
       </c>
       <c r="BH29" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="BI29" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="BK29" t="n">
         <v>0.92</v>
@@ -7483,43 +7483,43 @@
         <v>0.046796</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.046796</v>
+        <v>0.47</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.45</v>
+        <v>99.64297000000001</v>
       </c>
       <c r="AJ30" t="n">
-        <v>99.64297000000001</v>
+        <v>99.74066999999999</v>
       </c>
       <c r="AK30" t="n">
-        <v>99.74066999999999</v>
+        <v>4.7289</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="AN30" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="AO30" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="AP30" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="AS30" t="n">
         <v>27.42</v>
@@ -7561,13 +7561,13 @@
         <v>0.003057</v>
       </c>
       <c r="BH30" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BK30" t="n">
         <v>-0.04</v>
@@ -7807,43 +7807,43 @@
         <v>0.048116</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.048116</v>
+        <v>0.67</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.62</v>
+        <v>99.49797</v>
       </c>
       <c r="AJ31" t="n">
-        <v>99.49797</v>
+        <v>99.30903000000001</v>
       </c>
       <c r="AK31" t="n">
-        <v>99.30903000000001</v>
+        <v>5.238</v>
       </c>
       <c r="AL31" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="AM31" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="AN31" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="AO31" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="AP31" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="AQ31" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="AS31" t="n">
         <v>27.88</v>
@@ -7885,13 +7885,13 @@
         <v>0.00132</v>
       </c>
       <c r="BH31" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="BI31" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BK31" t="n">
         <v>0.46</v>
@@ -8131,43 +8131,43 @@
         <v>0.049037</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.049037</v>
+        <v>-0.68</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.6</v>
+        <v>101.41926</v>
       </c>
       <c r="AJ32" t="n">
-        <v>101.41926</v>
+        <v>103.96099</v>
       </c>
       <c r="AK32" t="n">
-        <v>103.96099</v>
+        <v>5.1884</v>
       </c>
       <c r="AL32" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="AM32" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="AN32" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="AO32" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="AP32" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="AS32" t="n">
         <v>29.24</v>
@@ -8209,13 +8209,13 @@
         <v>0.0009210000000000001</v>
       </c>
       <c r="BH32" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BI32" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="BK32" t="n">
         <v>1.36</v>
@@ -8459,43 +8459,43 @@
         <v>0.05056</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.05056</v>
+        <v>-0.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.31</v>
+        <v>101.10264</v>
       </c>
       <c r="AJ33" t="n">
-        <v>101.10264</v>
+        <v>104.50684</v>
       </c>
       <c r="AK33" t="n">
-        <v>104.50684</v>
+        <v>5.179</v>
       </c>
       <c r="AL33" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="AM33" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="AN33" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="AO33" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="AP33" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="AS33" t="n">
         <v>28.6</v>
@@ -8537,13 +8537,13 @@
         <v>0.001523</v>
       </c>
       <c r="BH33" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK33" t="n">
         <v>-0.64</v>
@@ -8783,43 +8783,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.050788</v>
+        <v>-0.29</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.29</v>
+        <v>-0.95</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.32</v>
+        <v>101.1562</v>
       </c>
       <c r="AJ34" t="n">
-        <v>101.1562</v>
+        <v>101.17889</v>
       </c>
       <c r="AK34" t="n">
-        <v>101.17889</v>
+        <v>5.4066</v>
       </c>
       <c r="AL34" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="AM34" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="AN34" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="AO34" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="AP34" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS34" t="n">
         <v>28.57</v>
@@ -8867,13 +8867,13 @@
         <v>0.000228</v>
       </c>
       <c r="BH34" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="BI34" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BJ34" t="n">
         <v>0.02</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>0.03</v>
       </c>
       <c r="BK34" t="n">
         <v>-0.03</v>
@@ -9117,43 +9117,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.050788</v>
+        <v>0.59</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.47</v>
+        <v>101.43769</v>
       </c>
       <c r="AJ35" t="n">
-        <v>101.43769</v>
+        <v>100.08276</v>
       </c>
       <c r="AK35" t="n">
-        <v>100.08276</v>
+        <v>5.257</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="AN35" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="AO35" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="AP35" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="AS35" t="n">
         <v>29.68</v>
@@ -9201,13 +9201,13 @@
         <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI35" t="n">
         <v>0.12</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="BK35" t="n">
         <v>1.11</v>
@@ -9447,43 +9447,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.050788</v>
+        <v>0.41</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.38</v>
+        <v>100.71743</v>
       </c>
       <c r="AJ36" t="n">
-        <v>100.71743</v>
+        <v>99.14758</v>
       </c>
       <c r="AK36" t="n">
-        <v>99.14758</v>
+        <v>5.2941</v>
       </c>
       <c r="AL36" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="AM36" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="AN36" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="AO36" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="AP36" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="AS36" t="n">
         <v>30.52</v>
@@ -9531,13 +9531,13 @@
         <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BJ36" t="n">
         <v>0.03</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>0.04</v>
       </c>
       <c r="BK36" t="n">
         <v>0.84</v>
@@ -9769,43 +9769,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.050788</v>
+        <v>0.62</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.6899999999999999</v>
+        <v>100.59088</v>
       </c>
       <c r="AJ37" t="n">
-        <v>100.59088</v>
+        <v>99.96181</v>
       </c>
       <c r="AK37" t="n">
-        <v>99.96181</v>
+        <v>5.2177</v>
       </c>
       <c r="AL37" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="AN37" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="AO37" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="AP37" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="AS37" t="n">
         <v>29.64</v>
@@ -9853,13 +9853,13 @@
         <v>-0</v>
       </c>
       <c r="BH37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BK37" t="n">
         <v>-0.88</v>
@@ -10095,43 +10095,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.050788</v>
+        <v>0.53</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.46</v>
+        <v>100.10409</v>
       </c>
       <c r="AJ38" t="n">
-        <v>100.10409</v>
+        <v>95.10406999999999</v>
       </c>
       <c r="AK38" t="n">
-        <v>95.10406999999999</v>
+        <v>5.0993</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="AM38" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="AN38" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="AO38" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="AP38" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="AS38" t="n">
         <v>30.54</v>
@@ -10179,13 +10179,13 @@
         <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BI38" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BJ38" t="n">
         <v>0.17</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>0.14</v>
       </c>
       <c r="BK38" t="n">
         <v>0.9</v>
@@ -10429,43 +10429,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.050788</v>
+        <v>0.84</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.84</v>
+        <v>-0.06</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.77</v>
+        <v>103.08488</v>
       </c>
       <c r="AJ39" t="n">
-        <v>103.08488</v>
+        <v>98.64819</v>
       </c>
       <c r="AK39" t="n">
-        <v>98.64819</v>
+        <v>5.2078</v>
       </c>
       <c r="AL39" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="AM39" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="AN39" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="AO39" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="AP39" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="AS39" t="n">
         <v>30.48</v>
@@ -10513,13 +10513,13 @@
         <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI39" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="BK39" t="n">
         <v>-0.06</v>
@@ -10763,43 +10763,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.050788</v>
+        <v>0.71</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.64</v>
+        <v>103.09631</v>
       </c>
       <c r="AJ40" t="n">
-        <v>103.09631</v>
+        <v>110.61458</v>
       </c>
       <c r="AK40" t="n">
-        <v>110.61458</v>
+        <v>5.0804</v>
       </c>
       <c r="AL40" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="AN40" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="AO40" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="AP40" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="AS40" t="n">
         <v>30.99</v>
@@ -10847,13 +10847,13 @@
         <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BI40" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BK40" t="n">
         <v>0.51</v>
@@ -11097,43 +11097,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.050788</v>
+        <v>0.61</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.53</v>
+        <v>103.92975</v>
       </c>
       <c r="AJ41" t="n">
-        <v>103.92975</v>
+        <v>104.04532</v>
       </c>
       <c r="AK41" t="n">
-        <v>104.04532</v>
+        <v>5.0007</v>
       </c>
       <c r="AL41" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="AN41" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="AO41" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="AP41" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="AS41" t="n">
         <v>31.62</v>
@@ -11181,13 +11181,13 @@
         <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="BK41" t="n">
         <v>0.63</v>
@@ -11419,43 +11419,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.050788</v>
+        <v>0.23</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.23</v>
+        <v>-1.84</v>
       </c>
       <c r="AH42" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.36</v>
+        <v>102.42356</v>
       </c>
       <c r="AJ42" t="n">
-        <v>102.42356</v>
+        <v>102.71431</v>
       </c>
       <c r="AK42" t="n">
-        <v>102.71431</v>
+        <v>5.0959</v>
       </c>
       <c r="AL42" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="AM42" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="AN42" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="AO42" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="AP42" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="AS42" t="n">
         <v>31.63</v>
@@ -11503,13 +11503,13 @@
         <v>-0</v>
       </c>
       <c r="BH42" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="BK42" t="n">
         <v>0.01</v>
@@ -11749,43 +11749,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.050788</v>
+        <v>-0.08</v>
       </c>
       <c r="AG43" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="AH43" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.1</v>
+        <v>102.38761</v>
       </c>
       <c r="AJ43" t="n">
-        <v>102.38761</v>
+        <v>102.27877</v>
       </c>
       <c r="AK43" t="n">
-        <v>102.27877</v>
+        <v>4.8192</v>
       </c>
       <c r="AL43" t="n">
-        <v>4.8192</v>
+        <v>4.8186</v>
       </c>
       <c r="AM43" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="AN43" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="AO43" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="AP43" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="AS43" t="n">
         <v>30.85</v>
@@ -11833,13 +11833,13 @@
         <v>0</v>
       </c>
       <c r="BH43" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="BI43" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BK43" t="n">
         <v>-0.78</v>
@@ -12075,43 +12075,43 @@
         <v>0.050788</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.050788</v>
+        <v>0.12</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.12</v>
+        <v>-0.72</v>
       </c>
       <c r="AH44" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="AI44" t="n">
-        <v>-0.09</v>
+        <v>102.90097</v>
       </c>
       <c r="AJ44" t="n">
-        <v>102.90097</v>
+        <v>105.3498</v>
       </c>
       <c r="AK44" t="n">
-        <v>105.3498</v>
+        <v>4.7415</v>
       </c>
       <c r="AL44" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="AM44" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="AN44" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="AO44" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="AP44" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="AS44" t="n">
         <v>30.43</v>
@@ -12159,13 +12159,13 @@
         <v>0</v>
       </c>
       <c r="BH44" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="BK44" t="n">
         <v>-0.42</v>
@@ -12401,43 +12401,43 @@
         <v>0.049189</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.049189</v>
+        <v>0.23</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.2</v>
+        <v>102.49883</v>
       </c>
       <c r="AJ45" t="n">
-        <v>102.49883</v>
+        <v>106.05633</v>
       </c>
       <c r="AK45" t="n">
-        <v>106.05633</v>
+        <v>4.9219</v>
       </c>
       <c r="AL45" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="AM45" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="AN45" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="AO45" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="AP45" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="AS45" t="n">
         <v>29.92</v>
@@ -12485,13 +12485,13 @@
         <v>-0.001599</v>
       </c>
       <c r="BH45" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="BI45" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="BK45" t="n">
         <v>-0.51</v>
@@ -12731,43 +12731,43 @@
         <v>0.048422</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.048422</v>
+        <v>0.26</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.11</v>
+        <v>102.5197</v>
       </c>
       <c r="AJ46" t="n">
-        <v>102.5197</v>
+        <v>101.75432</v>
       </c>
       <c r="AK46" t="n">
-        <v>101.75432</v>
+        <v>5.0076</v>
       </c>
       <c r="AL46" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="AM46" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="AN46" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="AO46" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="AP46" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="AS46" t="n">
         <v>29.66</v>
@@ -12815,13 +12815,13 @@
         <v>-0.000768</v>
       </c>
       <c r="BH46" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BI46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="BK46" t="n">
         <v>-0.26</v>
@@ -13057,43 +13057,43 @@
         <v>0.047279</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.047279</v>
+        <v>0.24</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.12</v>
+        <v>102.8499</v>
       </c>
       <c r="AJ47" t="n">
-        <v>102.8499</v>
+        <v>101.94034</v>
       </c>
       <c r="AK47" t="n">
-        <v>101.94034</v>
+        <v>5.0575</v>
       </c>
       <c r="AL47" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="AM47" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="AN47" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="AO47" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="AP47" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="AS47" t="n">
         <v>29.24</v>
@@ -13141,13 +13141,13 @@
         <v>-0.001143</v>
       </c>
       <c r="BH47" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="BK47" t="n">
         <v>-0.42</v>
@@ -13383,43 +13383,43 @@
         <v>0.045601</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.045601</v>
+        <v>0.28</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.1</v>
+        <v>103.60561</v>
       </c>
       <c r="AJ48" t="n">
-        <v>103.60561</v>
+        <v>101.67978</v>
       </c>
       <c r="AK48" t="n">
-        <v>101.67978</v>
+        <v>4.9355</v>
       </c>
       <c r="AL48" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="AM48" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="AN48" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="AO48" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="AP48" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AS48" t="n">
         <v>29.01</v>
@@ -13467,13 +13467,13 @@
         <v>-0.001678</v>
       </c>
       <c r="BH48" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="BI48" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="BK48" t="n">
         <v>-0.23</v>
@@ -13709,43 +13709,43 @@
         <v>0.044537</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.044537</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.55</v>
+        <v>104.8968</v>
       </c>
       <c r="AJ49" t="n">
-        <v>104.8968</v>
+        <v>101.67778</v>
       </c>
       <c r="AK49" t="n">
-        <v>101.67778</v>
+        <v>4.8413</v>
       </c>
       <c r="AL49" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="AM49" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="AN49" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="AO49" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="AP49" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AS49" t="n">
         <v>28.14</v>
@@ -13793,13 +13793,13 @@
         <v>-0.001064</v>
       </c>
       <c r="BH49" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="BI49" t="n">
-        <v>-0.24</v>
+        <v>-0.4</v>
       </c>
       <c r="BJ49" t="n">
-        <v>-0.4</v>
+        <v>-0.13</v>
       </c>
       <c r="BK49" t="n">
         <v>-0.87</v>
@@ -14039,43 +14039,43 @@
         <v>0.043739</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.043739</v>
+        <v>0.42</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.57</v>
+        <v>104.46088</v>
       </c>
       <c r="AJ50" t="n">
-        <v>104.46088</v>
+        <v>99.30432999999999</v>
       </c>
       <c r="AK50" t="n">
-        <v>99.30432999999999</v>
+        <v>4.9535</v>
       </c>
       <c r="AL50" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="AM50" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="AN50" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="AO50" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="AP50" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="AS50" t="n">
         <v>28</v>
@@ -14123,13 +14123,13 @@
         <v>-0.000798</v>
       </c>
       <c r="BH50" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="BI50" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
       <c r="BK50" t="n">
         <v>-0.14</v>
@@ -14365,43 +14365,43 @@
         <v>0.041957</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.041957</v>
+        <v>0.83</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="AH51" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.8100000000000001</v>
+        <v>104.65783</v>
       </c>
       <c r="AJ51" t="n">
-        <v>104.65783</v>
+        <v>102.15308</v>
       </c>
       <c r="AK51" t="n">
-        <v>102.15308</v>
+        <v>4.9833</v>
       </c>
       <c r="AL51" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="AM51" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="AN51" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="AO51" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="AP51" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="AQ51" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AS51" t="n">
         <v>27.85</v>
@@ -14449,13 +14449,13 @@
         <v>-0.001782</v>
       </c>
       <c r="BH51" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="BI51" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>0</v>
-      </c>
-      <c r="BJ51" t="n">
-        <v>-0.01</v>
       </c>
       <c r="BK51" t="n">
         <v>-0.15</v>
@@ -14687,43 +14687,43 @@
         <v>0.04142</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.04142</v>
+        <v>0.16</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="AH52" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.19</v>
+        <v>104.68489</v>
       </c>
       <c r="AJ52" t="n">
-        <v>104.68489</v>
+        <v>109.56238</v>
       </c>
       <c r="AK52" t="n">
-        <v>109.56238</v>
+        <v>4.9962</v>
       </c>
       <c r="AL52" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="AM52" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="AN52" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="AO52" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="AP52" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="AS52" t="n">
         <v>28.14</v>
@@ -14771,7 +14771,7 @@
         <v>-0.000537</v>
       </c>
       <c r="BH52" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BI52" t="n">
         <v>-0.05</v>
@@ -15017,43 +15017,43 @@
         <v>0.040168</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.040168</v>
+        <v>0.38</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.37</v>
+        <v>104.62189</v>
       </c>
       <c r="AJ53" t="n">
-        <v>104.62189</v>
+        <v>109.26273</v>
       </c>
       <c r="AK53" t="n">
-        <v>109.26273</v>
+        <v>5.1718</v>
       </c>
       <c r="AL53" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="AN53" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="AO53" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="AP53" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="AQ53" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AS53" t="n">
         <v>27.86</v>
@@ -15101,13 +15101,13 @@
         <v>-0.001252</v>
       </c>
       <c r="BH53" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="BI53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BJ53" t="n">
         <v>0.04</v>
-      </c>
-      <c r="BJ53" t="n">
-        <v>0.05</v>
       </c>
       <c r="BK53" t="n">
         <v>-0.28</v>
@@ -15343,43 +15343,43 @@
         <v>0.039484</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.039484</v>
+        <v>0.46</v>
       </c>
       <c r="AG54" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.46</v>
       </c>
-      <c r="AH54" t="n">
-        <v>0.89</v>
-      </c>
       <c r="AI54" t="n">
-        <v>0.46</v>
+        <v>105.5883</v>
       </c>
       <c r="AJ54" t="n">
-        <v>105.5883</v>
+        <v>104.70903</v>
       </c>
       <c r="AK54" t="n">
-        <v>104.70903</v>
+        <v>5.2416</v>
       </c>
       <c r="AL54" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="AM54" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="AN54" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="AO54" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="AP54" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="AQ54" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="AS54" t="n">
         <v>27.75</v>
@@ -15427,13 +15427,13 @@
         <v>-0.000684</v>
       </c>
       <c r="BH54" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="BI54" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK54" t="n">
         <v>-0.11</v>
@@ -15673,43 +15673,43 @@
         <v>0.03927</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.03927</v>
+        <v>0.21</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.25</v>
+        <v>106.56647</v>
       </c>
       <c r="AJ55" t="n">
-        <v>106.56647</v>
+        <v>105.86342</v>
       </c>
       <c r="AK55" t="n">
-        <v>105.86342</v>
+        <v>5.5589</v>
       </c>
       <c r="AL55" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="AM55" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="AN55" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="AO55" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="AP55" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="AS55" t="n">
         <v>27.81</v>
@@ -15757,13 +15757,13 @@
         <v>-0.000214</v>
       </c>
       <c r="BH55" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="BI55" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="BK55" t="n">
         <v>0.06</v>
@@ -16003,43 +16003,43 @@
         <v>0.03927</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.03927</v>
+        <v>0.38</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.26</v>
+        <v>107.07017</v>
       </c>
       <c r="AJ56" t="n">
-        <v>107.07017</v>
+        <v>111.51644</v>
       </c>
       <c r="AK56" t="n">
-        <v>111.51644</v>
+        <v>5.6621</v>
       </c>
       <c r="AL56" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="AM56" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="AN56" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="AO56" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="AP56" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="AQ56" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="AS56" t="n">
         <v>27.74</v>
@@ -16087,13 +16087,13 @@
         <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BI56" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="BJ56" t="n">
-        <v>-0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK56" t="n">
         <v>-0.07000000000000001</v>
@@ -16333,43 +16333,43 @@
         <v>0.03927</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.03927</v>
+        <v>-0.02</v>
       </c>
       <c r="AG57" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="AI57" t="n">
-        <v>-0.14</v>
+        <v>107.19578</v>
       </c>
       <c r="AJ57" t="n">
-        <v>107.19578</v>
+        <v>110.06495</v>
       </c>
       <c r="AK57" t="n">
-        <v>110.06495</v>
+        <v>5.6562</v>
       </c>
       <c r="AL57" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="AN57" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="AO57" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="AP57" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="AR57" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AS57" t="n">
         <v>27.59</v>
@@ -16417,13 +16417,13 @@
         <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI57" t="n">
         <v>0.03</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BK57" t="n">
         <v>-0.15</v>
@@ -16663,43 +16663,43 @@
         <v>0.039612</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.039612</v>
+        <v>0.44</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.48</v>
+        <v>108.05141</v>
       </c>
       <c r="AJ58" t="n">
-        <v>108.05141</v>
+        <v>107.07576</v>
       </c>
       <c r="AK58" t="n">
-        <v>107.07576</v>
+        <v>5.4481</v>
       </c>
       <c r="AL58" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="AM58" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="AN58" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="AO58" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="AP58" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="AQ58" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="AS58" t="n">
         <v>27.49</v>
@@ -16747,7 +16747,7 @@
         <v>0.000342</v>
       </c>
       <c r="BH58" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BI58" t="n">
         <v>0.01</v>
@@ -16993,43 +16993,43 @@
         <v>0.040168</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.040168</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.61</v>
+        <v>108.26621</v>
       </c>
       <c r="AJ59" t="n">
-        <v>108.26621</v>
+        <v>109.19299</v>
       </c>
       <c r="AK59" t="n">
-        <v>109.19299</v>
+        <v>5.7779</v>
       </c>
       <c r="AL59" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="AM59" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="AN59" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="AO59" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="AP59" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="AQ59" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR59" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="AS59" t="n">
         <v>27.94</v>
@@ -17077,7 +17077,7 @@
         <v>0.000556</v>
       </c>
       <c r="BH59" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BI59" t="n">
         <v>-0.04</v>
@@ -17315,43 +17315,43 @@
         <v>0.04158</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.04158</v>
+        <v>0.39</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.33</v>
+        <v>108.02232</v>
       </c>
       <c r="AJ60" t="n">
-        <v>108.02232</v>
+        <v>105.49378</v>
       </c>
       <c r="AK60" t="n">
-        <v>105.49378</v>
+        <v>6.0535</v>
       </c>
       <c r="AL60" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="AM60" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="AN60" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="AO60" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="AP60" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="AQ60" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS60" t="n">
         <v>28.45</v>
@@ -17399,13 +17399,13 @@
         <v>0.001412</v>
       </c>
       <c r="BH60" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="BI60" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ60" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="BK60" t="n">
         <v>0.51</v>
@@ -17645,43 +17645,43 @@
         <v>0.044158</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.044158</v>
+        <v>0.52</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.48</v>
+        <v>107.37891</v>
       </c>
       <c r="AJ61" t="n">
-        <v>107.37891</v>
+        <v>104.15073</v>
       </c>
       <c r="AK61" t="n">
-        <v>104.15073</v>
+        <v>6.1923</v>
       </c>
       <c r="AL61" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="AM61" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="AN61" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="AO61" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="AP61" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="AQ61" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="AS61" t="n">
         <v>28.5</v>
@@ -17729,13 +17729,13 @@
         <v>0.002578</v>
       </c>
       <c r="BH61" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="BI61" t="n">
-        <v>-0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="BJ61" t="n">
-        <v>-0.29</v>
+        <v>-0.12</v>
       </c>
       <c r="BK61" t="n">
         <v>0.05</v>
@@ -17975,43 +17975,43 @@
         <v>0.045833</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.045833</v>
+        <v>0.16</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>108.05509</v>
       </c>
       <c r="AJ62" t="n">
-        <v>108.05509</v>
+        <v>102.6229</v>
       </c>
       <c r="AK62" t="n">
-        <v>102.6229</v>
+        <v>5.8301</v>
       </c>
       <c r="AL62" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="AN62" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="AO62" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="AP62" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="AQ62" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="AR62" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="AS62" t="n">
         <v>29.88</v>
@@ -18059,13 +18059,13 @@
         <v>0.001675</v>
       </c>
       <c r="BH62" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="BI62" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BJ62" t="n">
         <v>0.26</v>
-      </c>
-      <c r="BJ62" t="n">
-        <v>0.22</v>
       </c>
       <c r="BK62" t="n">
         <v>1.38</v>
@@ -18309,43 +18309,43 @@
         <v>0.049037</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.049037</v>
+        <v>1.31</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.48</v>
+        <v>108.57481</v>
       </c>
       <c r="AJ63" t="n">
-        <v>108.57481</v>
+        <v>106.79048</v>
       </c>
       <c r="AK63" t="n">
-        <v>106.79048</v>
+        <v>5.8488</v>
       </c>
       <c r="AL63" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="AM63" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="AN63" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="AO63" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="AP63" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="AQ63" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="AS63" t="n">
         <v>30.53</v>
@@ -18393,13 +18393,13 @@
         <v>0.003204</v>
       </c>
       <c r="BH63" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BJ63" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="BJ63" t="n">
-        <v>0.09</v>
       </c>
       <c r="BK63" t="n">
         <v>0.65</v>
@@ -18639,43 +18639,43 @@
         <v>0.050508</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.050508</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="AH64" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.51</v>
+        <v>110.03087</v>
       </c>
       <c r="AJ64" t="n">
-        <v>110.03087</v>
+        <v>113.99468</v>
       </c>
       <c r="AK64" t="n">
-        <v>113.99468</v>
+        <v>5.7422</v>
       </c>
       <c r="AL64" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="AM64" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="AN64" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="AO64" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="AP64" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="AQ64" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="AS64" t="n">
         <v>31.34</v>
@@ -18723,13 +18723,13 @@
         <v>0.001471</v>
       </c>
       <c r="BH64" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="BI64" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ64" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK64" t="n">
         <v>0.8100000000000001</v>
@@ -18965,43 +18965,43 @@
         <v>0.052531</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.052531</v>
+        <v>0.43</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="AI65" t="n">
-        <v>0.48</v>
+        <v>109.51799</v>
       </c>
       <c r="AJ65" t="n">
-        <v>109.51799</v>
+        <v>112.60116</v>
       </c>
       <c r="AK65" t="n">
-        <v>112.60116</v>
+        <v>5.6608</v>
       </c>
       <c r="AL65" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="AM65" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="AN65" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="AO65" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="AP65" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="AQ65" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="AS65" t="n">
         <v>31.63</v>
@@ -19049,13 +19049,13 @@
         <v>0.002023</v>
       </c>
       <c r="BH65" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BI65" t="n">
         <v>0.23</v>
       </c>
       <c r="BJ65" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BK65" t="n">
         <v>0.29</v>
@@ -19299,43 +19299,43 @@
         <v>0.053936</v>
       </c>
       <c r="AF66" t="n">
-        <v>0.053936</v>
+        <v>0.26</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="AH66" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="AI66" t="n">
-        <v>0.35</v>
+        <v>108.88849</v>
       </c>
       <c r="AJ66" t="n">
-        <v>108.88849</v>
+        <v>108.58229</v>
       </c>
       <c r="AK66" t="n">
-        <v>108.58229</v>
+        <v>5.7087</v>
       </c>
       <c r="AL66" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="AM66" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="AN66" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="AO66" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="AP66" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="AQ66" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="AS66" t="n">
         <v>31.7</v>
@@ -19383,13 +19383,13 @@
         <v>0.001405</v>
       </c>
       <c r="BH66" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="BI66" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ66" t="n">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BK66" t="n">
         <v>0.07000000000000001</v>
@@ -19629,43 +19629,43 @@
         <v>0.054569</v>
       </c>
       <c r="AF67" t="n">
-        <v>0.054569</v>
+        <v>0.24</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="AH67" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="AI67" t="n">
-        <v>0.23</v>
+        <v>108.82565</v>
       </c>
       <c r="AJ67" t="n">
-        <v>108.82565</v>
+        <v>107.40511</v>
       </c>
       <c r="AK67" t="n">
-        <v>107.40511</v>
+        <v>5.4571</v>
       </c>
       <c r="AL67" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="AM67" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="AN67" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="AO67" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="AP67" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="AQ67" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="AS67" t="n">
         <v>31.85</v>
@@ -19713,13 +19713,13 @@
         <v>0.000633</v>
       </c>
       <c r="BH67" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="BI67" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BJ67" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BK67" t="n">
         <v>0.15</v>
@@ -19959,43 +19959,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF68" t="n">
-        <v>0.055131</v>
+        <v>0.26</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.26</v>
+        <v>-0.77</v>
       </c>
       <c r="AH68" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.21</v>
+        <v>108.60295</v>
       </c>
       <c r="AJ68" t="n">
-        <v>108.60295</v>
+        <v>113.20021</v>
       </c>
       <c r="AK68" t="n">
-        <v>113.20021</v>
+        <v>5.6021</v>
       </c>
       <c r="AL68" t="n">
-        <v>5.6021</v>
+        <v>5.6015</v>
       </c>
       <c r="AM68" t="n">
-        <v>5.6015</v>
+        <v>6733209</v>
       </c>
       <c r="AN68" t="n">
-        <v>6733209</v>
+        <v>2544400</v>
       </c>
       <c r="AO68" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="AP68" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="AQ68" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="AR68" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="AS68" t="n">
         <v>31.75</v>
@@ -20043,13 +20043,13 @@
         <v>0.000562</v>
       </c>
       <c r="BH68" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="BI68" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="BJ68" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="BK68" t="n">
         <v>-0.1</v>
@@ -20293,43 +20293,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF69" t="n">
-        <v>0.055131</v>
+        <v>-0.11</v>
       </c>
       <c r="AG69" t="n">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
       <c r="AH69" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="AI69" t="n">
-        <v>-0.21</v>
+        <v>108.84223</v>
       </c>
       <c r="AJ69" t="n">
-        <v>108.84223</v>
+        <v>110.38311</v>
       </c>
       <c r="AK69" t="n">
-        <v>110.38311</v>
+        <v>5.4264</v>
       </c>
       <c r="AL69" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="AM69" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="AN69" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="AO69" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="AP69" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="AQ69" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="AR69" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="AS69" t="n">
         <v>31.87</v>
@@ -20377,13 +20377,13 @@
         <v>0</v>
       </c>
       <c r="BH69" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="BI69" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BJ69" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="BK69" t="n">
         <v>0.12</v>
@@ -20623,43 +20623,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF70" t="n">
-        <v>0.055131</v>
+        <v>0.48</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="AH70" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.52</v>
+        <v>108.7154</v>
       </c>
       <c r="AJ70" t="n">
-        <v>108.7154</v>
+        <v>109.45662</v>
       </c>
       <c r="AK70" t="n">
-        <v>109.45662</v>
+        <v>5.3186</v>
       </c>
       <c r="AL70" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="AM70" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="AN70" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="AO70" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="AP70" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="AQ70" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="AS70" t="n">
         <v>31.47</v>
@@ -20707,13 +20707,13 @@
         <v>0</v>
       </c>
       <c r="BH70" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="BI70" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ70" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BK70" t="n">
         <v>-0.4</v>
@@ -20953,43 +20953,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF71" t="n">
-        <v>0.055131</v>
+        <v>0.09</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.09</v>
+        <v>-0.36</v>
       </c>
       <c r="AH71" t="n">
-        <v>-0.36</v>
+        <v>0.03</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.03</v>
+        <v>108.73877</v>
       </c>
       <c r="AJ71" t="n">
-        <v>108.73877</v>
+        <v>110.04186</v>
       </c>
       <c r="AK71" t="n">
-        <v>110.04186</v>
+        <v>5.3843</v>
       </c>
       <c r="AL71" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="AM71" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="AN71" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="AO71" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="AP71" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="AQ71" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="AR71" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="AS71" t="n">
         <v>32.04</v>
@@ -21037,13 +21037,13 @@
         <v>0</v>
       </c>
       <c r="BH71" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BI71" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="BJ71" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="BK71" t="n">
         <v>0.57</v>
@@ -21283,43 +21283,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF72" t="n">
-        <v>0.055131</v>
+        <v>0.18</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.03</v>
+        <v>109.25356</v>
       </c>
       <c r="AJ72" t="n">
-        <v>109.25356</v>
+        <v>106.5784</v>
       </c>
       <c r="AK72" t="n">
-        <v>106.5784</v>
+        <v>5.3338</v>
       </c>
       <c r="AL72" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="AM72" t="n">
-        <v>5.3332</v>
+        <v>7004223</v>
       </c>
       <c r="AN72" t="n">
-        <v>7004223</v>
+        <v>2616902</v>
       </c>
       <c r="AO72" t="n">
-        <v>2616902</v>
+        <v>4387321</v>
       </c>
       <c r="AP72" t="n">
-        <v>4387321</v>
+        <v>4.24</v>
       </c>
       <c r="AQ72" t="n">
-        <v>4.24</v>
+        <v>2.75</v>
       </c>
       <c r="AR72" t="n">
-        <v>2.75</v>
+        <v>5.12</v>
       </c>
       <c r="AS72" t="n">
         <v>32.2</v>
@@ -21367,13 +21367,13 @@
         <v>-0</v>
       </c>
       <c r="BH72" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="BI72" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BJ72" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="BK72" t="n">
         <v>0.16</v>
@@ -21617,43 +21617,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="AH73" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.21</v>
+        <v>109.47578</v>
       </c>
       <c r="AJ73" t="n">
-        <v>109.47578</v>
+        <v>107.19091</v>
       </c>
       <c r="AK73" t="n">
-        <v>107.19091</v>
+        <v>5.5024</v>
       </c>
       <c r="AL73" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="AM73" t="n">
-        <v>5.5018</v>
+        <v>7137252</v>
       </c>
       <c r="AN73" t="n">
-        <v>7137252</v>
+        <v>2701735</v>
       </c>
       <c r="AO73" t="n">
-        <v>2701735</v>
+        <v>4435517</v>
       </c>
       <c r="AP73" t="n">
-        <v>4435517</v>
+        <v>4.2</v>
       </c>
       <c r="AQ73" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AR73" t="n">
-        <v>2.7</v>
+        <v>5.12</v>
       </c>
       <c r="AS73" t="n">
         <v>31.87</v>
@@ -21701,13 +21701,13 @@
         <v>0</v>
       </c>
       <c r="BH73" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BI73" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ73" t="n">
         <v>0</v>
-      </c>
-      <c r="BI73" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BJ73" t="n">
-        <v>-0.05</v>
       </c>
       <c r="BK73" t="n">
         <v>-0.33</v>
@@ -21943,43 +21943,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.39</v>
+        <v>110.15169</v>
       </c>
       <c r="AJ74" t="n">
-        <v>110.15169</v>
+        <v>103.91741</v>
       </c>
       <c r="AK74" t="n">
-        <v>103.91741</v>
+        <v>5.2301</v>
       </c>
       <c r="AL74" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="AM74" t="n">
-        <v>5.2295</v>
+        <v>7130762</v>
       </c>
       <c r="AN74" t="n">
-        <v>7130762</v>
+        <v>2654220</v>
       </c>
       <c r="AO74" t="n">
-        <v>2654220</v>
+        <v>4476542</v>
       </c>
       <c r="AP74" t="n">
-        <v>4476542</v>
+        <v>4.44</v>
       </c>
       <c r="AQ74" t="n">
-        <v>4.44</v>
+        <v>2.87</v>
       </c>
       <c r="AR74" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="AS74" t="n">
         <v>32.45</v>
@@ -22027,13 +22027,13 @@
         <v>0</v>
       </c>
       <c r="BH74" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="BI74" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="BJ74" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="BK74" t="n">
         <v>0.58</v>
@@ -22273,43 +22273,43 @@
         <v>0.055131</v>
       </c>
       <c r="AF75" t="n">
-        <v>0.055131</v>
+        <v>0.7</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="AH75" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.5600000000000001</v>
+        <v>110.82485</v>
       </c>
       <c r="AJ75" t="n">
-        <v>110.82485</v>
+        <v>106.86101</v>
       </c>
       <c r="AK75" t="n">
-        <v>106.86101</v>
+        <v>5.1495</v>
       </c>
       <c r="AL75" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="AM75" t="n">
-        <v>5.1489</v>
+        <v>7157783</v>
       </c>
       <c r="AN75" t="n">
-        <v>7157783</v>
+        <v>2656484</v>
       </c>
       <c r="AO75" t="n">
-        <v>2656484</v>
+        <v>4501299</v>
       </c>
       <c r="AP75" t="n">
-        <v>4501299</v>
+        <v>4.64</v>
       </c>
       <c r="AQ75" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="AR75" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="AS75" t="n">
         <v>32.63</v>
@@ -22357,13 +22357,13 @@
         <v>0</v>
       </c>
       <c r="BH75" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BI75" t="n">
         <v>0.2</v>
       </c>
       <c r="BJ75" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BK75" t="n">
         <v>0.18</v>
@@ -22607,43 +22607,43 @@
         <v>0.054777</v>
       </c>
       <c r="AF76" t="n">
-        <v>0.054777</v>
+        <v>0.88</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="AH76" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.91</v>
+        <v>110.65755</v>
       </c>
       <c r="AJ76" t="n">
-        <v>110.65755</v>
+        <v>118.06619</v>
       </c>
       <c r="AK76" t="n">
-        <v>118.06619</v>
+        <v>5.2194</v>
       </c>
       <c r="AL76" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="AM76" t="n">
-        <v>5.2188</v>
+        <v>7240557</v>
       </c>
       <c r="AN76" t="n">
-        <v>7240557</v>
+        <v>2687535</v>
       </c>
       <c r="AO76" t="n">
-        <v>2687535</v>
+        <v>4553022</v>
       </c>
       <c r="AP76" t="n">
-        <v>4553022</v>
+        <v>4.52</v>
       </c>
       <c r="AQ76" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="AR76" t="n">
-        <v>3.06</v>
+        <v>5.39</v>
       </c>
       <c r="AS76" t="n">
         <v>32.84</v>
@@ -22691,13 +22691,13 @@
         <v>-0.000354</v>
       </c>
       <c r="BH76" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="BI76" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ76" t="n">
-        <v>-0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="BK76" t="n">
         <v>0.21</v>
@@ -22937,43 +22937,43 @@
         <v>0.054223</v>
       </c>
       <c r="AF77" t="n">
-        <v>0.054223</v>
+        <v>0.67</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.67</v>
+        <v>2.73</v>
       </c>
       <c r="AH77" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.8100000000000001</v>
+        <v>111.04254</v>
       </c>
       <c r="AJ77" t="n">
-        <v>111.04254</v>
+        <v>114.1592</v>
       </c>
       <c r="AK77" t="n">
-        <v>114.1592</v>
+        <v>4.9886</v>
       </c>
       <c r="AL77" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="AM77" t="n">
-        <v>4.988</v>
+        <v>7259766</v>
       </c>
       <c r="AN77" t="n">
-        <v>7259766</v>
+        <v>2685397</v>
       </c>
       <c r="AO77" t="n">
-        <v>2685397</v>
+        <v>4574368</v>
       </c>
       <c r="AP77" t="n">
-        <v>4574368</v>
+        <v>4.64</v>
       </c>
       <c r="AQ77" t="n">
-        <v>4.64</v>
+        <v>3.15</v>
       </c>
       <c r="AR77" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="AS77" t="n">
         <v>33.36</v>
@@ -23021,13 +23021,13 @@
         <v>-0.000554</v>
       </c>
       <c r="BH77" t="n">
-        <v>-0.000554</v>
+        <v>0.12</v>
       </c>
       <c r="BI77" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BJ77" t="n">
         <v>0.12</v>
-      </c>
-      <c r="BJ77" t="n">
-        <v>0.09</v>
       </c>
       <c r="BK77" t="n">
         <v>0.52</v>
@@ -23267,43 +23267,43 @@
         <v>0.0534</v>
       </c>
       <c r="AF78" t="n">
-        <v>0.0534</v>
+        <v>0.58</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="AH78" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.65</v>
+        <v>111.25061</v>
       </c>
       <c r="AJ78" t="n">
-        <v>111.25061</v>
+        <v>109.79468</v>
       </c>
       <c r="AK78" t="n">
-        <v>109.79468</v>
+        <v>5.0569</v>
       </c>
       <c r="AL78" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="AM78" t="n">
-        <v>5.0563</v>
+        <v>7305322</v>
       </c>
       <c r="AN78" t="n">
-        <v>7305322</v>
+        <v>2708154</v>
       </c>
       <c r="AO78" t="n">
-        <v>2708154</v>
+        <v>4597168</v>
       </c>
       <c r="AP78" t="n">
-        <v>4597168</v>
+        <v>4.75</v>
       </c>
       <c r="AQ78" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="AR78" t="n">
-        <v>3.25</v>
+        <v>5.63</v>
       </c>
       <c r="AS78" t="n">
         <v>32.97</v>
@@ -23351,13 +23351,13 @@
         <v>-0.0008229999999999999</v>
       </c>
       <c r="BH78" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="BI78" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BJ78" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="BK78" t="n">
         <v>-0.39</v>
@@ -23601,43 +23601,43 @@
         <v>0.053028</v>
       </c>
       <c r="AF79" t="n">
-        <v>0.053028</v>
+        <v>0.16</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="AH79" t="n">
-        <v>-0.5</v>
+        <v>0.14</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.14</v>
+        <v>110.37352</v>
       </c>
       <c r="AJ79" t="n">
-        <v>110.37352</v>
+        <v>110.18456</v>
       </c>
       <c r="AK79" t="n">
-        <v>110.18456</v>
+        <v>5.1766</v>
       </c>
       <c r="AL79" t="n">
-        <v>5.1766</v>
+        <v>5.176</v>
       </c>
       <c r="AM79" t="n">
-        <v>5.176</v>
+        <v>7353302</v>
       </c>
       <c r="AN79" t="n">
-        <v>7353302</v>
+        <v>2750634</v>
       </c>
       <c r="AO79" t="n">
-        <v>2750634</v>
+        <v>4602668</v>
       </c>
       <c r="AP79" t="n">
-        <v>4602668</v>
+        <v>4.58</v>
       </c>
       <c r="AQ79" t="n">
-        <v>4.58</v>
+        <v>3.18</v>
       </c>
       <c r="AR79" t="n">
-        <v>3.18</v>
+        <v>5.42</v>
       </c>
       <c r="AS79" t="n">
         <v>32.63</v>
@@ -23685,13 +23685,13 @@
         <v>-0.000372</v>
       </c>
       <c r="BH79" t="n">
-        <v>-0.000372</v>
+        <v>-0.17</v>
       </c>
       <c r="BI79" t="n">
-        <v>-0.17</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BJ79" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="BK79" t="n">
         <v>-0.34</v>
@@ -23931,43 +23931,43 @@
         <v>0.052531</v>
       </c>
       <c r="AF80" t="n">
-        <v>0.052531</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.16</v>
       </c>
       <c r="AH80" t="n">
-        <v>-1.16</v>
+        <v>-0.01</v>
       </c>
       <c r="AI80" t="n">
-        <v>-0.01</v>
+        <v>110.03188</v>
       </c>
       <c r="AJ80" t="n">
-        <v>110.03188</v>
+        <v>114.48992</v>
       </c>
       <c r="AK80" t="n">
-        <v>114.48992</v>
+        <v>5.0773</v>
       </c>
       <c r="AL80" t="n">
-        <v>5.0773</v>
+        <v>5.0767</v>
       </c>
       <c r="AM80" t="n">
-        <v>5.0767</v>
+        <v>7362305</v>
       </c>
       <c r="AN80" t="n">
-        <v>7362305</v>
+        <v>2729162</v>
       </c>
       <c r="AO80" t="n">
-        <v>2729162</v>
+        <v>4633143</v>
       </c>
       <c r="AP80" t="n">
-        <v>4633143</v>
+        <v>4.88</v>
       </c>
       <c r="AQ80" t="n">
-        <v>4.88</v>
+        <v>3.32</v>
       </c>
       <c r="AR80" t="n">
-        <v>3.32</v>
+        <v>5.8</v>
       </c>
       <c r="AS80" t="n">
         <v>32.06</v>
@@ -24015,13 +24015,13 @@
         <v>-0.000497</v>
       </c>
       <c r="BH80" t="n">
-        <v>-0.000497</v>
+        <v>0.3</v>
       </c>
       <c r="BI80" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="BK80" t="n">
         <v>-0.57</v>
@@ -24265,43 +24265,43 @@
         <v>0.051784</v>
       </c>
       <c r="AF81" t="n">
-        <v>0.051784</v>
+        <v>-0.32</v>
       </c>
       <c r="AG81" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AH81" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AH81" t="n">
-        <v>-0.22</v>
-      </c>
       <c r="AI81" t="n">
-        <v>-0.32</v>
+        <v>110.40624</v>
       </c>
       <c r="AJ81" t="n">
-        <v>110.40624</v>
+        <v>111.71919</v>
       </c>
       <c r="AK81" t="n">
-        <v>111.71919</v>
+        <v>5.1816</v>
       </c>
       <c r="AL81" t="n">
-        <v>5.1816</v>
+        <v>5.181</v>
       </c>
       <c r="AM81" t="n">
-        <v>5.181</v>
+        <v>7397669</v>
       </c>
       <c r="AN81" t="n">
-        <v>7397669</v>
+        <v>2727499</v>
       </c>
       <c r="AO81" t="n">
-        <v>2727499</v>
+        <v>4670170</v>
       </c>
       <c r="AP81" t="n">
-        <v>4670170</v>
+        <v>5.04</v>
       </c>
       <c r="AQ81" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
       <c r="AR81" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="AS81" t="n">
         <v>32.26</v>
@@ -24349,13 +24349,13 @@
         <v>-0.0007470000000000001</v>
       </c>
       <c r="BH81" t="n">
-        <v>-0.0007470000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="BI81" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="BJ81" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="BK81" t="n">
         <v>0.2</v>
@@ -24595,25 +24595,23 @@
         <v>0.051245</v>
       </c>
       <c r="AF82" t="n">
-        <v>0.051245</v>
+        <v>0.82</v>
       </c>
       <c r="AG82" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH82" t="n">
         <v>0.82</v>
       </c>
-      <c r="AH82" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>0.82</v>
-      </c>
+      <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
+      <c r="AK82" t="n">
+        <v>5.1809</v>
+      </c>
       <c r="AL82" t="n">
-        <v>5.1809</v>
-      </c>
-      <c r="AM82" t="n">
         <v>5.1803</v>
       </c>
+      <c r="AM82" t="inlineStr"/>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
       <c r="AP82" t="inlineStr"/>
@@ -24652,9 +24650,7 @@
       <c r="BG82" t="n">
         <v>-0.00054</v>
       </c>
-      <c r="BH82" t="n">
-        <v>-0.00054</v>
-      </c>
+      <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr"/>
       <c r="BJ82" t="inlineStr"/>
       <c r="BK82" t="inlineStr"/>
@@ -24799,88 +24795,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>205726.09375</v>
+        <v>205430</v>
       </c>
       <c r="C83" t="n">
-        <v>202.639999</v>
+        <v>201.389999</v>
       </c>
       <c r="D83" t="n">
-        <v>131.389999</v>
+        <v>130.830002</v>
       </c>
       <c r="E83" t="n">
-        <v>443.209991</v>
+        <v>444.450012</v>
       </c>
       <c r="F83" t="n">
-        <v>5.0767</v>
+        <v>5.0693</v>
       </c>
       <c r="G83" t="n">
-        <v>5.7122</v>
+        <v>5.7053</v>
       </c>
       <c r="H83" t="n">
-        <v>7733.080078</v>
+        <v>7659.439941</v>
       </c>
       <c r="I83" t="n">
-        <v>26499.583984</v>
+        <v>26140.029297</v>
       </c>
       <c r="J83" t="n">
-        <v>52400.160156</v>
+        <v>52002.410156</v>
       </c>
       <c r="K83" t="n">
-        <v>4207.799805</v>
+        <v>4181.100098</v>
       </c>
       <c r="L83" t="n">
-        <v>95.589996</v>
+        <v>101.410004</v>
       </c>
       <c r="M83" t="n">
-        <v>105.459999</v>
+        <v>109.860001</v>
       </c>
       <c r="N83" t="n">
-        <v>1253.75</v>
+        <v>1261.25</v>
       </c>
       <c r="O83" t="n">
-        <v>473.75</v>
+        <v>474.25</v>
       </c>
       <c r="P83" t="n">
-        <v>10.403614</v>
+        <v>10.244714</v>
       </c>
       <c r="Q83" t="n">
-        <v>10.082571</v>
+        <v>9.403518999999999</v>
       </c>
       <c r="R83" t="n">
-        <v>17.385865</v>
+        <v>16.885555</v>
       </c>
       <c r="S83" t="n">
-        <v>-0.92988</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="T83" t="n">
-        <v>-2.425565</v>
+        <v>-2.567794</v>
       </c>
       <c r="U83" t="n">
-        <v>-3.121077</v>
+        <v>-3.238106</v>
       </c>
       <c r="V83" t="n">
-        <v>1.065668</v>
+        <v>0.103246</v>
       </c>
       <c r="W83" t="n">
-        <v>-1.345727</v>
+        <v>-2.684299</v>
       </c>
       <c r="X83" t="n">
-        <v>2.935033</v>
+        <v>2.153692</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.503968</v>
+        <v>-0.133759</v>
       </c>
       <c r="Z83" t="n">
-        <v>5.71776</v>
+        <v>12.154397</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.864194</v>
+        <v>6.114172</v>
       </c>
       <c r="AB83" t="n">
-        <v>-3.035576</v>
+        <v>-2.45553</v>
       </c>
       <c r="AC83" t="n">
-        <v>-5.391912</v>
+        <v>-5.292062</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>
@@ -24888,20 +24884,18 @@
       <c r="AE83" t="n">
         <v>0.050788</v>
       </c>
-      <c r="AF83" t="n">
-        <v>0.050788</v>
-      </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
+      <c r="AK83" t="n">
+        <v>5.0826</v>
+      </c>
       <c r="AL83" t="n">
-        <v>5.0521</v>
-      </c>
-      <c r="AM83" t="n">
-        <v>5.0515</v>
-      </c>
+        <v>5.082</v>
+      </c>
+      <c r="AM83" t="inlineStr"/>
       <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="inlineStr"/>
       <c r="AP83" t="inlineStr"/>
@@ -24912,10 +24906,10 @@
       <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr"/>
       <c r="AW83" t="n">
-        <v>-2.486055</v>
+        <v>-1.897354</v>
       </c>
       <c r="AX83" t="n">
-        <v>-2.486342</v>
+        <v>-1.897573</v>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr"/>
@@ -24930,9 +24924,7 @@
       <c r="BG83" t="n">
         <v>-0.000457</v>
       </c>
-      <c r="BH83" t="n">
-        <v>-0.000457</v>
-      </c>
+      <c r="BH83" t="inlineStr"/>
       <c r="BI83" t="inlineStr"/>
       <c r="BJ83" t="inlineStr"/>
       <c r="BK83" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5211,9 +5211,7 @@
       <c r="F23" t="n">
         <v>5.6449</v>
       </c>
-      <c r="G23" t="n">
-        <v>6.593</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>4605.379883</v>
       </c>
@@ -5475,9 +5473,7 @@
       <c r="F24" t="n">
         <v>5.6007</v>
       </c>
-      <c r="G24" t="n">
-        <v>6.3223</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>4567</v>
       </c>
@@ -5517,9 +5513,7 @@
       <c r="T24" t="n">
         <v>-0.783007</v>
       </c>
-      <c r="U24" t="n">
-        <v>-4.10587</v>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
         <v>-0.833371</v>
       </c>
@@ -5803,9 +5797,7 @@
       <c r="F25" t="n">
         <v>5.5702</v>
       </c>
-      <c r="G25" t="n">
-        <v>6.3049</v>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>4766.180176</v>
       </c>
@@ -5845,9 +5837,7 @@
       <c r="T25" t="n">
         <v>-0.544574</v>
       </c>
-      <c r="U25" t="n">
-        <v>-0.275213</v>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
         <v>4.361291</v>
       </c>
@@ -6127,9 +6117,7 @@
       <c r="F26" t="n">
         <v>5.3626</v>
       </c>
-      <c r="G26" t="n">
-        <v>5.9782</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>4515.549805</v>
       </c>
@@ -6169,9 +6157,7 @@
       <c r="T26" t="n">
         <v>-3.726978</v>
       </c>
-      <c r="U26" t="n">
-        <v>-5.181687</v>
-      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
         <v>-5.258517</v>
       </c>
@@ -6443,9 +6429,7 @@
       <c r="F27" t="n">
         <v>5.1594</v>
       </c>
-      <c r="G27" t="n">
-        <v>5.814</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>4373.939941</v>
       </c>
@@ -6485,9 +6469,7 @@
       <c r="T27" t="n">
         <v>-3.789204</v>
       </c>
-      <c r="U27" t="n">
-        <v>-2.746643</v>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
         <v>-3.136049</v>
       </c>
@@ -6763,9 +6745,7 @@
       <c r="F28" t="n">
         <v>4.7697</v>
       </c>
-      <c r="G28" t="n">
-        <v>5.3198</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>4530.410156</v>
       </c>
@@ -6805,9 +6785,7 @@
       <c r="T28" t="n">
         <v>-7.553203</v>
       </c>
-      <c r="U28" t="n">
-        <v>-8.500176</v>
-      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
         <v>3.577329</v>
       </c>
@@ -7079,9 +7057,7 @@
       <c r="F29" t="n">
         <v>4.9378</v>
       </c>
-      <c r="G29" t="n">
-        <v>5.1837</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>4131.930176</v>
       </c>
@@ -7121,9 +7097,7 @@
       <c r="T29" t="n">
         <v>3.524328</v>
       </c>
-      <c r="U29" t="n">
-        <v>-2.558363</v>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
         <v>-8.795671</v>
       </c>
@@ -7407,9 +7381,7 @@
       <c r="F30" t="n">
         <v>4.7524</v>
       </c>
-      <c r="G30" t="n">
-        <v>5.1176</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>4132.149902</v>
       </c>
@@ -7449,9 +7421,7 @@
       <c r="T30" t="n">
         <v>-3.754709</v>
       </c>
-      <c r="U30" t="n">
-        <v>-1.275153</v>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
         <v>0.005318</v>
       </c>
@@ -7731,9 +7701,7 @@
       <c r="F31" t="n">
         <v>5.1809</v>
       </c>
-      <c r="G31" t="n">
-        <v>5.4098</v>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>3785.379883</v>
       </c>
@@ -7773,9 +7741,7 @@
       <c r="T31" t="n">
         <v>9.016501</v>
       </c>
-      <c r="U31" t="n">
-        <v>5.709709</v>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
         <v>-8.391999999999999</v>
       </c>
@@ -8055,9 +8021,7 @@
       <c r="F32" t="n">
         <v>5.1827</v>
       </c>
-      <c r="G32" t="n">
-        <v>5.2797</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>4130.290039</v>
       </c>
@@ -8097,9 +8061,7 @@
       <c r="T32" t="n">
         <v>0.034744</v>
       </c>
-      <c r="U32" t="n">
-        <v>-2.404899</v>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
         <v>9.111639</v>
       </c>
@@ -8383,9 +8345,7 @@
       <c r="F33" t="n">
         <v>5.1219</v>
       </c>
-      <c r="G33" t="n">
-        <v>5.1318</v>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>3955</v>
       </c>
@@ -8425,9 +8385,7 @@
       <c r="T33" t="n">
         <v>-1.173135</v>
       </c>
-      <c r="U33" t="n">
-        <v>-2.801289</v>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
         <v>-4.244013</v>
       </c>
@@ -8707,9 +8665,7 @@
       <c r="F34" t="n">
         <v>5.3962</v>
       </c>
-      <c r="G34" t="n">
-        <v>5.3031</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3585.620117</v>
       </c>
@@ -8749,9 +8705,7 @@
       <c r="T34" t="n">
         <v>5.355436</v>
       </c>
-      <c r="U34" t="n">
-        <v>3.338009</v>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
         <v>-9.339567000000001</v>
       </c>
@@ -9041,9 +8995,7 @@
       <c r="F35" t="n">
         <v>5.2885</v>
       </c>
-      <c r="G35" t="n">
-        <v>5.2737</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3871.97998</v>
       </c>
@@ -9083,9 +9035,7 @@
       <c r="T35" t="n">
         <v>-1.995855</v>
       </c>
-      <c r="U35" t="n">
-        <v>-0.55439</v>
-      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
         <v>7.986341</v>
       </c>
@@ -9371,9 +9321,7 @@
       <c r="F36" t="n">
         <v>5.2682</v>
       </c>
-      <c r="G36" t="n">
-        <v>5.4362</v>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>4080.110107</v>
       </c>
@@ -9413,9 +9361,7 @@
       <c r="T36" t="n">
         <v>-0.38385</v>
       </c>
-      <c r="U36" t="n">
-        <v>3.081326</v>
-      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
         <v>5.375289</v>
       </c>
@@ -9693,9 +9639,7 @@
       <c r="F37" t="n">
         <v>5.2846</v>
       </c>
-      <c r="G37" t="n">
-        <v>5.633</v>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3839.5</v>
       </c>
@@ -9735,9 +9679,7 @@
       <c r="T37" t="n">
         <v>0.311299</v>
       </c>
-      <c r="U37" t="n">
-        <v>3.620171</v>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
         <v>-5.897147</v>
       </c>
@@ -10019,9 +9961,7 @@
       <c r="F38" t="n">
         <v>5.1149</v>
       </c>
-      <c r="G38" t="n">
-        <v>5.5471</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>4076.600098</v>
       </c>
@@ -10061,9 +10001,7 @@
       <c r="T38" t="n">
         <v>-3.211211</v>
       </c>
-      <c r="U38" t="n">
-        <v>-1.524939</v>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
         <v>6.175286</v>
       </c>
@@ -10353,9 +10291,7 @@
       <c r="F39" t="n">
         <v>5.1997</v>
       </c>
-      <c r="G39" t="n">
-        <v>5.514</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>3970.149902</v>
       </c>
@@ -10395,9 +10331,7 @@
       <c r="T39" t="n">
         <v>1.657897</v>
       </c>
-      <c r="U39" t="n">
-        <v>-0.59671</v>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
         <v>-2.611249</v>
       </c>
@@ -10687,9 +10621,7 @@
       <c r="F40" t="n">
         <v>5.0927</v>
       </c>
-      <c r="G40" t="n">
-        <v>5.5518</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>4109.310059</v>
       </c>
@@ -10729,9 +10661,7 @@
       <c r="T40" t="n">
         <v>-2.057809</v>
       </c>
-      <c r="U40" t="n">
-        <v>0.6855250000000001</v>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
         <v>3.505161</v>
       </c>
@@ -11021,9 +10951,7 @@
       <c r="F41" t="n">
         <v>4.9762</v>
       </c>
-      <c r="G41" t="n">
-        <v>5.4883</v>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>4169.47998</v>
       </c>
@@ -11063,9 +10991,7 @@
       <c r="T41" t="n">
         <v>-2.287586</v>
       </c>
-      <c r="U41" t="n">
-        <v>-1.143772</v>
-      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
         <v>1.464234</v>
       </c>
@@ -11343,9 +11269,7 @@
       <c r="F42" t="n">
         <v>5.0348</v>
       </c>
-      <c r="G42" t="n">
-        <v>5.4012</v>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>4179.830078</v>
       </c>
@@ -11385,9 +11309,7 @@
       <c r="T42" t="n">
         <v>1.177604</v>
       </c>
-      <c r="U42" t="n">
-        <v>-1.587013</v>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
         <v>0.248235</v>
       </c>
@@ -11673,9 +11595,7 @@
       <c r="F43" t="n">
         <v>4.8556</v>
       </c>
-      <c r="G43" t="n">
-        <v>5.2739</v>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>4450.379883</v>
       </c>
@@ -11715,9 +11635,7 @@
       <c r="T43" t="n">
         <v>-3.559231</v>
       </c>
-      <c r="U43" t="n">
-        <v>-2.35688</v>
-      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
         <v>6.472746</v>
       </c>
@@ -11999,9 +11917,7 @@
       <c r="F44" t="n">
         <v>4.7233</v>
       </c>
-      <c r="G44" t="n">
-        <v>5.1895</v>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>4588.959961</v>
       </c>
@@ -12041,9 +11957,7 @@
       <c r="T44" t="n">
         <v>-2.724687</v>
       </c>
-      <c r="U44" t="n">
-        <v>-1.600337</v>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="n">
         <v>3.113893</v>
       </c>
@@ -12325,9 +12239,7 @@
       <c r="F45" t="n">
         <v>4.8884</v>
       </c>
-      <c r="G45" t="n">
-        <v>5.313</v>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>4507.660156</v>
       </c>
@@ -12367,9 +12279,7 @@
       <c r="T45" t="n">
         <v>3.49544</v>
       </c>
-      <c r="U45" t="n">
-        <v>2.379812</v>
-      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="n">
         <v>-1.771639</v>
       </c>
@@ -12655,9 +12565,7 @@
       <c r="F46" t="n">
         <v>5.0328</v>
       </c>
-      <c r="G46" t="n">
-        <v>5.3197</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>4288.049805</v>
       </c>
@@ -12697,9 +12605,7 @@
       <c r="T46" t="n">
         <v>2.953934</v>
       </c>
-      <c r="U46" t="n">
-        <v>0.126098</v>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
         <v>-4.871937</v>
       </c>
@@ -12981,9 +12887,7 @@
       <c r="F47" t="n">
         <v>5.0461</v>
       </c>
-      <c r="G47" t="n">
-        <v>5.3537</v>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>4193.799805</v>
       </c>
@@ -13023,9 +12927,7 @@
       <c r="T47" t="n">
         <v>0.264265</v>
       </c>
-      <c r="U47" t="n">
-        <v>0.639141</v>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
         <v>-2.197969</v>
       </c>
@@ -13307,9 +13209,7 @@
       <c r="F48" t="n">
         <v>4.9041</v>
       </c>
-      <c r="G48" t="n">
-        <v>5.3628</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>4567.799805</v>
       </c>
@@ -13349,9 +13249,7 @@
       <c r="T48" t="n">
         <v>-2.814058</v>
       </c>
-      <c r="U48" t="n">
-        <v>0.169975</v>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="n">
         <v>8.917927000000001</v>
       </c>
@@ -13633,9 +13531,7 @@
       <c r="F49" t="n">
         <v>4.8502</v>
       </c>
-      <c r="G49" t="n">
-        <v>5.343</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>4769.830078</v>
       </c>
@@ -13675,9 +13571,7 @@
       <c r="T49" t="n">
         <v>-1.099076</v>
       </c>
-      <c r="U49" t="n">
-        <v>-0.369214</v>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="n">
         <v>4.422923</v>
       </c>
@@ -13963,9 +13857,7 @@
       <c r="F50" t="n">
         <v>4.9503</v>
       </c>
-      <c r="G50" t="n">
-        <v>5.3604</v>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>4845.649902</v>
       </c>
@@ -14005,9 +13897,7 @@
       <c r="T50" t="n">
         <v>2.063833</v>
       </c>
-      <c r="U50" t="n">
-        <v>0.325665</v>
-      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="n">
         <v>1.589571</v>
       </c>
@@ -14289,9 +14179,7 @@
       <c r="F51" t="n">
         <v>4.9673</v>
       </c>
-      <c r="G51" t="n">
-        <v>5.381</v>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>5096.27002</v>
       </c>
@@ -14331,9 +14219,7 @@
       <c r="T51" t="n">
         <v>0.343408</v>
       </c>
-      <c r="U51" t="n">
-        <v>0.384297</v>
-      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="n">
         <v>5.172064</v>
       </c>
@@ -14611,9 +14497,7 @@
       <c r="F52" t="n">
         <v>5.0141</v>
       </c>
-      <c r="G52" t="n">
-        <v>5.4065</v>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>5254.350098</v>
       </c>
@@ -14653,9 +14537,7 @@
       <c r="T52" t="n">
         <v>0.942164</v>
       </c>
-      <c r="U52" t="n">
-        <v>0.473886</v>
-      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="n">
         <v>3.101878</v>
       </c>
@@ -14941,9 +14823,7 @@
       <c r="F53" t="n">
         <v>5.117</v>
       </c>
-      <c r="G53" t="n">
-        <v>5.4794</v>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>5035.689941</v>
       </c>
@@ -14983,9 +14863,7 @@
       <c r="T53" t="n">
         <v>2.052213</v>
       </c>
-      <c r="U53" t="n">
-        <v>1.348382</v>
-      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="n">
         <v>-4.161507</v>
       </c>
@@ -15267,9 +15145,7 @@
       <c r="F54" t="n">
         <v>5.2021</v>
       </c>
-      <c r="G54" t="n">
-        <v>5.6311</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>5277.509766</v>
       </c>
@@ -15309,9 +15185,7 @@
       <c r="T54" t="n">
         <v>1.663078</v>
       </c>
-      <c r="U54" t="n">
-        <v>2.768552</v>
-      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="n">
         <v>4.802119</v>
       </c>
@@ -15597,9 +15471,7 @@
       <c r="F55" t="n">
         <v>5.5005</v>
       </c>
-      <c r="G55" t="n">
-        <v>5.8909</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>5460.47998</v>
       </c>
@@ -15639,9 +15511,7 @@
       <c r="T55" t="n">
         <v>5.736153</v>
       </c>
-      <c r="U55" t="n">
-        <v>4.613663</v>
-      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="n">
         <v>3.46698</v>
       </c>
@@ -15927,9 +15797,7 @@
       <c r="F56" t="n">
         <v>5.6111</v>
       </c>
-      <c r="G56" t="n">
-        <v>6.0695</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>5522.299805</v>
       </c>
@@ -15969,9 +15837,7 @@
       <c r="T56" t="n">
         <v>2.010726</v>
       </c>
-      <c r="U56" t="n">
-        <v>3.031792</v>
-      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="n">
         <v>1.132132</v>
       </c>
@@ -16257,9 +16123,7 @@
       <c r="F57" t="n">
         <v>5.6277</v>
       </c>
-      <c r="G57" t="n">
-        <v>6.2224</v>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>5648.399902</v>
       </c>
@@ -16299,9 +16163,7 @@
       <c r="T57" t="n">
         <v>0.295836</v>
       </c>
-      <c r="U57" t="n">
-        <v>2.519157</v>
-      </c>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="n">
         <v>2.283471</v>
       </c>
@@ -16587,9 +16449,7 @@
       <c r="F58" t="n">
         <v>5.4332</v>
       </c>
-      <c r="G58" t="n">
-        <v>6.0652</v>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>5762.47998</v>
       </c>
@@ -16629,9 +16489,7 @@
       <c r="T58" t="n">
         <v>-3.456118</v>
       </c>
-      <c r="U58" t="n">
-        <v>-2.526362</v>
-      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="n">
         <v>2.019688</v>
       </c>
@@ -16917,9 +16775,7 @@
       <c r="F59" t="n">
         <v>5.7623</v>
       </c>
-      <c r="G59" t="n">
-        <v>6.2522</v>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>5705.450195</v>
       </c>
@@ -16959,9 +16815,7 @@
       <c r="T59" t="n">
         <v>6.057206</v>
       </c>
-      <c r="U59" t="n">
-        <v>3.083168</v>
-      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="n">
         <v>-0.9896740000000001</v>
       </c>
@@ -17239,9 +17093,7 @@
       <c r="F60" t="n">
         <v>6.0139</v>
       </c>
-      <c r="G60" t="n">
-        <v>6.345178</v>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>6032.379883</v>
       </c>
@@ -17281,9 +17133,7 @@
       <c r="T60" t="n">
         <v>4.366308</v>
       </c>
-      <c r="U60" t="n">
-        <v>1.487125</v>
-      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="n">
         <v>5.73013</v>
       </c>
@@ -17569,9 +17419,7 @@
       <c r="F61" t="n">
         <v>6.1779</v>
       </c>
-      <c r="G61" t="n">
-        <v>6.422608</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>5881.629883</v>
       </c>
@@ -17611,9 +17459,7 @@
       <c r="T61" t="n">
         <v>2.727016</v>
       </c>
-      <c r="U61" t="n">
-        <v>1.220293</v>
-      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="n">
         <v>-2.499014</v>
       </c>
@@ -17899,9 +17745,7 @@
       <c r="F62" t="n">
         <v>5.8745</v>
       </c>
-      <c r="G62" t="n">
-        <v>6.101281</v>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>6040.529785</v>
       </c>
@@ -17941,9 +17785,7 @@
       <c r="T62" t="n">
         <v>-4.911055</v>
       </c>
-      <c r="U62" t="n">
-        <v>-5.003057</v>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
         <v>2.70163</v>
       </c>
@@ -18233,9 +18075,7 @@
       <c r="F63" t="n">
         <v>5.839</v>
       </c>
-      <c r="G63" t="n">
-        <v>6.064281</v>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>5954.5</v>
       </c>
@@ -18275,9 +18115,7 @@
       <c r="T63" t="n">
         <v>-0.604299</v>
       </c>
-      <c r="U63" t="n">
-        <v>-0.606433</v>
-      </c>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="n">
         <v>-1.424209</v>
       </c>
@@ -18563,9 +18401,7 @@
       <c r="F64" t="n">
         <v>5.7581</v>
       </c>
-      <c r="G64" t="n">
-        <v>6.22665</v>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>5611.850098</v>
       </c>
@@ -18605,9 +18441,7 @@
       <c r="T64" t="n">
         <v>-1.385514</v>
       </c>
-      <c r="U64" t="n">
-        <v>2.677469</v>
-      </c>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="n">
         <v>-5.75447</v>
       </c>
@@ -18889,9 +18723,7 @@
       <c r="F65" t="n">
         <v>5.62</v>
       </c>
-      <c r="G65" t="n">
-        <v>6.393862</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>5569.060059</v>
       </c>
@@ -18931,9 +18763,7 @@
       <c r="T65" t="n">
         <v>-2.398363</v>
       </c>
-      <c r="U65" t="n">
-        <v>2.685417</v>
-      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="n">
         <v>-0.762494</v>
       </c>
@@ -19223,9 +19053,7 @@
       <c r="F66" t="n">
         <v>5.6651</v>
       </c>
-      <c r="G66" t="n">
-        <v>6.43915</v>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>5911.689941</v>
       </c>
@@ -19265,9 +19093,7 @@
       <c r="T66" t="n">
         <v>0.802495</v>
       </c>
-      <c r="U66" t="n">
-        <v>0.708306</v>
-      </c>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="n">
         <v>6.152383</v>
       </c>
@@ -19553,9 +19379,7 @@
       <c r="F67" t="n">
         <v>5.4784</v>
       </c>
-      <c r="G67" t="n">
-        <v>6.418485</v>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>6204.950195</v>
       </c>
@@ -19595,9 +19419,7 @@
       <c r="T67" t="n">
         <v>-3.295615</v>
       </c>
-      <c r="U67" t="n">
-        <v>-0.320923</v>
-      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="n">
         <v>4.960684</v>
       </c>
@@ -19883,9 +19705,7 @@
       <c r="F68" t="n">
         <v>5.5754</v>
       </c>
-      <c r="G68" t="n">
-        <v>6.365372</v>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>6339.390137</v>
       </c>
@@ -19925,9 +19745,7 @@
       <c r="T68" t="n">
         <v>1.770583</v>
       </c>
-      <c r="U68" t="n">
-        <v>-0.8275</v>
-      </c>
+      <c r="U68" t="inlineStr"/>
       <c r="V68" t="n">
         <v>2.166656</v>
       </c>
@@ -20217,9 +20035,7 @@
       <c r="F69" t="n">
         <v>5.413</v>
       </c>
-      <c r="G69" t="n">
-        <v>6.317119</v>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>6460.259766</v>
       </c>
@@ -20259,9 +20075,7 @@
       <c r="T69" t="n">
         <v>-2.912791</v>
       </c>
-      <c r="U69" t="n">
-        <v>-0.758056</v>
-      </c>
+      <c r="U69" t="inlineStr"/>
       <c r="V69" t="n">
         <v>1.906644</v>
       </c>
@@ -20547,9 +20361,7 @@
       <c r="F70" t="n">
         <v>5.3217</v>
       </c>
-      <c r="G70" t="n">
-        <v>6.238303</v>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>6688.459961</v>
       </c>
@@ -20589,9 +20401,7 @@
       <c r="T70" t="n">
         <v>-1.68668</v>
       </c>
-      <c r="U70" t="n">
-        <v>-1.247656</v>
-      </c>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="n">
         <v>3.532369</v>
       </c>
@@ -20877,9 +20687,7 @@
       <c r="F71" t="n">
         <v>5.382</v>
       </c>
-      <c r="G71" t="n">
-        <v>6.222775</v>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>6840.200195</v>
       </c>
@@ -20919,9 +20727,7 @@
       <c r="T71" t="n">
         <v>1.133094</v>
       </c>
-      <c r="U71" t="n">
-        <v>-0.248917</v>
-      </c>
+      <c r="U71" t="inlineStr"/>
       <c r="V71" t="n">
         <v>2.268687</v>
       </c>
@@ -21207,9 +21013,7 @@
       <c r="F72" t="n">
         <v>5.3554</v>
       </c>
-      <c r="G72" t="n">
-        <v>6.207325</v>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>6849.089844</v>
       </c>
@@ -21249,9 +21053,7 @@
       <c r="T72" t="n">
         <v>-0.494238</v>
       </c>
-      <c r="U72" t="n">
-        <v>-0.248282</v>
-      </c>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="n">
         <v>0.129962</v>
       </c>
@@ -21541,9 +21343,7 @@
       <c r="F73" t="n">
         <v>5.4762</v>
       </c>
-      <c r="G73" t="n">
-        <v>6.426735</v>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>6845.5</v>
       </c>
@@ -21583,9 +21383,7 @@
       <c r="T73" t="n">
         <v>2.255667</v>
       </c>
-      <c r="U73" t="n">
-        <v>3.534694</v>
-      </c>
+      <c r="U73" t="inlineStr"/>
       <c r="V73" t="n">
         <v>-0.052413</v>
       </c>
@@ -21867,9 +21665,7 @@
       <c r="F74" t="n">
         <v>5.1892</v>
       </c>
-      <c r="G74" t="n">
-        <v>6.203474</v>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>6939.029785</v>
       </c>
@@ -21909,9 +21705,7 @@
       <c r="T74" t="n">
         <v>-5.240864</v>
       </c>
-      <c r="U74" t="n">
-        <v>-3.473939</v>
-      </c>
+      <c r="U74" t="inlineStr"/>
       <c r="V74" t="n">
         <v>1.366296</v>
       </c>
@@ -22197,9 +21991,7 @@
       <c r="F75" t="n">
         <v>5.1366</v>
       </c>
-      <c r="G75" t="n">
-        <v>6.056935</v>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>6878.879883</v>
       </c>
@@ -22239,9 +22031,7 @@
       <c r="T75" t="n">
         <v>-1.013642</v>
       </c>
-      <c r="U75" t="n">
-        <v>-2.362212</v>
-      </c>
+      <c r="U75" t="inlineStr"/>
       <c r="V75" t="n">
         <v>-0.866834</v>
       </c>
@@ -22531,9 +22321,7 @@
       <c r="F76" t="n">
         <v>5.264</v>
       </c>
-      <c r="G76" t="n">
-        <v>6.027728</v>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>6528.52002</v>
       </c>
@@ -22573,9 +22361,7 @@
       <c r="T76" t="n">
         <v>2.480238</v>
       </c>
-      <c r="U76" t="n">
-        <v>-0.482204</v>
-      </c>
+      <c r="U76" t="inlineStr"/>
       <c r="V76" t="n">
         <v>-5.093269</v>
       </c>
@@ -22861,9 +22647,7 @@
       <c r="F77" t="n">
         <v>5.0175</v>
       </c>
-      <c r="G77" t="n">
-        <v>5.858231</v>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>7209.009766</v>
       </c>
@@ -22903,9 +22687,7 @@
       <c r="T77" t="n">
         <v>-4.682751</v>
       </c>
-      <c r="U77" t="n">
-        <v>-2.811955</v>
-      </c>
+      <c r="U77" t="inlineStr"/>
       <c r="V77" t="n">
         <v>10.423339</v>
       </c>
@@ -23191,9 +22973,7 @@
       <c r="F78" t="n">
         <v>5.0517</v>
       </c>
-      <c r="G78" t="n">
-        <v>5.882353</v>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>7580.060059</v>
       </c>
@@ -23233,9 +23013,7 @@
       <c r="T78" t="n">
         <v>0.6816179999999999</v>
       </c>
-      <c r="U78" t="n">
-        <v>0.411758</v>
-      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="n">
         <v>5.147036</v>
       </c>
@@ -23525,9 +23303,7 @@
       <c r="F79" t="n">
         <v>5.181787</v>
       </c>
-      <c r="G79" t="n">
-        <v>5.91716</v>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>7499.359863</v>
       </c>
@@ -23567,9 +23343,7 @@
       <c r="T79" t="n">
         <v>2.575111</v>
       </c>
-      <c r="U79" t="n">
-        <v>0.591722</v>
-      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="n">
         <v>-1.064638</v>
       </c>
@@ -23855,9 +23629,7 @@
       <c r="F80" t="n">
         <v>5.0781</v>
       </c>
-      <c r="G80" t="n">
-        <v>5.847953</v>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>7489.720215</v>
       </c>
@@ -23897,9 +23669,7 @@
       <c r="T80" t="n">
         <v>-2.000986</v>
       </c>
-      <c r="U80" t="n">
-        <v>-1.169601</v>
-      </c>
+      <c r="U80" t="inlineStr"/>
       <c r="V80" t="n">
         <v>-0.12854</v>
       </c>
@@ -24189,9 +23959,7 @@
       <c r="F81" t="n">
         <v>5.1912</v>
       </c>
-      <c r="G81" t="n">
-        <v>6.009615</v>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>7686.140137</v>
       </c>
@@ -24231,9 +23999,7 @@
       <c r="T81" t="n">
         <v>2.227203</v>
       </c>
-      <c r="U81" t="n">
-        <v>2.764422</v>
-      </c>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="n">
         <v>2.622527</v>
       </c>
@@ -24519,9 +24285,7 @@
       <c r="F82" t="n">
         <v>5.2029</v>
       </c>
-      <c r="G82" t="n">
-        <v>5.896226</v>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>7651.540039</v>
       </c>
@@ -24561,9 +24325,7 @@
       <c r="T82" t="n">
         <v>0.225384</v>
       </c>
-      <c r="U82" t="n">
-        <v>-1.886793</v>
-      </c>
+      <c r="U82" t="inlineStr"/>
       <c r="V82" t="n">
         <v>-0.450162</v>
       </c>
@@ -24798,20 +24560,18 @@
         <v>205430</v>
       </c>
       <c r="C83" t="n">
-        <v>201.389999</v>
+        <v>202.300003</v>
       </c>
       <c r="D83" t="n">
-        <v>130.830002</v>
+        <v>131</v>
       </c>
       <c r="E83" t="n">
-        <v>444.450012</v>
+        <v>438.549988</v>
       </c>
       <c r="F83" t="n">
         <v>5.0693</v>
       </c>
-      <c r="G83" t="n">
-        <v>5.7053</v>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>7659.439941</v>
       </c>
@@ -24825,7 +24585,7 @@
         <v>4181.100098</v>
       </c>
       <c r="L83" t="n">
-        <v>101.410004</v>
+        <v>99.019997</v>
       </c>
       <c r="M83" t="n">
         <v>109.860001</v>
@@ -24840,20 +24600,18 @@
         <v>10.244714</v>
       </c>
       <c r="Q83" t="n">
-        <v>9.403518999999999</v>
+        <v>9.897871</v>
       </c>
       <c r="R83" t="n">
-        <v>16.885555</v>
+        <v>17.037434</v>
       </c>
       <c r="S83" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-1.971524</v>
       </c>
       <c r="T83" t="n">
         <v>-2.567794</v>
       </c>
-      <c r="U83" t="n">
-        <v>-3.238106</v>
-      </c>
+      <c r="U83" t="inlineStr"/>
       <c r="V83" t="n">
         <v>0.103246</v>
       </c>
@@ -24867,7 +24625,7 @@
         <v>-0.133759</v>
       </c>
       <c r="Z83" t="n">
-        <v>12.154397</v>
+        <v>9.511169000000001</v>
       </c>
       <c r="AA83" t="n">
         <v>6.114172</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -573,77 +573,77 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>bcb_sgs_selic_over</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>bcb_sgs_cdi</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
@@ -713,27 +713,27 @@
       </c>
       <c r="BG1" t="inlineStr">
         <is>
+          <t>bcb_sgs_dif_selic_over</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
@@ -5211,7 +5211,9 @@
       <c r="F23" t="n">
         <v>5.6449</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>6.593</v>
+      </c>
       <c r="H23" t="n">
         <v>4605.379883</v>
       </c>
@@ -5254,49 +5256,49 @@
         <v>7.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.024801</v>
+        <v>0.024925</v>
       </c>
       <c r="AF23" t="n">
+        <v>0.024925</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AH23" t="n">
         <v>0.64</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AI23" t="n">
         <v>1.16</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
         <v>97.48845</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>96.53555</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AL23" t="n">
         <v>5.643</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AM23" t="n">
         <v>5.6424</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AN23" t="n">
         <v>4511956</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>1910940</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>2601017</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>2.33</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AS23" t="n">
         <v>2.99</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>22.89</v>
       </c>
       <c r="AT23" t="n">
         <v>367927</v>
@@ -5473,7 +5475,9 @@
       <c r="F24" t="n">
         <v>5.6007</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>6.3223</v>
+      </c>
       <c r="H24" t="n">
         <v>4567</v>
       </c>
@@ -5513,7 +5517,9 @@
       <c r="T24" t="n">
         <v>-0.783007</v>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>-4.10587</v>
+      </c>
       <c r="V24" t="n">
         <v>-0.833371</v>
       </c>
@@ -5545,46 +5551,46 @@
         <v>0.029256</v>
       </c>
       <c r="AF24" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0.95</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>0.84</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
         <v>99.05624</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AK24" t="n">
         <v>97.85102000000001</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AL24" t="n">
         <v>5.6199</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
         <v>5.6193</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AN24" t="n">
         <v>4597507</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>1933111</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>2664395</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AQ24" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AS24" t="n">
         <v>3.01</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>23.91</v>
       </c>
       <c r="AT24" t="n">
         <v>367772</v>
@@ -5620,19 +5626,19 @@
         <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.004455</v>
+        <v>0.004331</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.03</v>
+        <v>0.004331</v>
       </c>
       <c r="BI24" t="n">
         <v>0.03</v>
       </c>
       <c r="BJ24" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BK24" t="n">
         <v>0.02</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>1.02</v>
       </c>
       <c r="BL24" t="n">
         <v>20501766210</v>
@@ -5797,7 +5803,9 @@
       <c r="F25" t="n">
         <v>5.5702</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>6.3049</v>
+      </c>
       <c r="H25" t="n">
         <v>4766.180176</v>
       </c>
@@ -5837,7 +5845,9 @@
       <c r="T25" t="n">
         <v>-0.544574</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>-0.275213</v>
+      </c>
       <c r="V25" t="n">
         <v>4.361291</v>
       </c>
@@ -5869,46 +5879,46 @@
         <v>0.033316</v>
       </c>
       <c r="AF25" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="AG25" t="n">
         <v>0.73</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>0.87</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>0.73</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
         <v>99.38482</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AK25" t="n">
         <v>99.31835</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AL25" t="n">
         <v>5.5805</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AM25" t="n">
         <v>5.5799</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AN25" t="n">
         <v>4682852</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>1974391</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>2708461</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>2.35</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AS25" t="n">
         <v>3.05</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>24.21</v>
       </c>
       <c r="AT25" t="n">
         <v>362204</v>
@@ -5947,16 +5957,16 @@
         <v>0.00406</v>
       </c>
       <c r="BH25" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="BI25" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI25" t="n">
+      <c r="BJ25" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ25" t="n">
+      <c r="BK25" t="n">
         <v>0.04</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>0.3</v>
       </c>
       <c r="BL25" t="n">
         <v>24432406778</v>
@@ -6117,7 +6127,9 @@
       <c r="F26" t="n">
         <v>5.3626</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>5.9782</v>
+      </c>
       <c r="H26" t="n">
         <v>4515.549805</v>
       </c>
@@ -6157,7 +6169,9 @@
       <c r="T26" t="n">
         <v>-3.726978</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>-5.181687</v>
+      </c>
       <c r="V26" t="n">
         <v>-5.258517</v>
       </c>
@@ -6189,46 +6203,46 @@
         <v>0.034749</v>
       </c>
       <c r="AF26" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.54</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AH26" t="n">
         <v>1.82</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
         <v>97.4208</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AK26" t="n">
         <v>91.68112000000001</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
         <v>5.3574</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AM26" t="n">
         <v>5.3568</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AN26" t="n">
         <v>4682131</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>1947035</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>2735096</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>2.51</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AS26" t="n">
         <v>3.26</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>25.23</v>
       </c>
       <c r="AT26" t="n">
         <v>358398</v>
@@ -6267,16 +6281,16 @@
         <v>0.001433</v>
       </c>
       <c r="BH26" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="BI26" t="n">
         <v>0.16</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BJ26" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BK26" t="n">
         <v>0.21</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>1.02</v>
       </c>
       <c r="BL26" t="n">
         <v>19779928894</v>
@@ -6429,7 +6443,9 @@
       <c r="F27" t="n">
         <v>5.1594</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>5.814</v>
+      </c>
       <c r="H27" t="n">
         <v>4373.939941</v>
       </c>
@@ -6469,7 +6485,9 @@
       <c r="T27" t="n">
         <v>-3.789204</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>-2.746643</v>
+      </c>
       <c r="V27" t="n">
         <v>-3.136049</v>
       </c>
@@ -6501,46 +6519,46 @@
         <v>0.039598</v>
       </c>
       <c r="AF27" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.01</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AH27" t="n">
         <v>1.83</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>1</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>98.49135</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AK27" t="n">
         <v>95.64317</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AL27" t="n">
         <v>5.1394</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AM27" t="n">
         <v>5.1388</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AN27" t="n">
         <v>4727818</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AO27" t="n">
         <v>1971524</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>2756295</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>2.57</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AS27" t="n">
         <v>3.38</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>25.63</v>
       </c>
       <c r="AT27" t="n">
         <v>357740</v>
@@ -6579,16 +6597,16 @@
         <v>0.004849</v>
       </c>
       <c r="BH27" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="BI27" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BJ27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ27" t="n">
+      <c r="BK27" t="n">
         <v>0.12</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>0.4</v>
       </c>
       <c r="BL27" t="n">
         <v>23513305117</v>
@@ -6745,7 +6763,9 @@
       <c r="F28" t="n">
         <v>4.7697</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>5.3198</v>
+      </c>
       <c r="H28" t="n">
         <v>4530.410156</v>
       </c>
@@ -6785,7 +6805,9 @@
       <c r="T28" t="n">
         <v>-7.553203</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>-8.500176</v>
+      </c>
       <c r="V28" t="n">
         <v>3.577329</v>
       </c>
@@ -6817,46 +6839,46 @@
         <v>0.041954</v>
       </c>
       <c r="AF28" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="n">
         <v>1.74</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
         <v>99.56176000000001</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AK28" t="n">
         <v>104.54148</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AL28" t="n">
         <v>4.7378</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>4.7372</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AN28" t="n">
         <v>4794583</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AO28" t="n">
         <v>1994119</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>2800464</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AQ28" t="n">
         <v>2.66</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AR28" t="n">
         <v>1.55</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AS28" t="n">
         <v>3.45</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>26.54</v>
       </c>
       <c r="AT28" t="n">
         <v>353169</v>
@@ -6895,16 +6917,16 @@
         <v>0.002356</v>
       </c>
       <c r="BH28" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="BI28" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI28" t="n">
+      <c r="BJ28" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ28" t="n">
+      <c r="BK28" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>0.91</v>
       </c>
       <c r="BL28" t="n">
         <v>29422320196</v>
@@ -7057,7 +7079,9 @@
       <c r="F29" t="n">
         <v>4.9378</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>5.1837</v>
+      </c>
       <c r="H29" t="n">
         <v>4131.930176</v>
       </c>
@@ -7097,7 +7121,9 @@
       <c r="T29" t="n">
         <v>3.524328</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>-2.558363</v>
+      </c>
       <c r="V29" t="n">
         <v>-8.795671</v>
       </c>
@@ -7129,46 +7155,46 @@
         <v>0.043739</v>
       </c>
       <c r="AF29" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.06</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AH29" t="n">
         <v>1.41</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
         <v>1.04</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>99.45421</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AK29" t="n">
         <v>100.24567</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AL29" t="n">
         <v>4.9191</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AM29" t="n">
         <v>4.9185</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AN29" t="n">
         <v>4833732</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AO29" t="n">
         <v>2003312</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>2830420</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AQ29" t="n">
         <v>2.72</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AR29" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AS29" t="n">
         <v>3.54</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>27.46</v>
       </c>
       <c r="AT29" t="n">
         <v>345097</v>
@@ -7207,16 +7233,16 @@
         <v>0.001785</v>
       </c>
       <c r="BH29" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="BI29" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI29" t="n">
+      <c r="BJ29" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ29" t="n">
+      <c r="BK29" t="n">
         <v>0.09</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>0.92</v>
       </c>
       <c r="BL29" t="n">
         <v>28969694687</v>
@@ -7381,7 +7407,9 @@
       <c r="F30" t="n">
         <v>4.7524</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>5.1176</v>
+      </c>
       <c r="H30" t="n">
         <v>4132.149902</v>
       </c>
@@ -7421,7 +7449,9 @@
       <c r="T30" t="n">
         <v>-3.754709</v>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>-1.275153</v>
+      </c>
       <c r="V30" t="n">
         <v>0.005318</v>
       </c>
@@ -7453,46 +7483,46 @@
         <v>0.046796</v>
       </c>
       <c r="AF30" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.47</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>0.45</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
         <v>99.64297000000001</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AK30" t="n">
         <v>99.74066999999999</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AL30" t="n">
         <v>4.7289</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AM30" t="n">
         <v>4.7283</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AN30" t="n">
         <v>4889397</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AO30" t="n">
         <v>2013726</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>2875671</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>2.79</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AS30" t="n">
         <v>3.65</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>27.42</v>
       </c>
       <c r="AT30" t="n">
         <v>346415</v>
@@ -7531,16 +7561,16 @@
         <v>0.003057</v>
       </c>
       <c r="BH30" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="BI30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BJ30" t="n">
         <v>0</v>
       </c>
-      <c r="BJ30" t="n">
+      <c r="BK30" t="n">
         <v>0.11</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>-0.04</v>
       </c>
       <c r="BL30" t="n">
         <v>29642851197</v>
@@ -7701,7 +7731,9 @@
       <c r="F31" t="n">
         <v>5.1809</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>5.4098</v>
+      </c>
       <c r="H31" t="n">
         <v>3785.379883</v>
       </c>
@@ -7741,7 +7773,9 @@
       <c r="T31" t="n">
         <v>9.016501</v>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>5.709709</v>
+      </c>
       <c r="V31" t="n">
         <v>-8.391999999999999</v>
       </c>
@@ -7773,46 +7807,46 @@
         <v>0.048116</v>
       </c>
       <c r="AF31" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="AG31" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AI31" t="n">
         <v>0.62</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
         <v>99.49797</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AK31" t="n">
         <v>99.30903000000001</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>5.238</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AM31" t="n">
         <v>5.2374</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AN31" t="n">
         <v>4965603</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AO31" t="n">
         <v>2052569</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>2913035</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>2.73</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AS31" t="n">
         <v>3.57</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>27.88</v>
       </c>
       <c r="AT31" t="n">
         <v>341958</v>
@@ -7851,16 +7885,16 @@
         <v>0.00132</v>
       </c>
       <c r="BH31" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="BI31" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BJ31" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ31" t="n">
+      <c r="BK31" t="n">
         <v>-0.08</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>0.46</v>
       </c>
       <c r="BL31" t="n">
         <v>32742194543</v>
@@ -8021,7 +8055,9 @@
       <c r="F32" t="n">
         <v>5.1827</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>5.2797</v>
+      </c>
       <c r="H32" t="n">
         <v>4130.290039</v>
       </c>
@@ -8061,7 +8097,9 @@
       <c r="T32" t="n">
         <v>0.034744</v>
       </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>-2.404899</v>
+      </c>
       <c r="V32" t="n">
         <v>9.111639</v>
       </c>
@@ -8093,46 +8131,46 @@
         <v>0.049037</v>
       </c>
       <c r="AF32" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG32" t="n">
         <v>-0.68</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AH32" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AI32" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
         <v>101.41926</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AK32" t="n">
         <v>103.96099</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AL32" t="n">
         <v>5.1884</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AM32" t="n">
         <v>5.1878</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AN32" t="n">
         <v>4999244</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
         <v>2047038</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>2952207</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>2.84</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AS32" t="n">
         <v>3.71</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>29.24</v>
       </c>
       <c r="AT32" t="n">
         <v>346403</v>
@@ -8171,16 +8209,16 @@
         <v>0.0009210000000000001</v>
       </c>
       <c r="BH32" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="BI32" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI32" t="n">
+      <c r="BJ32" t="n">
         <v>0.08</v>
       </c>
-      <c r="BJ32" t="n">
+      <c r="BK32" t="n">
         <v>0.14</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>1.36</v>
       </c>
       <c r="BL32" t="n">
         <v>29844324640</v>
@@ -8345,7 +8383,9 @@
       <c r="F33" t="n">
         <v>5.1219</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>5.1318</v>
+      </c>
       <c r="H33" t="n">
         <v>3955</v>
       </c>
@@ -8385,7 +8425,9 @@
       <c r="T33" t="n">
         <v>-1.173135</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>-2.801289</v>
+      </c>
       <c r="V33" t="n">
         <v>-4.244013</v>
       </c>
@@ -8417,46 +8459,46 @@
         <v>0.05056</v>
       </c>
       <c r="AF33" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="AG33" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AI33" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
         <v>101.10264</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AK33" t="n">
         <v>104.50684</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AL33" t="n">
         <v>5.179</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AM33" t="n">
         <v>5.1784</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AN33" t="n">
         <v>5072711</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AO33" t="n">
         <v>2064183</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>3008528</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>2.9</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>1.62</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AS33" t="n">
         <v>3.78</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>28.6</v>
       </c>
       <c r="AT33" t="n">
         <v>339664</v>
@@ -8495,16 +8537,16 @@
         <v>0.001523</v>
       </c>
       <c r="BH33" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="BI33" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI33" t="n">
+      <c r="BJ33" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ33" t="n">
+      <c r="BK33" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>-0.64</v>
       </c>
       <c r="BL33" t="n">
         <v>30786908834</v>
@@ -8665,7 +8707,9 @@
       <c r="F34" t="n">
         <v>5.3962</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>5.3031</v>
+      </c>
       <c r="H34" t="n">
         <v>3585.620117</v>
       </c>
@@ -8705,7 +8749,9 @@
       <c r="T34" t="n">
         <v>5.355436</v>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>3.338009</v>
+      </c>
       <c r="V34" t="n">
         <v>-9.339567000000001</v>
       </c>
@@ -8737,46 +8783,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF34" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG34" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AH34" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AJ34" t="n">
         <v>101.1562</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AK34" t="n">
         <v>101.17889</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AL34" t="n">
         <v>5.4066</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AM34" t="n">
         <v>5.406</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
         <v>5164775</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>2109806</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>3054969</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>2.92</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>1.65</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>3.8</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>28.57</v>
       </c>
       <c r="AT34" t="n">
         <v>327580</v>
@@ -8821,16 +8867,16 @@
         <v>0.000228</v>
       </c>
       <c r="BH34" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="BI34" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI34" t="n">
+      <c r="BJ34" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ34" t="n">
+      <c r="BK34" t="n">
         <v>0.02</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>-0.03</v>
       </c>
       <c r="BL34" t="n">
         <v>28587334142</v>
@@ -8995,7 +9041,9 @@
       <c r="F35" t="n">
         <v>5.2885</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>5.2737</v>
+      </c>
       <c r="H35" t="n">
         <v>3871.97998</v>
       </c>
@@ -9035,7 +9083,9 @@
       <c r="T35" t="n">
         <v>-1.995855</v>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v>-0.55439</v>
+      </c>
       <c r="V35" t="n">
         <v>7.986341</v>
       </c>
@@ -9067,46 +9117,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF35" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.59</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>-0.97</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>0.47</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AJ35" t="n">
         <v>101.43769</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AK35" t="n">
         <v>100.08276</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AL35" t="n">
         <v>5.257</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AM35" t="n">
         <v>5.2564</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
         <v>5215990</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>2105856</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>3110134</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>3.04</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>1.77</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AS35" t="n">
         <v>3.89</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>29.68</v>
       </c>
       <c r="AT35" t="n">
         <v>325546</v>
@@ -9151,16 +9201,16 @@
         <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="BI35" t="n">
         <v>0.12</v>
       </c>
       <c r="BJ35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BK35" t="n">
         <v>0.09</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>1.11</v>
       </c>
       <c r="BL35" t="n">
         <v>26852476461</v>
@@ -9321,7 +9371,9 @@
       <c r="F36" t="n">
         <v>5.2682</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>5.4362</v>
+      </c>
       <c r="H36" t="n">
         <v>4080.110107</v>
       </c>
@@ -9361,7 +9413,9 @@
       <c r="T36" t="n">
         <v>-0.38385</v>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>3.081326</v>
+      </c>
       <c r="V36" t="n">
         <v>5.375289</v>
       </c>
@@ -9393,46 +9447,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF36" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG36" t="n">
         <v>0.41</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AH36" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AI36" t="n">
         <v>0.38</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AJ36" t="n">
         <v>100.71743</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AK36" t="n">
         <v>99.14758</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AL36" t="n">
         <v>5.2941</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AM36" t="n">
         <v>5.2935</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AN36" t="n">
         <v>5285657</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AO36" t="n">
         <v>2130312</v>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>3155345</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>1.81</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AS36" t="n">
         <v>3.92</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>30.52</v>
       </c>
       <c r="AT36" t="n">
         <v>331505</v>
@@ -9477,16 +9531,16 @@
         <v>0</v>
       </c>
       <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI36" t="n">
+      <c r="BJ36" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ36" t="n">
+      <c r="BK36" t="n">
         <v>0.03</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>0.84</v>
       </c>
       <c r="BL36" t="n">
         <v>27652303451</v>
@@ -9639,7 +9693,9 @@
       <c r="F37" t="n">
         <v>5.2846</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>5.633</v>
+      </c>
       <c r="H37" t="n">
         <v>3839.5</v>
       </c>
@@ -9679,7 +9735,9 @@
       <c r="T37" t="n">
         <v>0.311299</v>
       </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" t="n">
+        <v>3.620171</v>
+      </c>
       <c r="V37" t="n">
         <v>-5.897147</v>
       </c>
@@ -9711,46 +9769,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF37" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG37" t="n">
         <v>0.62</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AH37" t="n">
         <v>0.45</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AI37" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AJ37" t="n">
         <v>100.59088</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AK37" t="n">
         <v>99.96181</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AL37" t="n">
         <v>5.2177</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AM37" t="n">
         <v>5.2171</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AN37" t="n">
         <v>5366069</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AO37" t="n">
         <v>2178236</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>3187833</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>1.8</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AS37" t="n">
         <v>3.94</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>29.64</v>
       </c>
       <c r="AT37" t="n">
         <v>324703</v>
@@ -9795,16 +9853,16 @@
         <v>-0</v>
       </c>
       <c r="BH37" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI37" t="n">
         <v>0</v>
       </c>
-      <c r="BI37" t="n">
+      <c r="BJ37" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ37" t="n">
+      <c r="BK37" t="n">
         <v>0.02</v>
-      </c>
-      <c r="BK37" t="n">
-        <v>-0.88</v>
       </c>
       <c r="BL37" t="n">
         <v>26342396058</v>
@@ -9961,7 +10019,9 @@
       <c r="F38" t="n">
         <v>5.1149</v>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>5.5471</v>
+      </c>
       <c r="H38" t="n">
         <v>4076.600098</v>
       </c>
@@ -10001,7 +10061,9 @@
       <c r="T38" t="n">
         <v>-3.211211</v>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>-1.524939</v>
+      </c>
       <c r="V38" t="n">
         <v>6.175286</v>
       </c>
@@ -10033,46 +10095,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF38" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.53</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AH38" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AI38" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AJ38" t="n">
         <v>100.10409</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AK38" t="n">
         <v>95.10406999999999</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AL38" t="n">
         <v>5.0993</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AM38" t="n">
         <v>5.0987</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AN38" t="n">
         <v>5373231</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AO38" t="n">
         <v>2151399</v>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>3221831</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AQ38" t="n">
         <v>3.24</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AR38" t="n">
         <v>1.94</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AS38" t="n">
         <v>4.11</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>30.54</v>
       </c>
       <c r="AT38" t="n">
         <v>331122</v>
@@ -10117,16 +10179,16 @@
         <v>0</v>
       </c>
       <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
         <v>0.17</v>
       </c>
-      <c r="BI38" t="n">
+      <c r="BJ38" t="n">
         <v>0.14</v>
       </c>
-      <c r="BJ38" t="n">
+      <c r="BK38" t="n">
         <v>0.17</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>0.9</v>
       </c>
       <c r="BL38" t="n">
         <v>22796014477</v>
@@ -10291,7 +10353,9 @@
       <c r="F39" t="n">
         <v>5.1997</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>5.514</v>
+      </c>
       <c r="H39" t="n">
         <v>3970.149902</v>
       </c>
@@ -10331,7 +10395,9 @@
       <c r="T39" t="n">
         <v>1.657897</v>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="n">
+        <v>-0.59671</v>
+      </c>
       <c r="V39" t="n">
         <v>-2.611249</v>
       </c>
@@ -10363,46 +10429,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF39" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.84</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AH39" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AI39" t="n">
         <v>0.77</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AJ39" t="n">
         <v>103.08488</v>
       </c>
-      <c r="AJ39" t="n">
+      <c r="AK39" t="n">
         <v>98.64819</v>
       </c>
-      <c r="AK39" t="n">
+      <c r="AL39" t="n">
         <v>5.2078</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AM39" t="n">
         <v>5.2072</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AN39" t="n">
         <v>5370950</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>2136105</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>3234845</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>3.36</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>2.17</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AS39" t="n">
         <v>4.16</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>30.48</v>
       </c>
       <c r="AT39" t="n">
         <v>328098</v>
@@ -10447,16 +10513,16 @@
         <v>0</v>
       </c>
       <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI39" t="n">
+      <c r="BJ39" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ39" t="n">
+      <c r="BK39" t="n">
         <v>0.05</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>-0.06</v>
       </c>
       <c r="BL39" t="n">
         <v>20241628657</v>
@@ -10621,7 +10687,9 @@
       <c r="F40" t="n">
         <v>5.0927</v>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>5.5518</v>
+      </c>
       <c r="H40" t="n">
         <v>4109.310059</v>
       </c>
@@ -10661,7 +10729,9 @@
       <c r="T40" t="n">
         <v>-2.057809</v>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v>0.6855250000000001</v>
+      </c>
       <c r="V40" t="n">
         <v>3.505161</v>
       </c>
@@ -10693,46 +10763,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF40" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.71</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AI40" t="n">
         <v>0.64</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AJ40" t="n">
         <v>103.09631</v>
       </c>
-      <c r="AJ40" t="n">
+      <c r="AK40" t="n">
         <v>110.61458</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AL40" t="n">
         <v>5.0804</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AM40" t="n">
         <v>5.0798</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AN40" t="n">
         <v>5424811</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AO40" t="n">
         <v>2154900</v>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>3269910</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>2.2</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AS40" t="n">
         <v>4.11</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>30.99</v>
       </c>
       <c r="AT40" t="n">
         <v>341158</v>
@@ -10777,16 +10847,16 @@
         <v>0</v>
       </c>
       <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI40" t="n">
+      <c r="BJ40" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ40" t="n">
+      <c r="BK40" t="n">
         <v>-0.05</v>
-      </c>
-      <c r="BK40" t="n">
-        <v>0.51</v>
       </c>
       <c r="BL40" t="n">
         <v>32822911866</v>
@@ -10951,7 +11021,9 @@
       <c r="F41" t="n">
         <v>4.9762</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>5.4883</v>
+      </c>
       <c r="H41" t="n">
         <v>4169.47998</v>
       </c>
@@ -10991,7 +11063,9 @@
       <c r="T41" t="n">
         <v>-2.287586</v>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v>-1.143772</v>
+      </c>
       <c r="V41" t="n">
         <v>1.464234</v>
       </c>
@@ -11023,46 +11097,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF41" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG41" t="n">
         <v>0.61</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>0.53</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AJ41" t="n">
         <v>103.92975</v>
       </c>
-      <c r="AJ41" t="n">
+      <c r="AK41" t="n">
         <v>104.04532</v>
       </c>
-      <c r="AK41" t="n">
+      <c r="AL41" t="n">
         <v>5.0007</v>
       </c>
-      <c r="AL41" t="n">
+      <c r="AM41" t="n">
         <v>5.0001</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AN41" t="n">
         <v>5426307</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AO41" t="n">
         <v>2145000</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AP41" t="n">
         <v>3281308</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AQ41" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AR41" t="n">
         <v>2.45</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AS41" t="n">
         <v>4.26</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>31.62</v>
       </c>
       <c r="AT41" t="n">
         <v>345725</v>
@@ -11107,16 +11181,16 @@
         <v>0</v>
       </c>
       <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI41" t="n">
+      <c r="BJ41" t="n">
         <v>0.25</v>
       </c>
-      <c r="BJ41" t="n">
+      <c r="BK41" t="n">
         <v>0.15</v>
-      </c>
-      <c r="BK41" t="n">
-        <v>0.63</v>
       </c>
       <c r="BL41" t="n">
         <v>27100302410</v>
@@ -11269,7 +11343,9 @@
       <c r="F42" t="n">
         <v>5.0348</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>5.4012</v>
+      </c>
       <c r="H42" t="n">
         <v>4179.830078</v>
       </c>
@@ -11309,7 +11385,9 @@
       <c r="T42" t="n">
         <v>1.177604</v>
       </c>
-      <c r="U42" t="inlineStr"/>
+      <c r="U42" t="n">
+        <v>-1.587013</v>
+      </c>
       <c r="V42" t="n">
         <v>0.248235</v>
       </c>
@@ -11341,46 +11419,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF42" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG42" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AH42" t="n">
         <v>-1.84</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AI42" t="n">
         <v>0.36</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AJ42" t="n">
         <v>102.42356</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AK42" t="n">
         <v>102.71431</v>
       </c>
-      <c r="AK42" t="n">
+      <c r="AL42" t="n">
         <v>5.0959</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AM42" t="n">
         <v>5.0953</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AN42" t="n">
         <v>5453708</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>2145530</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
         <v>3308178</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AQ42" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AR42" t="n">
         <v>2.58</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AS42" t="n">
         <v>4.35</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>31.63</v>
       </c>
       <c r="AT42" t="n">
         <v>343489</v>
@@ -11425,16 +11503,16 @@
         <v>-0</v>
       </c>
       <c r="BH42" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI42" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI42" t="n">
+      <c r="BJ42" t="n">
         <v>0.13</v>
       </c>
-      <c r="BJ42" t="n">
+      <c r="BK42" t="n">
         <v>0.09</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>0.01</v>
       </c>
       <c r="BL42" t="n">
         <v>32666140787</v>
@@ -11595,7 +11673,9 @@
       <c r="F43" t="n">
         <v>4.8556</v>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>5.2739</v>
+      </c>
       <c r="H43" t="n">
         <v>4450.379883</v>
       </c>
@@ -11635,7 +11715,9 @@
       <c r="T43" t="n">
         <v>-3.559231</v>
       </c>
-      <c r="U43" t="inlineStr"/>
+      <c r="U43" t="n">
+        <v>-2.35688</v>
+      </c>
       <c r="V43" t="n">
         <v>6.472746</v>
       </c>
@@ -11667,46 +11749,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF43" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG43" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AH43" t="n">
         <v>-1.93</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AI43" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AJ43" t="n">
         <v>102.38761</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AK43" t="n">
         <v>102.27877</v>
       </c>
-      <c r="AK43" t="n">
+      <c r="AL43" t="n">
         <v>4.8192</v>
       </c>
-      <c r="AL43" t="n">
+      <c r="AM43" t="n">
         <v>4.8186</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AN43" t="n">
         <v>5479459</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AO43" t="n">
         <v>2169613</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AP43" t="n">
         <v>3309846</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AQ43" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
         <v>2.63</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AS43" t="n">
         <v>4.25</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>30.85</v>
       </c>
       <c r="AT43" t="n">
         <v>343620</v>
@@ -11751,16 +11833,16 @@
         <v>0</v>
       </c>
       <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BI43" t="n">
+      <c r="BJ43" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ43" t="n">
+      <c r="BK43" t="n">
         <v>-0.1</v>
-      </c>
-      <c r="BK43" t="n">
-        <v>-0.78</v>
       </c>
       <c r="BL43" t="n">
         <v>29600309149</v>
@@ -11917,7 +11999,9 @@
       <c r="F44" t="n">
         <v>4.7233</v>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>5.1895</v>
+      </c>
       <c r="H44" t="n">
         <v>4588.959961</v>
       </c>
@@ -11957,7 +12041,9 @@
       <c r="T44" t="n">
         <v>-2.724687</v>
       </c>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>-1.600337</v>
+      </c>
       <c r="V44" t="n">
         <v>3.113893</v>
       </c>
@@ -11989,46 +12075,46 @@
         <v>0.050788</v>
       </c>
       <c r="AF44" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG44" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AH44" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AI44" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AJ44" t="n">
         <v>102.90097</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AK44" t="n">
         <v>105.3498</v>
       </c>
-      <c r="AK44" t="n">
+      <c r="AL44" t="n">
         <v>4.7415</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AM44" t="n">
         <v>4.7409</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AN44" t="n">
         <v>5484871</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>2153541</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>3331330</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>3.63</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>2.73</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>4.22</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>30.43</v>
       </c>
       <c r="AT44" t="n">
         <v>345476</v>
@@ -12073,16 +12159,16 @@
         <v>0</v>
       </c>
       <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI44" t="n">
+      <c r="BJ44" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ44" t="n">
+      <c r="BK44" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="BK44" t="n">
-        <v>-0.42</v>
       </c>
       <c r="BL44" t="n">
         <v>28300073730</v>
@@ -12239,7 +12325,9 @@
       <c r="F45" t="n">
         <v>4.8884</v>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>5.313</v>
+      </c>
       <c r="H45" t="n">
         <v>4507.660156</v>
       </c>
@@ -12279,7 +12367,9 @@
       <c r="T45" t="n">
         <v>3.49544</v>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>2.379812</v>
+      </c>
       <c r="V45" t="n">
         <v>-1.771639</v>
       </c>
@@ -12311,46 +12401,46 @@
         <v>0.049189</v>
       </c>
       <c r="AF45" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="AG45" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AH45" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AI45" t="n">
         <v>0.2</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AJ45" t="n">
         <v>102.49883</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AK45" t="n">
         <v>106.05633</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AL45" t="n">
         <v>4.9219</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AM45" t="n">
         <v>4.9213</v>
       </c>
-      <c r="AM45" t="n">
+      <c r="AN45" t="n">
         <v>5559063</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AO45" t="n">
         <v>2172658</v>
       </c>
-      <c r="AO45" t="n">
+      <c r="AP45" t="n">
         <v>3386405</v>
       </c>
-      <c r="AP45" t="n">
+      <c r="AQ45" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AR45" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AS45" t="n">
         <v>4.12</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>29.92</v>
       </c>
       <c r="AT45" t="n">
         <v>344177</v>
@@ -12395,16 +12485,16 @@
         <v>-0.001599</v>
       </c>
       <c r="BH45" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="BI45" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BI45" t="n">
+      <c r="BJ45" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ45" t="n">
+      <c r="BK45" t="n">
         <v>-0.1</v>
-      </c>
-      <c r="BK45" t="n">
-        <v>-0.51</v>
       </c>
       <c r="BL45" t="n">
         <v>31101089774</v>
@@ -12565,7 +12655,9 @@
       <c r="F46" t="n">
         <v>5.0328</v>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>5.3197</v>
+      </c>
       <c r="H46" t="n">
         <v>4288.049805</v>
       </c>
@@ -12605,7 +12697,9 @@
       <c r="T46" t="n">
         <v>2.953934</v>
       </c>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>0.126098</v>
+      </c>
       <c r="V46" t="n">
         <v>-4.871937</v>
       </c>
@@ -12637,46 +12731,46 @@
         <v>0.048422</v>
       </c>
       <c r="AF46" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AH46" t="n">
         <v>0.37</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AI46" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AJ46" t="n">
         <v>102.5197</v>
       </c>
-      <c r="AJ46" t="n">
+      <c r="AK46" t="n">
         <v>101.75432</v>
       </c>
-      <c r="AK46" t="n">
+      <c r="AL46" t="n">
         <v>5.0076</v>
       </c>
-      <c r="AL46" t="n">
+      <c r="AM46" t="n">
         <v>5.007</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AN46" t="n">
         <v>5625945</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>2215175</v>
       </c>
-      <c r="AO46" t="n">
+      <c r="AP46" t="n">
         <v>3410769</v>
       </c>
-      <c r="AP46" t="n">
+      <c r="AQ46" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AR46" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AS46" t="n">
         <v>4</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>29.66</v>
       </c>
       <c r="AT46" t="n">
         <v>340324</v>
@@ -12721,16 +12815,16 @@
         <v>-0.000768</v>
       </c>
       <c r="BH46" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="BI46" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BI46" t="n">
+      <c r="BJ46" t="n">
         <v>0</v>
       </c>
-      <c r="BJ46" t="n">
+      <c r="BK46" t="n">
         <v>-0.12</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>-0.26</v>
       </c>
       <c r="BL46" t="n">
         <v>28713085056</v>
@@ -12887,7 +12981,9 @@
       <c r="F47" t="n">
         <v>5.0461</v>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>5.3537</v>
+      </c>
       <c r="H47" t="n">
         <v>4193.799805</v>
       </c>
@@ -12927,7 +13023,9 @@
       <c r="T47" t="n">
         <v>0.264265</v>
       </c>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>0.639141</v>
+      </c>
       <c r="V47" t="n">
         <v>-2.197969</v>
       </c>
@@ -12959,46 +13057,46 @@
         <v>0.047279</v>
       </c>
       <c r="AF47" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="AG47" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AJ47" t="n">
         <v>102.8499</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AK47" t="n">
         <v>101.94034</v>
       </c>
-      <c r="AK47" t="n">
+      <c r="AL47" t="n">
         <v>5.0575</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AM47" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AM47" t="n">
+      <c r="AN47" t="n">
         <v>5653808</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AO47" t="n">
         <v>2204808</v>
       </c>
-      <c r="AO47" t="n">
+      <c r="AP47" t="n">
         <v>3449000</v>
       </c>
-      <c r="AP47" t="n">
+      <c r="AQ47" t="n">
         <v>3.56</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AR47" t="n">
         <v>2.92</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AS47" t="n">
         <v>3.97</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>29.24</v>
       </c>
       <c r="AT47" t="n">
         <v>340247</v>
@@ -13043,16 +13141,16 @@
         <v>-0.001143</v>
       </c>
       <c r="BH47" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="BI47" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI47" t="n">
+      <c r="BJ47" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ47" t="n">
+      <c r="BK47" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="BK47" t="n">
-        <v>-0.42</v>
       </c>
       <c r="BL47" t="n">
         <v>29681867318</v>
@@ -13209,7 +13307,9 @@
       <c r="F48" t="n">
         <v>4.9041</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>5.3628</v>
+      </c>
       <c r="H48" t="n">
         <v>4567.799805</v>
       </c>
@@ -13249,7 +13349,9 @@
       <c r="T48" t="n">
         <v>-2.814058</v>
       </c>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>0.169975</v>
+      </c>
       <c r="V48" t="n">
         <v>8.917927000000001</v>
       </c>
@@ -13281,46 +13383,46 @@
         <v>0.045601</v>
       </c>
       <c r="AF48" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="AG48" t="n">
         <v>0.28</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AH48" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AI48" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AJ48" t="n">
         <v>103.60561</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AK48" t="n">
         <v>101.67978</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AL48" t="n">
         <v>4.9355</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AM48" t="n">
         <v>4.9349</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AN48" t="n">
         <v>5711103</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AO48" t="n">
         <v>2220766</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>3490337</v>
       </c>
-      <c r="AP48" t="n">
+      <c r="AQ48" t="n">
         <v>3.53</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AR48" t="n">
         <v>2.99</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AS48" t="n">
         <v>3.88</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>29.01</v>
       </c>
       <c r="AT48" t="n">
         <v>348406</v>
@@ -13365,16 +13467,16 @@
         <v>-0.001678</v>
       </c>
       <c r="BH48" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="BI48" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI48" t="n">
+      <c r="BJ48" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BK48" t="n">
         <v>-0.09</v>
-      </c>
-      <c r="BK48" t="n">
-        <v>-0.23</v>
       </c>
       <c r="BL48" t="n">
         <v>27886116219</v>
@@ -13531,7 +13633,9 @@
       <c r="F49" t="n">
         <v>4.8502</v>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>5.343</v>
+      </c>
       <c r="H49" t="n">
         <v>4769.830078</v>
       </c>
@@ -13571,7 +13675,9 @@
       <c r="T49" t="n">
         <v>-1.099076</v>
       </c>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v>-0.369214</v>
+      </c>
       <c r="V49" t="n">
         <v>4.422923</v>
       </c>
@@ -13603,46 +13709,46 @@
         <v>0.044537</v>
       </c>
       <c r="AF49" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="AG49" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AH49" t="n">
         <v>0.74</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AJ49" t="n">
         <v>104.8968</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AK49" t="n">
         <v>101.67778</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AL49" t="n">
         <v>4.8413</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AM49" t="n">
         <v>4.8407</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AN49" t="n">
         <v>5805157</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>2283485</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
         <v>3521672</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AQ49" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
         <v>2.59</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AS49" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>28.14</v>
       </c>
       <c r="AT49" t="n">
         <v>355034</v>
@@ -13687,16 +13793,16 @@
         <v>-0.001064</v>
       </c>
       <c r="BH49" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="BI49" t="n">
         <v>-0.24</v>
       </c>
-      <c r="BI49" t="n">
+      <c r="BJ49" t="n">
         <v>-0.4</v>
       </c>
-      <c r="BJ49" t="n">
+      <c r="BK49" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="BK49" t="n">
-        <v>-0.87</v>
       </c>
       <c r="BL49" t="n">
         <v>28786226565</v>
@@ -13857,7 +13963,9 @@
       <c r="F50" t="n">
         <v>4.9503</v>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>5.3604</v>
+      </c>
       <c r="H50" t="n">
         <v>4845.649902</v>
       </c>
@@ -13897,7 +14005,9 @@
       <c r="T50" t="n">
         <v>2.063833</v>
       </c>
-      <c r="U50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v>0.325665</v>
+      </c>
       <c r="V50" t="n">
         <v>1.589571</v>
       </c>
@@ -13929,46 +14039,46 @@
         <v>0.043739</v>
       </c>
       <c r="AF50" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG50" t="n">
         <v>0.42</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AH50" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AI50" t="n">
         <v>0.57</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AJ50" t="n">
         <v>104.46088</v>
       </c>
-      <c r="AJ50" t="n">
+      <c r="AK50" t="n">
         <v>99.30432999999999</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AL50" t="n">
         <v>4.9535</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AM50" t="n">
         <v>4.9529</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AN50" t="n">
         <v>5794707</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AO50" t="n">
         <v>2234362</v>
       </c>
-      <c r="AO50" t="n">
+      <c r="AP50" t="n">
         <v>3560345</v>
       </c>
-      <c r="AP50" t="n">
+      <c r="AQ50" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AR50" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>3.76</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>28</v>
       </c>
       <c r="AT50" t="n">
         <v>355066</v>
@@ -14013,16 +14123,16 @@
         <v>-0.000798</v>
       </c>
       <c r="BH50" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="BI50" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI50" t="n">
+      <c r="BJ50" t="n">
         <v>0.18</v>
       </c>
-      <c r="BJ50" t="n">
+      <c r="BK50" t="n">
         <v>0.01</v>
-      </c>
-      <c r="BK50" t="n">
-        <v>-0.14</v>
       </c>
       <c r="BL50" t="n">
         <v>26702655353</v>
@@ -14179,7 +14289,9 @@
       <c r="F51" t="n">
         <v>4.9673</v>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>5.381</v>
+      </c>
       <c r="H51" t="n">
         <v>5096.27002</v>
       </c>
@@ -14219,7 +14331,9 @@
       <c r="T51" t="n">
         <v>0.343408</v>
       </c>
-      <c r="U51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>0.384297</v>
+      </c>
       <c r="V51" t="n">
         <v>5.172064</v>
       </c>
@@ -14251,46 +14365,46 @@
         <v>0.041957</v>
       </c>
       <c r="AF51" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="AG51" t="n">
         <v>0.83</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AH51" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AI51" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AJ51" t="n">
         <v>104.65783</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AK51" t="n">
         <v>102.15308</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AL51" t="n">
         <v>4.9833</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AM51" t="n">
         <v>4.9827</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AN51" t="n">
         <v>5815954</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>2235302</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>3580652</v>
       </c>
-      <c r="AP51" t="n">
+      <c r="AQ51" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AR51" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AS51" t="n">
         <v>3.76</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>27.85</v>
       </c>
       <c r="AT51" t="n">
         <v>352705</v>
@@ -14335,16 +14449,16 @@
         <v>-0.001782</v>
       </c>
       <c r="BH51" t="n">
+        <v>-0.001782</v>
+      </c>
+      <c r="BI51" t="n">
         <v>0</v>
       </c>
-      <c r="BI51" t="n">
+      <c r="BJ51" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BK51" t="n">
         <v>0</v>
-      </c>
-      <c r="BK51" t="n">
-        <v>-0.15</v>
       </c>
       <c r="BL51" t="n">
         <v>23348254025</v>
@@ -14497,7 +14611,9 @@
       <c r="F52" t="n">
         <v>5.0141</v>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>5.4065</v>
+      </c>
       <c r="H52" t="n">
         <v>5254.350098</v>
       </c>
@@ -14537,7 +14653,9 @@
       <c r="T52" t="n">
         <v>0.942164</v>
       </c>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" t="n">
+        <v>0.473886</v>
+      </c>
       <c r="V52" t="n">
         <v>3.101878</v>
       </c>
@@ -14569,46 +14687,46 @@
         <v>0.04142</v>
       </c>
       <c r="AF52" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="AG52" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AH52" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AI52" t="n">
         <v>0.19</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AJ52" t="n">
         <v>104.68489</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AK52" t="n">
         <v>109.56238</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AL52" t="n">
         <v>4.9962</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AM52" t="n">
         <v>4.9956</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AN52" t="n">
         <v>5899742</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AO52" t="n">
         <v>2285775</v>
       </c>
-      <c r="AO52" t="n">
+      <c r="AP52" t="n">
         <v>3613967</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AR52" t="n">
         <v>2.71</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AS52" t="n">
         <v>3.71</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>28.14</v>
       </c>
       <c r="AT52" t="n">
         <v>355008</v>
@@ -14653,7 +14771,7 @@
         <v>-0.000537</v>
       </c>
       <c r="BH52" t="n">
-        <v>-0.05</v>
+        <v>-0.000537</v>
       </c>
       <c r="BI52" t="n">
         <v>-0.05</v>
@@ -14662,7 +14780,7 @@
         <v>-0.05</v>
       </c>
       <c r="BK52" t="n">
-        <v>0.29</v>
+        <v>-0.05</v>
       </c>
       <c r="BL52" t="n">
         <v>27657419417</v>
@@ -14823,7 +14941,9 @@
       <c r="F53" t="n">
         <v>5.117</v>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>5.4794</v>
+      </c>
       <c r="H53" t="n">
         <v>5035.689941</v>
       </c>
@@ -14863,7 +14983,9 @@
       <c r="T53" t="n">
         <v>2.052213</v>
       </c>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="n">
+        <v>1.348382</v>
+      </c>
       <c r="V53" t="n">
         <v>-4.161507</v>
       </c>
@@ -14895,46 +15017,46 @@
         <v>0.040168</v>
       </c>
       <c r="AF53" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG53" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AH53" t="n">
         <v>0.31</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AI53" t="n">
         <v>0.37</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
         <v>104.62189</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AK53" t="n">
         <v>109.26273</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AL53" t="n">
         <v>5.1718</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AM53" t="n">
         <v>5.1712</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AN53" t="n">
         <v>5915538</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AO53" t="n">
         <v>2268879</v>
       </c>
-      <c r="AO53" t="n">
+      <c r="AP53" t="n">
         <v>3646659</v>
       </c>
-      <c r="AP53" t="n">
+      <c r="AQ53" t="n">
         <v>3.37</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AR53" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AS53" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>27.86</v>
       </c>
       <c r="AT53" t="n">
         <v>351599</v>
@@ -14979,16 +15101,16 @@
         <v>-0.001252</v>
       </c>
       <c r="BH53" t="n">
+        <v>-0.001252</v>
+      </c>
+      <c r="BI53" t="n">
         <v>0.04</v>
       </c>
-      <c r="BI53" t="n">
+      <c r="BJ53" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ53" t="n">
+      <c r="BK53" t="n">
         <v>0.04</v>
-      </c>
-      <c r="BK53" t="n">
-        <v>-0.28</v>
       </c>
       <c r="BL53" t="n">
         <v>30327524963</v>
@@ -15145,7 +15267,9 @@
       <c r="F54" t="n">
         <v>5.2021</v>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>5.6311</v>
+      </c>
       <c r="H54" t="n">
         <v>5277.509766</v>
       </c>
@@ -15185,7 +15309,9 @@
       <c r="T54" t="n">
         <v>1.663078</v>
       </c>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="n">
+        <v>2.768552</v>
+      </c>
       <c r="V54" t="n">
         <v>4.802119</v>
       </c>
@@ -15217,46 +15343,46 @@
         <v>0.039484</v>
       </c>
       <c r="AF54" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="AG54" t="n">
         <v>0.46</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AH54" t="n">
         <v>0.89</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AI54" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AJ54" t="n">
         <v>105.5883</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AK54" t="n">
         <v>104.70903</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AL54" t="n">
         <v>5.2416</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AM54" t="n">
         <v>5.241</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AN54" t="n">
         <v>5953960</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AO54" t="n">
         <v>2278309</v>
       </c>
-      <c r="AO54" t="n">
+      <c r="AP54" t="n">
         <v>3675652</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AQ54" t="n">
         <v>3.43</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AR54" t="n">
         <v>2.8</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AS54" t="n">
         <v>3.82</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>27.75</v>
       </c>
       <c r="AT54" t="n">
         <v>355560</v>
@@ -15301,16 +15427,16 @@
         <v>-0.000684</v>
       </c>
       <c r="BH54" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="BI54" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI54" t="n">
+      <c r="BJ54" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ54" t="n">
+      <c r="BK54" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="BK54" t="n">
-        <v>-0.11</v>
       </c>
       <c r="BL54" t="n">
         <v>30190264650</v>
@@ -15471,7 +15597,9 @@
       <c r="F55" t="n">
         <v>5.5005</v>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>5.8909</v>
+      </c>
       <c r="H55" t="n">
         <v>5460.47998</v>
       </c>
@@ -15511,7 +15639,9 @@
       <c r="T55" t="n">
         <v>5.736153</v>
       </c>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="n">
+        <v>4.613663</v>
+      </c>
       <c r="V55" t="n">
         <v>3.46698</v>
       </c>
@@ -15543,46 +15673,46 @@
         <v>0.03927</v>
       </c>
       <c r="AF55" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG55" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AH55" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AI55" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
         <v>106.56647</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AK55" t="n">
         <v>105.86342</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AL55" t="n">
         <v>5.5589</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AM55" t="n">
         <v>5.5583</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AN55" t="n">
         <v>6041898</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AO55" t="n">
         <v>2336858</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AP55" t="n">
         <v>3705041</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AQ55" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AR55" t="n">
         <v>2.64</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AS55" t="n">
         <v>3.71</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>27.81</v>
       </c>
       <c r="AT55" t="n">
         <v>357827</v>
@@ -15627,16 +15757,16 @@
         <v>-0.000214</v>
       </c>
       <c r="BH55" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="BI55" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BI55" t="n">
+      <c r="BJ55" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BJ55" t="n">
+      <c r="BK55" t="n">
         <v>-0.11</v>
-      </c>
-      <c r="BK55" t="n">
-        <v>0.06</v>
       </c>
       <c r="BL55" t="n">
         <v>28731639979</v>
@@ -15797,7 +15927,9 @@
       <c r="F56" t="n">
         <v>5.6111</v>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>6.0695</v>
+      </c>
       <c r="H56" t="n">
         <v>5522.299805</v>
       </c>
@@ -15837,7 +15969,9 @@
       <c r="T56" t="n">
         <v>2.010726</v>
       </c>
-      <c r="U56" t="inlineStr"/>
+      <c r="U56" t="n">
+        <v>3.031792</v>
+      </c>
       <c r="V56" t="n">
         <v>1.132132</v>
       </c>
@@ -15869,46 +16003,46 @@
         <v>0.03927</v>
       </c>
       <c r="AF56" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG56" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AH56" t="n">
         <v>0.61</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AI56" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AJ56" t="n">
         <v>107.07017</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AK56" t="n">
         <v>111.51644</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AL56" t="n">
         <v>5.6621</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AM56" t="n">
         <v>5.6615</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AN56" t="n">
         <v>6069205</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AO56" t="n">
         <v>2323362</v>
       </c>
-      <c r="AO56" t="n">
+      <c r="AP56" t="n">
         <v>3745844</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AQ56" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AR56" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AS56" t="n">
         <v>3.78</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>27.74</v>
       </c>
       <c r="AT56" t="n">
         <v>363282</v>
@@ -15953,16 +16087,16 @@
         <v>0</v>
       </c>
       <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI56" t="n">
+      <c r="BJ56" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BJ56" t="n">
+      <c r="BK56" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="BK56" t="n">
-        <v>-0.07000000000000001</v>
       </c>
       <c r="BL56" t="n">
         <v>30841394890</v>
@@ -16123,7 +16257,9 @@
       <c r="F57" t="n">
         <v>5.6277</v>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>6.2224</v>
+      </c>
       <c r="H57" t="n">
         <v>5648.399902</v>
       </c>
@@ -16163,7 +16299,9 @@
       <c r="T57" t="n">
         <v>0.295836</v>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="n">
+        <v>2.519157</v>
+      </c>
       <c r="V57" t="n">
         <v>2.283471</v>
       </c>
@@ -16195,46 +16333,46 @@
         <v>0.03927</v>
       </c>
       <c r="AF57" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG57" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AH57" t="n">
         <v>0.29</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AI57" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AJ57" t="n">
         <v>107.19578</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AK57" t="n">
         <v>110.06495</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AL57" t="n">
         <v>5.6562</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AM57" t="n">
         <v>5.6556</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AN57" t="n">
         <v>6135298</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AO57" t="n">
         <v>2344397</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AP57" t="n">
         <v>3790900</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AQ57" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AR57" t="n">
         <v>2.55</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AS57" t="n">
         <v>3.82</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>27.59</v>
       </c>
       <c r="AT57" t="n">
         <v>369214</v>
@@ -16279,16 +16417,16 @@
         <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BI57" t="n">
         <v>0.03</v>
       </c>
       <c r="BJ57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BK57" t="n">
         <v>0.04</v>
-      </c>
-      <c r="BK57" t="n">
-        <v>-0.15</v>
       </c>
       <c r="BL57" t="n">
         <v>28736329972</v>
@@ -16449,7 +16587,9 @@
       <c r="F58" t="n">
         <v>5.4332</v>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>6.0652</v>
+      </c>
       <c r="H58" t="n">
         <v>5762.47998</v>
       </c>
@@ -16489,7 +16629,9 @@
       <c r="T58" t="n">
         <v>-3.456118</v>
       </c>
-      <c r="U58" t="inlineStr"/>
+      <c r="U58" t="n">
+        <v>-2.526362</v>
+      </c>
       <c r="V58" t="n">
         <v>2.019688</v>
       </c>
@@ -16521,46 +16663,46 @@
         <v>0.039612</v>
       </c>
       <c r="AF58" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="AG58" t="n">
         <v>0.44</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AH58" t="n">
         <v>0.62</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AI58" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AJ58" t="n">
         <v>108.05141</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AK58" t="n">
         <v>107.07576</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AL58" t="n">
         <v>5.4481</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AM58" t="n">
         <v>5.4475</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AN58" t="n">
         <v>6216528</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AO58" t="n">
         <v>2384828</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AP58" t="n">
         <v>3831700</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AQ58" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AR58" t="n">
         <v>2.56</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AS58" t="n">
         <v>3.83</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>27.49</v>
       </c>
       <c r="AT58" t="n">
         <v>372016</v>
@@ -16605,7 +16747,7 @@
         <v>0.000342</v>
       </c>
       <c r="BH58" t="n">
-        <v>0.01</v>
+        <v>0.000342</v>
       </c>
       <c r="BI58" t="n">
         <v>0.01</v>
@@ -16614,7 +16756,7 @@
         <v>0.01</v>
       </c>
       <c r="BK58" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="BL58" t="n">
         <v>28471402288</v>
@@ -16775,7 +16917,9 @@
       <c r="F59" t="n">
         <v>5.7623</v>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>6.2522</v>
+      </c>
       <c r="H59" t="n">
         <v>5705.450195</v>
       </c>
@@ -16815,7 +16959,9 @@
       <c r="T59" t="n">
         <v>6.057206</v>
       </c>
-      <c r="U59" t="inlineStr"/>
+      <c r="U59" t="n">
+        <v>3.083168</v>
+      </c>
       <c r="V59" t="n">
         <v>-0.9896740000000001</v>
       </c>
@@ -16847,46 +16993,46 @@
         <v>0.040168</v>
       </c>
       <c r="AF59" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG59" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AH59" t="n">
         <v>1.52</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AI59" t="n">
         <v>0.61</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AJ59" t="n">
         <v>108.26621</v>
       </c>
-      <c r="AJ59" t="n">
+      <c r="AK59" t="n">
         <v>109.19299</v>
       </c>
-      <c r="AK59" t="n">
+      <c r="AL59" t="n">
         <v>5.7779</v>
       </c>
-      <c r="AL59" t="n">
+      <c r="AM59" t="n">
         <v>5.7773</v>
       </c>
-      <c r="AM59" t="n">
+      <c r="AN59" t="n">
         <v>6275117</v>
       </c>
-      <c r="AN59" t="n">
+      <c r="AO59" t="n">
         <v>2397533</v>
       </c>
-      <c r="AO59" t="n">
+      <c r="AP59" t="n">
         <v>3877584</v>
       </c>
-      <c r="AP59" t="n">
+      <c r="AQ59" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AR59" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AS59" t="n">
         <v>3.79</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>27.94</v>
       </c>
       <c r="AT59" t="n">
         <v>366096</v>
@@ -16931,7 +17077,7 @@
         <v>0.000556</v>
       </c>
       <c r="BH59" t="n">
-        <v>-0.04</v>
+        <v>0.000556</v>
       </c>
       <c r="BI59" t="n">
         <v>-0.04</v>
@@ -16940,7 +17086,7 @@
         <v>-0.04</v>
       </c>
       <c r="BK59" t="n">
-        <v>0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="BL59" t="n">
         <v>29300866189</v>
@@ -17093,7 +17239,9 @@
       <c r="F60" t="n">
         <v>6.0139</v>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>6.345178</v>
+      </c>
       <c r="H60" t="n">
         <v>6032.379883</v>
       </c>
@@ -17133,7 +17281,9 @@
       <c r="T60" t="n">
         <v>4.366308</v>
       </c>
-      <c r="U60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>1.487125</v>
+      </c>
       <c r="V60" t="n">
         <v>5.73013</v>
       </c>
@@ -17165,46 +17315,46 @@
         <v>0.04158</v>
       </c>
       <c r="AF60" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="AG60" t="n">
         <v>0.39</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AH60" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AI60" t="n">
         <v>0.33</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AJ60" t="n">
         <v>108.02232</v>
       </c>
-      <c r="AJ60" t="n">
+      <c r="AK60" t="n">
         <v>105.49378</v>
       </c>
-      <c r="AK60" t="n">
+      <c r="AL60" t="n">
         <v>6.0535</v>
       </c>
-      <c r="AL60" t="n">
+      <c r="AM60" t="n">
         <v>6.0529</v>
       </c>
-      <c r="AM60" t="n">
+      <c r="AN60" t="n">
         <v>6365690</v>
       </c>
-      <c r="AN60" t="n">
+      <c r="AO60" t="n">
         <v>2436022</v>
       </c>
-      <c r="AO60" t="n">
+      <c r="AP60" t="n">
         <v>3929668</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AQ60" t="n">
         <v>3.27</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AR60" t="n">
         <v>2.5</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AS60" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>28.45</v>
       </c>
       <c r="AT60" t="n">
         <v>363003</v>
@@ -17249,16 +17399,16 @@
         <v>0.001412</v>
       </c>
       <c r="BH60" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="BI60" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI60" t="n">
+      <c r="BJ60" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ60" t="n">
+      <c r="BK60" t="n">
         <v>-0.04</v>
-      </c>
-      <c r="BK60" t="n">
-        <v>0.51</v>
       </c>
       <c r="BL60" t="n">
         <v>27857365197</v>
@@ -17419,7 +17569,9 @@
       <c r="F61" t="n">
         <v>6.1779</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>6.422608</v>
+      </c>
       <c r="H61" t="n">
         <v>5881.629883</v>
       </c>
@@ -17459,7 +17611,9 @@
       <c r="T61" t="n">
         <v>2.727016</v>
       </c>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>1.220293</v>
+      </c>
       <c r="V61" t="n">
         <v>-2.499014</v>
       </c>
@@ -17491,46 +17645,46 @@
         <v>0.044158</v>
       </c>
       <c r="AF61" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="AG61" t="n">
         <v>0.52</v>
       </c>
-      <c r="AG61" t="n">
+      <c r="AH61" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AH61" t="n">
+      <c r="AI61" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI61" t="n">
+      <c r="AJ61" t="n">
         <v>107.37891</v>
       </c>
-      <c r="AJ61" t="n">
+      <c r="AK61" t="n">
         <v>104.15073</v>
       </c>
-      <c r="AK61" t="n">
+      <c r="AL61" t="n">
         <v>6.1923</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AM61" t="n">
         <v>6.1917</v>
       </c>
-      <c r="AM61" t="n">
+      <c r="AN61" t="n">
         <v>6464602</v>
       </c>
-      <c r="AN61" t="n">
+      <c r="AO61" t="n">
         <v>2499177</v>
       </c>
-      <c r="AO61" t="n">
+      <c r="AP61" t="n">
         <v>3965425</v>
       </c>
-      <c r="AP61" t="n">
+      <c r="AQ61" t="n">
         <v>3.08</v>
       </c>
-      <c r="AQ61" t="n">
+      <c r="AR61" t="n">
         <v>2.21</v>
       </c>
-      <c r="AR61" t="n">
+      <c r="AS61" t="n">
         <v>3.63</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>28.5</v>
       </c>
       <c r="AT61" t="n">
         <v>329730</v>
@@ -17575,16 +17729,16 @@
         <v>0.002578</v>
       </c>
       <c r="BH61" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="BI61" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BI61" t="n">
+      <c r="BJ61" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BJ61" t="n">
+      <c r="BK61" t="n">
         <v>-0.12</v>
-      </c>
-      <c r="BK61" t="n">
-        <v>0.05</v>
       </c>
       <c r="BL61" t="n">
         <v>24881044787</v>
@@ -17745,7 +17899,9 @@
       <c r="F62" t="n">
         <v>5.8745</v>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>6.101281</v>
+      </c>
       <c r="H62" t="n">
         <v>6040.529785</v>
       </c>
@@ -17785,7 +17941,9 @@
       <c r="T62" t="n">
         <v>-4.911055</v>
       </c>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="n">
+        <v>-5.003057</v>
+      </c>
       <c r="V62" t="n">
         <v>2.70163</v>
       </c>
@@ -17817,46 +17975,46 @@
         <v>0.045833</v>
       </c>
       <c r="AF62" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="AG62" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG62" t="n">
+      <c r="AH62" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH62" t="n">
+      <c r="AI62" t="n">
         <v>0</v>
       </c>
-      <c r="AI62" t="n">
+      <c r="AJ62" t="n">
         <v>108.05509</v>
       </c>
-      <c r="AJ62" t="n">
+      <c r="AK62" t="n">
         <v>102.6229</v>
       </c>
-      <c r="AK62" t="n">
+      <c r="AL62" t="n">
         <v>5.8301</v>
       </c>
-      <c r="AL62" t="n">
+      <c r="AM62" t="n">
         <v>5.8295</v>
       </c>
-      <c r="AM62" t="n">
+      <c r="AN62" t="n">
         <v>6465016</v>
       </c>
-      <c r="AN62" t="n">
+      <c r="AO62" t="n">
         <v>2451957</v>
       </c>
-      <c r="AO62" t="n">
+      <c r="AP62" t="n">
         <v>4013059</v>
       </c>
-      <c r="AP62" t="n">
+      <c r="AQ62" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ62" t="n">
+      <c r="AR62" t="n">
         <v>2.43</v>
       </c>
-      <c r="AR62" t="n">
+      <c r="AS62" t="n">
         <v>3.89</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>29.88</v>
       </c>
       <c r="AT62" t="n">
         <v>328303</v>
@@ -17901,16 +18059,16 @@
         <v>0.001675</v>
       </c>
       <c r="BH62" t="n">
+        <v>0.001675</v>
+      </c>
+      <c r="BI62" t="n">
         <v>0.26</v>
       </c>
-      <c r="BI62" t="n">
+      <c r="BJ62" t="n">
         <v>0.22</v>
       </c>
-      <c r="BJ62" t="n">
+      <c r="BK62" t="n">
         <v>0.26</v>
-      </c>
-      <c r="BK62" t="n">
-        <v>1.38</v>
       </c>
       <c r="BL62" t="n">
         <v>25398231759</v>
@@ -18075,7 +18233,9 @@
       <c r="F63" t="n">
         <v>5.839</v>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>6.064281</v>
+      </c>
       <c r="H63" t="n">
         <v>5954.5</v>
       </c>
@@ -18115,7 +18275,9 @@
       <c r="T63" t="n">
         <v>-0.604299</v>
       </c>
-      <c r="U63" t="inlineStr"/>
+      <c r="U63" t="n">
+        <v>-0.606433</v>
+      </c>
       <c r="V63" t="n">
         <v>-1.424209</v>
       </c>
@@ -18147,46 +18309,46 @@
         <v>0.049037</v>
       </c>
       <c r="AF63" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG63" t="n">
         <v>1.31</v>
       </c>
-      <c r="AG63" t="n">
+      <c r="AH63" t="n">
         <v>1.06</v>
       </c>
-      <c r="AH63" t="n">
+      <c r="AI63" t="n">
         <v>1.48</v>
       </c>
-      <c r="AI63" t="n">
+      <c r="AJ63" t="n">
         <v>108.57481</v>
       </c>
-      <c r="AJ63" t="n">
+      <c r="AK63" t="n">
         <v>106.79048</v>
       </c>
-      <c r="AK63" t="n">
+      <c r="AL63" t="n">
         <v>5.8488</v>
       </c>
-      <c r="AL63" t="n">
+      <c r="AM63" t="n">
         <v>5.8482</v>
       </c>
-      <c r="AM63" t="n">
+      <c r="AN63" t="n">
         <v>6511444</v>
       </c>
-      <c r="AN63" t="n">
+      <c r="AO63" t="n">
         <v>2477151</v>
       </c>
-      <c r="AO63" t="n">
+      <c r="AP63" t="n">
         <v>4034293</v>
       </c>
-      <c r="AP63" t="n">
+      <c r="AQ63" t="n">
         <v>3.41</v>
       </c>
-      <c r="AQ63" t="n">
+      <c r="AR63" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR63" t="n">
+      <c r="AS63" t="n">
         <v>3.96</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>30.53</v>
       </c>
       <c r="AT63" t="n">
         <v>332508</v>
@@ -18231,16 +18393,16 @@
         <v>0.003204</v>
       </c>
       <c r="BH63" t="n">
+        <v>0.003204</v>
+      </c>
+      <c r="BI63" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BI63" t="n">
+      <c r="BJ63" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ63" t="n">
+      <c r="BK63" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="BK63" t="n">
-        <v>0.65</v>
       </c>
       <c r="BL63" t="n">
         <v>22753954039</v>
@@ -18401,7 +18563,9 @@
       <c r="F64" t="n">
         <v>5.7581</v>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>6.22665</v>
+      </c>
       <c r="H64" t="n">
         <v>5611.850098</v>
       </c>
@@ -18441,7 +18605,9 @@
       <c r="T64" t="n">
         <v>-1.385514</v>
       </c>
-      <c r="U64" t="inlineStr"/>
+      <c r="U64" t="n">
+        <v>2.677469</v>
+      </c>
       <c r="V64" t="n">
         <v>-5.75447</v>
       </c>
@@ -18473,46 +18639,46 @@
         <v>0.050508</v>
       </c>
       <c r="AF64" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="AG64" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG64" t="n">
+      <c r="AH64" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AH64" t="n">
+      <c r="AI64" t="n">
         <v>0.51</v>
       </c>
-      <c r="AI64" t="n">
+      <c r="AJ64" t="n">
         <v>110.03087</v>
       </c>
-      <c r="AJ64" t="n">
+      <c r="AK64" t="n">
         <v>113.99468</v>
       </c>
-      <c r="AK64" t="n">
+      <c r="AL64" t="n">
         <v>5.7422</v>
       </c>
-      <c r="AL64" t="n">
+      <c r="AM64" t="n">
         <v>5.7416</v>
       </c>
-      <c r="AM64" t="n">
+      <c r="AN64" t="n">
         <v>6576464</v>
       </c>
-      <c r="AN64" t="n">
+      <c r="AO64" t="n">
         <v>2498262</v>
       </c>
-      <c r="AO64" t="n">
+      <c r="AP64" t="n">
         <v>4078202</v>
       </c>
-      <c r="AP64" t="n">
+      <c r="AQ64" t="n">
         <v>3.44</v>
       </c>
-      <c r="AQ64" t="n">
+      <c r="AR64" t="n">
         <v>2.49</v>
       </c>
-      <c r="AR64" t="n">
+      <c r="AS64" t="n">
         <v>4.03</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>31.34</v>
       </c>
       <c r="AT64" t="n">
         <v>336157</v>
@@ -18557,16 +18723,16 @@
         <v>0.001471</v>
       </c>
       <c r="BH64" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="BI64" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI64" t="n">
+      <c r="BJ64" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ64" t="n">
+      <c r="BK64" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="BK64" t="n">
-        <v>0.8100000000000001</v>
       </c>
       <c r="BL64" t="n">
         <v>28725872006</v>
@@ -18723,7 +18889,9 @@
       <c r="F65" t="n">
         <v>5.62</v>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>6.393862</v>
+      </c>
       <c r="H65" t="n">
         <v>5569.060059</v>
       </c>
@@ -18763,7 +18931,9 @@
       <c r="T65" t="n">
         <v>-2.398363</v>
       </c>
-      <c r="U65" t="inlineStr"/>
+      <c r="U65" t="n">
+        <v>2.685417</v>
+      </c>
       <c r="V65" t="n">
         <v>-0.762494</v>
       </c>
@@ -18795,46 +18965,46 @@
         <v>0.052531</v>
       </c>
       <c r="AF65" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="AG65" t="n">
         <v>0.43</v>
       </c>
-      <c r="AG65" t="n">
+      <c r="AH65" t="n">
         <v>0.24</v>
       </c>
-      <c r="AH65" t="n">
+      <c r="AI65" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI65" t="n">
+      <c r="AJ65" t="n">
         <v>109.51799</v>
       </c>
-      <c r="AJ65" t="n">
+      <c r="AK65" t="n">
         <v>112.60116</v>
       </c>
-      <c r="AK65" t="n">
+      <c r="AL65" t="n">
         <v>5.6608</v>
       </c>
-      <c r="AL65" t="n">
+      <c r="AM65" t="n">
         <v>5.6602</v>
       </c>
-      <c r="AM65" t="n">
+      <c r="AN65" t="n">
         <v>6623948</v>
       </c>
-      <c r="AN65" t="n">
+      <c r="AO65" t="n">
         <v>2512426</v>
       </c>
-      <c r="AO65" t="n">
+      <c r="AP65" t="n">
         <v>4111522</v>
       </c>
-      <c r="AP65" t="n">
+      <c r="AQ65" t="n">
         <v>3.67</v>
       </c>
-      <c r="AQ65" t="n">
+      <c r="AR65" t="n">
         <v>2.72</v>
       </c>
-      <c r="AR65" t="n">
+      <c r="AS65" t="n">
         <v>4.25</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>31.63</v>
       </c>
       <c r="AT65" t="n">
         <v>340789</v>
@@ -18879,16 +19049,16 @@
         <v>0.002023</v>
       </c>
       <c r="BH65" t="n">
-        <v>0.23</v>
+        <v>0.002023</v>
       </c>
       <c r="BI65" t="n">
         <v>0.23</v>
       </c>
       <c r="BJ65" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BK65" t="n">
         <v>0.22</v>
-      </c>
-      <c r="BK65" t="n">
-        <v>0.29</v>
       </c>
       <c r="BL65" t="n">
         <v>29886134851</v>
@@ -19053,7 +19223,9 @@
       <c r="F66" t="n">
         <v>5.6651</v>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>6.43915</v>
+      </c>
       <c r="H66" t="n">
         <v>5911.689941</v>
       </c>
@@ -19093,7 +19265,9 @@
       <c r="T66" t="n">
         <v>0.802495</v>
       </c>
-      <c r="U66" t="inlineStr"/>
+      <c r="U66" t="n">
+        <v>0.708306</v>
+      </c>
       <c r="V66" t="n">
         <v>6.152383</v>
       </c>
@@ -19125,46 +19299,46 @@
         <v>0.053936</v>
       </c>
       <c r="AF66" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="AG66" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG66" t="n">
+      <c r="AH66" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AH66" t="n">
+      <c r="AI66" t="n">
         <v>0.35</v>
       </c>
-      <c r="AI66" t="n">
+      <c r="AJ66" t="n">
         <v>108.88849</v>
       </c>
-      <c r="AJ66" t="n">
+      <c r="AK66" t="n">
         <v>108.58229</v>
       </c>
-      <c r="AK66" t="n">
+      <c r="AL66" t="n">
         <v>5.7087</v>
       </c>
-      <c r="AL66" t="n">
+      <c r="AM66" t="n">
         <v>5.7081</v>
       </c>
-      <c r="AM66" t="n">
+      <c r="AN66" t="n">
         <v>6666287</v>
       </c>
-      <c r="AN66" t="n">
+      <c r="AO66" t="n">
         <v>2532708</v>
       </c>
-      <c r="AO66" t="n">
+      <c r="AP66" t="n">
         <v>4133579</v>
       </c>
-      <c r="AP66" t="n">
+      <c r="AQ66" t="n">
         <v>3.72</v>
       </c>
-      <c r="AQ66" t="n">
+      <c r="AR66" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR66" t="n">
+      <c r="AS66" t="n">
         <v>4.36</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>31.7</v>
       </c>
       <c r="AT66" t="n">
         <v>341459</v>
@@ -19209,16 +19383,16 @@
         <v>0.001405</v>
       </c>
       <c r="BH66" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="BI66" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI66" t="n">
+      <c r="BJ66" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ66" t="n">
+      <c r="BK66" t="n">
         <v>0.11</v>
-      </c>
-      <c r="BK66" t="n">
-        <v>0.07000000000000001</v>
       </c>
       <c r="BL66" t="n">
         <v>29920080781</v>
@@ -19379,7 +19553,9 @@
       <c r="F67" t="n">
         <v>5.4784</v>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>6.418485</v>
+      </c>
       <c r="H67" t="n">
         <v>6204.950195</v>
       </c>
@@ -19419,7 +19595,9 @@
       <c r="T67" t="n">
         <v>-3.295615</v>
       </c>
-      <c r="U67" t="inlineStr"/>
+      <c r="U67" t="n">
+        <v>-0.320923</v>
+      </c>
       <c r="V67" t="n">
         <v>4.960684</v>
       </c>
@@ -19451,46 +19629,46 @@
         <v>0.054569</v>
       </c>
       <c r="AF67" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="AG67" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG67" t="n">
+      <c r="AH67" t="n">
         <v>-1.67</v>
       </c>
-      <c r="AH67" t="n">
+      <c r="AI67" t="n">
         <v>0.23</v>
       </c>
-      <c r="AI67" t="n">
+      <c r="AJ67" t="n">
         <v>108.82565</v>
       </c>
-      <c r="AJ67" t="n">
+      <c r="AK67" t="n">
         <v>107.40511</v>
       </c>
-      <c r="AK67" t="n">
+      <c r="AL67" t="n">
         <v>5.4571</v>
       </c>
-      <c r="AL67" t="n">
+      <c r="AM67" t="n">
         <v>5.4565</v>
       </c>
-      <c r="AM67" t="n">
+      <c r="AN67" t="n">
         <v>6703663</v>
       </c>
-      <c r="AN67" t="n">
+      <c r="AO67" t="n">
         <v>2547693</v>
       </c>
-      <c r="AO67" t="n">
+      <c r="AP67" t="n">
         <v>4155970</v>
       </c>
-      <c r="AP67" t="n">
+      <c r="AQ67" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ67" t="n">
+      <c r="AR67" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR67" t="n">
+      <c r="AS67" t="n">
         <v>4.41</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>31.85</v>
       </c>
       <c r="AT67" t="n">
         <v>344440</v>
@@ -19535,16 +19713,16 @@
         <v>0.000633</v>
       </c>
       <c r="BH67" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="BI67" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI67" t="n">
+      <c r="BJ67" t="n">
         <v>0</v>
       </c>
-      <c r="BJ67" t="n">
+      <c r="BK67" t="n">
         <v>0.05</v>
-      </c>
-      <c r="BK67" t="n">
-        <v>0.15</v>
       </c>
       <c r="BL67" t="n">
         <v>29036249482</v>
@@ -19705,7 +19883,9 @@
       <c r="F68" t="n">
         <v>5.5754</v>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>6.365372</v>
+      </c>
       <c r="H68" t="n">
         <v>6339.390137</v>
       </c>
@@ -19745,7 +19925,9 @@
       <c r="T68" t="n">
         <v>1.770583</v>
       </c>
-      <c r="U68" t="inlineStr"/>
+      <c r="U68" t="n">
+        <v>-0.8275</v>
+      </c>
       <c r="V68" t="n">
         <v>2.166656</v>
       </c>
@@ -19777,46 +19959,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF68" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG68" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG68" t="n">
+      <c r="AH68" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AH68" t="n">
+      <c r="AI68" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI68" t="n">
+      <c r="AJ68" t="n">
         <v>108.60295</v>
       </c>
-      <c r="AJ68" t="n">
+      <c r="AK68" t="n">
         <v>113.20021</v>
       </c>
-      <c r="AK68" t="n">
+      <c r="AL68" t="n">
         <v>5.6021</v>
       </c>
-      <c r="AL68" t="n">
+      <c r="AM68" t="n">
         <v>5.6015</v>
       </c>
-      <c r="AM68" t="n">
+      <c r="AN68" t="n">
         <v>6733209</v>
       </c>
-      <c r="AN68" t="n">
+      <c r="AO68" t="n">
         <v>2544400</v>
       </c>
-      <c r="AO68" t="n">
+      <c r="AP68" t="n">
         <v>4188808</v>
       </c>
-      <c r="AP68" t="n">
+      <c r="AQ68" t="n">
         <v>3.96</v>
       </c>
-      <c r="AQ68" t="n">
+      <c r="AR68" t="n">
         <v>2.79</v>
       </c>
-      <c r="AR68" t="n">
+      <c r="AS68" t="n">
         <v>4.66</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>31.75</v>
       </c>
       <c r="AT68" t="n">
         <v>345111</v>
@@ -19861,16 +20043,16 @@
         <v>0.000562</v>
       </c>
       <c r="BH68" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BI68" t="n">
         <v>0.21</v>
       </c>
-      <c r="BI68" t="n">
+      <c r="BJ68" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ68" t="n">
+      <c r="BK68" t="n">
         <v>0.25</v>
-      </c>
-      <c r="BK68" t="n">
-        <v>-0.1</v>
       </c>
       <c r="BL68" t="n">
         <v>32128634276</v>
@@ -20035,7 +20217,9 @@
       <c r="F69" t="n">
         <v>5.413</v>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>6.317119</v>
+      </c>
       <c r="H69" t="n">
         <v>6460.259766</v>
       </c>
@@ -20075,7 +20259,9 @@
       <c r="T69" t="n">
         <v>-2.912791</v>
       </c>
-      <c r="U69" t="inlineStr"/>
+      <c r="U69" t="n">
+        <v>-0.758056</v>
+      </c>
       <c r="V69" t="n">
         <v>1.906644</v>
       </c>
@@ -20107,46 +20293,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF69" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG69" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AG69" t="n">
+      <c r="AH69" t="n">
         <v>0.36</v>
       </c>
-      <c r="AH69" t="n">
+      <c r="AI69" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AI69" t="n">
+      <c r="AJ69" t="n">
         <v>108.84223</v>
       </c>
-      <c r="AJ69" t="n">
+      <c r="AK69" t="n">
         <v>110.38311</v>
       </c>
-      <c r="AK69" t="n">
+      <c r="AL69" t="n">
         <v>5.4264</v>
       </c>
-      <c r="AL69" t="n">
+      <c r="AM69" t="n">
         <v>5.4258</v>
       </c>
-      <c r="AM69" t="n">
+      <c r="AN69" t="n">
         <v>6774436</v>
       </c>
-      <c r="AN69" t="n">
+      <c r="AO69" t="n">
         <v>2546265</v>
       </c>
-      <c r="AO69" t="n">
+      <c r="AP69" t="n">
         <v>4228171</v>
       </c>
-      <c r="AP69" t="n">
+      <c r="AQ69" t="n">
         <v>4.14</v>
       </c>
-      <c r="AQ69" t="n">
+      <c r="AR69" t="n">
         <v>2.85</v>
       </c>
-      <c r="AR69" t="n">
+      <c r="AS69" t="n">
         <v>4.92</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>31.87</v>
       </c>
       <c r="AT69" t="n">
         <v>350767</v>
@@ -20191,16 +20377,16 @@
         <v>0</v>
       </c>
       <c r="BH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI69" t="n">
         <v>0.18</v>
       </c>
-      <c r="BI69" t="n">
+      <c r="BJ69" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ69" t="n">
+      <c r="BK69" t="n">
         <v>0.26</v>
-      </c>
-      <c r="BK69" t="n">
-        <v>0.12</v>
       </c>
       <c r="BL69" t="n">
         <v>29558633290</v>
@@ -20361,7 +20547,9 @@
       <c r="F70" t="n">
         <v>5.3217</v>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>6.238303</v>
+      </c>
       <c r="H70" t="n">
         <v>6688.459961</v>
       </c>
@@ -20401,7 +20589,9 @@
       <c r="T70" t="n">
         <v>-1.68668</v>
       </c>
-      <c r="U70" t="inlineStr"/>
+      <c r="U70" t="n">
+        <v>-1.247656</v>
+      </c>
       <c r="V70" t="n">
         <v>3.532369</v>
       </c>
@@ -20433,46 +20623,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF70" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG70" t="n">
         <v>0.48</v>
       </c>
-      <c r="AG70" t="n">
+      <c r="AH70" t="n">
         <v>0.42</v>
       </c>
-      <c r="AH70" t="n">
+      <c r="AI70" t="n">
         <v>0.52</v>
       </c>
-      <c r="AI70" t="n">
+      <c r="AJ70" t="n">
         <v>108.7154</v>
       </c>
-      <c r="AJ70" t="n">
+      <c r="AK70" t="n">
         <v>109.45662</v>
       </c>
-      <c r="AK70" t="n">
+      <c r="AL70" t="n">
         <v>5.3186</v>
       </c>
-      <c r="AL70" t="n">
+      <c r="AM70" t="n">
         <v>5.318</v>
       </c>
-      <c r="AM70" t="n">
+      <c r="AN70" t="n">
         <v>6852705</v>
       </c>
-      <c r="AN70" t="n">
+      <c r="AO70" t="n">
         <v>2589817</v>
       </c>
-      <c r="AO70" t="n">
+      <c r="AP70" t="n">
         <v>4262888</v>
       </c>
-      <c r="AP70" t="n">
+      <c r="AQ70" t="n">
         <v>4.09</v>
       </c>
-      <c r="AQ70" t="n">
+      <c r="AR70" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR70" t="n">
+      <c r="AS70" t="n">
         <v>4.89</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>31.47</v>
       </c>
       <c r="AT70" t="n">
         <v>356582</v>
@@ -20517,16 +20707,16 @@
         <v>0</v>
       </c>
       <c r="BH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI70" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BI70" t="n">
+      <c r="BJ70" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ70" t="n">
+      <c r="BK70" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="BK70" t="n">
-        <v>-0.4</v>
       </c>
       <c r="BL70" t="n">
         <v>30486762259</v>
@@ -20687,7 +20877,9 @@
       <c r="F71" t="n">
         <v>5.382</v>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>6.222775</v>
+      </c>
       <c r="H71" t="n">
         <v>6840.200195</v>
       </c>
@@ -20727,7 +20919,9 @@
       <c r="T71" t="n">
         <v>1.133094</v>
       </c>
-      <c r="U71" t="inlineStr"/>
+      <c r="U71" t="n">
+        <v>-0.248917</v>
+      </c>
       <c r="V71" t="n">
         <v>2.268687</v>
       </c>
@@ -20759,46 +20953,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF71" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG71" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG71" t="n">
+      <c r="AH71" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AH71" t="n">
+      <c r="AI71" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI71" t="n">
+      <c r="AJ71" t="n">
         <v>108.73877</v>
       </c>
-      <c r="AJ71" t="n">
+      <c r="AK71" t="n">
         <v>110.04186</v>
       </c>
-      <c r="AK71" t="n">
+      <c r="AL71" t="n">
         <v>5.3843</v>
       </c>
-      <c r="AL71" t="n">
+      <c r="AM71" t="n">
         <v>5.3837</v>
       </c>
-      <c r="AM71" t="n">
+      <c r="AN71" t="n">
         <v>6923886</v>
       </c>
-      <c r="AN71" t="n">
+      <c r="AO71" t="n">
         <v>2597630</v>
       </c>
-      <c r="AO71" t="n">
+      <c r="AP71" t="n">
         <v>4326256</v>
       </c>
-      <c r="AP71" t="n">
+      <c r="AQ71" t="n">
         <v>4.18</v>
       </c>
-      <c r="AQ71" t="n">
+      <c r="AR71" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR71" t="n">
+      <c r="AS71" t="n">
         <v>4.99</v>
-      </c>
-      <c r="AS71" t="n">
-        <v>32.04</v>
       </c>
       <c r="AT71" t="n">
         <v>357103</v>
@@ -20843,16 +21037,16 @@
         <v>0</v>
       </c>
       <c r="BH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI71" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI71" t="n">
+      <c r="BJ71" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ71" t="n">
+      <c r="BK71" t="n">
         <v>0.1</v>
-      </c>
-      <c r="BK71" t="n">
-        <v>0.57</v>
       </c>
       <c r="BL71" t="n">
         <v>31508863381</v>
@@ -21013,7 +21207,9 @@
       <c r="F72" t="n">
         <v>5.3554</v>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>6.207325</v>
+      </c>
       <c r="H72" t="n">
         <v>6849.089844</v>
       </c>
@@ -21053,7 +21249,9 @@
       <c r="T72" t="n">
         <v>-0.494238</v>
       </c>
-      <c r="U72" t="inlineStr"/>
+      <c r="U72" t="n">
+        <v>-0.248282</v>
+      </c>
       <c r="V72" t="n">
         <v>0.129962</v>
       </c>
@@ -21085,46 +21283,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF72" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG72" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG72" t="n">
+      <c r="AH72" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH72" t="n">
+      <c r="AI72" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI72" t="n">
+      <c r="AJ72" t="n">
         <v>109.25356</v>
       </c>
-      <c r="AJ72" t="n">
+      <c r="AK72" t="n">
         <v>106.5784</v>
       </c>
-      <c r="AK72" t="n">
+      <c r="AL72" t="n">
         <v>5.3338</v>
       </c>
-      <c r="AL72" t="n">
+      <c r="AM72" t="n">
         <v>5.3332</v>
       </c>
-      <c r="AM72" t="n">
+      <c r="AN72" t="n">
         <v>7004223</v>
       </c>
-      <c r="AN72" t="n">
+      <c r="AO72" t="n">
         <v>2616902</v>
       </c>
-      <c r="AO72" t="n">
+      <c r="AP72" t="n">
         <v>4387321</v>
       </c>
-      <c r="AP72" t="n">
+      <c r="AQ72" t="n">
         <v>4.24</v>
       </c>
-      <c r="AQ72" t="n">
+      <c r="AR72" t="n">
         <v>2.75</v>
       </c>
-      <c r="AR72" t="n">
+      <c r="AS72" t="n">
         <v>5.12</v>
-      </c>
-      <c r="AS72" t="n">
-        <v>32.2</v>
       </c>
       <c r="AT72" t="n">
         <v>360578</v>
@@ -21169,16 +21367,16 @@
         <v>-0</v>
       </c>
       <c r="BH72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI72" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI72" t="n">
+      <c r="BJ72" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BJ72" t="n">
+      <c r="BK72" t="n">
         <v>0.13</v>
-      </c>
-      <c r="BK72" t="n">
-        <v>0.16</v>
       </c>
       <c r="BL72" t="n">
         <v>28164831149</v>
@@ -21343,7 +21541,9 @@
       <c r="F73" t="n">
         <v>5.4762</v>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>6.426735</v>
+      </c>
       <c r="H73" t="n">
         <v>6845.5</v>
       </c>
@@ -21383,7 +21583,9 @@
       <c r="T73" t="n">
         <v>2.255667</v>
       </c>
-      <c r="U73" t="inlineStr"/>
+      <c r="U73" t="n">
+        <v>3.534694</v>
+      </c>
       <c r="V73" t="n">
         <v>-0.052413</v>
       </c>
@@ -21415,46 +21617,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF73" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG73" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG73" t="n">
+      <c r="AH73" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH73" t="n">
+      <c r="AI73" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI73" t="n">
+      <c r="AJ73" t="n">
         <v>109.47578</v>
       </c>
-      <c r="AJ73" t="n">
+      <c r="AK73" t="n">
         <v>107.19091</v>
       </c>
-      <c r="AK73" t="n">
+      <c r="AL73" t="n">
         <v>5.5024</v>
       </c>
-      <c r="AL73" t="n">
+      <c r="AM73" t="n">
         <v>5.5018</v>
       </c>
-      <c r="AM73" t="n">
+      <c r="AN73" t="n">
         <v>7137252</v>
       </c>
-      <c r="AN73" t="n">
+      <c r="AO73" t="n">
         <v>2701735</v>
       </c>
-      <c r="AO73" t="n">
+      <c r="AP73" t="n">
         <v>4435517</v>
       </c>
-      <c r="AP73" t="n">
+      <c r="AQ73" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ73" t="n">
+      <c r="AR73" t="n">
         <v>2.7</v>
       </c>
-      <c r="AR73" t="n">
+      <c r="AS73" t="n">
         <v>5.12</v>
-      </c>
-      <c r="AS73" t="n">
-        <v>31.87</v>
       </c>
       <c r="AT73" t="n">
         <v>358234</v>
@@ -21499,16 +21701,16 @@
         <v>0</v>
       </c>
       <c r="BH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI73" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BI73" t="n">
+      <c r="BJ73" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ73" t="n">
+      <c r="BK73" t="n">
         <v>0</v>
-      </c>
-      <c r="BK73" t="n">
-        <v>-0.33</v>
       </c>
       <c r="BL73" t="n">
         <v>30710215227</v>
@@ -21665,7 +21867,9 @@
       <c r="F74" t="n">
         <v>5.1892</v>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>6.203474</v>
+      </c>
       <c r="H74" t="n">
         <v>6939.029785</v>
       </c>
@@ -21705,7 +21909,9 @@
       <c r="T74" t="n">
         <v>-5.240864</v>
       </c>
-      <c r="U74" t="inlineStr"/>
+      <c r="U74" t="n">
+        <v>-3.473939</v>
+      </c>
       <c r="V74" t="n">
         <v>1.366296</v>
       </c>
@@ -21737,46 +21943,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF74" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG74" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG74" t="n">
+      <c r="AH74" t="n">
         <v>0.41</v>
       </c>
-      <c r="AH74" t="n">
+      <c r="AI74" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI74" t="n">
+      <c r="AJ74" t="n">
         <v>110.15169</v>
       </c>
-      <c r="AJ74" t="n">
+      <c r="AK74" t="n">
         <v>103.91741</v>
       </c>
-      <c r="AK74" t="n">
+      <c r="AL74" t="n">
         <v>5.2301</v>
       </c>
-      <c r="AL74" t="n">
+      <c r="AM74" t="n">
         <v>5.2295</v>
       </c>
-      <c r="AM74" t="n">
+      <c r="AN74" t="n">
         <v>7130762</v>
       </c>
-      <c r="AN74" t="n">
+      <c r="AO74" t="n">
         <v>2654220</v>
       </c>
-      <c r="AO74" t="n">
+      <c r="AP74" t="n">
         <v>4476542</v>
       </c>
-      <c r="AP74" t="n">
+      <c r="AQ74" t="n">
         <v>4.44</v>
       </c>
-      <c r="AQ74" t="n">
+      <c r="AR74" t="n">
         <v>2.87</v>
       </c>
-      <c r="AR74" t="n">
+      <c r="AS74" t="n">
         <v>5.38</v>
-      </c>
-      <c r="AS74" t="n">
-        <v>32.45</v>
       </c>
       <c r="AT74" t="n">
         <v>364367</v>
@@ -21821,16 +22027,16 @@
         <v>0</v>
       </c>
       <c r="BH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI74" t="n">
         <v>0.24</v>
       </c>
-      <c r="BI74" t="n">
+      <c r="BJ74" t="n">
         <v>0.17</v>
       </c>
-      <c r="BJ74" t="n">
+      <c r="BK74" t="n">
         <v>0.26</v>
-      </c>
-      <c r="BK74" t="n">
-        <v>0.58</v>
       </c>
       <c r="BL74" t="n">
         <v>24573982812</v>
@@ -21991,7 +22197,9 @@
       <c r="F75" t="n">
         <v>5.1366</v>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>6.056935</v>
+      </c>
       <c r="H75" t="n">
         <v>6878.879883</v>
       </c>
@@ -22031,7 +22239,9 @@
       <c r="T75" t="n">
         <v>-1.013642</v>
       </c>
-      <c r="U75" t="inlineStr"/>
+      <c r="U75" t="n">
+        <v>-2.362212</v>
+      </c>
       <c r="V75" t="n">
         <v>-0.866834</v>
       </c>
@@ -22063,46 +22273,46 @@
         <v>0.055131</v>
       </c>
       <c r="AF75" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG75" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG75" t="n">
+      <c r="AH75" t="n">
         <v>-0.73</v>
       </c>
-      <c r="AH75" t="n">
+      <c r="AI75" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AI75" t="n">
+      <c r="AJ75" t="n">
         <v>110.82485</v>
       </c>
-      <c r="AJ75" t="n">
+      <c r="AK75" t="n">
         <v>106.86101</v>
       </c>
-      <c r="AK75" t="n">
+      <c r="AL75" t="n">
         <v>5.1495</v>
       </c>
-      <c r="AL75" t="n">
+      <c r="AM75" t="n">
         <v>5.1489</v>
       </c>
-      <c r="AM75" t="n">
+      <c r="AN75" t="n">
         <v>7157783</v>
       </c>
-      <c r="AN75" t="n">
+      <c r="AO75" t="n">
         <v>2656484</v>
       </c>
-      <c r="AO75" t="n">
+      <c r="AP75" t="n">
         <v>4501299</v>
       </c>
-      <c r="AP75" t="n">
+      <c r="AQ75" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ75" t="n">
+      <c r="AR75" t="n">
         <v>3.07</v>
       </c>
-      <c r="AR75" t="n">
+      <c r="AS75" t="n">
         <v>5.56</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>32.63</v>
       </c>
       <c r="AT75" t="n">
         <v>371074</v>
@@ -22147,13 +22357,13 @@
         <v>0</v>
       </c>
       <c r="BH75" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="BI75" t="n">
         <v>0.2</v>
       </c>
       <c r="BJ75" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BK75" t="n">
         <v>0.18</v>
@@ -22321,7 +22531,9 @@
       <c r="F76" t="n">
         <v>5.264</v>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>6.027728</v>
+      </c>
       <c r="H76" t="n">
         <v>6528.52002</v>
       </c>
@@ -22361,7 +22573,9 @@
       <c r="T76" t="n">
         <v>2.480238</v>
       </c>
-      <c r="U76" t="inlineStr"/>
+      <c r="U76" t="n">
+        <v>-0.482204</v>
+      </c>
       <c r="V76" t="n">
         <v>-5.093269</v>
       </c>
@@ -22393,46 +22607,46 @@
         <v>0.054777</v>
       </c>
       <c r="AF76" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="AG76" t="n">
         <v>0.88</v>
       </c>
-      <c r="AG76" t="n">
+      <c r="AH76" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH76" t="n">
+      <c r="AI76" t="n">
         <v>0.91</v>
       </c>
-      <c r="AI76" t="n">
+      <c r="AJ76" t="n">
         <v>110.65755</v>
       </c>
-      <c r="AJ76" t="n">
+      <c r="AK76" t="n">
         <v>118.06619</v>
       </c>
-      <c r="AK76" t="n">
+      <c r="AL76" t="n">
         <v>5.2194</v>
       </c>
-      <c r="AL76" t="n">
+      <c r="AM76" t="n">
         <v>5.2188</v>
       </c>
-      <c r="AM76" t="n">
+      <c r="AN76" t="n">
         <v>7240557</v>
       </c>
-      <c r="AN76" t="n">
+      <c r="AO76" t="n">
         <v>2687535</v>
       </c>
-      <c r="AO76" t="n">
+      <c r="AP76" t="n">
         <v>4553022</v>
       </c>
-      <c r="AP76" t="n">
+      <c r="AQ76" t="n">
         <v>4.52</v>
       </c>
-      <c r="AQ76" t="n">
+      <c r="AR76" t="n">
         <v>3.06</v>
       </c>
-      <c r="AR76" t="n">
+      <c r="AS76" t="n">
         <v>5.39</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>32.84</v>
       </c>
       <c r="AT76" t="n">
         <v>362002</v>
@@ -22477,16 +22691,16 @@
         <v>-0.000354</v>
       </c>
       <c r="BH76" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="BI76" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BI76" t="n">
+      <c r="BJ76" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ76" t="n">
+      <c r="BK76" t="n">
         <v>-0.17</v>
-      </c>
-      <c r="BK76" t="n">
-        <v>0.21</v>
       </c>
       <c r="BL76" t="n">
         <v>31766018083</v>
@@ -22647,7 +22861,9 @@
       <c r="F77" t="n">
         <v>5.0175</v>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>5.858231</v>
+      </c>
       <c r="H77" t="n">
         <v>7209.009766</v>
       </c>
@@ -22687,7 +22903,9 @@
       <c r="T77" t="n">
         <v>-4.682751</v>
       </c>
-      <c r="U77" t="inlineStr"/>
+      <c r="U77" t="n">
+        <v>-2.811955</v>
+      </c>
       <c r="V77" t="n">
         <v>10.423339</v>
       </c>
@@ -22719,46 +22937,46 @@
         <v>0.054223</v>
       </c>
       <c r="AF77" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="AG77" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG77" t="n">
+      <c r="AH77" t="n">
         <v>2.73</v>
       </c>
-      <c r="AH77" t="n">
+      <c r="AI77" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI77" t="n">
+      <c r="AJ77" t="n">
         <v>111.04254</v>
       </c>
-      <c r="AJ77" t="n">
+      <c r="AK77" t="n">
         <v>114.1592</v>
       </c>
-      <c r="AK77" t="n">
+      <c r="AL77" t="n">
         <v>4.9886</v>
       </c>
-      <c r="AL77" t="n">
+      <c r="AM77" t="n">
         <v>4.988</v>
       </c>
-      <c r="AM77" t="n">
+      <c r="AN77" t="n">
         <v>7259766</v>
       </c>
-      <c r="AN77" t="n">
+      <c r="AO77" t="n">
         <v>2685397</v>
       </c>
-      <c r="AO77" t="n">
+      <c r="AP77" t="n">
         <v>4574368</v>
       </c>
-      <c r="AP77" t="n">
+      <c r="AQ77" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ77" t="n">
+      <c r="AR77" t="n">
         <v>3.15</v>
       </c>
-      <c r="AR77" t="n">
+      <c r="AS77" t="n">
         <v>5.51</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>33.36</v>
       </c>
       <c r="AT77" t="n">
         <v>366913</v>
@@ -22803,16 +23021,16 @@
         <v>-0.000554</v>
       </c>
       <c r="BH77" t="n">
+        <v>-0.000554</v>
+      </c>
+      <c r="BI77" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI77" t="n">
+      <c r="BJ77" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ77" t="n">
+      <c r="BK77" t="n">
         <v>0.12</v>
-      </c>
-      <c r="BK77" t="n">
-        <v>0.52</v>
       </c>
       <c r="BL77" t="n">
         <v>34286658184</v>
@@ -22973,7 +23191,9 @@
       <c r="F78" t="n">
         <v>5.0517</v>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>5.882353</v>
+      </c>
       <c r="H78" t="n">
         <v>7580.060059</v>
       </c>
@@ -23013,7 +23233,9 @@
       <c r="T78" t="n">
         <v>0.6816179999999999</v>
       </c>
-      <c r="U78" t="inlineStr"/>
+      <c r="U78" t="n">
+        <v>0.411758</v>
+      </c>
       <c r="V78" t="n">
         <v>5.147036</v>
       </c>
@@ -23045,46 +23267,46 @@
         <v>0.0534</v>
       </c>
       <c r="AF78" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="AG78" t="n">
         <v>0.58</v>
       </c>
-      <c r="AG78" t="n">
+      <c r="AH78" t="n">
         <v>0.84</v>
       </c>
-      <c r="AH78" t="n">
+      <c r="AI78" t="n">
         <v>0.65</v>
       </c>
-      <c r="AI78" t="n">
+      <c r="AJ78" t="n">
         <v>111.25061</v>
       </c>
-      <c r="AJ78" t="n">
+      <c r="AK78" t="n">
         <v>109.79468</v>
       </c>
-      <c r="AK78" t="n">
+      <c r="AL78" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AL78" t="n">
+      <c r="AM78" t="n">
         <v>5.0563</v>
       </c>
-      <c r="AM78" t="n">
+      <c r="AN78" t="n">
         <v>7305322</v>
       </c>
-      <c r="AN78" t="n">
+      <c r="AO78" t="n">
         <v>2708154</v>
       </c>
-      <c r="AO78" t="n">
+      <c r="AP78" t="n">
         <v>4597168</v>
       </c>
-      <c r="AP78" t="n">
+      <c r="AQ78" t="n">
         <v>4.75</v>
       </c>
-      <c r="AQ78" t="n">
+      <c r="AR78" t="n">
         <v>3.25</v>
       </c>
-      <c r="AR78" t="n">
+      <c r="AS78" t="n">
         <v>5.63</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>32.97</v>
       </c>
       <c r="AT78" t="n">
         <v>371137</v>
@@ -23129,16 +23351,16 @@
         <v>-0.0008229999999999999</v>
       </c>
       <c r="BH78" t="n">
+        <v>-0.0008229999999999999</v>
+      </c>
+      <c r="BI78" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI78" t="n">
+      <c r="BJ78" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ78" t="n">
+      <c r="BK78" t="n">
         <v>0.12</v>
-      </c>
-      <c r="BK78" t="n">
-        <v>-0.39</v>
       </c>
       <c r="BL78" t="n">
         <v>31529852245</v>
@@ -23303,7 +23525,9 @@
       <c r="F79" t="n">
         <v>5.181787</v>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>5.91716</v>
+      </c>
       <c r="H79" t="n">
         <v>7499.359863</v>
       </c>
@@ -23343,7 +23567,9 @@
       <c r="T79" t="n">
         <v>2.575111</v>
       </c>
-      <c r="U79" t="inlineStr"/>
+      <c r="U79" t="n">
+        <v>0.591722</v>
+      </c>
       <c r="V79" t="n">
         <v>-1.064638</v>
       </c>
@@ -23375,46 +23601,46 @@
         <v>0.053028</v>
       </c>
       <c r="AF79" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="AG79" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG79" t="n">
+      <c r="AH79" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AH79" t="n">
+      <c r="AI79" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI79" t="n">
+      <c r="AJ79" t="n">
         <v>110.37352</v>
       </c>
-      <c r="AJ79" t="n">
+      <c r="AK79" t="n">
         <v>110.18456</v>
       </c>
-      <c r="AK79" t="n">
+      <c r="AL79" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AL79" t="n">
+      <c r="AM79" t="n">
         <v>5.176</v>
       </c>
-      <c r="AM79" t="n">
+      <c r="AN79" t="n">
         <v>7353302</v>
       </c>
-      <c r="AN79" t="n">
+      <c r="AO79" t="n">
         <v>2750634</v>
       </c>
-      <c r="AO79" t="n">
+      <c r="AP79" t="n">
         <v>4602668</v>
       </c>
-      <c r="AP79" t="n">
+      <c r="AQ79" t="n">
         <v>4.58</v>
       </c>
-      <c r="AQ79" t="n">
+      <c r="AR79" t="n">
         <v>3.18</v>
       </c>
-      <c r="AR79" t="n">
+      <c r="AS79" t="n">
         <v>5.42</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>32.63</v>
       </c>
       <c r="AT79" t="n">
         <v>367558</v>
@@ -23459,16 +23685,16 @@
         <v>-0.000372</v>
       </c>
       <c r="BH79" t="n">
+        <v>-0.000372</v>
+      </c>
+      <c r="BI79" t="n">
         <v>-0.17</v>
       </c>
-      <c r="BI79" t="n">
+      <c r="BJ79" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BJ79" t="n">
+      <c r="BK79" t="n">
         <v>-0.21</v>
-      </c>
-      <c r="BK79" t="n">
-        <v>-0.34</v>
       </c>
       <c r="BL79" t="n">
         <v>35499628278</v>
@@ -23629,7 +23855,9 @@
       <c r="F80" t="n">
         <v>5.0781</v>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>5.847953</v>
+      </c>
       <c r="H80" t="n">
         <v>7489.720215</v>
       </c>
@@ -23669,7 +23897,9 @@
       <c r="T80" t="n">
         <v>-2.000986</v>
       </c>
-      <c r="U80" t="inlineStr"/>
+      <c r="U80" t="n">
+        <v>-1.169601</v>
+      </c>
       <c r="V80" t="n">
         <v>-0.12854</v>
       </c>
@@ -23701,46 +23931,46 @@
         <v>0.052531</v>
       </c>
       <c r="AF80" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="AG80" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AG80" t="n">
+      <c r="AH80" t="n">
         <v>-1.16</v>
       </c>
-      <c r="AH80" t="n">
+      <c r="AI80" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AI80" t="n">
+      <c r="AJ80" t="n">
         <v>110.03188</v>
       </c>
-      <c r="AJ80" t="n">
+      <c r="AK80" t="n">
         <v>114.48992</v>
       </c>
-      <c r="AK80" t="n">
+      <c r="AL80" t="n">
         <v>5.0773</v>
       </c>
-      <c r="AL80" t="n">
+      <c r="AM80" t="n">
         <v>5.0767</v>
       </c>
-      <c r="AM80" t="n">
+      <c r="AN80" t="n">
         <v>7362305</v>
       </c>
-      <c r="AN80" t="n">
+      <c r="AO80" t="n">
         <v>2729162</v>
       </c>
-      <c r="AO80" t="n">
+      <c r="AP80" t="n">
         <v>4633143</v>
       </c>
-      <c r="AP80" t="n">
+      <c r="AQ80" t="n">
         <v>4.88</v>
       </c>
-      <c r="AQ80" t="n">
+      <c r="AR80" t="n">
         <v>3.32</v>
       </c>
-      <c r="AR80" t="n">
+      <c r="AS80" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AS80" t="n">
-        <v>32.06</v>
       </c>
       <c r="AT80" t="n">
         <v>369742</v>
@@ -23785,16 +24015,16 @@
         <v>-0.000497</v>
       </c>
       <c r="BH80" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="BI80" t="n">
         <v>0.3</v>
       </c>
-      <c r="BI80" t="n">
+      <c r="BJ80" t="n">
         <v>0.14</v>
       </c>
-      <c r="BJ80" t="n">
+      <c r="BK80" t="n">
         <v>0.38</v>
-      </c>
-      <c r="BK80" t="n">
-        <v>-0.57</v>
       </c>
       <c r="BL80" t="n">
         <v>33577433983</v>
@@ -23959,7 +24189,9 @@
       <c r="F81" t="n">
         <v>5.1912</v>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>6.009615</v>
+      </c>
       <c r="H81" t="n">
         <v>7686.140137</v>
       </c>
@@ -23999,7 +24231,9 @@
       <c r="T81" t="n">
         <v>2.227203</v>
       </c>
-      <c r="U81" t="inlineStr"/>
+      <c r="U81" t="n">
+        <v>2.764422</v>
+      </c>
       <c r="V81" t="n">
         <v>2.622527</v>
       </c>
@@ -24031,46 +24265,46 @@
         <v>0.051784</v>
       </c>
       <c r="AF81" t="n">
+        <v>0.051784</v>
+      </c>
+      <c r="AG81" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AG81" t="n">
+      <c r="AH81" t="n">
         <v>-0.22</v>
       </c>
-      <c r="AH81" t="n">
+      <c r="AI81" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AI81" t="n">
+      <c r="AJ81" t="n">
         <v>110.40624</v>
       </c>
-      <c r="AJ81" t="n">
+      <c r="AK81" t="n">
         <v>111.71919</v>
       </c>
-      <c r="AK81" t="n">
+      <c r="AL81" t="n">
         <v>5.1816</v>
       </c>
-      <c r="AL81" t="n">
+      <c r="AM81" t="n">
         <v>5.181</v>
       </c>
-      <c r="AM81" t="n">
+      <c r="AN81" t="n">
         <v>7397669</v>
       </c>
-      <c r="AN81" t="n">
+      <c r="AO81" t="n">
         <v>2727499</v>
       </c>
-      <c r="AO81" t="n">
+      <c r="AP81" t="n">
         <v>4670170</v>
       </c>
-      <c r="AP81" t="n">
+      <c r="AQ81" t="n">
         <v>5.04</v>
       </c>
-      <c r="AQ81" t="n">
+      <c r="AR81" t="n">
         <v>3.35</v>
       </c>
-      <c r="AR81" t="n">
+      <c r="AS81" t="n">
         <v>6.03</v>
-      </c>
-      <c r="AS81" t="n">
-        <v>32.26</v>
       </c>
       <c r="AT81" t="n">
         <v>372616</v>
@@ -24115,16 +24349,16 @@
         <v>-0.0007470000000000001</v>
       </c>
       <c r="BH81" t="n">
+        <v>-0.0007470000000000001</v>
+      </c>
+      <c r="BI81" t="n">
         <v>0.16</v>
       </c>
-      <c r="BI81" t="n">
+      <c r="BJ81" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ81" t="n">
+      <c r="BK81" t="n">
         <v>0.23</v>
-      </c>
-      <c r="BK81" t="n">
-        <v>0.2</v>
       </c>
       <c r="BL81" t="n">
         <v>32732183002</v>
@@ -24285,7 +24519,9 @@
       <c r="F82" t="n">
         <v>5.2029</v>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>5.896226</v>
+      </c>
       <c r="H82" t="n">
         <v>7651.540039</v>
       </c>
@@ -24325,7 +24561,9 @@
       <c r="T82" t="n">
         <v>0.225384</v>
       </c>
-      <c r="U82" t="inlineStr"/>
+      <c r="U82" t="n">
+        <v>-1.886793</v>
+      </c>
       <c r="V82" t="n">
         <v>-0.450162</v>
       </c>
@@ -24357,23 +24595,25 @@
         <v>0.051245</v>
       </c>
       <c r="AF82" t="n">
+        <v>0.051245</v>
+      </c>
+      <c r="AG82" t="n">
         <v>0.82</v>
       </c>
-      <c r="AG82" t="n">
+      <c r="AH82" t="n">
         <v>1.57</v>
       </c>
-      <c r="AH82" t="n">
+      <c r="AI82" t="n">
         <v>0.82</v>
       </c>
-      <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="n">
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="n">
         <v>5.1809</v>
       </c>
-      <c r="AL82" t="n">
+      <c r="AM82" t="n">
         <v>5.1803</v>
       </c>
-      <c r="AM82" t="inlineStr"/>
       <c r="AN82" t="inlineStr"/>
       <c r="AO82" t="inlineStr"/>
       <c r="AP82" t="inlineStr"/>
@@ -24412,7 +24652,9 @@
       <c r="BG82" t="n">
         <v>-0.00054</v>
       </c>
-      <c r="BH82" t="inlineStr"/>
+      <c r="BH82" t="n">
+        <v>-0.00054</v>
+      </c>
       <c r="BI82" t="inlineStr"/>
       <c r="BJ82" t="inlineStr"/>
       <c r="BK82" t="inlineStr"/>
@@ -24557,84 +24799,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>205430</v>
+        <v>204667.15625</v>
       </c>
       <c r="C83" t="n">
-        <v>202.300003</v>
+        <v>201.429993</v>
       </c>
       <c r="D83" t="n">
-        <v>131</v>
+        <v>133.410004</v>
       </c>
       <c r="E83" t="n">
-        <v>438.549988</v>
+        <v>440.230011</v>
       </c>
       <c r="F83" t="n">
-        <v>5.0693</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
+        <v>5.0579</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5.673</v>
+      </c>
       <c r="H83" t="n">
-        <v>7659.439941</v>
+        <v>7708.77002</v>
       </c>
       <c r="I83" t="n">
-        <v>26140.029297</v>
+        <v>26522.501953</v>
       </c>
       <c r="J83" t="n">
-        <v>52002.410156</v>
+        <v>52020.359375</v>
       </c>
       <c r="K83" t="n">
-        <v>4181.100098</v>
+        <v>4161.899902</v>
       </c>
       <c r="L83" t="n">
-        <v>99.019997</v>
+        <v>98.599998</v>
       </c>
       <c r="M83" t="n">
-        <v>109.860001</v>
+        <v>109.400002</v>
       </c>
       <c r="N83" t="n">
-        <v>1261.25</v>
+        <v>1251</v>
       </c>
       <c r="O83" t="n">
-        <v>474.25</v>
+        <v>467.75</v>
       </c>
       <c r="P83" t="n">
-        <v>10.244714</v>
+        <v>9.835331</v>
       </c>
       <c r="Q83" t="n">
-        <v>9.897871</v>
+        <v>9.425245</v>
       </c>
       <c r="R83" t="n">
-        <v>17.037434</v>
+        <v>19.190568</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.971524</v>
+        <v>-1.595991</v>
       </c>
       <c r="T83" t="n">
-        <v>-2.567794</v>
-      </c>
-      <c r="U83" t="inlineStr"/>
+        <v>-2.786907</v>
+      </c>
+      <c r="U83" t="n">
+        <v>-3.785914</v>
+      </c>
       <c r="V83" t="n">
-        <v>0.103246</v>
+        <v>0.747954</v>
       </c>
       <c r="W83" t="n">
-        <v>-2.684299</v>
+        <v>-1.260407</v>
       </c>
       <c r="X83" t="n">
-        <v>2.153692</v>
+        <v>2.188951</v>
       </c>
       <c r="Y83" t="n">
-        <v>-0.133759</v>
+        <v>-0.592359</v>
       </c>
       <c r="Z83" t="n">
-        <v>9.511169000000001</v>
+        <v>9.046671999999999</v>
       </c>
       <c r="AA83" t="n">
-        <v>6.114172</v>
+        <v>5.669857</v>
       </c>
       <c r="AB83" t="n">
-        <v>-2.45553</v>
+        <v>-3.24826</v>
       </c>
       <c r="AC83" t="n">
-        <v>-5.292062</v>
+        <v>-6.590115</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>
@@ -24642,18 +24888,20 @@
       <c r="AE83" t="n">
         <v>0.050788</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
+      <c r="AF83" t="n">
+        <v>0.050788</v>
+      </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="n">
-        <v>5.0826</v>
-      </c>
+      <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="n">
-        <v>5.082</v>
-      </c>
-      <c r="AM83" t="inlineStr"/>
+        <v>5.0564</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>5.0558</v>
+      </c>
       <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="inlineStr"/>
       <c r="AP83" t="inlineStr"/>
@@ -24664,10 +24912,10 @@
       <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr"/>
       <c r="AW83" t="n">
-        <v>-1.897354</v>
+        <v>-2.403057</v>
       </c>
       <c r="AX83" t="n">
-        <v>-1.897573</v>
+        <v>-2.403336</v>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr"/>
@@ -24682,7 +24930,9 @@
       <c r="BG83" t="n">
         <v>-0.000457</v>
       </c>
-      <c r="BH83" t="inlineStr"/>
+      <c r="BH83" t="n">
+        <v>-0.000457</v>
+      </c>
       <c r="BI83" t="inlineStr"/>
       <c r="BJ83" t="inlineStr"/>
       <c r="BK83" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -633,17 +633,17 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_total</t>
+          <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
+          <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
+          <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_total</t>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
+          <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
@@ -5256,10 +5256,10 @@
         <v>7.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.024925</v>
+        <v>0.025079</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.024925</v>
+        <v>0.025079</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
@@ -5292,13 +5292,13 @@
         <v>2601017</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="AT23" t="n">
         <v>367927</v>
@@ -5584,13 +5584,13 @@
         <v>2664395</v>
       </c>
       <c r="AQ24" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="AT24" t="n">
         <v>367772</v>
@@ -5626,19 +5626,19 @@
         <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.004331</v>
+        <v>0.004177</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.004331</v>
+        <v>0.004177</v>
       </c>
       <c r="BI24" t="n">
         <v>0.03</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="BL24" t="n">
         <v>20501766210</v>
@@ -5912,13 +5912,13 @@
         <v>2708461</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="AT25" t="n">
         <v>362204</v>
@@ -5960,13 +5960,13 @@
         <v>0.00406</v>
       </c>
       <c r="BI25" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="BL25" t="n">
         <v>24432406778</v>
@@ -6236,13 +6236,13 @@
         <v>2735096</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="AT26" t="n">
         <v>358398</v>
@@ -6284,13 +6284,13 @@
         <v>0.001433</v>
       </c>
       <c r="BI26" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.21</v>
+        <v>1.02</v>
       </c>
       <c r="BL26" t="n">
         <v>19779928894</v>
@@ -6552,13 +6552,13 @@
         <v>2756295</v>
       </c>
       <c r="AQ27" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AS27" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="AT27" t="n">
         <v>357740</v>
@@ -6600,13 +6600,13 @@
         <v>0.004849</v>
       </c>
       <c r="BI27" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-0.02</v>
+        <v>0.12</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="BL27" t="n">
         <v>23513305117</v>
@@ -6872,13 +6872,13 @@
         <v>2800464</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="AT28" t="n">
         <v>353169</v>
@@ -6920,13 +6920,13 @@
         <v>0.002356</v>
       </c>
       <c r="BI28" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="BL28" t="n">
         <v>29422320196</v>
@@ -7188,13 +7188,13 @@
         <v>2830420</v>
       </c>
       <c r="AQ29" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="AT29" t="n">
         <v>345097</v>
@@ -7236,13 +7236,13 @@
         <v>0.001785</v>
       </c>
       <c r="BI29" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.09</v>
+        <v>0.92</v>
       </c>
       <c r="BL29" t="n">
         <v>28969694687</v>
@@ -7516,13 +7516,13 @@
         <v>2875671</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="AT30" t="n">
         <v>346415</v>
@@ -7564,13 +7564,13 @@
         <v>0.003057</v>
       </c>
       <c r="BI30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="BL30" t="n">
         <v>29642851197</v>
@@ -7840,13 +7840,13 @@
         <v>2913035</v>
       </c>
       <c r="AQ31" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="AT31" t="n">
         <v>341958</v>
@@ -7888,13 +7888,13 @@
         <v>0.00132</v>
       </c>
       <c r="BI31" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BK31" t="n">
-        <v>-0.08</v>
+        <v>0.46</v>
       </c>
       <c r="BL31" t="n">
         <v>32742194543</v>
@@ -8164,13 +8164,13 @@
         <v>2952207</v>
       </c>
       <c r="AQ32" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="AT32" t="n">
         <v>346403</v>
@@ -8212,13 +8212,13 @@
         <v>0.0009210000000000001</v>
       </c>
       <c r="BI32" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.14</v>
+        <v>1.36</v>
       </c>
       <c r="BL32" t="n">
         <v>29844324640</v>
@@ -8492,13 +8492,13 @@
         <v>3008528</v>
       </c>
       <c r="AQ33" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="AT33" t="n">
         <v>339664</v>
@@ -8540,13 +8540,13 @@
         <v>0.001523</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK33" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="BL33" t="n">
         <v>30786908834</v>
@@ -8816,13 +8816,13 @@
         <v>3054969</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="AT34" t="n">
         <v>327580</v>
@@ -8870,13 +8870,13 @@
         <v>0.000228</v>
       </c>
       <c r="BI34" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BJ34" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ34" t="n">
-        <v>0.03</v>
-      </c>
       <c r="BK34" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BL34" t="n">
         <v>28587334142</v>
@@ -9150,13 +9150,13 @@
         <v>3110134</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="AT35" t="n">
         <v>325546</v>
@@ -9207,10 +9207,10 @@
         <v>0.12</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.09</v>
+        <v>1.11</v>
       </c>
       <c r="BL35" t="n">
         <v>26852476461</v>
@@ -9480,13 +9480,13 @@
         <v>3155345</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="AT36" t="n">
         <v>331505</v>
@@ -9534,13 +9534,13 @@
         <v>0</v>
       </c>
       <c r="BI36" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BJ36" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ36" t="n">
-        <v>0.04</v>
-      </c>
       <c r="BK36" t="n">
-        <v>0.03</v>
+        <v>0.84</v>
       </c>
       <c r="BL36" t="n">
         <v>27652303451</v>
@@ -9802,13 +9802,13 @@
         <v>3187833</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="AT37" t="n">
         <v>324703</v>
@@ -9856,13 +9856,13 @@
         <v>-0</v>
       </c>
       <c r="BI37" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ37" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BK37" t="n">
-        <v>0.02</v>
+        <v>-0.88</v>
       </c>
       <c r="BL37" t="n">
         <v>26342396058</v>
@@ -10128,13 +10128,13 @@
         <v>3221831</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="AS38" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="AT38" t="n">
         <v>331122</v>
@@ -10182,13 +10182,13 @@
         <v>0</v>
       </c>
       <c r="BI38" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BJ38" t="n">
         <v>0.17</v>
       </c>
-      <c r="BJ38" t="n">
-        <v>0.14</v>
-      </c>
       <c r="BK38" t="n">
-        <v>0.17</v>
+        <v>0.9</v>
       </c>
       <c r="BL38" t="n">
         <v>22796014477</v>
@@ -10462,13 +10462,13 @@
         <v>3234845</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="AT39" t="n">
         <v>328098</v>
@@ -10516,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="BI39" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="BL39" t="n">
         <v>20241628657</v>
@@ -10796,13 +10796,13 @@
         <v>3269910</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="AT40" t="n">
         <v>341158</v>
@@ -10850,13 +10850,13 @@
         <v>0</v>
       </c>
       <c r="BI40" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="BK40" t="n">
-        <v>-0.05</v>
+        <v>0.51</v>
       </c>
       <c r="BL40" t="n">
         <v>32822911866</v>
@@ -11130,13 +11130,13 @@
         <v>3281308</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="AS41" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="AT41" t="n">
         <v>345725</v>
@@ -11184,13 +11184,13 @@
         <v>0</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="BK41" t="n">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="BL41" t="n">
         <v>27100302410</v>
@@ -11452,13 +11452,13 @@
         <v>3308178</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="AT42" t="n">
         <v>343489</v>
@@ -11506,13 +11506,13 @@
         <v>-0</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="BK42" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="BL42" t="n">
         <v>32666140787</v>
@@ -11782,13 +11782,13 @@
         <v>3309846</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="AS43" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="AT43" t="n">
         <v>343620</v>
@@ -11836,13 +11836,13 @@
         <v>0</v>
       </c>
       <c r="BI43" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="BK43" t="n">
-        <v>-0.1</v>
+        <v>-0.78</v>
       </c>
       <c r="BL43" t="n">
         <v>29600309149</v>
@@ -12108,13 +12108,13 @@
         <v>3331330</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="AS44" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="AT44" t="n">
         <v>345476</v>
@@ -12162,13 +12162,13 @@
         <v>0</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="BK44" t="n">
-        <v>-0.03</v>
+        <v>-0.42</v>
       </c>
       <c r="BL44" t="n">
         <v>28300073730</v>
@@ -12434,13 +12434,13 @@
         <v>3386405</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="AT45" t="n">
         <v>344177</v>
@@ -12488,13 +12488,13 @@
         <v>-0.001599</v>
       </c>
       <c r="BI45" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="BK45" t="n">
-        <v>-0.1</v>
+        <v>-0.51</v>
       </c>
       <c r="BL45" t="n">
         <v>31101089774</v>
@@ -12764,13 +12764,13 @@
         <v>3410769</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="AS46" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="AT46" t="n">
         <v>340324</v>
@@ -12818,13 +12818,13 @@
         <v>-0.000768</v>
       </c>
       <c r="BI46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="BK46" t="n">
-        <v>-0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="BL46" t="n">
         <v>28713085056</v>
@@ -13090,13 +13090,13 @@
         <v>3449000</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="AS47" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="AT47" t="n">
         <v>340247</v>
@@ -13144,13 +13144,13 @@
         <v>-0.001143</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="BK47" t="n">
-        <v>-0.03</v>
+        <v>-0.42</v>
       </c>
       <c r="BL47" t="n">
         <v>29681867318</v>
@@ -13416,13 +13416,13 @@
         <v>3490337</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="AT48" t="n">
         <v>348406</v>
@@ -13470,13 +13470,13 @@
         <v>-0.001678</v>
       </c>
       <c r="BI48" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="BK48" t="n">
-        <v>-0.09</v>
+        <v>-0.23</v>
       </c>
       <c r="BL48" t="n">
         <v>27886116219</v>
@@ -13742,13 +13742,13 @@
         <v>3521672</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="AT49" t="n">
         <v>355034</v>
@@ -13796,13 +13796,13 @@
         <v>-0.001064</v>
       </c>
       <c r="BI49" t="n">
-        <v>-0.24</v>
+        <v>-0.4</v>
       </c>
       <c r="BJ49" t="n">
-        <v>-0.4</v>
+        <v>-0.13</v>
       </c>
       <c r="BK49" t="n">
-        <v>-0.13</v>
+        <v>-0.87</v>
       </c>
       <c r="BL49" t="n">
         <v>28786226565</v>
@@ -14072,13 +14072,13 @@
         <v>3560345</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="AT50" t="n">
         <v>355066</v>
@@ -14126,13 +14126,13 @@
         <v>-0.000798</v>
       </c>
       <c r="BI50" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
       <c r="BK50" t="n">
-        <v>0.01</v>
+        <v>-0.14</v>
       </c>
       <c r="BL50" t="n">
         <v>26702655353</v>
@@ -14398,13 +14398,13 @@
         <v>3580652</v>
       </c>
       <c r="AQ51" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AS51" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="AT51" t="n">
         <v>352705</v>
@@ -14452,13 +14452,13 @@
         <v>-0.001782</v>
       </c>
       <c r="BI51" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>0</v>
       </c>
-      <c r="BJ51" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="BK51" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="BL51" t="n">
         <v>23348254025</v>
@@ -14720,13 +14720,13 @@
         <v>3613967</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="AS52" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="AT52" t="n">
         <v>355008</v>
@@ -14780,7 +14780,7 @@
         <v>-0.05</v>
       </c>
       <c r="BK52" t="n">
-        <v>-0.05</v>
+        <v>0.29</v>
       </c>
       <c r="BL52" t="n">
         <v>27657419417</v>
@@ -15050,13 +15050,13 @@
         <v>3646659</v>
       </c>
       <c r="AQ53" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AS53" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="AT53" t="n">
         <v>351599</v>
@@ -15104,13 +15104,13 @@
         <v>-0.001252</v>
       </c>
       <c r="BI53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BJ53" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ53" t="n">
-        <v>0.05</v>
-      </c>
       <c r="BK53" t="n">
-        <v>0.04</v>
+        <v>-0.28</v>
       </c>
       <c r="BL53" t="n">
         <v>30327524963</v>
@@ -15376,13 +15376,13 @@
         <v>3675652</v>
       </c>
       <c r="AQ54" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="AS54" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="AT54" t="n">
         <v>355560</v>
@@ -15430,13 +15430,13 @@
         <v>-0.000684</v>
       </c>
       <c r="BI54" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK54" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="BL54" t="n">
         <v>30190264650</v>
@@ -15706,13 +15706,13 @@
         <v>3705041</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="AS55" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="AT55" t="n">
         <v>357827</v>
@@ -15760,13 +15760,13 @@
         <v>-0.000214</v>
       </c>
       <c r="BI55" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="BK55" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="BL55" t="n">
         <v>28731639979</v>
@@ -16036,13 +16036,13 @@
         <v>3745844</v>
       </c>
       <c r="AQ56" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="AS56" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="AT56" t="n">
         <v>363282</v>
@@ -16090,13 +16090,13 @@
         <v>0</v>
       </c>
       <c r="BI56" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="BJ56" t="n">
-        <v>-0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK56" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BL56" t="n">
         <v>30841394890</v>
@@ -16366,13 +16366,13 @@
         <v>3790900</v>
       </c>
       <c r="AQ57" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="AR57" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AS57" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="AT57" t="n">
         <v>369214</v>
@@ -16423,10 +16423,10 @@
         <v>0.03</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BK57" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="BL57" t="n">
         <v>28736329972</v>
@@ -16696,13 +16696,13 @@
         <v>3831700</v>
       </c>
       <c r="AQ58" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AR58" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="AS58" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="AT58" t="n">
         <v>372016</v>
@@ -16756,7 +16756,7 @@
         <v>0.01</v>
       </c>
       <c r="BK58" t="n">
-        <v>0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="BL58" t="n">
         <v>28471402288</v>
@@ -17026,13 +17026,13 @@
         <v>3877584</v>
       </c>
       <c r="AQ59" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR59" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="AS59" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="AT59" t="n">
         <v>366096</v>
@@ -17086,7 +17086,7 @@
         <v>-0.04</v>
       </c>
       <c r="BK59" t="n">
-        <v>-0.04</v>
+        <v>0.45</v>
       </c>
       <c r="BL59" t="n">
         <v>29300866189</v>
@@ -17348,13 +17348,13 @@
         <v>3929668</v>
       </c>
       <c r="AQ60" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS60" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="AT60" t="n">
         <v>363003</v>
@@ -17402,13 +17402,13 @@
         <v>0.001412</v>
       </c>
       <c r="BI60" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ60" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="BK60" t="n">
-        <v>-0.04</v>
+        <v>0.51</v>
       </c>
       <c r="BL60" t="n">
         <v>27857365197</v>
@@ -17678,13 +17678,13 @@
         <v>3965425</v>
       </c>
       <c r="AQ61" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="AS61" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="AT61" t="n">
         <v>329730</v>
@@ -17732,13 +17732,13 @@
         <v>0.002578</v>
       </c>
       <c r="BI61" t="n">
-        <v>-0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="BJ61" t="n">
-        <v>-0.29</v>
+        <v>-0.12</v>
       </c>
       <c r="BK61" t="n">
-        <v>-0.12</v>
+        <v>0.05</v>
       </c>
       <c r="BL61" t="n">
         <v>24881044787</v>
@@ -18008,13 +18008,13 @@
         <v>4013059</v>
       </c>
       <c r="AQ62" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="AR62" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="AS62" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="AT62" t="n">
         <v>328303</v>
@@ -18062,13 +18062,13 @@
         <v>0.001675</v>
       </c>
       <c r="BI62" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BJ62" t="n">
         <v>0.26</v>
       </c>
-      <c r="BJ62" t="n">
-        <v>0.22</v>
-      </c>
       <c r="BK62" t="n">
-        <v>0.26</v>
+        <v>1.38</v>
       </c>
       <c r="BL62" t="n">
         <v>25398231759</v>
@@ -18342,13 +18342,13 @@
         <v>4034293</v>
       </c>
       <c r="AQ63" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="AR63" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="AT63" t="n">
         <v>332508</v>
@@ -18396,13 +18396,13 @@
         <v>0.003204</v>
       </c>
       <c r="BI63" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BJ63" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ63" t="n">
-        <v>0.09</v>
-      </c>
       <c r="BK63" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BL63" t="n">
         <v>22753954039</v>
@@ -18672,13 +18672,13 @@
         <v>4078202</v>
       </c>
       <c r="AQ64" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="AS64" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="AT64" t="n">
         <v>336157</v>
@@ -18726,13 +18726,13 @@
         <v>0.001471</v>
       </c>
       <c r="BI64" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ64" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK64" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL64" t="n">
         <v>28725872006</v>
@@ -18998,13 +18998,13 @@
         <v>4111522</v>
       </c>
       <c r="AQ65" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="AT65" t="n">
         <v>340789</v>
@@ -19055,10 +19055,10 @@
         <v>0.23</v>
       </c>
       <c r="BJ65" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BK65" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="BL65" t="n">
         <v>29886134851</v>
@@ -19332,13 +19332,13 @@
         <v>4133579</v>
       </c>
       <c r="AQ66" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="AS66" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="AT66" t="n">
         <v>341459</v>
@@ -19386,13 +19386,13 @@
         <v>0.001405</v>
       </c>
       <c r="BI66" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ66" t="n">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BK66" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BL66" t="n">
         <v>29920080781</v>
@@ -19662,13 +19662,13 @@
         <v>4155970</v>
       </c>
       <c r="AQ67" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="AS67" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="AT67" t="n">
         <v>344440</v>
@@ -19716,13 +19716,13 @@
         <v>0.000633</v>
       </c>
       <c r="BI67" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BJ67" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BK67" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="BL67" t="n">
         <v>29036249482</v>
@@ -19992,13 +19992,13 @@
         <v>4188808</v>
       </c>
       <c r="AQ68" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="AR68" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="AS68" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="AT68" t="n">
         <v>345111</v>
@@ -20046,13 +20046,13 @@
         <v>0.000562</v>
       </c>
       <c r="BI68" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="BJ68" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="BK68" t="n">
-        <v>0.25</v>
+        <v>-0.1</v>
       </c>
       <c r="BL68" t="n">
         <v>32128634276</v>
@@ -20326,13 +20326,13 @@
         <v>4228171</v>
       </c>
       <c r="AQ69" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="AR69" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="AS69" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="AT69" t="n">
         <v>350767</v>
@@ -20380,13 +20380,13 @@
         <v>0</v>
       </c>
       <c r="BI69" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BJ69" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="BK69" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="BL69" t="n">
         <v>29558633290</v>
@@ -20656,13 +20656,13 @@
         <v>4262888</v>
       </c>
       <c r="AQ70" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="AS70" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="AT70" t="n">
         <v>356582</v>
@@ -20710,13 +20710,13 @@
         <v>0</v>
       </c>
       <c r="BI70" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ70" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="BK70" t="n">
-        <v>-0.03</v>
+        <v>-0.4</v>
       </c>
       <c r="BL70" t="n">
         <v>30486762259</v>
@@ -20986,13 +20986,13 @@
         <v>4326256</v>
       </c>
       <c r="AQ71" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="AR71" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="AS71" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="AT71" t="n">
         <v>357103</v>
@@ -21040,13 +21040,13 @@
         <v>0</v>
       </c>
       <c r="BI71" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="BJ71" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="BK71" t="n">
-        <v>0.1</v>
+        <v>0.57</v>
       </c>
       <c r="BL71" t="n">
         <v>31508863381</v>
@@ -21316,13 +21316,13 @@
         <v>4387321</v>
       </c>
       <c r="AQ72" t="n">
-        <v>4.24</v>
+        <v>2.75</v>
       </c>
       <c r="AR72" t="n">
-        <v>2.75</v>
+        <v>5.12</v>
       </c>
       <c r="AS72" t="n">
-        <v>5.12</v>
+        <v>32.2</v>
       </c>
       <c r="AT72" t="n">
         <v>360578</v>
@@ -21370,13 +21370,13 @@
         <v>-0</v>
       </c>
       <c r="BI72" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BJ72" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="BK72" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="BL72" t="n">
         <v>28164831149</v>
@@ -21650,13 +21650,13 @@
         <v>4435517</v>
       </c>
       <c r="AQ73" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AR73" t="n">
-        <v>2.7</v>
+        <v>5.12</v>
       </c>
       <c r="AS73" t="n">
-        <v>5.12</v>
+        <v>31.87</v>
       </c>
       <c r="AT73" t="n">
         <v>358234</v>
@@ -21704,13 +21704,13 @@
         <v>0</v>
       </c>
       <c r="BI73" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ73" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="BK73" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="BL73" t="n">
         <v>30710215227</v>
@@ -21976,13 +21976,13 @@
         <v>4476542</v>
       </c>
       <c r="AQ74" t="n">
-        <v>4.44</v>
+        <v>2.87</v>
       </c>
       <c r="AR74" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="AS74" t="n">
-        <v>5.38</v>
+        <v>32.45</v>
       </c>
       <c r="AT74" t="n">
         <v>364367</v>
@@ -22030,13 +22030,13 @@
         <v>0</v>
       </c>
       <c r="BI74" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="BJ74" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="BK74" t="n">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="BL74" t="n">
         <v>24573982812</v>
@@ -22306,13 +22306,13 @@
         <v>4501299</v>
       </c>
       <c r="AQ75" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="AR75" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="AS75" t="n">
-        <v>5.56</v>
+        <v>32.63</v>
       </c>
       <c r="AT75" t="n">
         <v>371074</v>
@@ -22363,7 +22363,7 @@
         <v>0.2</v>
       </c>
       <c r="BJ75" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BK75" t="n">
         <v>0.18</v>
@@ -22640,13 +22640,13 @@
         <v>4553022</v>
       </c>
       <c r="AQ76" t="n">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="AR76" t="n">
-        <v>3.06</v>
+        <v>5.39</v>
       </c>
       <c r="AS76" t="n">
-        <v>5.39</v>
+        <v>32.84</v>
       </c>
       <c r="AT76" t="n">
         <v>362002</v>
@@ -22694,13 +22694,13 @@
         <v>-0.000354</v>
       </c>
       <c r="BI76" t="n">
-        <v>-0.12</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ76" t="n">
-        <v>-0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="BK76" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="BL76" t="n">
         <v>31766018083</v>
@@ -22970,13 +22970,13 @@
         <v>4574368</v>
       </c>
       <c r="AQ77" t="n">
-        <v>4.64</v>
+        <v>3.15</v>
       </c>
       <c r="AR77" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="AS77" t="n">
-        <v>5.51</v>
+        <v>33.36</v>
       </c>
       <c r="AT77" t="n">
         <v>366913</v>
@@ -23024,13 +23024,13 @@
         <v>-0.000554</v>
       </c>
       <c r="BI77" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BJ77" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ77" t="n">
-        <v>0.09</v>
-      </c>
       <c r="BK77" t="n">
-        <v>0.12</v>
+        <v>0.52</v>
       </c>
       <c r="BL77" t="n">
         <v>34286658184</v>
@@ -23300,13 +23300,13 @@
         <v>4597168</v>
       </c>
       <c r="AQ78" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="AR78" t="n">
-        <v>3.25</v>
+        <v>5.63</v>
       </c>
       <c r="AS78" t="n">
-        <v>5.63</v>
+        <v>32.97</v>
       </c>
       <c r="AT78" t="n">
         <v>371137</v>
@@ -23354,13 +23354,13 @@
         <v>-0.0008229999999999999</v>
       </c>
       <c r="BI78" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BJ78" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="BK78" t="n">
-        <v>0.12</v>
+        <v>-0.39</v>
       </c>
       <c r="BL78" t="n">
         <v>31529852245</v>
@@ -23634,13 +23634,13 @@
         <v>4602668</v>
       </c>
       <c r="AQ79" t="n">
-        <v>4.58</v>
+        <v>3.18</v>
       </c>
       <c r="AR79" t="n">
-        <v>3.18</v>
+        <v>5.42</v>
       </c>
       <c r="AS79" t="n">
-        <v>5.42</v>
+        <v>32.63</v>
       </c>
       <c r="AT79" t="n">
         <v>367558</v>
@@ -23688,13 +23688,13 @@
         <v>-0.000372</v>
       </c>
       <c r="BI79" t="n">
-        <v>-0.17</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BJ79" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="BK79" t="n">
-        <v>-0.21</v>
+        <v>-0.34</v>
       </c>
       <c r="BL79" t="n">
         <v>35499628278</v>
@@ -23964,13 +23964,13 @@
         <v>4633143</v>
       </c>
       <c r="AQ80" t="n">
-        <v>4.88</v>
+        <v>3.32</v>
       </c>
       <c r="AR80" t="n">
-        <v>3.32</v>
+        <v>5.8</v>
       </c>
       <c r="AS80" t="n">
-        <v>5.8</v>
+        <v>32.06</v>
       </c>
       <c r="AT80" t="n">
         <v>369742</v>
@@ -24018,13 +24018,13 @@
         <v>-0.000497</v>
       </c>
       <c r="BI80" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="BK80" t="n">
-        <v>0.38</v>
+        <v>-0.57</v>
       </c>
       <c r="BL80" t="n">
         <v>33577433983</v>
@@ -24298,13 +24298,13 @@
         <v>4670170</v>
       </c>
       <c r="AQ81" t="n">
-        <v>5.04</v>
+        <v>3.35</v>
       </c>
       <c r="AR81" t="n">
-        <v>3.35</v>
+        <v>6.03</v>
       </c>
       <c r="AS81" t="n">
-        <v>6.03</v>
+        <v>32.26</v>
       </c>
       <c r="AT81" t="n">
         <v>372616</v>
@@ -24352,13 +24352,13 @@
         <v>-0.0007470000000000001</v>
       </c>
       <c r="BI81" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="BJ81" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="BK81" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="BL81" t="n">
         <v>32732183002</v>
@@ -24799,88 +24799,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>204667.15625</v>
+        <v>207377.765625</v>
       </c>
       <c r="C83" t="n">
-        <v>201.429993</v>
+        <v>204.220001</v>
       </c>
       <c r="D83" t="n">
-        <v>133.410004</v>
+        <v>137.440002</v>
       </c>
       <c r="E83" t="n">
-        <v>440.230011</v>
+        <v>437.529999</v>
       </c>
       <c r="F83" t="n">
-        <v>5.0579</v>
+        <v>5.01</v>
       </c>
       <c r="G83" t="n">
-        <v>5.673</v>
+        <v>5.6383</v>
       </c>
       <c r="H83" t="n">
-        <v>7708.77002</v>
+        <v>7736.75</v>
       </c>
       <c r="I83" t="n">
-        <v>26522.501953</v>
+        <v>26544.773438</v>
       </c>
       <c r="J83" t="n">
-        <v>52020.359375</v>
+        <v>52561.949219</v>
       </c>
       <c r="K83" t="n">
-        <v>4161.899902</v>
+        <v>4169.299805</v>
       </c>
       <c r="L83" t="n">
-        <v>98.599998</v>
+        <v>96.30999799999999</v>
       </c>
       <c r="M83" t="n">
-        <v>109.400002</v>
+        <v>107</v>
       </c>
       <c r="N83" t="n">
-        <v>1251</v>
+        <v>1253.25</v>
       </c>
       <c r="O83" t="n">
-        <v>467.75</v>
+        <v>462.75</v>
       </c>
       <c r="P83" t="n">
-        <v>9.835331</v>
+        <v>11.289989</v>
       </c>
       <c r="Q83" t="n">
-        <v>9.425245</v>
+        <v>10.940895</v>
       </c>
       <c r="R83" t="n">
-        <v>19.190568</v>
+        <v>22.791032</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.595991</v>
+        <v>-2.199521</v>
       </c>
       <c r="T83" t="n">
-        <v>-2.786907</v>
+        <v>-3.707542</v>
       </c>
       <c r="U83" t="n">
-        <v>-3.785914</v>
+        <v>-4.374425</v>
       </c>
       <c r="V83" t="n">
-        <v>0.747954</v>
+        <v>1.113632</v>
       </c>
       <c r="W83" t="n">
-        <v>-1.260407</v>
+        <v>-1.177493</v>
       </c>
       <c r="X83" t="n">
-        <v>2.188951</v>
+        <v>3.252852</v>
       </c>
       <c r="Y83" t="n">
-        <v>-0.592359</v>
+        <v>-0.415611</v>
       </c>
       <c r="Z83" t="n">
-        <v>9.046671999999999</v>
+        <v>6.514045</v>
       </c>
       <c r="AA83" t="n">
-        <v>5.669857</v>
+        <v>3.351687</v>
       </c>
       <c r="AB83" t="n">
-        <v>-3.24826</v>
+        <v>-3.074246</v>
       </c>
       <c r="AC83" t="n">
-        <v>-6.590115</v>
+        <v>-7.588617</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5308,10 +5308,10 @@
         <v>7.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.025278</v>
+        <v>0.025543</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.025278</v>
+        <v>0.025543</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
@@ -5685,10 +5685,10 @@
         <v>0</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.003978</v>
+        <v>0.003713</v>
       </c>
       <c r="BI24" t="n">
-        <v>0.003978</v>
+        <v>0.003713</v>
       </c>
       <c r="BJ24" t="n">
         <v>0.03</v>
@@ -9987,10 +9987,10 @@
         <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ37" t="n">
         <v>0</v>
@@ -10659,10 +10659,10 @@
         <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ39" t="n">
         <v>0.12</v>
@@ -11339,10 +11339,10 @@
         <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI41" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ41" t="n">
         <v>0.19</v>
@@ -11667,10 +11667,10 @@
         <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI42" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ42" t="n">
         <v>0.11</v>
@@ -20703,10 +20703,10 @@
         <v>0</v>
       </c>
       <c r="BH69" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI69" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ69" t="n">
         <v>0.18</v>
@@ -22383,10 +22383,10 @@
         <v>0</v>
       </c>
       <c r="BH74" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI74" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ74" t="n">
         <v>0.24</v>
@@ -25205,88 +25205,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>207602.875</v>
+        <v>203775.984375</v>
       </c>
       <c r="C83" t="n">
-        <v>204.389999</v>
+        <v>200.619995</v>
       </c>
       <c r="D83" t="n">
-        <v>137.669998</v>
+        <v>134.389999</v>
       </c>
       <c r="E83" t="n">
-        <v>438.600006</v>
+        <v>435.700012</v>
       </c>
       <c r="F83" t="n">
-        <v>5.023</v>
+        <v>5.0487</v>
       </c>
       <c r="G83" t="n">
-        <v>5.6414</v>
+        <v>5.6493</v>
       </c>
       <c r="H83" t="n">
-        <v>7733.419922</v>
+        <v>7649.620117</v>
       </c>
       <c r="I83" t="n">
-        <v>26607.212891</v>
+        <v>26096.677734</v>
       </c>
       <c r="J83" t="n">
-        <v>52536.589844</v>
+        <v>52570.058594</v>
       </c>
       <c r="K83" t="n">
-        <v>4149.100098</v>
+        <v>4069.300049</v>
       </c>
       <c r="L83" t="n">
-        <v>97.800003</v>
+        <v>98.410004</v>
       </c>
       <c r="M83" t="n">
-        <v>109.040001</v>
+        <v>111.389999</v>
       </c>
       <c r="N83" t="n">
-        <v>1238.5</v>
+        <v>1263.75</v>
       </c>
       <c r="O83" t="n">
-        <v>456.25</v>
+        <v>459.75</v>
       </c>
       <c r="P83" t="n">
-        <v>11.410795</v>
+        <v>9.357081000000001</v>
       </c>
       <c r="Q83" t="n">
-        <v>11.033245</v>
+        <v>8.98522</v>
       </c>
       <c r="R83" t="n">
-        <v>22.996514</v>
+        <v>20.066112</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.960344</v>
+        <v>-2.608575</v>
       </c>
       <c r="T83" t="n">
-        <v>-3.45769</v>
+        <v>-2.963733</v>
       </c>
       <c r="U83" t="n">
-        <v>-4.32185</v>
+        <v>-4.187862</v>
       </c>
       <c r="V83" t="n">
-        <v>1.07011</v>
+        <v>-0.025092</v>
       </c>
       <c r="W83" t="n">
-        <v>-0.94504</v>
+        <v>-2.845691</v>
       </c>
       <c r="X83" t="n">
-        <v>3.203036</v>
+        <v>3.268782</v>
       </c>
       <c r="Y83" t="n">
-        <v>-0.898084</v>
+        <v>-2.804121</v>
       </c>
       <c r="Z83" t="n">
-        <v>8.161917000000001</v>
+        <v>8.836546999999999</v>
       </c>
       <c r="AA83" t="n">
-        <v>5.322131</v>
+        <v>7.592003</v>
       </c>
       <c r="AB83" t="n">
-        <v>-4.215004</v>
+        <v>-2.262181</v>
       </c>
       <c r="AC83" t="n">
-        <v>-8.886670000000001</v>
+        <v>-8.187718</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>
@@ -25303,10 +25303,10 @@
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="n">
-        <v>5.014</v>
+        <v>5.0277</v>
       </c>
       <c r="AM83" t="n">
-        <v>5.0134</v>
+        <v>5.027</v>
       </c>
       <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="inlineStr"/>
@@ -25319,10 +25319,10 @@
       <c r="AV83" t="inlineStr"/>
       <c r="AW83" t="inlineStr"/>
       <c r="AX83" t="n">
-        <v>-3.221448</v>
+        <v>-2.957015</v>
       </c>
       <c r="AY83" t="n">
-        <v>-3.221821</v>
+        <v>-2.959288</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -25217,7 +25217,7 @@
         <v>430</v>
       </c>
       <c r="F83" t="n">
-        <v>4.9964</v>
+        <v>4.9652</v>
       </c>
       <c r="G83" t="n">
         <v>5.5626</v>
@@ -25238,7 +25238,7 @@
         <v>103.269997</v>
       </c>
       <c r="M83" t="n">
-        <v>116.720001</v>
+        <v>111.699997</v>
       </c>
       <c r="N83" t="n">
         <v>1256.5</v>
@@ -25259,7 +25259,7 @@
         <v>-3.882691</v>
       </c>
       <c r="T83" t="n">
-        <v>-3.968941</v>
+        <v>-4.568606</v>
       </c>
       <c r="U83" t="n">
         <v>-5.658294</v>
@@ -25280,7 +25280,7 @@
         <v>14.211456</v>
       </c>
       <c r="AA83" t="n">
-        <v>12.740271</v>
+        <v>7.891431</v>
       </c>
       <c r="AB83" t="n">
         <v>-2.822892</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -5308,10 +5308,10 @@
         <v>7.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0274</v>
+        <v>0.029256</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.0274</v>
+        <v>0.029256</v>
       </c>
       <c r="AG23" t="n">
         <v>1.25</v>
@@ -5685,10 +5685,10 @@
         <v>0</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.001856</v>
+        <v>-0</v>
       </c>
       <c r="BI24" t="n">
-        <v>0.001856</v>
+        <v>-0</v>
       </c>
       <c r="BJ24" t="n">
         <v>0.03</v>
@@ -25205,88 +25205,88 @@
         <v>46326</v>
       </c>
       <c r="B83" t="n">
-        <v>176027.578125</v>
+        <v>171106.125</v>
       </c>
       <c r="C83" t="n">
-        <v>173.179993</v>
+        <v>168.339996</v>
       </c>
       <c r="D83" t="n">
-        <v>100.730003</v>
+        <v>94.989998</v>
       </c>
       <c r="E83" t="n">
-        <v>465.970001</v>
+        <v>469.320007</v>
       </c>
       <c r="F83" t="n">
-        <v>5.3271</v>
+        <v>5.3707</v>
       </c>
       <c r="G83" t="n">
-        <v>5.9472</v>
+        <v>5.9943</v>
       </c>
       <c r="H83" t="n">
-        <v>7721.919922</v>
+        <v>7734.149902</v>
       </c>
       <c r="I83" t="n">
-        <v>26448.109375</v>
+        <v>26453.009766</v>
       </c>
       <c r="J83" t="n">
-        <v>52447.628906</v>
+        <v>52486.179688</v>
       </c>
       <c r="K83" t="n">
-        <v>4072.300049</v>
+        <v>4051.699951</v>
       </c>
       <c r="L83" t="n">
-        <v>100.040001</v>
+        <v>103.459999</v>
       </c>
       <c r="M83" t="n">
-        <v>109.370003</v>
+        <v>112.5</v>
       </c>
       <c r="N83" t="n">
-        <v>1249.75</v>
+        <v>1243</v>
       </c>
       <c r="O83" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
       <c r="P83" t="n">
-        <v>-5.534197</v>
+        <v>-8.175311000000001</v>
       </c>
       <c r="Q83" t="n">
-        <v>-5.921343</v>
+        <v>-8.550632999999999</v>
       </c>
       <c r="R83" t="n">
-        <v>-10.006251</v>
+        <v>-15.134461</v>
       </c>
       <c r="S83" t="n">
-        <v>4.157634</v>
+        <v>4.906456</v>
       </c>
       <c r="T83" t="n">
-        <v>2.387128</v>
+        <v>3.225124</v>
       </c>
       <c r="U83" t="n">
-        <v>0.864517</v>
+        <v>1.663334</v>
       </c>
       <c r="V83" t="n">
-        <v>0.919813</v>
+        <v>1.07965</v>
       </c>
       <c r="W83" t="n">
-        <v>-1.53736</v>
+        <v>-1.519116</v>
       </c>
       <c r="X83" t="n">
-        <v>3.028281</v>
+        <v>3.10401</v>
       </c>
       <c r="Y83" t="n">
-        <v>-2.732466</v>
+        <v>-3.224502</v>
       </c>
       <c r="Z83" t="n">
-        <v>10.639242</v>
+        <v>14.421589</v>
       </c>
       <c r="AA83" t="n">
-        <v>5.640881</v>
+        <v>8.664156999999999</v>
       </c>
       <c r="AB83" t="n">
-        <v>-3.344934</v>
+        <v>-3.866976</v>
       </c>
       <c r="AC83" t="n">
-        <v>-9.835247000000001</v>
+        <v>-9.785322000000001</v>
       </c>
       <c r="AD83" t="n">
         <v>13.75</v>
@@ -25303,10 +25303,10 @@
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="n">
-        <v>5.5007</v>
+        <v>5.342</v>
       </c>
       <c r="AM83" t="n">
-        <v>5.4998</v>
+        <v>5.3414</v>
       </c>
       <c r="AN83" t="inlineStr"/>
       <c r="AO83" t="inlineStr"/>
@@ -25319,10 +25319,10 @@
       <c r="AV83" t="inlineStr"/>
       <c r="AW83" t="inlineStr"/>
       <c r="AX83" t="n">
-        <v>6.172673</v>
+        <v>3.109498</v>
       </c>
       <c r="AY83" t="n">
-        <v>6.167596</v>
+        <v>3.109859</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="inlineStr"/>
